--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
@@ -171,8 +171,8 @@
     <t xml:space="preserve">intro</t>
   </si>
   <si>
-    <t xml:space="preserve">SAY: I’m coming to check up on you. On my visit on {last_visit_date}, I gave you a referral to the health facility for the following reasons:
-{referral_reasons}</t>
+    <t xml:space="preserve">SAY: I’m coming to check up on you. On my visit on ${last_visit_date}, I gave you a referral to the health facility for the following reasons:
+${referral_reasons}</t>
   </si>
   <si>
     <t xml:space="preserve">select_one yes_no</t>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="129">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -81,6 +81,9 @@
     <t xml:space="preserve">inputs</t>
   </si>
   <si>
+    <t xml:space="preserve">NO_LABEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">hidden</t>
   </si>
   <si>
@@ -90,7 +93,25 @@
     <t xml:space="preserve">last_visit_date</t>
   </si>
   <si>
-    <t xml:space="preserve">referral_reasons</t>
+    <t xml:space="preserve">refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_muac_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
     <t xml:space="preserve">user</t>
@@ -135,6 +156,33 @@
     <t xml:space="preserve">calculate</t>
   </si>
   <si>
+    <t xml:space="preserve">last_visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/last_visit_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_muac_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
     <t xml:space="preserve">client</t>
   </si>
   <si>
@@ -147,18 +195,6 @@
     <t xml:space="preserve">../inputs/contact/name</t>
   </si>
   <si>
-    <t xml:space="preserve">last_visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/last_visit_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reasons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/reasons</t>
-  </si>
-  <si>
     <t xml:space="preserve">referral_follow_up</t>
   </si>
   <si>
@@ -171,8 +207,70 @@
     <t xml:space="preserve">intro</t>
   </si>
   <si>
-    <t xml:space="preserve">SAY: I’m coming to check up on you. On my visit on ${last_visit_date}, I gave you a referral to the health facility for the following reasons:
-${referral_reasons}</t>
+    <t xml:space="preserve">SAY: I’m coming to check up on you. On my visit on ${last_visit_date}, I gave you a referral to the health facility for the following reasons:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../refer_flag_small_baby = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neonatal danger sign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_neonatal_danger_sign_flag = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child danger sign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_child_danger_sign_flag = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_muac_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_muac_flag = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palm pallor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_refer_palm_pallor_flag = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_vaccines_flag = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reason_refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../../inputs/refer_slow_to_learn_specifics_flag = 1</t>
   </si>
   <si>
     <t xml:space="preserve">select_one yes_no</t>
@@ -393,13 +491,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -431,7 +533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q1048576"/>
   <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="14.43"/>
@@ -497,121 +599,148 @@
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C2" s="0" t="s">
+        <v>19</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
+      <c r="C7" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>30</v>
@@ -619,219 +748,452 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>42</v>
+      <c r="C19" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>24</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="L29" s="0" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>73</v>
+        <v>53</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
+        <v>57</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -856,7 +1218,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -870,74 +1232,74 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -964,32 +1326,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="C2" s="5" t="n">
         <v>43584</v>
       </c>
     </row>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,18 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heix\Documents\GitHub\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB06BAD3-3CA6-46A7-A7CB-F9DEB2D9C744}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,430 +27,418 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="129">
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">label::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">relevant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">read_only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">constraint_message::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hint::sw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repeat_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">begin group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO_LABEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">last_visit_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_muac_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_vaccines_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">facility_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db:person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db-object</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">last_visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/last_visit_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_muac_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_vaccines_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/contact/_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">client_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../inputs/contact/name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">referral_follow_up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral follow-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAY: I’m coming to check up on you. On my visit on ${last_visit_date}, I gave you a referral to the health facility for the following reasons:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../refer_flag_small_baby = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neonatal danger sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_neonatal_danger_sign_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child danger sign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_child_danger_sign_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_muac_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_muac_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palm pallor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_refer_palm_pallor_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_vaccines_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaccines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_vaccines_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">../../inputs/refer_slow_to_learn_specifics_flag = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">went_to_facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKS: Did you go to the health facility?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">congratulate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Congratulate the client on making the visit to the health facility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${went_to_facility},"yes")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">got_services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASK: Did you get the services?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reasons_no_services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discuss the reasons, and try to solve the problems and plan for the referral completion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${went_to_facility},"yes") and selected(${got_services},"no")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">did_not_go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${went_to_facility},"no")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_multiple reason_didnt_go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reason_didnt_go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASK: Why did you not go to the facility?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">discuss_reasons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discuss the reasons, and try to solve the problems through advice, and plan how the client may get services.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">complete_referral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASK: Do you think you need to complete this referral?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">next_follow_up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I will come back 3 days from now to make sure you completed this referral.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(${complete_referral},"yes")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes_no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndiyo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hapana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I have no money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">did_not_want</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I did not want to go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_permission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I did not have permission to go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">form_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">style</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instance_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referral Follow-up</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="132">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_muac_flag</t>
+  </si>
+  <si>
+    <t>refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t>refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>db:person</t>
+  </si>
+  <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>db-object</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>last_visit</t>
+  </si>
+  <si>
+    <t>../inputs/last_visit_date</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>../inputs/refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_muac_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>../inputs/contact/name</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>Referral follow-up</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>intro</t>
+  </si>
+  <si>
+    <t>SAY: I’m coming to check up on you. On my visit on ${last_visit_date}, I gave you a referral to the health facility for the following reasons:</t>
+  </si>
+  <si>
+    <t>reason_refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>Small baby</t>
+  </si>
+  <si>
+    <t>../../refer_flag_small_baby = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>Neonatal danger sign</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_neonatal_danger_sign_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>Child danger sign</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_child_danger_sign_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_muac_flag</t>
+  </si>
+  <si>
+    <t>MUAC</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_muac_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>Palm pallor</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_refer_palm_pallor_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t>Vaccines</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_vaccines_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t>Slow learning</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_slow_to_learn_specifics_flag = 1</t>
+  </si>
+  <si>
+    <t>select_one yes_no</t>
+  </si>
+  <si>
+    <t>went_to_facility</t>
+  </si>
+  <si>
+    <t>AKS: Did you go to the health facility?</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>congratulate</t>
+  </si>
+  <si>
+    <t>Congratulate the client on making the visit to the health facility.</t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility},"yes")</t>
+  </si>
+  <si>
+    <t>got_services</t>
+  </si>
+  <si>
+    <t>ASK: Did you get the services?</t>
+  </si>
+  <si>
+    <t>reasons_no_services</t>
+  </si>
+  <si>
+    <t>Discuss the reasons, and try to solve the problems and plan for the referral completion.</t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility},"yes") and selected(${got_services},"no")</t>
+  </si>
+  <si>
+    <t>did_not_go</t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility},"no")</t>
+  </si>
+  <si>
+    <t>select_multiple reason_didnt_go</t>
+  </si>
+  <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>ASK: Why did you not go to the facility?</t>
+  </si>
+  <si>
+    <t>discuss_reasons</t>
+  </si>
+  <si>
+    <t>Discuss the reasons, and try to solve the problems through advice, and plan how the client may get services.</t>
+  </si>
+  <si>
+    <t>complete_referral</t>
+  </si>
+  <si>
+    <t>ASK: Do you think you need to complete this referral?</t>
+  </si>
+  <si>
+    <t>next_follow_up</t>
+  </si>
+  <si>
+    <t>I will come back 3 days from now to make sure you completed this referral.</t>
+  </si>
+  <si>
+    <t>selected(${complete_referral},"yes")</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
+    <t>no_permission</t>
+  </si>
+  <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
+    <t>has_referral</t>
+  </si>
+  <si>
+    <t>if(selected(${complete_referral},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>referral_days</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="M/D/YYYY"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -458,7 +451,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -466,80 +459,341 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:Q1048576"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q54"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="14.43"/>
+    <col min="1" max="1025" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,120 +846,120 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -716,7 +970,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -727,7 +981,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -738,7 +992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -746,65 +1000,65 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -812,7 +1066,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -820,7 +1074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -831,84 +1085,84 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="0" t="s">
+      <c r="L25" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="0" t="s">
+      <c r="L26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="0" t="s">
+      <c r="L27" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L28" s="0" t="s">
+      <c r="L28" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="0" t="s">
+      <c r="L29" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L30" s="0" t="s">
+      <c r="L30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -919,7 +1173,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>43</v>
       </c>
@@ -930,7 +1184,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
@@ -941,7 +1195,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
@@ -952,7 +1206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>
@@ -962,11 +1216,11 @@
       <c r="C35" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
@@ -976,11 +1230,11 @@
       <c r="C36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>59</v>
       </c>
@@ -990,11 +1244,11 @@
       <c r="C37" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>59</v>
       </c>
@@ -1004,11 +1258,11 @@
       <c r="C38" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>59</v>
       </c>
@@ -1018,11 +1272,11 @@
       <c r="C39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>59</v>
       </c>
@@ -1032,11 +1286,11 @@
       <c r="C40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>59</v>
       </c>
@@ -1046,11 +1300,11 @@
       <c r="C41" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1064,7 +1318,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>59</v>
       </c>
@@ -1078,7 +1332,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>83</v>
       </c>
@@ -1095,7 +1349,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>59</v>
       </c>
@@ -1109,14 +1363,14 @@
         <v>94</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="E46" s="1"/>
@@ -1124,7 +1378,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>97</v>
       </c>
@@ -1138,7 +1392,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>59</v>
       </c>
@@ -1149,7 +1403,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>83</v>
       </c>
@@ -1163,7 +1417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>59</v>
       </c>
@@ -1177,7 +1431,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>36</v>
       </c>
@@ -1185,7 +1439,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>36</v>
       </c>
@@ -1193,30 +1447,43 @@
         <v>57</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" t="s">
+        <v>129</v>
+      </c>
+      <c r="L53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L54">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="14.43"/>
+    <col min="1" max="1025" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
@@ -1230,7 +1497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>108</v>
       </c>
@@ -1244,7 +1511,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>108</v>
       </c>
@@ -1258,7 +1525,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>98</v>
       </c>
@@ -1269,7 +1536,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>98</v>
       </c>
@@ -1280,7 +1547,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>98</v>
       </c>
@@ -1291,7 +1558,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>98</v>
       </c>
@@ -1303,28 +1570,20 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="14.43"/>
+    <col min="1" max="1025" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
@@ -1344,24 +1603,19 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="5">
         <v>43584</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heix\Documents\GitHub\config-dtree\forms\app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Heiko Hornung\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB06BAD3-3CA6-46A7-A7CB-F9DEB2D9C744}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="159">
   <si>
     <t>type</t>
   </si>
@@ -95,6 +94,12 @@
     <t>string</t>
   </si>
   <si>
+    <t>source_form</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
     <t>last_visit_date</t>
   </si>
   <si>
@@ -161,6 +166,24 @@
     <t>calculate</t>
   </si>
   <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t>referral_source_form</t>
+  </si>
+  <si>
+    <t>../inputs/source_form</t>
+  </si>
+  <si>
+    <t>referral_source_id</t>
+  </si>
+  <si>
+    <t>../inputs/source_id</t>
+  </si>
+  <si>
     <t>last_visit</t>
   </si>
   <si>
@@ -191,9 +214,6 @@
     <t>client</t>
   </si>
   <si>
-    <t>../inputs/contact/_id</t>
-  </si>
-  <si>
     <t>client_name</t>
   </si>
   <si>
@@ -350,6 +370,15 @@
     <t>selected(${complete_referral},"yes")</t>
   </si>
   <si>
+    <t>has_referral</t>
+  </si>
+  <si>
+    <t>if(selected(${complete_referral},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>referral_days</t>
+  </si>
+  <si>
     <t>list_name</t>
   </si>
   <si>
@@ -416,20 +445,71 @@
     <t>Referral Follow-up</t>
   </si>
   <si>
-    <t>has_referral</t>
-  </si>
-  <si>
-    <t>if(selected(${complete_referral},"yes"),1,0)</t>
-  </si>
-  <si>
-    <t>referral_days</t>
+    <t>Sina pesa</t>
+  </si>
+  <si>
+    <t>Sikutaka kwenda</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
+    <t>Ufuasi wa rufaa</t>
+  </si>
+  <si>
+    <t>SEMA: Nimekuja kukuangalia. Wakati nilipokutemebela mara ya mwisho nilikupa rufaa ya kuenda kituo cha afya kutokana na sababu zifuatazo:</t>
+  </si>
+  <si>
+    <t>Mtoto Njiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalili za hatari kwa mtoto baada ya kuzaliwa </t>
+  </si>
+  <si>
+    <t>Dalili za hatari kwa mtoto</t>
+  </si>
+  <si>
+    <t>Viganja viko vyeupe sana</t>
+  </si>
+  <si>
+    <t>Chanjo</t>
+  </si>
+  <si>
+    <t>Mzito kujifunza</t>
+  </si>
+  <si>
+    <t>ULIZA: Je ulienda kituo cha afya?</t>
+  </si>
+  <si>
+    <t>Mpongeze mteja kwa kuenda kituo cha afya</t>
+  </si>
+  <si>
+    <t>ULIZA: Je ulipata huduma?</t>
+  </si>
+  <si>
+    <t>Jadili sababu na jaribu kutatua tatizo na panga naye kuhusu kukamilisha rufaa</t>
+  </si>
+  <si>
+    <t>ULIZA: Kwa nini hukwenda kituo cha afya?</t>
+  </si>
+  <si>
+    <t>Jadili sababu na jaribu kumpa ushauri wa jinsi ya kutatua tatizo na panga naye njia ya yeye kupata huduma</t>
+  </si>
+  <si>
+    <t>ULIZA: Je unafikiri unahitaji kuikamilisha rufaa hii?</t>
+  </si>
+  <si>
+    <t>Nitarudi baba ya siku 3 ili kuhakikisha kuwa umekamilisha hii rufaa.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -438,6 +518,11 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -462,17 +547,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +591,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -519,7 +603,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -566,23 +650,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -618,23 +685,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -786,11 +836,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1025" width="14.42578125" customWidth="1"/>
+    <col min="1" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="4" width="14.42578125" style="6" customWidth="1"/>
+    <col min="5" max="1025" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -853,7 +905,7 @@
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -867,20 +919,22 @@
       <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -889,7 +943,7 @@
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -897,10 +951,10 @@
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -911,7 +965,7 @@
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -922,7 +976,7 @@
       <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -933,7 +987,7 @@
       <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -944,18 +998,18 @@
       <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -966,19 +1020,19 @@
       <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -986,29 +1040,32 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1016,35 +1073,32 @@
         <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1052,431 +1106,538 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" t="s">
-        <v>46</v>
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" t="s">
         <v>48</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L29" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="L31" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="L32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="B38" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D38" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F36" t="s">
+      <c r="B39" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D39" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F37" t="s">
+      <c r="C40" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="4" t="s">
+    </row>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F38" t="s">
+      <c r="C41" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="D41" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="4" t="s">
+    </row>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F39" t="s">
+      <c r="C42" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="4" t="s">
+    </row>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F40" t="s">
+      <c r="C43" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="4" t="s">
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F41" t="s">
+      <c r="C44" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F44" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="1" t="s">
+    </row>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C45" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="1" t="s">
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" s="1" t="s">
+    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D47" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="1" t="s">
+    </row>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
+      <c r="D48" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" t="s">
-        <v>129</v>
-      </c>
-      <c r="L53" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="L54">
+        <v>109</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="L58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L59">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1485,7 +1646,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1499,74 +1660,86 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
+      </c>
+      <c r="D7" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +1749,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1585,30 +1758,30 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C2" s="5">
         <v>43584</v>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
@@ -13,17 +13,119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="231">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
   <si>
     <t>form_title</t>
   </si>
   <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>source_form</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_muac_flag</t>
+  </si>
+  <si>
+    <t>refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>refer_vaccines_flag</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
+    <t>refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
     <t>style</t>
   </si>
   <si>
@@ -33,30 +135,24 @@
     <t>instance_name</t>
   </si>
   <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
     <t>yes_no</t>
   </si>
   <si>
+    <t>due_date</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
     <t>Ndiyo</t>
   </si>
   <si>
@@ -81,124 +177,82 @@
     <t>Sina pesa</t>
   </si>
   <si>
-    <t>required</t>
+    <t>due_date_human_readable</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>pages</t>
   </si>
   <si>
     <t>did_not_want</t>
   </si>
   <si>
-    <t>relevant</t>
+    <t>facility_id</t>
   </si>
   <si>
     <t>I did not want to go</t>
   </si>
   <si>
-    <t>appearance</t>
-  </si>
-  <si>
     <t>Sikutaka kwenda</t>
   </si>
   <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
+    <t>Facility ID for the parent user</t>
   </si>
   <si>
     <t>no_permission</t>
   </si>
   <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
     <t>I did not have permission to go</t>
   </si>
   <si>
-    <t>calculation</t>
-  </si>
-  <si>
     <t>Sikupewa ruhusa ya kwenda</t>
   </si>
   <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>data</t>
   </si>
   <si>
     <t>other</t>
   </si>
   <si>
+    <t>end group</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
     <t>Nyenginezo</t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
     <t>reason_didnt_get_svc</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>source_form</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>last_visit_date</t>
-  </si>
-  <si>
-    <t>refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t>refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_muac_flag</t>
+    <t>contact</t>
   </si>
   <si>
     <t>too_many_people</t>
   </si>
   <si>
-    <t>refer_palm_pallor_flag</t>
-  </si>
-  <si>
     <t>There were too many people</t>
   </si>
   <si>
     <t>Kulikuwa na watu wengi</t>
   </si>
   <si>
-    <t>refer_vaccines_flag</t>
+    <t>db:person</t>
+  </si>
+  <si>
+    <t>_id</t>
   </si>
   <si>
     <t>services_not_offered</t>
@@ -207,45 +261,36 @@
     <t>The services I needed were not offered when I went</t>
   </si>
   <si>
+    <t>db-object</t>
+  </si>
+  <si>
     <t>Huduma nilizotaka hazikuwepo.</t>
   </si>
   <si>
-    <t>refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
     <t>no_service_provider_available</t>
   </si>
   <si>
     <t>No service providers were available</t>
   </si>
   <si>
-    <t>user</t>
-  </si>
-  <si>
     <t>Hakukuwa na mtoa huduma</t>
   </si>
   <si>
-    <t>contact_id</t>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
   </si>
   <si>
     <t>was_asked_to_pay</t>
   </si>
   <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
     <t>I was asked to pay for services</t>
   </si>
   <si>
     <t>Walitaka nilipie huduma</t>
   </si>
   <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
     <t>was_treated_badly</t>
   </si>
   <si>
@@ -255,30 +300,6 @@
     <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
-    <t>end group</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>db:person</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
@@ -342,7 +363,120 @@
     <t>../inputs/contact/name</t>
   </si>
   <si>
-    <t>referral_follow_up</t>
+    <t>client_date_of_birth</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t>../inputs/due_date</t>
+  </si>
+  <si>
+    <t>due_date_pretty_print</t>
+  </si>
+  <si>
+    <t>../inputs/due_date_human_readable</t>
+  </si>
+  <si>
+    <t>age_days</t>
+  </si>
+  <si>
+    <t>decimal-date-time(today())-decimal-date-time(${client_date_of_birth})</t>
+  </si>
+  <si>
+    <t>age_months</t>
+  </si>
+  <si>
+    <t>round(${age_days} div 30,0)</t>
+  </si>
+  <si>
+    <t>age_years</t>
+  </si>
+  <si>
+    <t>round(${age_months} div 12,0)</t>
+  </si>
+  <si>
+    <t>household_head</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/household_head</t>
+  </si>
+  <si>
+    <t>house_number</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/house_number</t>
+  </si>
+  <si>
+    <t>kitongoji</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/kitongoji</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>instance('contact-summary')/context/phone</t>
+  </si>
+  <si>
+    <t>client_information</t>
+  </si>
+  <si>
+    <t>Client Information</t>
+  </si>
+  <si>
+    <t>Maelezo ya Mteja</t>
+  </si>
+  <si>
+    <t>field-list</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>intro_note</t>
+  </si>
+  <si>
+    <t>Visit type: &lt;span style="font-weight:bold"&gt;Referral Follow-up&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Aina ya tembeleo: &lt;span style="font-weight:bold"&gt;Ufuatiliaji wa Rufaa&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>household_note</t>
+  </si>
+  <si>
+    <t>Name: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
+Age: &lt;span style="font-weight:bold"&gt;${age_years} years, ${age_months} months&lt;/span&gt;
+Contact person: &lt;span style="font-weight:bold"&gt;${household_head}&lt;/span&gt; 
+House number: &lt;span style="font-weight:bold"&gt;${house_number}&lt;/span&gt;
+Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Jina: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
+Umri: &lt;span style="font-weight:bold"&gt;${age_years} miaka, ${age_months} miezi&lt;/span&gt;
+Mtu wa karibu kwa mawasiliano: &lt;span style="font-weight:bold"&gt;${household_head}&lt;/span&gt; 
+Namba ya nyumba: &lt;span style="font-weight:bold"&gt;${house_number}&lt;/span&gt;
+Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>phone_note</t>
+  </si>
+  <si>
+    <t>Phone: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>due_date_note</t>
+  </si>
+  <si>
+    <t>Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print}&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print}&lt;/span&gt;</t>
   </si>
   <si>
     <t>Referral follow-up</t>
@@ -351,16 +485,10 @@
     <t>Ufatiliaji wa rufaa</t>
   </si>
   <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>intro</t>
   </si>
   <si>
     <t>I’m coming to check up on you. On my visit on ${last_visit_formatted}, I gave you a referral to the health facility for the following reasons:</t>
-  </si>
-  <si>
-    <t>Referral Follow-up</t>
   </si>
   <si>
     <t xml:space="preserve">Nimekuja kukuangalia. Wakati nilipokutembelea mara ya mwisho nilikupa rufaa ya kuenda kituo cha afya kutokana na sababu zifuatazo:
@@ -593,43 +721,84 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font/>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
     <font>
       <sz val="10.0"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <right/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -639,19 +808,19 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
@@ -662,4729 +831,4972 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="G21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="G19" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="L25" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="A25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="L26" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="L27" s="2" t="s">
-        <v>94</v>
+      <c r="A27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="L28" s="2" t="s">
-        <v>96</v>
+      <c r="B28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="A29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="L31" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="L32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="L33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="L34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="L35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="L36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="L37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="L38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="L39" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="L29" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="L30" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="L31" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="L32" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="L33" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="L34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="L35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="L36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="L37" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="L38" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40" s="4" t="s">
+      <c r="A40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="L41" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="2" t="s">
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9"/>
+      <c r="L42" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="4" t="s">
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F41" t="s">
+      <c r="C43" s="8"/>
+      <c r="D43" s="9"/>
+      <c r="L43" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" s="2" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="9"/>
+      <c r="L44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="4" t="s">
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F42" t="s">
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
+      <c r="L45" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C46" s="8"/>
+      <c r="D46" s="9"/>
+      <c r="L46" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D43" s="4" t="s">
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="F43" t="s">
+      <c r="C47" s="8"/>
+      <c r="D47" s="9"/>
+      <c r="L47" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" s="2" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C48" s="8"/>
+      <c r="D48" s="9"/>
+      <c r="L48" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F44" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F45" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F46" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>150</v>
+        <v>95</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="9"/>
+      <c r="L49" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="F50" s="2"/>
+      <c r="A50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9"/>
+      <c r="L50" s="12" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="2"/>
+      <c r="A51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>112</v>
+      <c r="A53" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F60" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
+      <c r="C61" s="7" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="2" t="s">
+      <c r="D61" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="4" t="s">
+      <c r="F61" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="4" t="s">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="2" t="s">
+      <c r="C62" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="F62" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="4" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="4" t="s">
+      <c r="C63" s="7" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="D63" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="F63" t="s">
         <v>176</v>
       </c>
-      <c r="D60" s="4" t="s">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="4" t="s">
+      <c r="C64" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D64" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="F64" t="s">
         <v>180</v>
       </c>
-      <c r="F61" s="2" t="s">
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="4" t="s">
+      <c r="C65" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="L62" s="4" t="s">
+      <c r="D65" s="7" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B63" s="4" t="s">
+      <c r="F65" t="s">
         <v>184</v>
       </c>
-      <c r="C63" s="4" t="s">
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="B66" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E63" s="4"/>
-      <c r="F63" t="s">
+      <c r="C66" s="7" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-    </row>
-    <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" t="s">
-        <v>88</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="D66" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="L66" t="s">
+      <c r="E66" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="L67">
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="L80" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" ht="12.75" customHeight="1">
+      <c r="A84" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" t="s">
+        <v>228</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="L84" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="85" ht="12.75" customHeight="1">
+      <c r="A85" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="L85">
         <v>3.0</v>
       </c>
     </row>
-    <row r="68" ht="12.75" customHeight="1">
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-    </row>
-    <row r="69" ht="12.75" customHeight="1">
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-    </row>
-    <row r="70" ht="12.75" customHeight="1">
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-    </row>
-    <row r="71" ht="12.75" customHeight="1">
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-    </row>
-    <row r="72" ht="12.75" customHeight="1">
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-    </row>
-    <row r="73" ht="12.75" customHeight="1">
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-    </row>
-    <row r="74" ht="12.75" customHeight="1">
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-    </row>
-    <row r="75" ht="12.75" customHeight="1">
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-    </row>
-    <row r="76" ht="12.75" customHeight="1">
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-    </row>
-    <row r="77" ht="12.75" customHeight="1">
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-    </row>
-    <row r="78" ht="12.75" customHeight="1">
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-    </row>
-    <row r="79" ht="12.75" customHeight="1">
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-    </row>
-    <row r="80" ht="12.75" customHeight="1">
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-    </row>
-    <row r="81" ht="12.75" customHeight="1">
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-    </row>
-    <row r="82" ht="12.75" customHeight="1">
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-    </row>
-    <row r="83" ht="12.75" customHeight="1">
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-    </row>
-    <row r="84" ht="12.75" customHeight="1">
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-    </row>
-    <row r="85" ht="12.75" customHeight="1">
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-    </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="C314" s="2"/>
-      <c r="D314" s="2"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="C354" s="2"/>
-      <c r="D354" s="2"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="C355" s="2"/>
-      <c r="D355" s="2"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="C356" s="2"/>
-      <c r="D356" s="2"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="C357" s="2"/>
-      <c r="D357" s="2"/>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="C358" s="2"/>
-      <c r="D358" s="2"/>
+      <c r="C358" s="1"/>
+      <c r="D358" s="1"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="C359" s="2"/>
-      <c r="D359" s="2"/>
+      <c r="C359" s="1"/>
+      <c r="D359" s="1"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="C360" s="2"/>
-      <c r="D360" s="2"/>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="C361" s="2"/>
-      <c r="D361" s="2"/>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="C362" s="2"/>
-      <c r="D362" s="2"/>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="C363" s="2"/>
-      <c r="D363" s="2"/>
+      <c r="C363" s="1"/>
+      <c r="D363" s="1"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="C364" s="2"/>
-      <c r="D364" s="2"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="C365" s="2"/>
-      <c r="D365" s="2"/>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
+      <c r="C366" s="1"/>
+      <c r="D366" s="1"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="C367" s="2"/>
-      <c r="D367" s="2"/>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="C368" s="2"/>
-      <c r="D368" s="2"/>
+      <c r="C368" s="1"/>
+      <c r="D368" s="1"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="C369" s="2"/>
-      <c r="D369" s="2"/>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="C370" s="2"/>
-      <c r="D370" s="2"/>
+      <c r="C370" s="1"/>
+      <c r="D370" s="1"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="C371" s="2"/>
-      <c r="D371" s="2"/>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="C372" s="2"/>
-      <c r="D372" s="2"/>
+      <c r="C372" s="1"/>
+      <c r="D372" s="1"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="C373" s="2"/>
-      <c r="D373" s="2"/>
+      <c r="C373" s="1"/>
+      <c r="D373" s="1"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="C374" s="2"/>
-      <c r="D374" s="2"/>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
+      <c r="C375" s="1"/>
+      <c r="D375" s="1"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="C376" s="2"/>
-      <c r="D376" s="2"/>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="C377" s="2"/>
-      <c r="D377" s="2"/>
+      <c r="C377" s="1"/>
+      <c r="D377" s="1"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="C378" s="2"/>
-      <c r="D378" s="2"/>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="C379" s="2"/>
-      <c r="D379" s="2"/>
+      <c r="C379" s="1"/>
+      <c r="D379" s="1"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="C380" s="2"/>
-      <c r="D380" s="2"/>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="C381" s="2"/>
-      <c r="D381" s="2"/>
+      <c r="C381" s="1"/>
+      <c r="D381" s="1"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="C382" s="2"/>
-      <c r="D382" s="2"/>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="C383" s="2"/>
-      <c r="D383" s="2"/>
+      <c r="C383" s="1"/>
+      <c r="D383" s="1"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="C384" s="2"/>
-      <c r="D384" s="2"/>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="C385" s="2"/>
-      <c r="D385" s="2"/>
+      <c r="C385" s="1"/>
+      <c r="D385" s="1"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="C386" s="2"/>
-      <c r="D386" s="2"/>
+      <c r="C386" s="1"/>
+      <c r="D386" s="1"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="2"/>
-      <c r="D387" s="2"/>
+      <c r="C387" s="1"/>
+      <c r="D387" s="1"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="C388" s="2"/>
-      <c r="D388" s="2"/>
+      <c r="C388" s="1"/>
+      <c r="D388" s="1"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="C389" s="2"/>
-      <c r="D389" s="2"/>
+      <c r="C389" s="1"/>
+      <c r="D389" s="1"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="C390" s="2"/>
-      <c r="D390" s="2"/>
+      <c r="C390" s="1"/>
+      <c r="D390" s="1"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="C391" s="2"/>
-      <c r="D391" s="2"/>
+      <c r="C391" s="1"/>
+      <c r="D391" s="1"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="C392" s="2"/>
-      <c r="D392" s="2"/>
+      <c r="C392" s="1"/>
+      <c r="D392" s="1"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="C393" s="2"/>
-      <c r="D393" s="2"/>
+      <c r="C393" s="1"/>
+      <c r="D393" s="1"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="C394" s="2"/>
-      <c r="D394" s="2"/>
+      <c r="C394" s="1"/>
+      <c r="D394" s="1"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
+      <c r="C395" s="1"/>
+      <c r="D395" s="1"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
+      <c r="C396" s="1"/>
+      <c r="D396" s="1"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="C397" s="2"/>
-      <c r="D397" s="2"/>
+      <c r="C397" s="1"/>
+      <c r="D397" s="1"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="C398" s="2"/>
-      <c r="D398" s="2"/>
+      <c r="C398" s="1"/>
+      <c r="D398" s="1"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="C399" s="2"/>
-      <c r="D399" s="2"/>
+      <c r="C399" s="1"/>
+      <c r="D399" s="1"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="C400" s="2"/>
-      <c r="D400" s="2"/>
+      <c r="C400" s="1"/>
+      <c r="D400" s="1"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="C401" s="2"/>
-      <c r="D401" s="2"/>
+      <c r="C401" s="1"/>
+      <c r="D401" s="1"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="C402" s="2"/>
-      <c r="D402" s="2"/>
+      <c r="C402" s="1"/>
+      <c r="D402" s="1"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="C403" s="2"/>
-      <c r="D403" s="2"/>
+      <c r="C403" s="1"/>
+      <c r="D403" s="1"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="C404" s="2"/>
-      <c r="D404" s="2"/>
+      <c r="C404" s="1"/>
+      <c r="D404" s="1"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="C405" s="2"/>
-      <c r="D405" s="2"/>
+      <c r="C405" s="1"/>
+      <c r="D405" s="1"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="C406" s="2"/>
-      <c r="D406" s="2"/>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="C407" s="2"/>
-      <c r="D407" s="2"/>
+      <c r="C407" s="1"/>
+      <c r="D407" s="1"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="C408" s="2"/>
-      <c r="D408" s="2"/>
+      <c r="C408" s="1"/>
+      <c r="D408" s="1"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="C409" s="2"/>
-      <c r="D409" s="2"/>
+      <c r="C409" s="1"/>
+      <c r="D409" s="1"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="C410" s="2"/>
-      <c r="D410" s="2"/>
+      <c r="C410" s="1"/>
+      <c r="D410" s="1"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="C411" s="2"/>
-      <c r="D411" s="2"/>
+      <c r="C411" s="1"/>
+      <c r="D411" s="1"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
+      <c r="C412" s="1"/>
+      <c r="D412" s="1"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="C413" s="2"/>
-      <c r="D413" s="2"/>
+      <c r="C413" s="1"/>
+      <c r="D413" s="1"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="C414" s="2"/>
-      <c r="D414" s="2"/>
+      <c r="C414" s="1"/>
+      <c r="D414" s="1"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="C415" s="2"/>
-      <c r="D415" s="2"/>
+      <c r="C415" s="1"/>
+      <c r="D415" s="1"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="C416" s="2"/>
-      <c r="D416" s="2"/>
+      <c r="C416" s="1"/>
+      <c r="D416" s="1"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="C417" s="2"/>
-      <c r="D417" s="2"/>
+      <c r="C417" s="1"/>
+      <c r="D417" s="1"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="C418" s="2"/>
-      <c r="D418" s="2"/>
+      <c r="C418" s="1"/>
+      <c r="D418" s="1"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="C419" s="2"/>
-      <c r="D419" s="2"/>
+      <c r="C419" s="1"/>
+      <c r="D419" s="1"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="C420" s="2"/>
-      <c r="D420" s="2"/>
+      <c r="C420" s="1"/>
+      <c r="D420" s="1"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="C421" s="2"/>
-      <c r="D421" s="2"/>
+      <c r="C421" s="1"/>
+      <c r="D421" s="1"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="C422" s="2"/>
-      <c r="D422" s="2"/>
+      <c r="C422" s="1"/>
+      <c r="D422" s="1"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="C423" s="2"/>
-      <c r="D423" s="2"/>
+      <c r="C423" s="1"/>
+      <c r="D423" s="1"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="C424" s="2"/>
-      <c r="D424" s="2"/>
+      <c r="C424" s="1"/>
+      <c r="D424" s="1"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="C425" s="2"/>
-      <c r="D425" s="2"/>
+      <c r="C425" s="1"/>
+      <c r="D425" s="1"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="C426" s="2"/>
-      <c r="D426" s="2"/>
+      <c r="C426" s="1"/>
+      <c r="D426" s="1"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="C427" s="2"/>
-      <c r="D427" s="2"/>
+      <c r="C427" s="1"/>
+      <c r="D427" s="1"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="C428" s="2"/>
-      <c r="D428" s="2"/>
+      <c r="C428" s="1"/>
+      <c r="D428" s="1"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="C429" s="2"/>
-      <c r="D429" s="2"/>
+      <c r="C429" s="1"/>
+      <c r="D429" s="1"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="C430" s="2"/>
-      <c r="D430" s="2"/>
+      <c r="C430" s="1"/>
+      <c r="D430" s="1"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="C431" s="2"/>
-      <c r="D431" s="2"/>
+      <c r="C431" s="1"/>
+      <c r="D431" s="1"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="C432" s="2"/>
-      <c r="D432" s="2"/>
+      <c r="C432" s="1"/>
+      <c r="D432" s="1"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="C433" s="2"/>
-      <c r="D433" s="2"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="C434" s="2"/>
-      <c r="D434" s="2"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="C435" s="2"/>
-      <c r="D435" s="2"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="C436" s="2"/>
-      <c r="D436" s="2"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="C437" s="2"/>
-      <c r="D437" s="2"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="C438" s="2"/>
-      <c r="D438" s="2"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="C439" s="2"/>
-      <c r="D439" s="2"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="C440" s="2"/>
-      <c r="D440" s="2"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="C441" s="2"/>
-      <c r="D441" s="2"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="C442" s="2"/>
-      <c r="D442" s="2"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="C443" s="2"/>
-      <c r="D443" s="2"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="C444" s="2"/>
-      <c r="D444" s="2"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="C445" s="2"/>
-      <c r="D445" s="2"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="C446" s="2"/>
-      <c r="D446" s="2"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="C447" s="2"/>
-      <c r="D447" s="2"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="C448" s="2"/>
-      <c r="D448" s="2"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="C449" s="2"/>
-      <c r="D449" s="2"/>
+      <c r="C449" s="1"/>
+      <c r="D449" s="1"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="C450" s="2"/>
-      <c r="D450" s="2"/>
+      <c r="C450" s="1"/>
+      <c r="D450" s="1"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="C451" s="2"/>
-      <c r="D451" s="2"/>
+      <c r="C451" s="1"/>
+      <c r="D451" s="1"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="C452" s="2"/>
-      <c r="D452" s="2"/>
+      <c r="C452" s="1"/>
+      <c r="D452" s="1"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="C453" s="2"/>
-      <c r="D453" s="2"/>
+      <c r="C453" s="1"/>
+      <c r="D453" s="1"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="C454" s="2"/>
-      <c r="D454" s="2"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="C455" s="2"/>
-      <c r="D455" s="2"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="C456" s="2"/>
-      <c r="D456" s="2"/>
+      <c r="C456" s="1"/>
+      <c r="D456" s="1"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="C457" s="2"/>
-      <c r="D457" s="2"/>
+      <c r="C457" s="1"/>
+      <c r="D457" s="1"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="C458" s="2"/>
-      <c r="D458" s="2"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="C459" s="2"/>
-      <c r="D459" s="2"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="C460" s="2"/>
-      <c r="D460" s="2"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="C461" s="2"/>
-      <c r="D461" s="2"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="C462" s="2"/>
-      <c r="D462" s="2"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="C463" s="2"/>
-      <c r="D463" s="2"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="C464" s="2"/>
-      <c r="D464" s="2"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="C465" s="2"/>
-      <c r="D465" s="2"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="C466" s="2"/>
-      <c r="D466" s="2"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="C467" s="2"/>
-      <c r="D467" s="2"/>
+      <c r="C467" s="1"/>
+      <c r="D467" s="1"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="C468" s="2"/>
-      <c r="D468" s="2"/>
+      <c r="C468" s="1"/>
+      <c r="D468" s="1"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="C469" s="2"/>
-      <c r="D469" s="2"/>
+      <c r="C469" s="1"/>
+      <c r="D469" s="1"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="C470" s="2"/>
-      <c r="D470" s="2"/>
+      <c r="C470" s="1"/>
+      <c r="D470" s="1"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="C471" s="2"/>
-      <c r="D471" s="2"/>
+      <c r="C471" s="1"/>
+      <c r="D471" s="1"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="C472" s="2"/>
-      <c r="D472" s="2"/>
+      <c r="C472" s="1"/>
+      <c r="D472" s="1"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="C473" s="2"/>
-      <c r="D473" s="2"/>
+      <c r="C473" s="1"/>
+      <c r="D473" s="1"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="C474" s="2"/>
-      <c r="D474" s="2"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="C475" s="2"/>
-      <c r="D475" s="2"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="C476" s="2"/>
-      <c r="D476" s="2"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="C477" s="2"/>
-      <c r="D477" s="2"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="C478" s="2"/>
-      <c r="D478" s="2"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="C479" s="2"/>
-      <c r="D479" s="2"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="C480" s="2"/>
-      <c r="D480" s="2"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="C481" s="2"/>
-      <c r="D481" s="2"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="C482" s="2"/>
-      <c r="D482" s="2"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="C483" s="2"/>
-      <c r="D483" s="2"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="C484" s="2"/>
-      <c r="D484" s="2"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="C485" s="2"/>
-      <c r="D485" s="2"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="C486" s="2"/>
-      <c r="D486" s="2"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
+      <c r="C488" s="1"/>
+      <c r="D488" s="1"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
+      <c r="C489" s="1"/>
+      <c r="D489" s="1"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
+      <c r="C490" s="1"/>
+      <c r="D490" s="1"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
+      <c r="C491" s="1"/>
+      <c r="D491" s="1"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
+      <c r="C492" s="1"/>
+      <c r="D492" s="1"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
+      <c r="C493" s="1"/>
+      <c r="D493" s="1"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
+      <c r="C494" s="1"/>
+      <c r="D494" s="1"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
+      <c r="C495" s="1"/>
+      <c r="D495" s="1"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
+      <c r="C496" s="1"/>
+      <c r="D496" s="1"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
+      <c r="C497" s="1"/>
+      <c r="D497" s="1"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
+      <c r="C498" s="1"/>
+      <c r="D498" s="1"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
+      <c r="C499" s="1"/>
+      <c r="D499" s="1"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
+      <c r="C500" s="1"/>
+      <c r="D500" s="1"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="C501" s="2"/>
-      <c r="D501" s="2"/>
+      <c r="C501" s="1"/>
+      <c r="D501" s="1"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="C502" s="2"/>
-      <c r="D502" s="2"/>
+      <c r="C502" s="1"/>
+      <c r="D502" s="1"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="C503" s="2"/>
-      <c r="D503" s="2"/>
+      <c r="C503" s="1"/>
+      <c r="D503" s="1"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="C504" s="2"/>
-      <c r="D504" s="2"/>
+      <c r="C504" s="1"/>
+      <c r="D504" s="1"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="C505" s="2"/>
-      <c r="D505" s="2"/>
+      <c r="C505" s="1"/>
+      <c r="D505" s="1"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="C506" s="2"/>
-      <c r="D506" s="2"/>
+      <c r="C506" s="1"/>
+      <c r="D506" s="1"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="C507" s="2"/>
-      <c r="D507" s="2"/>
+      <c r="C507" s="1"/>
+      <c r="D507" s="1"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="C508" s="2"/>
-      <c r="D508" s="2"/>
+      <c r="C508" s="1"/>
+      <c r="D508" s="1"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="C509" s="2"/>
-      <c r="D509" s="2"/>
+      <c r="C509" s="1"/>
+      <c r="D509" s="1"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="C510" s="2"/>
-      <c r="D510" s="2"/>
+      <c r="C510" s="1"/>
+      <c r="D510" s="1"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
+      <c r="C511" s="1"/>
+      <c r="D511" s="1"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
+      <c r="C512" s="1"/>
+      <c r="D512" s="1"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
+      <c r="C513" s="1"/>
+      <c r="D513" s="1"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
+      <c r="C514" s="1"/>
+      <c r="D514" s="1"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
+      <c r="C515" s="1"/>
+      <c r="D515" s="1"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
+      <c r="C516" s="1"/>
+      <c r="D516" s="1"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
+      <c r="C517" s="1"/>
+      <c r="D517" s="1"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
+      <c r="C518" s="1"/>
+      <c r="D518" s="1"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
+      <c r="C519" s="1"/>
+      <c r="D519" s="1"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
+      <c r="C520" s="1"/>
+      <c r="D520" s="1"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
+      <c r="C521" s="1"/>
+      <c r="D521" s="1"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
+      <c r="C522" s="1"/>
+      <c r="D522" s="1"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
+      <c r="C523" s="1"/>
+      <c r="D523" s="1"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
+      <c r="C524" s="1"/>
+      <c r="D524" s="1"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="C525" s="2"/>
-      <c r="D525" s="2"/>
+      <c r="C525" s="1"/>
+      <c r="D525" s="1"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="C526" s="2"/>
-      <c r="D526" s="2"/>
+      <c r="C526" s="1"/>
+      <c r="D526" s="1"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="C527" s="2"/>
-      <c r="D527" s="2"/>
+      <c r="C527" s="1"/>
+      <c r="D527" s="1"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="C528" s="2"/>
-      <c r="D528" s="2"/>
+      <c r="C528" s="1"/>
+      <c r="D528" s="1"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="C529" s="2"/>
-      <c r="D529" s="2"/>
+      <c r="C529" s="1"/>
+      <c r="D529" s="1"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="C530" s="2"/>
-      <c r="D530" s="2"/>
+      <c r="C530" s="1"/>
+      <c r="D530" s="1"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="C531" s="2"/>
-      <c r="D531" s="2"/>
+      <c r="C531" s="1"/>
+      <c r="D531" s="1"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="C532" s="2"/>
-      <c r="D532" s="2"/>
+      <c r="C532" s="1"/>
+      <c r="D532" s="1"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="C533" s="2"/>
-      <c r="D533" s="2"/>
+      <c r="C533" s="1"/>
+      <c r="D533" s="1"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="C534" s="2"/>
-      <c r="D534" s="2"/>
+      <c r="C534" s="1"/>
+      <c r="D534" s="1"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="C535" s="2"/>
-      <c r="D535" s="2"/>
+      <c r="C535" s="1"/>
+      <c r="D535" s="1"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="C536" s="2"/>
-      <c r="D536" s="2"/>
+      <c r="C536" s="1"/>
+      <c r="D536" s="1"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="C537" s="2"/>
-      <c r="D537" s="2"/>
+      <c r="C537" s="1"/>
+      <c r="D537" s="1"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="C538" s="2"/>
-      <c r="D538" s="2"/>
+      <c r="C538" s="1"/>
+      <c r="D538" s="1"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="C539" s="2"/>
-      <c r="D539" s="2"/>
+      <c r="C539" s="1"/>
+      <c r="D539" s="1"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="C540" s="2"/>
-      <c r="D540" s="2"/>
+      <c r="C540" s="1"/>
+      <c r="D540" s="1"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="C541" s="2"/>
-      <c r="D541" s="2"/>
+      <c r="C541" s="1"/>
+      <c r="D541" s="1"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="C542" s="2"/>
-      <c r="D542" s="2"/>
+      <c r="C542" s="1"/>
+      <c r="D542" s="1"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="C543" s="2"/>
-      <c r="D543" s="2"/>
+      <c r="C543" s="1"/>
+      <c r="D543" s="1"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="C544" s="2"/>
-      <c r="D544" s="2"/>
+      <c r="C544" s="1"/>
+      <c r="D544" s="1"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="C545" s="2"/>
-      <c r="D545" s="2"/>
+      <c r="C545" s="1"/>
+      <c r="D545" s="1"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="C546" s="2"/>
-      <c r="D546" s="2"/>
+      <c r="C546" s="1"/>
+      <c r="D546" s="1"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="C547" s="2"/>
-      <c r="D547" s="2"/>
+      <c r="C547" s="1"/>
+      <c r="D547" s="1"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="C548" s="2"/>
-      <c r="D548" s="2"/>
+      <c r="C548" s="1"/>
+      <c r="D548" s="1"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="C549" s="2"/>
-      <c r="D549" s="2"/>
+      <c r="C549" s="1"/>
+      <c r="D549" s="1"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="C550" s="2"/>
-      <c r="D550" s="2"/>
+      <c r="C550" s="1"/>
+      <c r="D550" s="1"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="C551" s="2"/>
-      <c r="D551" s="2"/>
+      <c r="C551" s="1"/>
+      <c r="D551" s="1"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
+      <c r="C552" s="1"/>
+      <c r="D552" s="1"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
+      <c r="C553" s="1"/>
+      <c r="D553" s="1"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="C554" s="2"/>
-      <c r="D554" s="2"/>
+      <c r="C554" s="1"/>
+      <c r="D554" s="1"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="C555" s="2"/>
-      <c r="D555" s="2"/>
+      <c r="C555" s="1"/>
+      <c r="D555" s="1"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="C556" s="2"/>
-      <c r="D556" s="2"/>
+      <c r="C556" s="1"/>
+      <c r="D556" s="1"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="C557" s="2"/>
-      <c r="D557" s="2"/>
+      <c r="C557" s="1"/>
+      <c r="D557" s="1"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="C558" s="2"/>
-      <c r="D558" s="2"/>
+      <c r="C558" s="1"/>
+      <c r="D558" s="1"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="C559" s="2"/>
-      <c r="D559" s="2"/>
+      <c r="C559" s="1"/>
+      <c r="D559" s="1"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="C560" s="2"/>
-      <c r="D560" s="2"/>
+      <c r="C560" s="1"/>
+      <c r="D560" s="1"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="C561" s="2"/>
-      <c r="D561" s="2"/>
+      <c r="C561" s="1"/>
+      <c r="D561" s="1"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="C562" s="2"/>
-      <c r="D562" s="2"/>
+      <c r="C562" s="1"/>
+      <c r="D562" s="1"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="C563" s="2"/>
-      <c r="D563" s="2"/>
+      <c r="C563" s="1"/>
+      <c r="D563" s="1"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="C564" s="2"/>
-      <c r="D564" s="2"/>
+      <c r="C564" s="1"/>
+      <c r="D564" s="1"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="C565" s="2"/>
-      <c r="D565" s="2"/>
+      <c r="C565" s="1"/>
+      <c r="D565" s="1"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
+      <c r="C566" s="1"/>
+      <c r="D566" s="1"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="C567" s="2"/>
-      <c r="D567" s="2"/>
+      <c r="C567" s="1"/>
+      <c r="D567" s="1"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="C568" s="2"/>
-      <c r="D568" s="2"/>
+      <c r="C568" s="1"/>
+      <c r="D568" s="1"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="C569" s="2"/>
-      <c r="D569" s="2"/>
+      <c r="C569" s="1"/>
+      <c r="D569" s="1"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="C570" s="2"/>
-      <c r="D570" s="2"/>
+      <c r="C570" s="1"/>
+      <c r="D570" s="1"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="C571" s="2"/>
-      <c r="D571" s="2"/>
+      <c r="C571" s="1"/>
+      <c r="D571" s="1"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="C572" s="2"/>
-      <c r="D572" s="2"/>
+      <c r="C572" s="1"/>
+      <c r="D572" s="1"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="C573" s="2"/>
-      <c r="D573" s="2"/>
+      <c r="C573" s="1"/>
+      <c r="D573" s="1"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="C574" s="2"/>
-      <c r="D574" s="2"/>
+      <c r="C574" s="1"/>
+      <c r="D574" s="1"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="C575" s="2"/>
-      <c r="D575" s="2"/>
+      <c r="C575" s="1"/>
+      <c r="D575" s="1"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="C576" s="2"/>
-      <c r="D576" s="2"/>
+      <c r="C576" s="1"/>
+      <c r="D576" s="1"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="C577" s="2"/>
-      <c r="D577" s="2"/>
+      <c r="C577" s="1"/>
+      <c r="D577" s="1"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="C578" s="2"/>
-      <c r="D578" s="2"/>
+      <c r="C578" s="1"/>
+      <c r="D578" s="1"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="C579" s="2"/>
-      <c r="D579" s="2"/>
+      <c r="C579" s="1"/>
+      <c r="D579" s="1"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="C580" s="2"/>
-      <c r="D580" s="2"/>
+      <c r="C580" s="1"/>
+      <c r="D580" s="1"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="C581" s="2"/>
-      <c r="D581" s="2"/>
+      <c r="C581" s="1"/>
+      <c r="D581" s="1"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="C582" s="2"/>
-      <c r="D582" s="2"/>
+      <c r="C582" s="1"/>
+      <c r="D582" s="1"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="C583" s="2"/>
-      <c r="D583" s="2"/>
+      <c r="C583" s="1"/>
+      <c r="D583" s="1"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="2"/>
-      <c r="D584" s="2"/>
+      <c r="C584" s="1"/>
+      <c r="D584" s="1"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="2"/>
-      <c r="D585" s="2"/>
+      <c r="C585" s="1"/>
+      <c r="D585" s="1"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="2"/>
-      <c r="D586" s="2"/>
+      <c r="C586" s="1"/>
+      <c r="D586" s="1"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="C587" s="2"/>
-      <c r="D587" s="2"/>
+      <c r="C587" s="1"/>
+      <c r="D587" s="1"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="C588" s="2"/>
-      <c r="D588" s="2"/>
+      <c r="C588" s="1"/>
+      <c r="D588" s="1"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="C589" s="2"/>
-      <c r="D589" s="2"/>
+      <c r="C589" s="1"/>
+      <c r="D589" s="1"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="C590" s="2"/>
-      <c r="D590" s="2"/>
+      <c r="C590" s="1"/>
+      <c r="D590" s="1"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="C591" s="2"/>
-      <c r="D591" s="2"/>
+      <c r="C591" s="1"/>
+      <c r="D591" s="1"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="C592" s="2"/>
-      <c r="D592" s="2"/>
+      <c r="C592" s="1"/>
+      <c r="D592" s="1"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="C593" s="2"/>
-      <c r="D593" s="2"/>
+      <c r="C593" s="1"/>
+      <c r="D593" s="1"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="C594" s="2"/>
-      <c r="D594" s="2"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="1"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="C595" s="2"/>
-      <c r="D595" s="2"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="1"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="C596" s="2"/>
-      <c r="D596" s="2"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="1"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="C597" s="2"/>
-      <c r="D597" s="2"/>
+      <c r="C597" s="1"/>
+      <c r="D597" s="1"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="C598" s="2"/>
-      <c r="D598" s="2"/>
+      <c r="C598" s="1"/>
+      <c r="D598" s="1"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="C599" s="2"/>
-      <c r="D599" s="2"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="2"/>
-      <c r="D600" s="2"/>
+      <c r="C600" s="1"/>
+      <c r="D600" s="1"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="2"/>
-      <c r="D601" s="2"/>
+      <c r="C601" s="1"/>
+      <c r="D601" s="1"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="2"/>
-      <c r="D602" s="2"/>
+      <c r="C602" s="1"/>
+      <c r="D602" s="1"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="C603" s="2"/>
-      <c r="D603" s="2"/>
+      <c r="C603" s="1"/>
+      <c r="D603" s="1"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="C604" s="2"/>
-      <c r="D604" s="2"/>
+      <c r="C604" s="1"/>
+      <c r="D604" s="1"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="C605" s="2"/>
-      <c r="D605" s="2"/>
+      <c r="C605" s="1"/>
+      <c r="D605" s="1"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="C606" s="2"/>
-      <c r="D606" s="2"/>
+      <c r="C606" s="1"/>
+      <c r="D606" s="1"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="C607" s="2"/>
-      <c r="D607" s="2"/>
+      <c r="C607" s="1"/>
+      <c r="D607" s="1"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
+      <c r="C608" s="1"/>
+      <c r="D608" s="1"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="C609" s="2"/>
-      <c r="D609" s="2"/>
+      <c r="C609" s="1"/>
+      <c r="D609" s="1"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="C610" s="2"/>
-      <c r="D610" s="2"/>
+      <c r="C610" s="1"/>
+      <c r="D610" s="1"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="C611" s="2"/>
-      <c r="D611" s="2"/>
+      <c r="C611" s="1"/>
+      <c r="D611" s="1"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="C612" s="2"/>
-      <c r="D612" s="2"/>
+      <c r="C612" s="1"/>
+      <c r="D612" s="1"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="C613" s="2"/>
-      <c r="D613" s="2"/>
+      <c r="C613" s="1"/>
+      <c r="D613" s="1"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="C614" s="2"/>
-      <c r="D614" s="2"/>
+      <c r="C614" s="1"/>
+      <c r="D614" s="1"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
+      <c r="C615" s="1"/>
+      <c r="D615" s="1"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="2"/>
-      <c r="D616" s="2"/>
+      <c r="C616" s="1"/>
+      <c r="D616" s="1"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="2"/>
-      <c r="D617" s="2"/>
+      <c r="C617" s="1"/>
+      <c r="D617" s="1"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="2"/>
-      <c r="D618" s="2"/>
+      <c r="C618" s="1"/>
+      <c r="D618" s="1"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="C619" s="2"/>
-      <c r="D619" s="2"/>
+      <c r="C619" s="1"/>
+      <c r="D619" s="1"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="C620" s="2"/>
-      <c r="D620" s="2"/>
+      <c r="C620" s="1"/>
+      <c r="D620" s="1"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="C621" s="2"/>
-      <c r="D621" s="2"/>
+      <c r="C621" s="1"/>
+      <c r="D621" s="1"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
+      <c r="C622" s="1"/>
+      <c r="D622" s="1"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="C623" s="2"/>
-      <c r="D623" s="2"/>
+      <c r="C623" s="1"/>
+      <c r="D623" s="1"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
+      <c r="C624" s="1"/>
+      <c r="D624" s="1"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
+      <c r="C625" s="1"/>
+      <c r="D625" s="1"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
+      <c r="C626" s="1"/>
+      <c r="D626" s="1"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="C627" s="2"/>
-      <c r="D627" s="2"/>
+      <c r="C627" s="1"/>
+      <c r="D627" s="1"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="C628" s="2"/>
-      <c r="D628" s="2"/>
+      <c r="C628" s="1"/>
+      <c r="D628" s="1"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="C629" s="2"/>
-      <c r="D629" s="2"/>
+      <c r="C629" s="1"/>
+      <c r="D629" s="1"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="C630" s="2"/>
-      <c r="D630" s="2"/>
+      <c r="C630" s="1"/>
+      <c r="D630" s="1"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="C631" s="2"/>
-      <c r="D631" s="2"/>
+      <c r="C631" s="1"/>
+      <c r="D631" s="1"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="C632" s="2"/>
-      <c r="D632" s="2"/>
+      <c r="C632" s="1"/>
+      <c r="D632" s="1"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="C633" s="2"/>
-      <c r="D633" s="2"/>
+      <c r="C633" s="1"/>
+      <c r="D633" s="1"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
+      <c r="C634" s="1"/>
+      <c r="D634" s="1"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
+      <c r="C635" s="1"/>
+      <c r="D635" s="1"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
+      <c r="C636" s="1"/>
+      <c r="D636" s="1"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
+      <c r="C637" s="1"/>
+      <c r="D637" s="1"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="C638" s="2"/>
-      <c r="D638" s="2"/>
+      <c r="C638" s="1"/>
+      <c r="D638" s="1"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="C639" s="2"/>
-      <c r="D639" s="2"/>
+      <c r="C639" s="1"/>
+      <c r="D639" s="1"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="C640" s="2"/>
-      <c r="D640" s="2"/>
+      <c r="C640" s="1"/>
+      <c r="D640" s="1"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="C641" s="2"/>
-      <c r="D641" s="2"/>
+      <c r="C641" s="1"/>
+      <c r="D641" s="1"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
+      <c r="C642" s="1"/>
+      <c r="D642" s="1"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="C643" s="2"/>
-      <c r="D643" s="2"/>
+      <c r="C643" s="1"/>
+      <c r="D643" s="1"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="C644" s="2"/>
-      <c r="D644" s="2"/>
+      <c r="C644" s="1"/>
+      <c r="D644" s="1"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="C645" s="2"/>
-      <c r="D645" s="2"/>
+      <c r="C645" s="1"/>
+      <c r="D645" s="1"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="C646" s="2"/>
-      <c r="D646" s="2"/>
+      <c r="C646" s="1"/>
+      <c r="D646" s="1"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
+      <c r="C647" s="1"/>
+      <c r="D647" s="1"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="C648" s="2"/>
-      <c r="D648" s="2"/>
+      <c r="C648" s="1"/>
+      <c r="D648" s="1"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="C649" s="2"/>
-      <c r="D649" s="2"/>
+      <c r="C649" s="1"/>
+      <c r="D649" s="1"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="C650" s="2"/>
-      <c r="D650" s="2"/>
+      <c r="C650" s="1"/>
+      <c r="D650" s="1"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="C651" s="2"/>
-      <c r="D651" s="2"/>
+      <c r="C651" s="1"/>
+      <c r="D651" s="1"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="C652" s="2"/>
-      <c r="D652" s="2"/>
+      <c r="C652" s="1"/>
+      <c r="D652" s="1"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="C653" s="2"/>
-      <c r="D653" s="2"/>
+      <c r="C653" s="1"/>
+      <c r="D653" s="1"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="C654" s="2"/>
-      <c r="D654" s="2"/>
+      <c r="C654" s="1"/>
+      <c r="D654" s="1"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
+      <c r="C655" s="1"/>
+      <c r="D655" s="1"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
+      <c r="C656" s="1"/>
+      <c r="D656" s="1"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
+      <c r="C657" s="1"/>
+      <c r="D657" s="1"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
+      <c r="C658" s="1"/>
+      <c r="D658" s="1"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
+      <c r="C659" s="1"/>
+      <c r="D659" s="1"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
+      <c r="C660" s="1"/>
+      <c r="D660" s="1"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
+      <c r="C661" s="1"/>
+      <c r="D661" s="1"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
+      <c r="C662" s="1"/>
+      <c r="D662" s="1"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
+      <c r="C663" s="1"/>
+      <c r="D663" s="1"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
+      <c r="C664" s="1"/>
+      <c r="D664" s="1"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
+      <c r="C665" s="1"/>
+      <c r="D665" s="1"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
+      <c r="C666" s="1"/>
+      <c r="D666" s="1"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
+      <c r="C667" s="1"/>
+      <c r="D667" s="1"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
+      <c r="C668" s="1"/>
+      <c r="D668" s="1"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
+      <c r="C669" s="1"/>
+      <c r="D669" s="1"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
+      <c r="C670" s="1"/>
+      <c r="D670" s="1"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
+      <c r="C671" s="1"/>
+      <c r="D671" s="1"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
+      <c r="C672" s="1"/>
+      <c r="D672" s="1"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
+      <c r="C673" s="1"/>
+      <c r="D673" s="1"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
+      <c r="C674" s="1"/>
+      <c r="D674" s="1"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
+      <c r="C675" s="1"/>
+      <c r="D675" s="1"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
+      <c r="C676" s="1"/>
+      <c r="D676" s="1"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
+      <c r="C677" s="1"/>
+      <c r="D677" s="1"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
+      <c r="C678" s="1"/>
+      <c r="D678" s="1"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
+      <c r="C679" s="1"/>
+      <c r="D679" s="1"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
+      <c r="C680" s="1"/>
+      <c r="D680" s="1"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
+      <c r="C681" s="1"/>
+      <c r="D681" s="1"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="C682" s="2"/>
-      <c r="D682" s="2"/>
+      <c r="C682" s="1"/>
+      <c r="D682" s="1"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="C683" s="2"/>
-      <c r="D683" s="2"/>
+      <c r="C683" s="1"/>
+      <c r="D683" s="1"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="C684" s="2"/>
-      <c r="D684" s="2"/>
+      <c r="C684" s="1"/>
+      <c r="D684" s="1"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="C685" s="2"/>
-      <c r="D685" s="2"/>
+      <c r="C685" s="1"/>
+      <c r="D685" s="1"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="C686" s="2"/>
-      <c r="D686" s="2"/>
+      <c r="C686" s="1"/>
+      <c r="D686" s="1"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="C687" s="2"/>
-      <c r="D687" s="2"/>
+      <c r="C687" s="1"/>
+      <c r="D687" s="1"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="C688" s="2"/>
-      <c r="D688" s="2"/>
+      <c r="C688" s="1"/>
+      <c r="D688" s="1"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="C689" s="2"/>
-      <c r="D689" s="2"/>
+      <c r="C689" s="1"/>
+      <c r="D689" s="1"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="C690" s="2"/>
-      <c r="D690" s="2"/>
+      <c r="C690" s="1"/>
+      <c r="D690" s="1"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="C691" s="2"/>
-      <c r="D691" s="2"/>
+      <c r="C691" s="1"/>
+      <c r="D691" s="1"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="C692" s="2"/>
-      <c r="D692" s="2"/>
+      <c r="C692" s="1"/>
+      <c r="D692" s="1"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="C693" s="2"/>
-      <c r="D693" s="2"/>
+      <c r="C693" s="1"/>
+      <c r="D693" s="1"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
+      <c r="C694" s="1"/>
+      <c r="D694" s="1"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
+      <c r="C695" s="1"/>
+      <c r="D695" s="1"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
+      <c r="C696" s="1"/>
+      <c r="D696" s="1"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="C697" s="2"/>
-      <c r="D697" s="2"/>
+      <c r="C697" s="1"/>
+      <c r="D697" s="1"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="C698" s="2"/>
-      <c r="D698" s="2"/>
+      <c r="C698" s="1"/>
+      <c r="D698" s="1"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="C699" s="2"/>
-      <c r="D699" s="2"/>
+      <c r="C699" s="1"/>
+      <c r="D699" s="1"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="C700" s="2"/>
-      <c r="D700" s="2"/>
+      <c r="C700" s="1"/>
+      <c r="D700" s="1"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
+      <c r="C701" s="1"/>
+      <c r="D701" s="1"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
+      <c r="C702" s="1"/>
+      <c r="D702" s="1"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
+      <c r="C703" s="1"/>
+      <c r="D703" s="1"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
+      <c r="C704" s="1"/>
+      <c r="D704" s="1"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
+      <c r="C705" s="1"/>
+      <c r="D705" s="1"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
+      <c r="C706" s="1"/>
+      <c r="D706" s="1"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
+      <c r="C707" s="1"/>
+      <c r="D707" s="1"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
+      <c r="C708" s="1"/>
+      <c r="D708" s="1"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
+      <c r="C709" s="1"/>
+      <c r="D709" s="1"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
+      <c r="C710" s="1"/>
+      <c r="D710" s="1"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
+      <c r="C711" s="1"/>
+      <c r="D711" s="1"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
+      <c r="C712" s="1"/>
+      <c r="D712" s="1"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
+      <c r="C713" s="1"/>
+      <c r="D713" s="1"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
+      <c r="C714" s="1"/>
+      <c r="D714" s="1"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="C715" s="2"/>
-      <c r="D715" s="2"/>
+      <c r="C715" s="1"/>
+      <c r="D715" s="1"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="C716" s="2"/>
-      <c r="D716" s="2"/>
+      <c r="C716" s="1"/>
+      <c r="D716" s="1"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="C717" s="2"/>
-      <c r="D717" s="2"/>
+      <c r="C717" s="1"/>
+      <c r="D717" s="1"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="C718" s="2"/>
-      <c r="D718" s="2"/>
+      <c r="C718" s="1"/>
+      <c r="D718" s="1"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="C719" s="2"/>
-      <c r="D719" s="2"/>
+      <c r="C719" s="1"/>
+      <c r="D719" s="1"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="C720" s="2"/>
-      <c r="D720" s="2"/>
+      <c r="C720" s="1"/>
+      <c r="D720" s="1"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="C721" s="2"/>
-      <c r="D721" s="2"/>
+      <c r="C721" s="1"/>
+      <c r="D721" s="1"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="C722" s="2"/>
-      <c r="D722" s="2"/>
+      <c r="C722" s="1"/>
+      <c r="D722" s="1"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="C723" s="2"/>
-      <c r="D723" s="2"/>
+      <c r="C723" s="1"/>
+      <c r="D723" s="1"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="C724" s="2"/>
-      <c r="D724" s="2"/>
+      <c r="C724" s="1"/>
+      <c r="D724" s="1"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="C725" s="2"/>
-      <c r="D725" s="2"/>
+      <c r="C725" s="1"/>
+      <c r="D725" s="1"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="C726" s="2"/>
-      <c r="D726" s="2"/>
+      <c r="C726" s="1"/>
+      <c r="D726" s="1"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="C727" s="2"/>
-      <c r="D727" s="2"/>
+      <c r="C727" s="1"/>
+      <c r="D727" s="1"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="C728" s="2"/>
-      <c r="D728" s="2"/>
+      <c r="C728" s="1"/>
+      <c r="D728" s="1"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="C729" s="2"/>
-      <c r="D729" s="2"/>
+      <c r="C729" s="1"/>
+      <c r="D729" s="1"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="C730" s="2"/>
-      <c r="D730" s="2"/>
+      <c r="C730" s="1"/>
+      <c r="D730" s="1"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="C731" s="2"/>
-      <c r="D731" s="2"/>
+      <c r="C731" s="1"/>
+      <c r="D731" s="1"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="C732" s="2"/>
-      <c r="D732" s="2"/>
+      <c r="C732" s="1"/>
+      <c r="D732" s="1"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="C733" s="2"/>
-      <c r="D733" s="2"/>
+      <c r="C733" s="1"/>
+      <c r="D733" s="1"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="C734" s="2"/>
-      <c r="D734" s="2"/>
+      <c r="C734" s="1"/>
+      <c r="D734" s="1"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="C735" s="2"/>
-      <c r="D735" s="2"/>
+      <c r="C735" s="1"/>
+      <c r="D735" s="1"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="C736" s="2"/>
-      <c r="D736" s="2"/>
+      <c r="C736" s="1"/>
+      <c r="D736" s="1"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="C737" s="2"/>
-      <c r="D737" s="2"/>
+      <c r="C737" s="1"/>
+      <c r="D737" s="1"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="C738" s="2"/>
-      <c r="D738" s="2"/>
+      <c r="C738" s="1"/>
+      <c r="D738" s="1"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="C739" s="2"/>
-      <c r="D739" s="2"/>
+      <c r="C739" s="1"/>
+      <c r="D739" s="1"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="C740" s="2"/>
-      <c r="D740" s="2"/>
+      <c r="C740" s="1"/>
+      <c r="D740" s="1"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="C741" s="2"/>
-      <c r="D741" s="2"/>
+      <c r="C741" s="1"/>
+      <c r="D741" s="1"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="C742" s="2"/>
-      <c r="D742" s="2"/>
+      <c r="C742" s="1"/>
+      <c r="D742" s="1"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="C743" s="2"/>
-      <c r="D743" s="2"/>
+      <c r="C743" s="1"/>
+      <c r="D743" s="1"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="C744" s="2"/>
-      <c r="D744" s="2"/>
+      <c r="C744" s="1"/>
+      <c r="D744" s="1"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="C745" s="2"/>
-      <c r="D745" s="2"/>
+      <c r="C745" s="1"/>
+      <c r="D745" s="1"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="C746" s="2"/>
-      <c r="D746" s="2"/>
+      <c r="C746" s="1"/>
+      <c r="D746" s="1"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="C747" s="2"/>
-      <c r="D747" s="2"/>
+      <c r="C747" s="1"/>
+      <c r="D747" s="1"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="C748" s="2"/>
-      <c r="D748" s="2"/>
+      <c r="C748" s="1"/>
+      <c r="D748" s="1"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="C749" s="2"/>
-      <c r="D749" s="2"/>
+      <c r="C749" s="1"/>
+      <c r="D749" s="1"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="C750" s="2"/>
-      <c r="D750" s="2"/>
+      <c r="C750" s="1"/>
+      <c r="D750" s="1"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="C751" s="2"/>
-      <c r="D751" s="2"/>
+      <c r="C751" s="1"/>
+      <c r="D751" s="1"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="C752" s="2"/>
-      <c r="D752" s="2"/>
+      <c r="C752" s="1"/>
+      <c r="D752" s="1"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="C753" s="2"/>
-      <c r="D753" s="2"/>
+      <c r="C753" s="1"/>
+      <c r="D753" s="1"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="C754" s="2"/>
-      <c r="D754" s="2"/>
+      <c r="C754" s="1"/>
+      <c r="D754" s="1"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="C755" s="2"/>
-      <c r="D755" s="2"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="C756" s="2"/>
-      <c r="D756" s="2"/>
+      <c r="C756" s="1"/>
+      <c r="D756" s="1"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="C757" s="2"/>
-      <c r="D757" s="2"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="C758" s="2"/>
-      <c r="D758" s="2"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="C759" s="2"/>
-      <c r="D759" s="2"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="C760" s="2"/>
-      <c r="D760" s="2"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="C761" s="2"/>
-      <c r="D761" s="2"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="C762" s="2"/>
-      <c r="D762" s="2"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="C763" s="2"/>
-      <c r="D763" s="2"/>
+      <c r="C763" s="1"/>
+      <c r="D763" s="1"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="C764" s="2"/>
-      <c r="D764" s="2"/>
+      <c r="C764" s="1"/>
+      <c r="D764" s="1"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="C765" s="2"/>
-      <c r="D765" s="2"/>
+      <c r="C765" s="1"/>
+      <c r="D765" s="1"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="C766" s="2"/>
-      <c r="D766" s="2"/>
+      <c r="C766" s="1"/>
+      <c r="D766" s="1"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
+      <c r="C767" s="1"/>
+      <c r="D767" s="1"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="C768" s="2"/>
-      <c r="D768" s="2"/>
+      <c r="C768" s="1"/>
+      <c r="D768" s="1"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="C769" s="2"/>
-      <c r="D769" s="2"/>
+      <c r="C769" s="1"/>
+      <c r="D769" s="1"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="C770" s="2"/>
-      <c r="D770" s="2"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="C771" s="2"/>
-      <c r="D771" s="2"/>
+      <c r="C771" s="1"/>
+      <c r="D771" s="1"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="C772" s="2"/>
-      <c r="D772" s="2"/>
+      <c r="C772" s="1"/>
+      <c r="D772" s="1"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
+      <c r="C773" s="1"/>
+      <c r="D773" s="1"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
+      <c r="C774" s="1"/>
+      <c r="D774" s="1"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
+      <c r="C775" s="1"/>
+      <c r="D775" s="1"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
+      <c r="C776" s="1"/>
+      <c r="D776" s="1"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="C777" s="2"/>
-      <c r="D777" s="2"/>
+      <c r="C777" s="1"/>
+      <c r="D777" s="1"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="C778" s="2"/>
-      <c r="D778" s="2"/>
+      <c r="C778" s="1"/>
+      <c r="D778" s="1"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="C779" s="2"/>
-      <c r="D779" s="2"/>
+      <c r="C779" s="1"/>
+      <c r="D779" s="1"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="C780" s="2"/>
-      <c r="D780" s="2"/>
+      <c r="C780" s="1"/>
+      <c r="D780" s="1"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="C781" s="2"/>
-      <c r="D781" s="2"/>
+      <c r="C781" s="1"/>
+      <c r="D781" s="1"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="C782" s="2"/>
-      <c r="D782" s="2"/>
+      <c r="C782" s="1"/>
+      <c r="D782" s="1"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="C783" s="2"/>
-      <c r="D783" s="2"/>
+      <c r="C783" s="1"/>
+      <c r="D783" s="1"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="C784" s="2"/>
-      <c r="D784" s="2"/>
+      <c r="C784" s="1"/>
+      <c r="D784" s="1"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="C785" s="2"/>
-      <c r="D785" s="2"/>
+      <c r="C785" s="1"/>
+      <c r="D785" s="1"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="C786" s="2"/>
-      <c r="D786" s="2"/>
+      <c r="C786" s="1"/>
+      <c r="D786" s="1"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="C787" s="2"/>
-      <c r="D787" s="2"/>
+      <c r="C787" s="1"/>
+      <c r="D787" s="1"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="C788" s="2"/>
-      <c r="D788" s="2"/>
+      <c r="C788" s="1"/>
+      <c r="D788" s="1"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="C789" s="2"/>
-      <c r="D789" s="2"/>
+      <c r="C789" s="1"/>
+      <c r="D789" s="1"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="C790" s="2"/>
-      <c r="D790" s="2"/>
+      <c r="C790" s="1"/>
+      <c r="D790" s="1"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="C791" s="2"/>
-      <c r="D791" s="2"/>
+      <c r="C791" s="1"/>
+      <c r="D791" s="1"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="C792" s="2"/>
-      <c r="D792" s="2"/>
+      <c r="C792" s="1"/>
+      <c r="D792" s="1"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="C793" s="2"/>
-      <c r="D793" s="2"/>
+      <c r="C793" s="1"/>
+      <c r="D793" s="1"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="C794" s="2"/>
-      <c r="D794" s="2"/>
+      <c r="C794" s="1"/>
+      <c r="D794" s="1"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="C795" s="2"/>
-      <c r="D795" s="2"/>
+      <c r="C795" s="1"/>
+      <c r="D795" s="1"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="C796" s="2"/>
-      <c r="D796" s="2"/>
+      <c r="C796" s="1"/>
+      <c r="D796" s="1"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="C797" s="2"/>
-      <c r="D797" s="2"/>
+      <c r="C797" s="1"/>
+      <c r="D797" s="1"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="C798" s="2"/>
-      <c r="D798" s="2"/>
+      <c r="C798" s="1"/>
+      <c r="D798" s="1"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="C799" s="2"/>
-      <c r="D799" s="2"/>
+      <c r="C799" s="1"/>
+      <c r="D799" s="1"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="C800" s="2"/>
-      <c r="D800" s="2"/>
+      <c r="C800" s="1"/>
+      <c r="D800" s="1"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="C801" s="2"/>
-      <c r="D801" s="2"/>
+      <c r="C801" s="1"/>
+      <c r="D801" s="1"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="C802" s="2"/>
-      <c r="D802" s="2"/>
+      <c r="C802" s="1"/>
+      <c r="D802" s="1"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="C803" s="2"/>
-      <c r="D803" s="2"/>
+      <c r="C803" s="1"/>
+      <c r="D803" s="1"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="C804" s="2"/>
-      <c r="D804" s="2"/>
+      <c r="C804" s="1"/>
+      <c r="D804" s="1"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="C805" s="2"/>
-      <c r="D805" s="2"/>
+      <c r="C805" s="1"/>
+      <c r="D805" s="1"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="C806" s="2"/>
-      <c r="D806" s="2"/>
+      <c r="C806" s="1"/>
+      <c r="D806" s="1"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="C807" s="2"/>
-      <c r="D807" s="2"/>
+      <c r="C807" s="1"/>
+      <c r="D807" s="1"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="C808" s="2"/>
-      <c r="D808" s="2"/>
+      <c r="C808" s="1"/>
+      <c r="D808" s="1"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="C809" s="2"/>
-      <c r="D809" s="2"/>
+      <c r="C809" s="1"/>
+      <c r="D809" s="1"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="C810" s="2"/>
-      <c r="D810" s="2"/>
+      <c r="C810" s="1"/>
+      <c r="D810" s="1"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="C811" s="2"/>
-      <c r="D811" s="2"/>
+      <c r="C811" s="1"/>
+      <c r="D811" s="1"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="C812" s="2"/>
-      <c r="D812" s="2"/>
+      <c r="C812" s="1"/>
+      <c r="D812" s="1"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="C813" s="2"/>
-      <c r="D813" s="2"/>
+      <c r="C813" s="1"/>
+      <c r="D813" s="1"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="C814" s="2"/>
-      <c r="D814" s="2"/>
+      <c r="C814" s="1"/>
+      <c r="D814" s="1"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="C815" s="2"/>
-      <c r="D815" s="2"/>
+      <c r="C815" s="1"/>
+      <c r="D815" s="1"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="C816" s="2"/>
-      <c r="D816" s="2"/>
+      <c r="C816" s="1"/>
+      <c r="D816" s="1"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="C817" s="2"/>
-      <c r="D817" s="2"/>
+      <c r="C817" s="1"/>
+      <c r="D817" s="1"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="C818" s="2"/>
-      <c r="D818" s="2"/>
+      <c r="C818" s="1"/>
+      <c r="D818" s="1"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="C819" s="2"/>
-      <c r="D819" s="2"/>
+      <c r="C819" s="1"/>
+      <c r="D819" s="1"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="C820" s="2"/>
-      <c r="D820" s="2"/>
+      <c r="C820" s="1"/>
+      <c r="D820" s="1"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="C821" s="2"/>
-      <c r="D821" s="2"/>
+      <c r="C821" s="1"/>
+      <c r="D821" s="1"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="C822" s="2"/>
-      <c r="D822" s="2"/>
+      <c r="C822" s="1"/>
+      <c r="D822" s="1"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="C823" s="2"/>
-      <c r="D823" s="2"/>
+      <c r="C823" s="1"/>
+      <c r="D823" s="1"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="C824" s="2"/>
-      <c r="D824" s="2"/>
+      <c r="C824" s="1"/>
+      <c r="D824" s="1"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="C825" s="2"/>
-      <c r="D825" s="2"/>
+      <c r="C825" s="1"/>
+      <c r="D825" s="1"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="C826" s="2"/>
-      <c r="D826" s="2"/>
+      <c r="C826" s="1"/>
+      <c r="D826" s="1"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="C827" s="2"/>
-      <c r="D827" s="2"/>
+      <c r="C827" s="1"/>
+      <c r="D827" s="1"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="C828" s="2"/>
-      <c r="D828" s="2"/>
+      <c r="C828" s="1"/>
+      <c r="D828" s="1"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="C829" s="2"/>
-      <c r="D829" s="2"/>
+      <c r="C829" s="1"/>
+      <c r="D829" s="1"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="C830" s="2"/>
-      <c r="D830" s="2"/>
+      <c r="C830" s="1"/>
+      <c r="D830" s="1"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="C831" s="2"/>
-      <c r="D831" s="2"/>
+      <c r="C831" s="1"/>
+      <c r="D831" s="1"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="C832" s="2"/>
-      <c r="D832" s="2"/>
+      <c r="C832" s="1"/>
+      <c r="D832" s="1"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="C833" s="2"/>
-      <c r="D833" s="2"/>
+      <c r="C833" s="1"/>
+      <c r="D833" s="1"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="C834" s="2"/>
-      <c r="D834" s="2"/>
+      <c r="C834" s="1"/>
+      <c r="D834" s="1"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="C835" s="2"/>
-      <c r="D835" s="2"/>
+      <c r="C835" s="1"/>
+      <c r="D835" s="1"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="C836" s="2"/>
-      <c r="D836" s="2"/>
+      <c r="C836" s="1"/>
+      <c r="D836" s="1"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="C837" s="2"/>
-      <c r="D837" s="2"/>
+      <c r="C837" s="1"/>
+      <c r="D837" s="1"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="C838" s="2"/>
-      <c r="D838" s="2"/>
+      <c r="C838" s="1"/>
+      <c r="D838" s="1"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="C839" s="2"/>
-      <c r="D839" s="2"/>
+      <c r="C839" s="1"/>
+      <c r="D839" s="1"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="C840" s="2"/>
-      <c r="D840" s="2"/>
+      <c r="C840" s="1"/>
+      <c r="D840" s="1"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="C841" s="2"/>
-      <c r="D841" s="2"/>
+      <c r="C841" s="1"/>
+      <c r="D841" s="1"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="C842" s="2"/>
-      <c r="D842" s="2"/>
+      <c r="C842" s="1"/>
+      <c r="D842" s="1"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="C843" s="2"/>
-      <c r="D843" s="2"/>
+      <c r="C843" s="1"/>
+      <c r="D843" s="1"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="C844" s="2"/>
-      <c r="D844" s="2"/>
+      <c r="C844" s="1"/>
+      <c r="D844" s="1"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="C845" s="2"/>
-      <c r="D845" s="2"/>
+      <c r="C845" s="1"/>
+      <c r="D845" s="1"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="C846" s="2"/>
-      <c r="D846" s="2"/>
+      <c r="C846" s="1"/>
+      <c r="D846" s="1"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="C847" s="2"/>
-      <c r="D847" s="2"/>
+      <c r="C847" s="1"/>
+      <c r="D847" s="1"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="C848" s="2"/>
-      <c r="D848" s="2"/>
+      <c r="C848" s="1"/>
+      <c r="D848" s="1"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="C849" s="2"/>
-      <c r="D849" s="2"/>
+      <c r="C849" s="1"/>
+      <c r="D849" s="1"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="C850" s="2"/>
-      <c r="D850" s="2"/>
+      <c r="C850" s="1"/>
+      <c r="D850" s="1"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="C851" s="2"/>
-      <c r="D851" s="2"/>
+      <c r="C851" s="1"/>
+      <c r="D851" s="1"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="C852" s="2"/>
-      <c r="D852" s="2"/>
+      <c r="C852" s="1"/>
+      <c r="D852" s="1"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="C853" s="2"/>
-      <c r="D853" s="2"/>
+      <c r="C853" s="1"/>
+      <c r="D853" s="1"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="C854" s="2"/>
-      <c r="D854" s="2"/>
+      <c r="C854" s="1"/>
+      <c r="D854" s="1"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="C855" s="2"/>
-      <c r="D855" s="2"/>
+      <c r="C855" s="1"/>
+      <c r="D855" s="1"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="C856" s="2"/>
-      <c r="D856" s="2"/>
+      <c r="C856" s="1"/>
+      <c r="D856" s="1"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="C857" s="2"/>
-      <c r="D857" s="2"/>
+      <c r="C857" s="1"/>
+      <c r="D857" s="1"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="C858" s="2"/>
-      <c r="D858" s="2"/>
+      <c r="C858" s="1"/>
+      <c r="D858" s="1"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="C859" s="2"/>
-      <c r="D859" s="2"/>
+      <c r="C859" s="1"/>
+      <c r="D859" s="1"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="C860" s="2"/>
-      <c r="D860" s="2"/>
+      <c r="C860" s="1"/>
+      <c r="D860" s="1"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="C861" s="2"/>
-      <c r="D861" s="2"/>
+      <c r="C861" s="1"/>
+      <c r="D861" s="1"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="C862" s="2"/>
-      <c r="D862" s="2"/>
+      <c r="C862" s="1"/>
+      <c r="D862" s="1"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="C863" s="2"/>
-      <c r="D863" s="2"/>
+      <c r="C863" s="1"/>
+      <c r="D863" s="1"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="C864" s="2"/>
-      <c r="D864" s="2"/>
+      <c r="C864" s="1"/>
+      <c r="D864" s="1"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="C865" s="2"/>
-      <c r="D865" s="2"/>
+      <c r="C865" s="1"/>
+      <c r="D865" s="1"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="C866" s="2"/>
-      <c r="D866" s="2"/>
+      <c r="C866" s="1"/>
+      <c r="D866" s="1"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="C867" s="2"/>
-      <c r="D867" s="2"/>
+      <c r="C867" s="1"/>
+      <c r="D867" s="1"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="C868" s="2"/>
-      <c r="D868" s="2"/>
+      <c r="C868" s="1"/>
+      <c r="D868" s="1"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="C869" s="2"/>
-      <c r="D869" s="2"/>
+      <c r="C869" s="1"/>
+      <c r="D869" s="1"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="C870" s="2"/>
-      <c r="D870" s="2"/>
+      <c r="C870" s="1"/>
+      <c r="D870" s="1"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="C871" s="2"/>
-      <c r="D871" s="2"/>
+      <c r="C871" s="1"/>
+      <c r="D871" s="1"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="C872" s="2"/>
-      <c r="D872" s="2"/>
+      <c r="C872" s="1"/>
+      <c r="D872" s="1"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="C873" s="2"/>
-      <c r="D873" s="2"/>
+      <c r="C873" s="1"/>
+      <c r="D873" s="1"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="C874" s="2"/>
-      <c r="D874" s="2"/>
+      <c r="C874" s="1"/>
+      <c r="D874" s="1"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="C875" s="2"/>
-      <c r="D875" s="2"/>
+      <c r="C875" s="1"/>
+      <c r="D875" s="1"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="C876" s="2"/>
-      <c r="D876" s="2"/>
+      <c r="C876" s="1"/>
+      <c r="D876" s="1"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="C877" s="2"/>
-      <c r="D877" s="2"/>
+      <c r="C877" s="1"/>
+      <c r="D877" s="1"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="C878" s="2"/>
-      <c r="D878" s="2"/>
+      <c r="C878" s="1"/>
+      <c r="D878" s="1"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="C879" s="2"/>
-      <c r="D879" s="2"/>
+      <c r="C879" s="1"/>
+      <c r="D879" s="1"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="C880" s="2"/>
-      <c r="D880" s="2"/>
+      <c r="C880" s="1"/>
+      <c r="D880" s="1"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="C881" s="2"/>
-      <c r="D881" s="2"/>
+      <c r="C881" s="1"/>
+      <c r="D881" s="1"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="C882" s="2"/>
-      <c r="D882" s="2"/>
+      <c r="C882" s="1"/>
+      <c r="D882" s="1"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="C883" s="2"/>
-      <c r="D883" s="2"/>
+      <c r="C883" s="1"/>
+      <c r="D883" s="1"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="C884" s="2"/>
-      <c r="D884" s="2"/>
+      <c r="C884" s="1"/>
+      <c r="D884" s="1"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="C885" s="2"/>
-      <c r="D885" s="2"/>
+      <c r="C885" s="1"/>
+      <c r="D885" s="1"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="C886" s="2"/>
-      <c r="D886" s="2"/>
+      <c r="C886" s="1"/>
+      <c r="D886" s="1"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="C887" s="2"/>
-      <c r="D887" s="2"/>
+      <c r="C887" s="1"/>
+      <c r="D887" s="1"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="C888" s="2"/>
-      <c r="D888" s="2"/>
+      <c r="C888" s="1"/>
+      <c r="D888" s="1"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="C889" s="2"/>
-      <c r="D889" s="2"/>
+      <c r="C889" s="1"/>
+      <c r="D889" s="1"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="C890" s="2"/>
-      <c r="D890" s="2"/>
+      <c r="C890" s="1"/>
+      <c r="D890" s="1"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="C891" s="2"/>
-      <c r="D891" s="2"/>
+      <c r="C891" s="1"/>
+      <c r="D891" s="1"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="C892" s="2"/>
-      <c r="D892" s="2"/>
+      <c r="C892" s="1"/>
+      <c r="D892" s="1"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="C893" s="2"/>
-      <c r="D893" s="2"/>
+      <c r="C893" s="1"/>
+      <c r="D893" s="1"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="C894" s="2"/>
-      <c r="D894" s="2"/>
+      <c r="C894" s="1"/>
+      <c r="D894" s="1"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="C895" s="2"/>
-      <c r="D895" s="2"/>
+      <c r="C895" s="1"/>
+      <c r="D895" s="1"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="C896" s="2"/>
-      <c r="D896" s="2"/>
+      <c r="C896" s="1"/>
+      <c r="D896" s="1"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="C897" s="2"/>
-      <c r="D897" s="2"/>
+      <c r="C897" s="1"/>
+      <c r="D897" s="1"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="C898" s="2"/>
-      <c r="D898" s="2"/>
+      <c r="C898" s="1"/>
+      <c r="D898" s="1"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="C899" s="2"/>
-      <c r="D899" s="2"/>
+      <c r="C899" s="1"/>
+      <c r="D899" s="1"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="C900" s="2"/>
-      <c r="D900" s="2"/>
+      <c r="C900" s="1"/>
+      <c r="D900" s="1"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="C901" s="2"/>
-      <c r="D901" s="2"/>
+      <c r="C901" s="1"/>
+      <c r="D901" s="1"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="C902" s="2"/>
-      <c r="D902" s="2"/>
+      <c r="C902" s="1"/>
+      <c r="D902" s="1"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="C903" s="2"/>
-      <c r="D903" s="2"/>
+      <c r="C903" s="1"/>
+      <c r="D903" s="1"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="C904" s="2"/>
-      <c r="D904" s="2"/>
+      <c r="C904" s="1"/>
+      <c r="D904" s="1"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="C905" s="2"/>
-      <c r="D905" s="2"/>
+      <c r="C905" s="1"/>
+      <c r="D905" s="1"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="C906" s="2"/>
-      <c r="D906" s="2"/>
+      <c r="C906" s="1"/>
+      <c r="D906" s="1"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="C907" s="2"/>
-      <c r="D907" s="2"/>
+      <c r="C907" s="1"/>
+      <c r="D907" s="1"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="C908" s="2"/>
-      <c r="D908" s="2"/>
+      <c r="C908" s="1"/>
+      <c r="D908" s="1"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="C909" s="2"/>
-      <c r="D909" s="2"/>
+      <c r="C909" s="1"/>
+      <c r="D909" s="1"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="C910" s="2"/>
-      <c r="D910" s="2"/>
+      <c r="C910" s="1"/>
+      <c r="D910" s="1"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="C911" s="2"/>
-      <c r="D911" s="2"/>
+      <c r="C911" s="1"/>
+      <c r="D911" s="1"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="C912" s="2"/>
-      <c r="D912" s="2"/>
+      <c r="C912" s="1"/>
+      <c r="D912" s="1"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="C913" s="2"/>
-      <c r="D913" s="2"/>
+      <c r="C913" s="1"/>
+      <c r="D913" s="1"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="C914" s="2"/>
-      <c r="D914" s="2"/>
+      <c r="C914" s="1"/>
+      <c r="D914" s="1"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="C915" s="2"/>
-      <c r="D915" s="2"/>
+      <c r="C915" s="1"/>
+      <c r="D915" s="1"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="C916" s="2"/>
-      <c r="D916" s="2"/>
+      <c r="C916" s="1"/>
+      <c r="D916" s="1"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="C917" s="2"/>
-      <c r="D917" s="2"/>
+      <c r="C917" s="1"/>
+      <c r="D917" s="1"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="C918" s="2"/>
-      <c r="D918" s="2"/>
+      <c r="C918" s="1"/>
+      <c r="D918" s="1"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="C919" s="2"/>
-      <c r="D919" s="2"/>
+      <c r="C919" s="1"/>
+      <c r="D919" s="1"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="C920" s="2"/>
-      <c r="D920" s="2"/>
+      <c r="C920" s="1"/>
+      <c r="D920" s="1"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="C921" s="2"/>
-      <c r="D921" s="2"/>
+      <c r="C921" s="1"/>
+      <c r="D921" s="1"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="C922" s="2"/>
-      <c r="D922" s="2"/>
+      <c r="C922" s="1"/>
+      <c r="D922" s="1"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="C923" s="2"/>
-      <c r="D923" s="2"/>
+      <c r="C923" s="1"/>
+      <c r="D923" s="1"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="C924" s="2"/>
-      <c r="D924" s="2"/>
+      <c r="C924" s="1"/>
+      <c r="D924" s="1"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="C925" s="2"/>
-      <c r="D925" s="2"/>
+      <c r="C925" s="1"/>
+      <c r="D925" s="1"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="C926" s="2"/>
-      <c r="D926" s="2"/>
+      <c r="C926" s="1"/>
+      <c r="D926" s="1"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="C927" s="2"/>
-      <c r="D927" s="2"/>
+      <c r="C927" s="1"/>
+      <c r="D927" s="1"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="C928" s="2"/>
-      <c r="D928" s="2"/>
+      <c r="C928" s="1"/>
+      <c r="D928" s="1"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="C929" s="2"/>
-      <c r="D929" s="2"/>
+      <c r="C929" s="1"/>
+      <c r="D929" s="1"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="C930" s="2"/>
-      <c r="D930" s="2"/>
+      <c r="C930" s="1"/>
+      <c r="D930" s="1"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="C931" s="2"/>
-      <c r="D931" s="2"/>
+      <c r="C931" s="1"/>
+      <c r="D931" s="1"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="C932" s="2"/>
-      <c r="D932" s="2"/>
+      <c r="C932" s="1"/>
+      <c r="D932" s="1"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="C933" s="2"/>
-      <c r="D933" s="2"/>
+      <c r="C933" s="1"/>
+      <c r="D933" s="1"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="C934" s="2"/>
-      <c r="D934" s="2"/>
+      <c r="C934" s="1"/>
+      <c r="D934" s="1"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="C935" s="2"/>
-      <c r="D935" s="2"/>
+      <c r="C935" s="1"/>
+      <c r="D935" s="1"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="C936" s="2"/>
-      <c r="D936" s="2"/>
+      <c r="C936" s="1"/>
+      <c r="D936" s="1"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="C937" s="2"/>
-      <c r="D937" s="2"/>
+      <c r="C937" s="1"/>
+      <c r="D937" s="1"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="C938" s="2"/>
-      <c r="D938" s="2"/>
+      <c r="C938" s="1"/>
+      <c r="D938" s="1"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="C939" s="2"/>
-      <c r="D939" s="2"/>
+      <c r="C939" s="1"/>
+      <c r="D939" s="1"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="C940" s="2"/>
-      <c r="D940" s="2"/>
+      <c r="C940" s="1"/>
+      <c r="D940" s="1"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="C941" s="2"/>
-      <c r="D941" s="2"/>
+      <c r="C941" s="1"/>
+      <c r="D941" s="1"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="C942" s="2"/>
-      <c r="D942" s="2"/>
+      <c r="C942" s="1"/>
+      <c r="D942" s="1"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="C943" s="2"/>
-      <c r="D943" s="2"/>
+      <c r="C943" s="1"/>
+      <c r="D943" s="1"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="C944" s="2"/>
-      <c r="D944" s="2"/>
+      <c r="C944" s="1"/>
+      <c r="D944" s="1"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="C945" s="2"/>
-      <c r="D945" s="2"/>
+      <c r="C945" s="1"/>
+      <c r="D945" s="1"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="C946" s="2"/>
-      <c r="D946" s="2"/>
+      <c r="C946" s="1"/>
+      <c r="D946" s="1"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="C947" s="2"/>
-      <c r="D947" s="2"/>
+      <c r="C947" s="1"/>
+      <c r="D947" s="1"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="C948" s="2"/>
-      <c r="D948" s="2"/>
+      <c r="C948" s="1"/>
+      <c r="D948" s="1"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="C949" s="2"/>
-      <c r="D949" s="2"/>
+      <c r="C949" s="1"/>
+      <c r="D949" s="1"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="C950" s="2"/>
-      <c r="D950" s="2"/>
+      <c r="C950" s="1"/>
+      <c r="D950" s="1"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="C951" s="2"/>
-      <c r="D951" s="2"/>
+      <c r="C951" s="1"/>
+      <c r="D951" s="1"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
+      <c r="C952" s="1"/>
+      <c r="D952" s="1"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
+      <c r="C953" s="1"/>
+      <c r="D953" s="1"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
+      <c r="C954" s="1"/>
+      <c r="D954" s="1"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
+      <c r="C955" s="1"/>
+      <c r="D955" s="1"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
+      <c r="C956" s="1"/>
+      <c r="D956" s="1"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
+      <c r="C957" s="1"/>
+      <c r="D957" s="1"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
+      <c r="C958" s="1"/>
+      <c r="D958" s="1"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
+      <c r="C959" s="1"/>
+      <c r="D959" s="1"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
+      <c r="C960" s="1"/>
+      <c r="D960" s="1"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
+      <c r="C961" s="1"/>
+      <c r="D961" s="1"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
+      <c r="C962" s="1"/>
+      <c r="D962" s="1"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
+      <c r="C963" s="1"/>
+      <c r="D963" s="1"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
+      <c r="C964" s="1"/>
+      <c r="D964" s="1"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
+      <c r="C965" s="1"/>
+      <c r="D965" s="1"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
+      <c r="C966" s="1"/>
+      <c r="D966" s="1"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
+      <c r="C967" s="1"/>
+      <c r="D967" s="1"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
+      <c r="C968" s="1"/>
+      <c r="D968" s="1"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
+      <c r="C969" s="1"/>
+      <c r="D969" s="1"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
+      <c r="C970" s="1"/>
+      <c r="D970" s="1"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
+      <c r="C971" s="1"/>
+      <c r="D971" s="1"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
+      <c r="C972" s="1"/>
+      <c r="D972" s="1"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
+      <c r="C973" s="1"/>
+      <c r="D973" s="1"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
+      <c r="C974" s="1"/>
+      <c r="D974" s="1"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
+      <c r="C975" s="1"/>
+      <c r="D975" s="1"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
+      <c r="C976" s="1"/>
+      <c r="D976" s="1"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
+      <c r="C977" s="1"/>
+      <c r="D977" s="1"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
+      <c r="C978" s="1"/>
+      <c r="D978" s="1"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
+      <c r="C979" s="1"/>
+      <c r="D979" s="1"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
+      <c r="C980" s="1"/>
+      <c r="D980" s="1"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
+      <c r="C981" s="1"/>
+      <c r="D981" s="1"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
+      <c r="C982" s="1"/>
+      <c r="D982" s="1"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
+      <c r="C983" s="1"/>
+      <c r="D983" s="1"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
+      <c r="C984" s="1"/>
+      <c r="D984" s="1"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
+      <c r="C985" s="1"/>
+      <c r="D985" s="1"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
+      <c r="C986" s="1"/>
+      <c r="D986" s="1"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
+      <c r="C987" s="1"/>
+      <c r="D987" s="1"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
+      <c r="C988" s="1"/>
+      <c r="D988" s="1"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
+      <c r="C989" s="1"/>
+      <c r="D989" s="1"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
+      <c r="C990" s="1"/>
+      <c r="D990" s="1"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
+      <c r="C991" s="1"/>
+      <c r="D991" s="1"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
+      <c r="C992" s="1"/>
+      <c r="D992" s="1"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
+      <c r="C993" s="1"/>
+      <c r="D993" s="1"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
+      <c r="C994" s="1"/>
+      <c r="D994" s="1"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
+      <c r="C995" s="1"/>
+      <c r="D995" s="1"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
+      <c r="C996" s="1"/>
+      <c r="D996" s="1"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
+      <c r="C997" s="1"/>
+      <c r="D997" s="1"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
+      <c r="C998" s="1"/>
+      <c r="D998" s="1"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
+      <c r="C999" s="1"/>
+      <c r="D999" s="1"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
+      <c r="C1000" s="1"/>
+      <c r="D1000" s="1"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="C1001" s="2"/>
-      <c r="D1001" s="2"/>
+      <c r="C1001" s="1"/>
+      <c r="D1001" s="1"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
-      <c r="C1002" s="2"/>
-      <c r="D1002" s="2"/>
+      <c r="C1002" s="1"/>
+      <c r="D1002" s="1"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
-      <c r="C1003" s="2"/>
-      <c r="D1003" s="2"/>
+      <c r="C1003" s="1"/>
+      <c r="D1003" s="1"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
-      <c r="C1004" s="2"/>
-      <c r="D1004" s="2"/>
+      <c r="C1004" s="1"/>
+      <c r="D1004" s="1"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
-      <c r="C1005" s="2"/>
-      <c r="D1005" s="2"/>
+      <c r="C1005" s="1"/>
+      <c r="D1005" s="1"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
-      <c r="C1006" s="2"/>
-      <c r="D1006" s="2"/>
+      <c r="C1006" s="1"/>
+      <c r="D1006" s="1"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
-      <c r="C1007" s="2"/>
-      <c r="D1007" s="2"/>
+      <c r="C1007" s="1"/>
+      <c r="D1007" s="1"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
-      <c r="C1008" s="2"/>
-      <c r="D1008" s="2"/>
+      <c r="C1008" s="1"/>
+      <c r="D1008" s="1"/>
+    </row>
+    <row r="1009" ht="12.75" customHeight="1">
+      <c r="C1009" s="1"/>
+      <c r="D1009" s="1"/>
+    </row>
+    <row r="1010" ht="12.75" customHeight="1">
+      <c r="C1010" s="1"/>
+      <c r="D1010" s="1"/>
+    </row>
+    <row r="1011" ht="12.75" customHeight="1">
+      <c r="C1011" s="1"/>
+      <c r="D1011" s="1"/>
+    </row>
+    <row r="1012" ht="12.75" customHeight="1">
+      <c r="C1012" s="1"/>
+      <c r="D1012" s="1"/>
+    </row>
+    <row r="1013" ht="12.75" customHeight="1">
+      <c r="C1013" s="1"/>
+      <c r="D1013" s="1"/>
+    </row>
+    <row r="1014" ht="12.75" customHeight="1">
+      <c r="C1014" s="1"/>
+      <c r="D1014" s="1"/>
+    </row>
+    <row r="1015" ht="12.75" customHeight="1">
+      <c r="C1015" s="1"/>
+      <c r="D1015" s="1"/>
+    </row>
+    <row r="1016" ht="12.75" customHeight="1">
+      <c r="C1016" s="1"/>
+      <c r="D1016" s="1"/>
+    </row>
+    <row r="1017" ht="12.75" customHeight="1">
+      <c r="C1017" s="1"/>
+      <c r="D1017" s="1"/>
+    </row>
+    <row r="1018" ht="12.75" customHeight="1">
+      <c r="C1018" s="1"/>
+      <c r="D1018" s="1"/>
+    </row>
+    <row r="1019" ht="12.75" customHeight="1">
+      <c r="C1019" s="1"/>
+      <c r="D1019" s="1"/>
+    </row>
+    <row r="1020" ht="12.75" customHeight="1">
+      <c r="C1020" s="1"/>
+      <c r="D1020" s="1"/>
+    </row>
+    <row r="1021" ht="12.75" customHeight="1">
+      <c r="C1021" s="1"/>
+      <c r="D1021" s="1"/>
+    </row>
+    <row r="1022" ht="12.75" customHeight="1">
+      <c r="C1022" s="1"/>
+      <c r="D1022" s="1"/>
+    </row>
+    <row r="1023" ht="12.75" customHeight="1">
+      <c r="C1023" s="1"/>
+      <c r="D1023" s="1"/>
+    </row>
+    <row r="1024" ht="12.75" customHeight="1">
+      <c r="C1024" s="1"/>
+      <c r="D1024" s="1"/>
+    </row>
+    <row r="1025" ht="12.75" customHeight="1">
+      <c r="C1025" s="1"/>
+      <c r="D1025" s="1"/>
+    </row>
+    <row r="1026" ht="12.75" customHeight="1">
+      <c r="C1026" s="1"/>
+      <c r="D1026" s="1"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5395,7 +5807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
@@ -5406,185 +5818,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
+      <c r="A2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
+      <c r="A4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>42</v>
+      <c r="A7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>60</v>
+      <c r="A8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
+      <c r="A9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -6583,7 +6995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
@@ -6594,34 +7006,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5">
         <v>43584.0</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="233">
   <si>
     <t>type</t>
   </si>
@@ -78,12 +78,12 @@
     <t>./source = 'user'</t>
   </si>
   <si>
+    <t>form_title</t>
+  </si>
+  <si>
     <t>list_name</t>
   </si>
   <si>
-    <t>form_title</t>
-  </si>
-  <si>
     <t>hidden</t>
   </si>
   <si>
@@ -108,145 +108,181 @@
     <t>refer_child_danger_sign_flag</t>
   </si>
   <si>
+    <t>form_id</t>
+  </si>
+  <si>
     <t>refer_muac_flag</t>
   </si>
   <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
     <t>refer_palm_pallor_flag</t>
   </si>
   <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>refer_vaccines_flag</t>
   </si>
   <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
   </si>
   <si>
     <t>refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>yes_no</t>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>Sina pesa</t>
   </si>
   <si>
     <t>due_date</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
-    <t>Sina pesa</t>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
+    <t>Sikutaka kwenda</t>
+  </si>
+  <si>
+    <t>no_permission</t>
+  </si>
+  <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
+    <t>reason_didnt_get_svc</t>
+  </si>
+  <si>
+    <t>data</t>
   </si>
   <si>
     <t>due_date_human_readable</t>
   </si>
   <si>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
+    <t>services_not_offered</t>
+  </si>
+  <si>
     <t>contact_id</t>
   </si>
   <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
     <t>Contact ID of the logged in user</t>
   </si>
   <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>did_not_want</t>
+    <t>Huduma nilizotaka hazikuwepo.</t>
   </si>
   <si>
     <t>facility_id</t>
   </si>
   <si>
-    <t>I did not want to go</t>
-  </si>
-  <si>
-    <t>Sikutaka kwenda</t>
-  </si>
-  <si>
     <t>Facility ID for the parent user</t>
   </si>
   <si>
-    <t>no_permission</t>
-  </si>
-  <si>
-    <t>I did not have permission to go</t>
-  </si>
-  <si>
-    <t>Sikupewa ruhusa ya kwenda</t>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
   </si>
   <si>
     <t>Name of the logged in user</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
     <t>end group</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Nyenginezo</t>
-  </si>
-  <si>
-    <t>reason_didnt_get_svc</t>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
+    <t>Walitaka nilipie huduma</t>
   </si>
   <si>
     <t>contact</t>
   </si>
   <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
     <t>db:person</t>
@@ -255,51 +291,15 @@
     <t>_id</t>
   </si>
   <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
     <t>db-object</t>
   </si>
   <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
     <t>sex</t>
   </si>
   <si>
     <t>date_of_birth</t>
   </si>
   <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
@@ -381,19 +381,25 @@
     <t>age_days</t>
   </si>
   <si>
-    <t>decimal-date-time(today())-decimal-date-time(${client_date_of_birth})</t>
+    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
   </si>
   <si>
     <t>age_months</t>
   </si>
   <si>
-    <t>round(${age_days} div 30,0)</t>
+    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
   </si>
   <si>
     <t>age_years</t>
   </si>
   <si>
-    <t>round(${age_months} div 12,0)</t>
+    <t>int(${age_days} div (30 *12),0)</t>
+  </si>
+  <si>
+    <t>age_days_display</t>
+  </si>
+  <si>
+    <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
   </si>
   <si>
     <t>household_head</t>
@@ -448,14 +454,14 @@
   </si>
   <si>
     <t>Name: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
-Age: &lt;span style="font-weight:bold"&gt;${age_years} years, ${age_months} months&lt;/span&gt;
+Age: &lt;span style="font-weight:bold"&gt;${age_years} years, ${age_months} months, ${age_days_display} days&lt;/span&gt;
 Contact person: &lt;span style="font-weight:bold"&gt;${household_head}&lt;/span&gt; 
 House number: &lt;span style="font-weight:bold"&gt;${house_number}&lt;/span&gt;
 Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
     <t>Jina: &lt;span style="font-weight:bold"&gt;${client_name}&lt;/span&gt;
-Umri: &lt;span style="font-weight:bold"&gt;${age_years} miaka, ${age_months} miezi&lt;/span&gt;
+Umri: &lt;span style="font-weight:bold"&gt;${age_years} miaka, ${age_months} miezi, ${age_days_display} siku&lt;/span&gt;
 Mtu wa karibu kwa mawasiliano: &lt;span style="font-weight:bold"&gt;${household_head}&lt;/span&gt; 
 Namba ya nyumba: &lt;span style="font-weight:bold"&gt;${house_number}&lt;/span&gt;
 Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
@@ -767,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -776,12 +782,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -790,8 +796,14 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -980,7 +992,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
@@ -992,7 +1004,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
@@ -1004,7 +1016,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>
@@ -1016,7 +1028,7 @@
         <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>19</v>
@@ -1027,8 +1039,8 @@
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>41</v>
+      <c r="B13" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -1039,8 +1051,8 @@
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>54</v>
+      <c r="B14" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>19</v>
@@ -1052,7 +1064,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>19</v>
@@ -1064,10 +1076,10 @@
         <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -1076,10 +1088,10 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -1091,16 +1103,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -1110,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>19</v>
@@ -1119,17 +1131,17 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1149,7 +1161,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>19</v>
@@ -1161,7 +1173,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>19</v>
@@ -1170,17 +1182,17 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>18</v>
@@ -1297,7 +1309,7 @@
         <v>95</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -1310,7 +1322,7 @@
         <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -1323,7 +1335,7 @@
         <v>95</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -1336,7 +1348,7 @@
         <v>95</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -1371,672 +1383,681 @@
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9"/>
-      <c r="L41" s="4" t="s">
+      <c r="L41" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>41</v>
+      <c r="B42" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9"/>
-      <c r="L42" s="4" t="s">
+      <c r="L42" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="6" t="s">
         <v>119</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
-      <c r="L43" s="4" t="s">
+      <c r="L43" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9"/>
-      <c r="L44" s="4" t="s">
+      <c r="L44" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="6" t="s">
         <v>123</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9"/>
-      <c r="L46" s="10" t="s">
+      <c r="L46" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="12" t="s">
         <v>127</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9"/>
-      <c r="L47" s="12" t="s">
+      <c r="L47" s="11" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="13" t="s">
         <v>129</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9"/>
-      <c r="L48" s="12" t="s">
+      <c r="L48" s="14" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="13" t="s">
         <v>131</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
-      <c r="L49" s="12" t="s">
+      <c r="L49" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
-      <c r="L50" s="12" t="s">
+      <c r="L50" s="14" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9"/>
+      <c r="L51" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D51" s="9" t="s">
+      <c r="B52" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="C52" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="4" t="s">
+      <c r="D52" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C52" s="4" t="s">
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="B53" s="6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" s="4" t="s">
+      <c r="C53" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D53" s="4" t="s">
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D54" s="4" t="s">
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D55" s="4" t="s">
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="7"/>
+      <c r="C56" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>138</v>
-      </c>
+      <c r="A57" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="D58" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>156</v>
+      <c r="G58" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="F59" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="F60" t="s">
         <v>162</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F60" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="F61" t="s">
         <v>166</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F61" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="F62" t="s">
         <v>170</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="F62" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="F63" t="s">
         <v>174</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F63" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="F64" t="s">
         <v>178</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F64" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="F65" t="s">
         <v>182</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F65" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="F66" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="7" t="s">
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="B67" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="7" t="s">
+      <c r="C67" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C67" s="7" t="s">
+      <c r="B68" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="7" t="s">
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F68" s="1"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="D69" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="7" t="s">
+      <c r="C70" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="D70" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="E70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="B71" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" s="7" t="s">
+      <c r="C71" s="7" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B71" s="7" t="s">
+      <c r="D71" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="E71" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="D71" s="7" t="s">
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="C72" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="A73" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="F73" s="1"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="D75" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>212</v>
+      <c r="E75" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
+        <v>212</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="A77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="7" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B78" s="1" t="s">
+      <c r="A78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C78" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B79" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="D79" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="C80" s="7" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B80" s="7" t="s">
+      <c r="D80" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="L80" s="7" t="s">
+      <c r="F80" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="L81" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D81" s="7" t="s">
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E81" s="7"/>
-      <c r="F81" t="s">
+      <c r="C82" s="7" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
+      <c r="D82" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E82" s="7"/>
+      <c r="F82" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>45</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>215</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
     </row>
-    <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" t="s">
-        <v>95</v>
-      </c>
-      <c r="B84" t="s">
-        <v>228</v>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
-      <c r="L84" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
         <v>230</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
-      <c r="L85">
-        <v>3.0</v>
+      <c r="L85" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
+      <c r="L86">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="C87" s="1"/>
@@ -5797,6 +5818,10 @@
     <row r="1026" ht="12.75" customHeight="1">
       <c r="C1026" s="1"/>
       <c r="D1026" s="1"/>
+    </row>
+    <row r="1027" ht="12.75" customHeight="1">
+      <c r="C1027" s="1"/>
+      <c r="D1027" s="1"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5819,7 +5844,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -5833,170 +5858,170 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" t="s">
         <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="4" t="s">
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>71</v>
+      <c r="A13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7007,19 +7032,19 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>39</v>
@@ -7027,19 +7052,19 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>68</v>
+      <c r="D2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -15,6 +15,33 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="233">
   <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -27,6 +54,102 @@
     <t>label::sw</t>
   </si>
   <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>Sina pesa</t>
+  </si>
+  <si>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
+    <t>Sikutaka kwenda</t>
+  </si>
+  <si>
+    <t>no_permission</t>
+  </si>
+  <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
+    <t>reason_didnt_get_svc</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
+  </si>
+  <si>
+    <t>services_not_offered</t>
+  </si>
+  <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
+    <t>Huduma nilizotaka hazikuwepo.</t>
+  </si>
+  <si>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -39,9 +162,18 @@
     <t>read_only</t>
   </si>
   <si>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
     <t>constraint</t>
   </si>
   <si>
+    <t>Walitaka nilipie huduma</t>
+  </si>
+  <si>
     <t>constraint_message::en</t>
   </si>
   <si>
@@ -54,12 +186,21 @@
     <t>choice_filter</t>
   </si>
   <si>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
     <t>hint::en</t>
   </si>
   <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
     <t>hint::sw</t>
   </si>
   <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
+  </si>
+  <si>
     <t>default</t>
   </si>
   <si>
@@ -78,12 +219,6 @@
     <t>./source = 'user'</t>
   </si>
   <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
     <t>hidden</t>
   </si>
   <si>
@@ -108,181 +243,46 @@
     <t>refer_child_danger_sign_flag</t>
   </si>
   <si>
-    <t>form_id</t>
-  </si>
-  <si>
     <t>refer_muac_flag</t>
   </si>
   <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
     <t>refer_palm_pallor_flag</t>
   </si>
   <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>refer_vaccines_flag</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
     <t>refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
-    <t>Sina pesa</t>
-  </si>
-  <si>
     <t>due_date</t>
   </si>
   <si>
-    <t>did_not_want</t>
-  </si>
-  <si>
-    <t>I did not want to go</t>
-  </si>
-  <si>
-    <t>Sikutaka kwenda</t>
-  </si>
-  <si>
-    <t>no_permission</t>
-  </si>
-  <si>
-    <t>I did not have permission to go</t>
-  </si>
-  <si>
-    <t>Sikupewa ruhusa ya kwenda</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Nyenginezo</t>
-  </si>
-  <si>
-    <t>reason_didnt_get_svc</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>due_date_human_readable</t>
   </si>
   <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
     <t>contact_id</t>
   </si>
   <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
     <t>Contact ID of the logged in user</t>
   </si>
   <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
     <t>facility_id</t>
   </si>
   <si>
     <t>Facility ID for the parent user</t>
   </si>
   <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
     <t>Name of the logged in user</t>
   </si>
   <si>
     <t>end group</t>
   </si>
   <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
     <t>contact</t>
-  </si>
-  <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
     <t>db:person</t>
@@ -733,17 +733,17 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Roboto"/>
-    </font>
     <font>
       <sz val="10.0"/>
       <name val="Arial"/>
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font/>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -778,28 +778,28 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -808,7 +808,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -843,412 +843,412 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
+      <c r="E1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>23</v>
+      <c r="A2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="F2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1"/>
+      <c r="A5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1"/>
+      <c r="A6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1"/>
+      <c r="A7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="1"/>
+      <c r="A8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1"/>
+      <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1"/>
+      <c r="A10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1"/>
+      <c r="A11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1"/>
+      <c r="A12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1"/>
+      <c r="A13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1"/>
+      <c r="A15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="1"/>
+      <c r="A16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="1"/>
+      <c r="A17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="1"/>
+      <c r="A18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="5"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1"/>
+      <c r="A20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="5"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="G21" s="1" t="s">
+      <c r="C21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="G21" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1"/>
+      <c r="A22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="5"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1"/>
+      <c r="C23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="5"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1"/>
+      <c r="C24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="5"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="A25" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="L27" s="1" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="L27" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="L28" s="1" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="L28" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="L29" s="1" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="L29" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="L30" s="1" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="L30" s="5" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1259,173 +1259,173 @@
       <c r="B31" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
       <c r="L31" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
       <c r="L32" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="B33" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
       <c r="L33" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="B34" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
       <c r="L34" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="B35" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
       <c r="L35" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
       <c r="L36" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="B37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
       <c r="L37" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="B38" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
       <c r="L38" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="L39" s="1" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="L39" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="L40" s="1" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="L40" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="9"/>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>53</v>
+      <c r="B42" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="9"/>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>121</v>
       </c>
       <c r="C44" s="8"/>
@@ -1435,10 +1435,10 @@
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C45" s="8"/>
@@ -1448,10 +1448,10 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>125</v>
       </c>
       <c r="C46" s="8"/>
@@ -1461,7 +1461,7 @@
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B47" s="12" t="s">
@@ -1474,7 +1474,7 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -1487,7 +1487,7 @@
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="13" t="s">
@@ -1500,7 +1500,7 @@
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B50" s="13" t="s">
@@ -1513,7 +1513,7 @@
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B51" s="13" t="s">
@@ -1526,10 +1526,10 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="A52" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C52" s="8" t="s">
@@ -1538,98 +1538,98 @@
       <c r="D52" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="A57" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C57" s="1"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" s="1" t="s">
+      <c r="A58" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>154</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="5" t="s">
         <v>156</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -1640,13 +1640,13 @@
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="5" t="s">
         <v>160</v>
       </c>
       <c r="D60" s="7" t="s">
@@ -1657,13 +1657,13 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="5" t="s">
         <v>164</v>
       </c>
       <c r="D61" s="7" t="s">
@@ -1674,10 +1674,10 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="5" t="s">
         <v>167</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -1691,10 +1691,10 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="5" t="s">
         <v>171</v>
       </c>
       <c r="C63" s="7" t="s">
@@ -1708,10 +1708,10 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="5" t="s">
         <v>175</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -1725,10 +1725,10 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="5" t="s">
         <v>179</v>
       </c>
       <c r="C65" s="7" t="s">
@@ -1742,10 +1742,10 @@
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="5" t="s">
         <v>183</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -1759,10 +1759,10 @@
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="5" t="s">
         <v>188</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -1771,31 +1771,31 @@
       <c r="D67" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>36</v>
+      <c r="E67" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="7" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>191</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="5" t="s">
         <v>193</v>
       </c>
       <c r="C69" s="7" t="s">
@@ -1804,13 +1804,13 @@
       <c r="D69" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F69" s="1"/>
+      <c r="F69" s="5"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="5" t="s">
         <v>196</v>
       </c>
       <c r="C70" s="7" t="s">
@@ -1819,16 +1819,16 @@
       <c r="D70" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F70" s="1"/>
+      <c r="E70" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="5"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="5" t="s">
         <v>200</v>
       </c>
       <c r="C71" s="7" t="s">
@@ -1838,14 +1838,14 @@
         <v>202</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="5" t="s">
         <v>141</v>
       </c>
       <c r="B72" s="7" t="s">
@@ -1863,38 +1863,38 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="A74" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
+      <c r="C74" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>49</v>
+      <c r="B75" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>210</v>
@@ -1902,15 +1902,15 @@
       <c r="D75" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>36</v>
+      <c r="E75" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="5" t="s">
         <v>212</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -1921,37 +1921,37 @@
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="A77" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="7" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
       <c r="F78" s="7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="5" t="s">
         <v>217</v>
       </c>
       <c r="C79" s="7" t="s">
@@ -1960,12 +1960,12 @@
       <c r="D79" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>36</v>
+      <c r="E79" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="5" t="s">
         <v>141</v>
       </c>
       <c r="B80" s="7" t="s">
@@ -1974,10 +1974,10 @@
       <c r="C80" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="5" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2014,24 +2014,24 @@
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="1" t="s">
-        <v>82</v>
+      <c r="A83" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
+      <c r="A84" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" t="s">
@@ -2040,3788 +2040,3788 @@
       <c r="B85" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
       <c r="L85" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
       <c r="L86">
         <v>3.0</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="5"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="5"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="5"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="5"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="5"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="5"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="5"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="5"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="5"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="5"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="5"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="5"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="5"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="5"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="5"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="5"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="5"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="5"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="5"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="5"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="5"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="5"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="5"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="C204" s="5"/>
+      <c r="D204" s="5"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="5"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="5"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="C208" s="5"/>
+      <c r="D208" s="5"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="5"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="C210" s="5"/>
+      <c r="D210" s="5"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="5"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="C212" s="5"/>
+      <c r="D212" s="5"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="5"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="5"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="C216" s="5"/>
+      <c r="D216" s="5"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="C217" s="5"/>
+      <c r="D217" s="5"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="C220" s="5"/>
+      <c r="D220" s="5"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="C221" s="5"/>
+      <c r="D221" s="5"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="C222" s="5"/>
+      <c r="D222" s="5"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="C223" s="5"/>
+      <c r="D223" s="5"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="C224" s="5"/>
+      <c r="D224" s="5"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="C225" s="5"/>
+      <c r="D225" s="5"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="C226" s="5"/>
+      <c r="D226" s="5"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="C227" s="5"/>
+      <c r="D227" s="5"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="C228" s="5"/>
+      <c r="D228" s="5"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="C229" s="5"/>
+      <c r="D229" s="5"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="C230" s="5"/>
+      <c r="D230" s="5"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="C231" s="5"/>
+      <c r="D231" s="5"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="C232" s="5"/>
+      <c r="D232" s="5"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="C234" s="5"/>
+      <c r="D234" s="5"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="C235" s="5"/>
+      <c r="D235" s="5"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="C236" s="5"/>
+      <c r="D236" s="5"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="C237" s="5"/>
+      <c r="D237" s="5"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="C238" s="5"/>
+      <c r="D238" s="5"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="C239" s="5"/>
+      <c r="D239" s="5"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="C240" s="5"/>
+      <c r="D240" s="5"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
+      <c r="C241" s="5"/>
+      <c r="D241" s="5"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
+      <c r="C242" s="5"/>
+      <c r="D242" s="5"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="5"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
+      <c r="C244" s="5"/>
+      <c r="D244" s="5"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="5"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
+      <c r="C246" s="5"/>
+      <c r="D246" s="5"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
+      <c r="C247" s="5"/>
+      <c r="D247" s="5"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
+      <c r="C248" s="5"/>
+      <c r="D248" s="5"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="5"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
+      <c r="C250" s="5"/>
+      <c r="D250" s="5"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
+      <c r="C251" s="5"/>
+      <c r="D251" s="5"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
+      <c r="C252" s="5"/>
+      <c r="D252" s="5"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="5"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
+      <c r="C254" s="5"/>
+      <c r="D254" s="5"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="5"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
+      <c r="C256" s="5"/>
+      <c r="D256" s="5"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
+      <c r="C258" s="5"/>
+      <c r="D258" s="5"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
+      <c r="C259" s="5"/>
+      <c r="D259" s="5"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="C260" s="1"/>
-      <c r="D260" s="1"/>
+      <c r="C260" s="5"/>
+      <c r="D260" s="5"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="C261" s="1"/>
-      <c r="D261" s="1"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="5"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="C262" s="1"/>
-      <c r="D262" s="1"/>
+      <c r="C262" s="5"/>
+      <c r="D262" s="5"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="C263" s="1"/>
-      <c r="D263" s="1"/>
+      <c r="C263" s="5"/>
+      <c r="D263" s="5"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
+      <c r="C264" s="5"/>
+      <c r="D264" s="5"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="C265" s="1"/>
-      <c r="D265" s="1"/>
+      <c r="C265" s="5"/>
+      <c r="D265" s="5"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="C266" s="1"/>
-      <c r="D266" s="1"/>
+      <c r="C266" s="5"/>
+      <c r="D266" s="5"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="C267" s="1"/>
-      <c r="D267" s="1"/>
+      <c r="C267" s="5"/>
+      <c r="D267" s="5"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="C268" s="1"/>
-      <c r="D268" s="1"/>
+      <c r="C268" s="5"/>
+      <c r="D268" s="5"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="C269" s="1"/>
-      <c r="D269" s="1"/>
+      <c r="C269" s="5"/>
+      <c r="D269" s="5"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
+      <c r="C270" s="5"/>
+      <c r="D270" s="5"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
+      <c r="C271" s="5"/>
+      <c r="D271" s="5"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
+      <c r="C272" s="5"/>
+      <c r="D272" s="5"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
+      <c r="C273" s="5"/>
+      <c r="D273" s="5"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
+      <c r="C274" s="5"/>
+      <c r="D274" s="5"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
+      <c r="C275" s="5"/>
+      <c r="D275" s="5"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
+      <c r="C276" s="5"/>
+      <c r="D276" s="5"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
+      <c r="C277" s="5"/>
+      <c r="D277" s="5"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
+      <c r="C278" s="5"/>
+      <c r="D278" s="5"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
+      <c r="C279" s="5"/>
+      <c r="D279" s="5"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
+      <c r="C280" s="5"/>
+      <c r="D280" s="5"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+      <c r="C281" s="5"/>
+      <c r="D281" s="5"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
+      <c r="C282" s="5"/>
+      <c r="D282" s="5"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="C283" s="1"/>
-      <c r="D283" s="1"/>
+      <c r="C283" s="5"/>
+      <c r="D283" s="5"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="C284" s="1"/>
-      <c r="D284" s="1"/>
+      <c r="C284" s="5"/>
+      <c r="D284" s="5"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="C285" s="1"/>
-      <c r="D285" s="1"/>
+      <c r="C285" s="5"/>
+      <c r="D285" s="5"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="C286" s="1"/>
-      <c r="D286" s="1"/>
+      <c r="C286" s="5"/>
+      <c r="D286" s="5"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="C287" s="1"/>
-      <c r="D287" s="1"/>
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="C288" s="1"/>
-      <c r="D288" s="1"/>
+      <c r="C288" s="5"/>
+      <c r="D288" s="5"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="C289" s="1"/>
-      <c r="D289" s="1"/>
+      <c r="C289" s="5"/>
+      <c r="D289" s="5"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="C290" s="1"/>
-      <c r="D290" s="1"/>
+      <c r="C290" s="5"/>
+      <c r="D290" s="5"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="C291" s="1"/>
-      <c r="D291" s="1"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="C292" s="1"/>
-      <c r="D292" s="1"/>
+      <c r="C292" s="5"/>
+      <c r="D292" s="5"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="C293" s="1"/>
-      <c r="D293" s="1"/>
+      <c r="C293" s="5"/>
+      <c r="D293" s="5"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
+      <c r="C294" s="5"/>
+      <c r="D294" s="5"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="C295" s="1"/>
-      <c r="D295" s="1"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="C296" s="1"/>
-      <c r="D296" s="1"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="C298" s="1"/>
-      <c r="D298" s="1"/>
+      <c r="C298" s="5"/>
+      <c r="D298" s="5"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="C299" s="1"/>
-      <c r="D299" s="1"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="5"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="C300" s="1"/>
-      <c r="D300" s="1"/>
+      <c r="C300" s="5"/>
+      <c r="D300" s="5"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="C301" s="1"/>
-      <c r="D301" s="1"/>
+      <c r="C301" s="5"/>
+      <c r="D301" s="5"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="C302" s="1"/>
-      <c r="D302" s="1"/>
+      <c r="C302" s="5"/>
+      <c r="D302" s="5"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="C303" s="1"/>
-      <c r="D303" s="1"/>
+      <c r="C303" s="5"/>
+      <c r="D303" s="5"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="C304" s="1"/>
-      <c r="D304" s="1"/>
+      <c r="C304" s="5"/>
+      <c r="D304" s="5"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="C305" s="1"/>
-      <c r="D305" s="1"/>
+      <c r="C305" s="5"/>
+      <c r="D305" s="5"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="C306" s="1"/>
-      <c r="D306" s="1"/>
+      <c r="C306" s="5"/>
+      <c r="D306" s="5"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="C307" s="1"/>
-      <c r="D307" s="1"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="5"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="C308" s="1"/>
-      <c r="D308" s="1"/>
+      <c r="C308" s="5"/>
+      <c r="D308" s="5"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="1"/>
-      <c r="D309" s="1"/>
+      <c r="C309" s="5"/>
+      <c r="D309" s="5"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="C310" s="1"/>
-      <c r="D310" s="1"/>
+      <c r="C310" s="5"/>
+      <c r="D310" s="5"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="C311" s="1"/>
-      <c r="D311" s="1"/>
+      <c r="C311" s="5"/>
+      <c r="D311" s="5"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="C312" s="1"/>
-      <c r="D312" s="1"/>
+      <c r="C312" s="5"/>
+      <c r="D312" s="5"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
+      <c r="C313" s="5"/>
+      <c r="D313" s="5"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="C314" s="1"/>
-      <c r="D314" s="1"/>
+      <c r="C314" s="5"/>
+      <c r="D314" s="5"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="C315" s="1"/>
-      <c r="D315" s="1"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="5"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="C316" s="1"/>
-      <c r="D316" s="1"/>
+      <c r="C316" s="5"/>
+      <c r="D316" s="5"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
+      <c r="C317" s="5"/>
+      <c r="D317" s="5"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
+      <c r="C318" s="5"/>
+      <c r="D318" s="5"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
+      <c r="C319" s="5"/>
+      <c r="D319" s="5"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
+      <c r="C320" s="5"/>
+      <c r="D320" s="5"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
+      <c r="C321" s="5"/>
+      <c r="D321" s="5"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
+      <c r="C322" s="5"/>
+      <c r="D322" s="5"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="C323" s="1"/>
-      <c r="D323" s="1"/>
+      <c r="C323" s="5"/>
+      <c r="D323" s="5"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="C324" s="1"/>
-      <c r="D324" s="1"/>
+      <c r="C324" s="5"/>
+      <c r="D324" s="5"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="C325" s="1"/>
-      <c r="D325" s="1"/>
+      <c r="C325" s="5"/>
+      <c r="D325" s="5"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="C326" s="1"/>
-      <c r="D326" s="1"/>
+      <c r="C326" s="5"/>
+      <c r="D326" s="5"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="C327" s="1"/>
-      <c r="D327" s="1"/>
+      <c r="C327" s="5"/>
+      <c r="D327" s="5"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="C328" s="1"/>
-      <c r="D328" s="1"/>
+      <c r="C328" s="5"/>
+      <c r="D328" s="5"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="C329" s="1"/>
-      <c r="D329" s="1"/>
+      <c r="C329" s="5"/>
+      <c r="D329" s="5"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="C330" s="1"/>
-      <c r="D330" s="1"/>
+      <c r="C330" s="5"/>
+      <c r="D330" s="5"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="C331" s="1"/>
-      <c r="D331" s="1"/>
+      <c r="C331" s="5"/>
+      <c r="D331" s="5"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="C332" s="1"/>
-      <c r="D332" s="1"/>
+      <c r="C332" s="5"/>
+      <c r="D332" s="5"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="C333" s="1"/>
-      <c r="D333" s="1"/>
+      <c r="C333" s="5"/>
+      <c r="D333" s="5"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="C334" s="1"/>
-      <c r="D334" s="1"/>
+      <c r="C334" s="5"/>
+      <c r="D334" s="5"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="C335" s="1"/>
-      <c r="D335" s="1"/>
+      <c r="C335" s="5"/>
+      <c r="D335" s="5"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="C336" s="1"/>
-      <c r="D336" s="1"/>
+      <c r="C336" s="5"/>
+      <c r="D336" s="5"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="C337" s="1"/>
-      <c r="D337" s="1"/>
+      <c r="C337" s="5"/>
+      <c r="D337" s="5"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
+      <c r="C338" s="5"/>
+      <c r="D338" s="5"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
+      <c r="C339" s="5"/>
+      <c r="D339" s="5"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
+      <c r="C340" s="5"/>
+      <c r="D340" s="5"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
+      <c r="C341" s="5"/>
+      <c r="D341" s="5"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
+      <c r="C342" s="5"/>
+      <c r="D342" s="5"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
+      <c r="C343" s="5"/>
+      <c r="D343" s="5"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
+      <c r="C344" s="5"/>
+      <c r="D344" s="5"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
+      <c r="C345" s="5"/>
+      <c r="D345" s="5"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
+      <c r="C346" s="5"/>
+      <c r="D346" s="5"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
+      <c r="C347" s="5"/>
+      <c r="D347" s="5"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="C348" s="1"/>
-      <c r="D348" s="1"/>
+      <c r="C348" s="5"/>
+      <c r="D348" s="5"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="C349" s="1"/>
-      <c r="D349" s="1"/>
+      <c r="C349" s="5"/>
+      <c r="D349" s="5"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="C350" s="1"/>
-      <c r="D350" s="1"/>
+      <c r="C350" s="5"/>
+      <c r="D350" s="5"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="C351" s="1"/>
-      <c r="D351" s="1"/>
+      <c r="C351" s="5"/>
+      <c r="D351" s="5"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="C352" s="1"/>
-      <c r="D352" s="1"/>
+      <c r="C352" s="5"/>
+      <c r="D352" s="5"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="C353" s="1"/>
-      <c r="D353" s="1"/>
+      <c r="C353" s="5"/>
+      <c r="D353" s="5"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="C354" s="1"/>
-      <c r="D354" s="1"/>
+      <c r="C354" s="5"/>
+      <c r="D354" s="5"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="C355" s="1"/>
-      <c r="D355" s="1"/>
+      <c r="C355" s="5"/>
+      <c r="D355" s="5"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="C356" s="1"/>
-      <c r="D356" s="1"/>
+      <c r="C356" s="5"/>
+      <c r="D356" s="5"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="C357" s="1"/>
-      <c r="D357" s="1"/>
+      <c r="C357" s="5"/>
+      <c r="D357" s="5"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="C358" s="1"/>
-      <c r="D358" s="1"/>
+      <c r="C358" s="5"/>
+      <c r="D358" s="5"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="C359" s="1"/>
-      <c r="D359" s="1"/>
+      <c r="C359" s="5"/>
+      <c r="D359" s="5"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="C360" s="1"/>
-      <c r="D360" s="1"/>
+      <c r="C360" s="5"/>
+      <c r="D360" s="5"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="C361" s="1"/>
-      <c r="D361" s="1"/>
+      <c r="C361" s="5"/>
+      <c r="D361" s="5"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="C362" s="1"/>
-      <c r="D362" s="1"/>
+      <c r="C362" s="5"/>
+      <c r="D362" s="5"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="C363" s="1"/>
-      <c r="D363" s="1"/>
+      <c r="C363" s="5"/>
+      <c r="D363" s="5"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="C364" s="1"/>
-      <c r="D364" s="1"/>
+      <c r="C364" s="5"/>
+      <c r="D364" s="5"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="C365" s="1"/>
-      <c r="D365" s="1"/>
+      <c r="C365" s="5"/>
+      <c r="D365" s="5"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="C366" s="1"/>
-      <c r="D366" s="1"/>
+      <c r="C366" s="5"/>
+      <c r="D366" s="5"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="C367" s="1"/>
-      <c r="D367" s="1"/>
+      <c r="C367" s="5"/>
+      <c r="D367" s="5"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="C368" s="1"/>
-      <c r="D368" s="1"/>
+      <c r="C368" s="5"/>
+      <c r="D368" s="5"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="C369" s="1"/>
-      <c r="D369" s="1"/>
+      <c r="C369" s="5"/>
+      <c r="D369" s="5"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="C370" s="1"/>
-      <c r="D370" s="1"/>
+      <c r="C370" s="5"/>
+      <c r="D370" s="5"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
+      <c r="C371" s="5"/>
+      <c r="D371" s="5"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="C372" s="1"/>
-      <c r="D372" s="1"/>
+      <c r="C372" s="5"/>
+      <c r="D372" s="5"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="C373" s="1"/>
-      <c r="D373" s="1"/>
+      <c r="C373" s="5"/>
+      <c r="D373" s="5"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="C374" s="1"/>
-      <c r="D374" s="1"/>
+      <c r="C374" s="5"/>
+      <c r="D374" s="5"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="C375" s="1"/>
-      <c r="D375" s="1"/>
+      <c r="C375" s="5"/>
+      <c r="D375" s="5"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="C376" s="1"/>
-      <c r="D376" s="1"/>
+      <c r="C376" s="5"/>
+      <c r="D376" s="5"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="C377" s="1"/>
-      <c r="D377" s="1"/>
+      <c r="C377" s="5"/>
+      <c r="D377" s="5"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="C378" s="1"/>
-      <c r="D378" s="1"/>
+      <c r="C378" s="5"/>
+      <c r="D378" s="5"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="C379" s="1"/>
-      <c r="D379" s="1"/>
+      <c r="C379" s="5"/>
+      <c r="D379" s="5"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="C380" s="1"/>
-      <c r="D380" s="1"/>
+      <c r="C380" s="5"/>
+      <c r="D380" s="5"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="C381" s="1"/>
-      <c r="D381" s="1"/>
+      <c r="C381" s="5"/>
+      <c r="D381" s="5"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="C382" s="1"/>
-      <c r="D382" s="1"/>
+      <c r="C382" s="5"/>
+      <c r="D382" s="5"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="C383" s="1"/>
-      <c r="D383" s="1"/>
+      <c r="C383" s="5"/>
+      <c r="D383" s="5"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="C384" s="1"/>
-      <c r="D384" s="1"/>
+      <c r="C384" s="5"/>
+      <c r="D384" s="5"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="C385" s="1"/>
-      <c r="D385" s="1"/>
+      <c r="C385" s="5"/>
+      <c r="D385" s="5"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="C386" s="1"/>
-      <c r="D386" s="1"/>
+      <c r="C386" s="5"/>
+      <c r="D386" s="5"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="1"/>
-      <c r="D387" s="1"/>
+      <c r="C387" s="5"/>
+      <c r="D387" s="5"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="C388" s="1"/>
-      <c r="D388" s="1"/>
+      <c r="C388" s="5"/>
+      <c r="D388" s="5"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="C389" s="1"/>
-      <c r="D389" s="1"/>
+      <c r="C389" s="5"/>
+      <c r="D389" s="5"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="C390" s="1"/>
-      <c r="D390" s="1"/>
+      <c r="C390" s="5"/>
+      <c r="D390" s="5"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="C391" s="1"/>
-      <c r="D391" s="1"/>
+      <c r="C391" s="5"/>
+      <c r="D391" s="5"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="C392" s="1"/>
-      <c r="D392" s="1"/>
+      <c r="C392" s="5"/>
+      <c r="D392" s="5"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="C393" s="1"/>
-      <c r="D393" s="1"/>
+      <c r="C393" s="5"/>
+      <c r="D393" s="5"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="C394" s="1"/>
-      <c r="D394" s="1"/>
+      <c r="C394" s="5"/>
+      <c r="D394" s="5"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="C395" s="1"/>
-      <c r="D395" s="1"/>
+      <c r="C395" s="5"/>
+      <c r="D395" s="5"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="C396" s="1"/>
-      <c r="D396" s="1"/>
+      <c r="C396" s="5"/>
+      <c r="D396" s="5"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="C397" s="1"/>
-      <c r="D397" s="1"/>
+      <c r="C397" s="5"/>
+      <c r="D397" s="5"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="C398" s="1"/>
-      <c r="D398" s="1"/>
+      <c r="C398" s="5"/>
+      <c r="D398" s="5"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="C399" s="1"/>
-      <c r="D399" s="1"/>
+      <c r="C399" s="5"/>
+      <c r="D399" s="5"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="C400" s="1"/>
-      <c r="D400" s="1"/>
+      <c r="C400" s="5"/>
+      <c r="D400" s="5"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="C401" s="1"/>
-      <c r="D401" s="1"/>
+      <c r="C401" s="5"/>
+      <c r="D401" s="5"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="C402" s="1"/>
-      <c r="D402" s="1"/>
+      <c r="C402" s="5"/>
+      <c r="D402" s="5"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="C403" s="1"/>
-      <c r="D403" s="1"/>
+      <c r="C403" s="5"/>
+      <c r="D403" s="5"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="C404" s="1"/>
-      <c r="D404" s="1"/>
+      <c r="C404" s="5"/>
+      <c r="D404" s="5"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="C405" s="1"/>
-      <c r="D405" s="1"/>
+      <c r="C405" s="5"/>
+      <c r="D405" s="5"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="C406" s="1"/>
-      <c r="D406" s="1"/>
+      <c r="C406" s="5"/>
+      <c r="D406" s="5"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="C407" s="1"/>
-      <c r="D407" s="1"/>
+      <c r="C407" s="5"/>
+      <c r="D407" s="5"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="C408" s="1"/>
-      <c r="D408" s="1"/>
+      <c r="C408" s="5"/>
+      <c r="D408" s="5"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="C409" s="1"/>
-      <c r="D409" s="1"/>
+      <c r="C409" s="5"/>
+      <c r="D409" s="5"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="C410" s="1"/>
-      <c r="D410" s="1"/>
+      <c r="C410" s="5"/>
+      <c r="D410" s="5"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="C411" s="1"/>
-      <c r="D411" s="1"/>
+      <c r="C411" s="5"/>
+      <c r="D411" s="5"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="C412" s="1"/>
-      <c r="D412" s="1"/>
+      <c r="C412" s="5"/>
+      <c r="D412" s="5"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="C413" s="1"/>
-      <c r="D413" s="1"/>
+      <c r="C413" s="5"/>
+      <c r="D413" s="5"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="C414" s="1"/>
-      <c r="D414" s="1"/>
+      <c r="C414" s="5"/>
+      <c r="D414" s="5"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="C415" s="1"/>
-      <c r="D415" s="1"/>
+      <c r="C415" s="5"/>
+      <c r="D415" s="5"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="C416" s="1"/>
-      <c r="D416" s="1"/>
+      <c r="C416" s="5"/>
+      <c r="D416" s="5"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="C417" s="1"/>
-      <c r="D417" s="1"/>
+      <c r="C417" s="5"/>
+      <c r="D417" s="5"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="C418" s="1"/>
-      <c r="D418" s="1"/>
+      <c r="C418" s="5"/>
+      <c r="D418" s="5"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="C419" s="1"/>
-      <c r="D419" s="1"/>
+      <c r="C419" s="5"/>
+      <c r="D419" s="5"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="C420" s="1"/>
-      <c r="D420" s="1"/>
+      <c r="C420" s="5"/>
+      <c r="D420" s="5"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="C421" s="1"/>
-      <c r="D421" s="1"/>
+      <c r="C421" s="5"/>
+      <c r="D421" s="5"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="C422" s="1"/>
-      <c r="D422" s="1"/>
+      <c r="C422" s="5"/>
+      <c r="D422" s="5"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="C423" s="1"/>
-      <c r="D423" s="1"/>
+      <c r="C423" s="5"/>
+      <c r="D423" s="5"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="C424" s="1"/>
-      <c r="D424" s="1"/>
+      <c r="C424" s="5"/>
+      <c r="D424" s="5"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="C425" s="1"/>
-      <c r="D425" s="1"/>
+      <c r="C425" s="5"/>
+      <c r="D425" s="5"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="C426" s="1"/>
-      <c r="D426" s="1"/>
+      <c r="C426" s="5"/>
+      <c r="D426" s="5"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="C427" s="1"/>
-      <c r="D427" s="1"/>
+      <c r="C427" s="5"/>
+      <c r="D427" s="5"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="C428" s="1"/>
-      <c r="D428" s="1"/>
+      <c r="C428" s="5"/>
+      <c r="D428" s="5"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="C429" s="1"/>
-      <c r="D429" s="1"/>
+      <c r="C429" s="5"/>
+      <c r="D429" s="5"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="C430" s="1"/>
-      <c r="D430" s="1"/>
+      <c r="C430" s="5"/>
+      <c r="D430" s="5"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="C431" s="1"/>
-      <c r="D431" s="1"/>
+      <c r="C431" s="5"/>
+      <c r="D431" s="5"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="C432" s="1"/>
-      <c r="D432" s="1"/>
+      <c r="C432" s="5"/>
+      <c r="D432" s="5"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="C433" s="1"/>
-      <c r="D433" s="1"/>
+      <c r="C433" s="5"/>
+      <c r="D433" s="5"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="C434" s="1"/>
-      <c r="D434" s="1"/>
+      <c r="C434" s="5"/>
+      <c r="D434" s="5"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="C435" s="1"/>
-      <c r="D435" s="1"/>
+      <c r="C435" s="5"/>
+      <c r="D435" s="5"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="C436" s="1"/>
-      <c r="D436" s="1"/>
+      <c r="C436" s="5"/>
+      <c r="D436" s="5"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="C437" s="1"/>
-      <c r="D437" s="1"/>
+      <c r="C437" s="5"/>
+      <c r="D437" s="5"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="C438" s="1"/>
-      <c r="D438" s="1"/>
+      <c r="C438" s="5"/>
+      <c r="D438" s="5"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="C439" s="1"/>
-      <c r="D439" s="1"/>
+      <c r="C439" s="5"/>
+      <c r="D439" s="5"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="C440" s="1"/>
-      <c r="D440" s="1"/>
+      <c r="C440" s="5"/>
+      <c r="D440" s="5"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="C441" s="1"/>
-      <c r="D441" s="1"/>
+      <c r="C441" s="5"/>
+      <c r="D441" s="5"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="C442" s="1"/>
-      <c r="D442" s="1"/>
+      <c r="C442" s="5"/>
+      <c r="D442" s="5"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="C443" s="1"/>
-      <c r="D443" s="1"/>
+      <c r="C443" s="5"/>
+      <c r="D443" s="5"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="C444" s="1"/>
-      <c r="D444" s="1"/>
+      <c r="C444" s="5"/>
+      <c r="D444" s="5"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="C445" s="1"/>
-      <c r="D445" s="1"/>
+      <c r="C445" s="5"/>
+      <c r="D445" s="5"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="C446" s="1"/>
-      <c r="D446" s="1"/>
+      <c r="C446" s="5"/>
+      <c r="D446" s="5"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="C447" s="1"/>
-      <c r="D447" s="1"/>
+      <c r="C447" s="5"/>
+      <c r="D447" s="5"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="C448" s="1"/>
-      <c r="D448" s="1"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="5"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="C449" s="1"/>
-      <c r="D449" s="1"/>
+      <c r="C449" s="5"/>
+      <c r="D449" s="5"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="C450" s="1"/>
-      <c r="D450" s="1"/>
+      <c r="C450" s="5"/>
+      <c r="D450" s="5"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="C451" s="1"/>
-      <c r="D451" s="1"/>
+      <c r="C451" s="5"/>
+      <c r="D451" s="5"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="C452" s="1"/>
-      <c r="D452" s="1"/>
+      <c r="C452" s="5"/>
+      <c r="D452" s="5"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="C453" s="1"/>
-      <c r="D453" s="1"/>
+      <c r="C453" s="5"/>
+      <c r="D453" s="5"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="C454" s="1"/>
-      <c r="D454" s="1"/>
+      <c r="C454" s="5"/>
+      <c r="D454" s="5"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="C455" s="1"/>
-      <c r="D455" s="1"/>
+      <c r="C455" s="5"/>
+      <c r="D455" s="5"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="C456" s="1"/>
-      <c r="D456" s="1"/>
+      <c r="C456" s="5"/>
+      <c r="D456" s="5"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="C457" s="1"/>
-      <c r="D457" s="1"/>
+      <c r="C457" s="5"/>
+      <c r="D457" s="5"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="C458" s="1"/>
-      <c r="D458" s="1"/>
+      <c r="C458" s="5"/>
+      <c r="D458" s="5"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="C459" s="1"/>
-      <c r="D459" s="1"/>
+      <c r="C459" s="5"/>
+      <c r="D459" s="5"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="C460" s="1"/>
-      <c r="D460" s="1"/>
+      <c r="C460" s="5"/>
+      <c r="D460" s="5"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="C461" s="1"/>
-      <c r="D461" s="1"/>
+      <c r="C461" s="5"/>
+      <c r="D461" s="5"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="C462" s="1"/>
-      <c r="D462" s="1"/>
+      <c r="C462" s="5"/>
+      <c r="D462" s="5"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="C463" s="1"/>
-      <c r="D463" s="1"/>
+      <c r="C463" s="5"/>
+      <c r="D463" s="5"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="C464" s="1"/>
-      <c r="D464" s="1"/>
+      <c r="C464" s="5"/>
+      <c r="D464" s="5"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="C465" s="1"/>
-      <c r="D465" s="1"/>
+      <c r="C465" s="5"/>
+      <c r="D465" s="5"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="C466" s="1"/>
-      <c r="D466" s="1"/>
+      <c r="C466" s="5"/>
+      <c r="D466" s="5"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="C467" s="1"/>
-      <c r="D467" s="1"/>
+      <c r="C467" s="5"/>
+      <c r="D467" s="5"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="C468" s="1"/>
-      <c r="D468" s="1"/>
+      <c r="C468" s="5"/>
+      <c r="D468" s="5"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="C469" s="1"/>
-      <c r="D469" s="1"/>
+      <c r="C469" s="5"/>
+      <c r="D469" s="5"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="C470" s="1"/>
-      <c r="D470" s="1"/>
+      <c r="C470" s="5"/>
+      <c r="D470" s="5"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="C471" s="1"/>
-      <c r="D471" s="1"/>
+      <c r="C471" s="5"/>
+      <c r="D471" s="5"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="C472" s="1"/>
-      <c r="D472" s="1"/>
+      <c r="C472" s="5"/>
+      <c r="D472" s="5"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="C473" s="1"/>
-      <c r="D473" s="1"/>
+      <c r="C473" s="5"/>
+      <c r="D473" s="5"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="C474" s="1"/>
-      <c r="D474" s="1"/>
+      <c r="C474" s="5"/>
+      <c r="D474" s="5"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="C475" s="1"/>
-      <c r="D475" s="1"/>
+      <c r="C475" s="5"/>
+      <c r="D475" s="5"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="C476" s="1"/>
-      <c r="D476" s="1"/>
+      <c r="C476" s="5"/>
+      <c r="D476" s="5"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="C477" s="1"/>
-      <c r="D477" s="1"/>
+      <c r="C477" s="5"/>
+      <c r="D477" s="5"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="C478" s="1"/>
-      <c r="D478" s="1"/>
+      <c r="C478" s="5"/>
+      <c r="D478" s="5"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="C479" s="1"/>
-      <c r="D479" s="1"/>
+      <c r="C479" s="5"/>
+      <c r="D479" s="5"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="C480" s="1"/>
-      <c r="D480" s="1"/>
+      <c r="C480" s="5"/>
+      <c r="D480" s="5"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="C481" s="1"/>
-      <c r="D481" s="1"/>
+      <c r="C481" s="5"/>
+      <c r="D481" s="5"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="C482" s="1"/>
-      <c r="D482" s="1"/>
+      <c r="C482" s="5"/>
+      <c r="D482" s="5"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="C483" s="1"/>
-      <c r="D483" s="1"/>
+      <c r="C483" s="5"/>
+      <c r="D483" s="5"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="C484" s="1"/>
-      <c r="D484" s="1"/>
+      <c r="C484" s="5"/>
+      <c r="D484" s="5"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="C485" s="1"/>
-      <c r="D485" s="1"/>
+      <c r="C485" s="5"/>
+      <c r="D485" s="5"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="C486" s="1"/>
-      <c r="D486" s="1"/>
+      <c r="C486" s="5"/>
+      <c r="D486" s="5"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="C487" s="1"/>
-      <c r="D487" s="1"/>
+      <c r="C487" s="5"/>
+      <c r="D487" s="5"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="C488" s="1"/>
-      <c r="D488" s="1"/>
+      <c r="C488" s="5"/>
+      <c r="D488" s="5"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="C489" s="1"/>
-      <c r="D489" s="1"/>
+      <c r="C489" s="5"/>
+      <c r="D489" s="5"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="C490" s="1"/>
-      <c r="D490" s="1"/>
+      <c r="C490" s="5"/>
+      <c r="D490" s="5"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="C491" s="1"/>
-      <c r="D491" s="1"/>
+      <c r="C491" s="5"/>
+      <c r="D491" s="5"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="C492" s="1"/>
-      <c r="D492" s="1"/>
+      <c r="C492" s="5"/>
+      <c r="D492" s="5"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="C493" s="1"/>
-      <c r="D493" s="1"/>
+      <c r="C493" s="5"/>
+      <c r="D493" s="5"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="C494" s="1"/>
-      <c r="D494" s="1"/>
+      <c r="C494" s="5"/>
+      <c r="D494" s="5"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="C495" s="1"/>
-      <c r="D495" s="1"/>
+      <c r="C495" s="5"/>
+      <c r="D495" s="5"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="C496" s="1"/>
-      <c r="D496" s="1"/>
+      <c r="C496" s="5"/>
+      <c r="D496" s="5"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="C497" s="1"/>
-      <c r="D497" s="1"/>
+      <c r="C497" s="5"/>
+      <c r="D497" s="5"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="C498" s="1"/>
-      <c r="D498" s="1"/>
+      <c r="C498" s="5"/>
+      <c r="D498" s="5"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="C499" s="1"/>
-      <c r="D499" s="1"/>
+      <c r="C499" s="5"/>
+      <c r="D499" s="5"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="C500" s="1"/>
-      <c r="D500" s="1"/>
+      <c r="C500" s="5"/>
+      <c r="D500" s="5"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="C501" s="1"/>
-      <c r="D501" s="1"/>
+      <c r="C501" s="5"/>
+      <c r="D501" s="5"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="C502" s="1"/>
-      <c r="D502" s="1"/>
+      <c r="C502" s="5"/>
+      <c r="D502" s="5"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="C503" s="1"/>
-      <c r="D503" s="1"/>
+      <c r="C503" s="5"/>
+      <c r="D503" s="5"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="C504" s="1"/>
-      <c r="D504" s="1"/>
+      <c r="C504" s="5"/>
+      <c r="D504" s="5"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="C505" s="1"/>
-      <c r="D505" s="1"/>
+      <c r="C505" s="5"/>
+      <c r="D505" s="5"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="C506" s="1"/>
-      <c r="D506" s="1"/>
+      <c r="C506" s="5"/>
+      <c r="D506" s="5"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="C507" s="1"/>
-      <c r="D507" s="1"/>
+      <c r="C507" s="5"/>
+      <c r="D507" s="5"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="C508" s="1"/>
-      <c r="D508" s="1"/>
+      <c r="C508" s="5"/>
+      <c r="D508" s="5"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="C509" s="1"/>
-      <c r="D509" s="1"/>
+      <c r="C509" s="5"/>
+      <c r="D509" s="5"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="C510" s="1"/>
-      <c r="D510" s="1"/>
+      <c r="C510" s="5"/>
+      <c r="D510" s="5"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="C511" s="1"/>
-      <c r="D511" s="1"/>
+      <c r="C511" s="5"/>
+      <c r="D511" s="5"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="C512" s="1"/>
-      <c r="D512" s="1"/>
+      <c r="C512" s="5"/>
+      <c r="D512" s="5"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="C513" s="1"/>
-      <c r="D513" s="1"/>
+      <c r="C513" s="5"/>
+      <c r="D513" s="5"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="C514" s="1"/>
-      <c r="D514" s="1"/>
+      <c r="C514" s="5"/>
+      <c r="D514" s="5"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="C515" s="1"/>
-      <c r="D515" s="1"/>
+      <c r="C515" s="5"/>
+      <c r="D515" s="5"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="C516" s="1"/>
-      <c r="D516" s="1"/>
+      <c r="C516" s="5"/>
+      <c r="D516" s="5"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="C517" s="1"/>
-      <c r="D517" s="1"/>
+      <c r="C517" s="5"/>
+      <c r="D517" s="5"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="C518" s="1"/>
-      <c r="D518" s="1"/>
+      <c r="C518" s="5"/>
+      <c r="D518" s="5"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="C519" s="1"/>
-      <c r="D519" s="1"/>
+      <c r="C519" s="5"/>
+      <c r="D519" s="5"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="C520" s="1"/>
-      <c r="D520" s="1"/>
+      <c r="C520" s="5"/>
+      <c r="D520" s="5"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="C521" s="1"/>
-      <c r="D521" s="1"/>
+      <c r="C521" s="5"/>
+      <c r="D521" s="5"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="C522" s="1"/>
-      <c r="D522" s="1"/>
+      <c r="C522" s="5"/>
+      <c r="D522" s="5"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="C523" s="1"/>
-      <c r="D523" s="1"/>
+      <c r="C523" s="5"/>
+      <c r="D523" s="5"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="C524" s="1"/>
-      <c r="D524" s="1"/>
+      <c r="C524" s="5"/>
+      <c r="D524" s="5"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="C525" s="1"/>
-      <c r="D525" s="1"/>
+      <c r="C525" s="5"/>
+      <c r="D525" s="5"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="C526" s="1"/>
-      <c r="D526" s="1"/>
+      <c r="C526" s="5"/>
+      <c r="D526" s="5"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="C527" s="1"/>
-      <c r="D527" s="1"/>
+      <c r="C527" s="5"/>
+      <c r="D527" s="5"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="C528" s="1"/>
-      <c r="D528" s="1"/>
+      <c r="C528" s="5"/>
+      <c r="D528" s="5"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="C529" s="1"/>
-      <c r="D529" s="1"/>
+      <c r="C529" s="5"/>
+      <c r="D529" s="5"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="C530" s="1"/>
-      <c r="D530" s="1"/>
+      <c r="C530" s="5"/>
+      <c r="D530" s="5"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="C531" s="1"/>
-      <c r="D531" s="1"/>
+      <c r="C531" s="5"/>
+      <c r="D531" s="5"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="C532" s="1"/>
-      <c r="D532" s="1"/>
+      <c r="C532" s="5"/>
+      <c r="D532" s="5"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="C533" s="1"/>
-      <c r="D533" s="1"/>
+      <c r="C533" s="5"/>
+      <c r="D533" s="5"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="C534" s="1"/>
-      <c r="D534" s="1"/>
+      <c r="C534" s="5"/>
+      <c r="D534" s="5"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="C535" s="1"/>
-      <c r="D535" s="1"/>
+      <c r="C535" s="5"/>
+      <c r="D535" s="5"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="C536" s="1"/>
-      <c r="D536" s="1"/>
+      <c r="C536" s="5"/>
+      <c r="D536" s="5"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="C537" s="1"/>
-      <c r="D537" s="1"/>
+      <c r="C537" s="5"/>
+      <c r="D537" s="5"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="C538" s="1"/>
-      <c r="D538" s="1"/>
+      <c r="C538" s="5"/>
+      <c r="D538" s="5"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="C539" s="1"/>
-      <c r="D539" s="1"/>
+      <c r="C539" s="5"/>
+      <c r="D539" s="5"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="C540" s="1"/>
-      <c r="D540" s="1"/>
+      <c r="C540" s="5"/>
+      <c r="D540" s="5"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="C541" s="1"/>
-      <c r="D541" s="1"/>
+      <c r="C541" s="5"/>
+      <c r="D541" s="5"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="C542" s="1"/>
-      <c r="D542" s="1"/>
+      <c r="C542" s="5"/>
+      <c r="D542" s="5"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="C543" s="1"/>
-      <c r="D543" s="1"/>
+      <c r="C543" s="5"/>
+      <c r="D543" s="5"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="C544" s="1"/>
-      <c r="D544" s="1"/>
+      <c r="C544" s="5"/>
+      <c r="D544" s="5"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="C545" s="1"/>
-      <c r="D545" s="1"/>
+      <c r="C545" s="5"/>
+      <c r="D545" s="5"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="C546" s="1"/>
-      <c r="D546" s="1"/>
+      <c r="C546" s="5"/>
+      <c r="D546" s="5"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="C547" s="1"/>
-      <c r="D547" s="1"/>
+      <c r="C547" s="5"/>
+      <c r="D547" s="5"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="C548" s="1"/>
-      <c r="D548" s="1"/>
+      <c r="C548" s="5"/>
+      <c r="D548" s="5"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="C549" s="1"/>
-      <c r="D549" s="1"/>
+      <c r="C549" s="5"/>
+      <c r="D549" s="5"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="C550" s="1"/>
-      <c r="D550" s="1"/>
+      <c r="C550" s="5"/>
+      <c r="D550" s="5"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="C551" s="1"/>
-      <c r="D551" s="1"/>
+      <c r="C551" s="5"/>
+      <c r="D551" s="5"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="C552" s="1"/>
-      <c r="D552" s="1"/>
+      <c r="C552" s="5"/>
+      <c r="D552" s="5"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="C553" s="1"/>
-      <c r="D553" s="1"/>
+      <c r="C553" s="5"/>
+      <c r="D553" s="5"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="C554" s="1"/>
-      <c r="D554" s="1"/>
+      <c r="C554" s="5"/>
+      <c r="D554" s="5"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="C555" s="1"/>
-      <c r="D555" s="1"/>
+      <c r="C555" s="5"/>
+      <c r="D555" s="5"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="C556" s="1"/>
-      <c r="D556" s="1"/>
+      <c r="C556" s="5"/>
+      <c r="D556" s="5"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="C557" s="1"/>
-      <c r="D557" s="1"/>
+      <c r="C557" s="5"/>
+      <c r="D557" s="5"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="C558" s="1"/>
-      <c r="D558" s="1"/>
+      <c r="C558" s="5"/>
+      <c r="D558" s="5"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="C559" s="1"/>
-      <c r="D559" s="1"/>
+      <c r="C559" s="5"/>
+      <c r="D559" s="5"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="C560" s="1"/>
-      <c r="D560" s="1"/>
+      <c r="C560" s="5"/>
+      <c r="D560" s="5"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="C561" s="1"/>
-      <c r="D561" s="1"/>
+      <c r="C561" s="5"/>
+      <c r="D561" s="5"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="C562" s="1"/>
-      <c r="D562" s="1"/>
+      <c r="C562" s="5"/>
+      <c r="D562" s="5"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="C563" s="1"/>
-      <c r="D563" s="1"/>
+      <c r="C563" s="5"/>
+      <c r="D563" s="5"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="C564" s="1"/>
-      <c r="D564" s="1"/>
+      <c r="C564" s="5"/>
+      <c r="D564" s="5"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="C565" s="1"/>
-      <c r="D565" s="1"/>
+      <c r="C565" s="5"/>
+      <c r="D565" s="5"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="C566" s="1"/>
-      <c r="D566" s="1"/>
+      <c r="C566" s="5"/>
+      <c r="D566" s="5"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="C567" s="1"/>
-      <c r="D567" s="1"/>
+      <c r="C567" s="5"/>
+      <c r="D567" s="5"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="C568" s="1"/>
-      <c r="D568" s="1"/>
+      <c r="C568" s="5"/>
+      <c r="D568" s="5"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="C569" s="1"/>
-      <c r="D569" s="1"/>
+      <c r="C569" s="5"/>
+      <c r="D569" s="5"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="C570" s="1"/>
-      <c r="D570" s="1"/>
+      <c r="C570" s="5"/>
+      <c r="D570" s="5"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="C571" s="1"/>
-      <c r="D571" s="1"/>
+      <c r="C571" s="5"/>
+      <c r="D571" s="5"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="C572" s="1"/>
-      <c r="D572" s="1"/>
+      <c r="C572" s="5"/>
+      <c r="D572" s="5"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="C573" s="1"/>
-      <c r="D573" s="1"/>
+      <c r="C573" s="5"/>
+      <c r="D573" s="5"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="C574" s="1"/>
-      <c r="D574" s="1"/>
+      <c r="C574" s="5"/>
+      <c r="D574" s="5"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="C575" s="1"/>
-      <c r="D575" s="1"/>
+      <c r="C575" s="5"/>
+      <c r="D575" s="5"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="C576" s="1"/>
-      <c r="D576" s="1"/>
+      <c r="C576" s="5"/>
+      <c r="D576" s="5"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="C577" s="1"/>
-      <c r="D577" s="1"/>
+      <c r="C577" s="5"/>
+      <c r="D577" s="5"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="C578" s="1"/>
-      <c r="D578" s="1"/>
+      <c r="C578" s="5"/>
+      <c r="D578" s="5"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="C579" s="1"/>
-      <c r="D579" s="1"/>
+      <c r="C579" s="5"/>
+      <c r="D579" s="5"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="C580" s="1"/>
-      <c r="D580" s="1"/>
+      <c r="C580" s="5"/>
+      <c r="D580" s="5"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="C581" s="1"/>
-      <c r="D581" s="1"/>
+      <c r="C581" s="5"/>
+      <c r="D581" s="5"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="C582" s="1"/>
-      <c r="D582" s="1"/>
+      <c r="C582" s="5"/>
+      <c r="D582" s="5"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="C583" s="1"/>
-      <c r="D583" s="1"/>
+      <c r="C583" s="5"/>
+      <c r="D583" s="5"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="1"/>
-      <c r="D584" s="1"/>
+      <c r="C584" s="5"/>
+      <c r="D584" s="5"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="1"/>
-      <c r="D585" s="1"/>
+      <c r="C585" s="5"/>
+      <c r="D585" s="5"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="1"/>
-      <c r="D586" s="1"/>
+      <c r="C586" s="5"/>
+      <c r="D586" s="5"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="C587" s="1"/>
-      <c r="D587" s="1"/>
+      <c r="C587" s="5"/>
+      <c r="D587" s="5"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="C588" s="1"/>
-      <c r="D588" s="1"/>
+      <c r="C588" s="5"/>
+      <c r="D588" s="5"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="C589" s="1"/>
-      <c r="D589" s="1"/>
+      <c r="C589" s="5"/>
+      <c r="D589" s="5"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="C590" s="1"/>
-      <c r="D590" s="1"/>
+      <c r="C590" s="5"/>
+      <c r="D590" s="5"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="C591" s="1"/>
-      <c r="D591" s="1"/>
+      <c r="C591" s="5"/>
+      <c r="D591" s="5"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="C592" s="1"/>
-      <c r="D592" s="1"/>
+      <c r="C592" s="5"/>
+      <c r="D592" s="5"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="C593" s="1"/>
-      <c r="D593" s="1"/>
+      <c r="C593" s="5"/>
+      <c r="D593" s="5"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="C594" s="1"/>
-      <c r="D594" s="1"/>
+      <c r="C594" s="5"/>
+      <c r="D594" s="5"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="C595" s="1"/>
-      <c r="D595" s="1"/>
+      <c r="C595" s="5"/>
+      <c r="D595" s="5"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="C596" s="1"/>
-      <c r="D596" s="1"/>
+      <c r="C596" s="5"/>
+      <c r="D596" s="5"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="C597" s="1"/>
-      <c r="D597" s="1"/>
+      <c r="C597" s="5"/>
+      <c r="D597" s="5"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="C598" s="1"/>
-      <c r="D598" s="1"/>
+      <c r="C598" s="5"/>
+      <c r="D598" s="5"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="C599" s="1"/>
-      <c r="D599" s="1"/>
+      <c r="C599" s="5"/>
+      <c r="D599" s="5"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="1"/>
-      <c r="D600" s="1"/>
+      <c r="C600" s="5"/>
+      <c r="D600" s="5"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="1"/>
-      <c r="D601" s="1"/>
+      <c r="C601" s="5"/>
+      <c r="D601" s="5"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="1"/>
-      <c r="D602" s="1"/>
+      <c r="C602" s="5"/>
+      <c r="D602" s="5"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="C603" s="1"/>
-      <c r="D603" s="1"/>
+      <c r="C603" s="5"/>
+      <c r="D603" s="5"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="C604" s="1"/>
-      <c r="D604" s="1"/>
+      <c r="C604" s="5"/>
+      <c r="D604" s="5"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="C605" s="1"/>
-      <c r="D605" s="1"/>
+      <c r="C605" s="5"/>
+      <c r="D605" s="5"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="C606" s="1"/>
-      <c r="D606" s="1"/>
+      <c r="C606" s="5"/>
+      <c r="D606" s="5"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="C607" s="1"/>
-      <c r="D607" s="1"/>
+      <c r="C607" s="5"/>
+      <c r="D607" s="5"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="C608" s="1"/>
-      <c r="D608" s="1"/>
+      <c r="C608" s="5"/>
+      <c r="D608" s="5"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="C609" s="1"/>
-      <c r="D609" s="1"/>
+      <c r="C609" s="5"/>
+      <c r="D609" s="5"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="C610" s="1"/>
-      <c r="D610" s="1"/>
+      <c r="C610" s="5"/>
+      <c r="D610" s="5"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="C611" s="1"/>
-      <c r="D611" s="1"/>
+      <c r="C611" s="5"/>
+      <c r="D611" s="5"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="C612" s="1"/>
-      <c r="D612" s="1"/>
+      <c r="C612" s="5"/>
+      <c r="D612" s="5"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="C613" s="1"/>
-      <c r="D613" s="1"/>
+      <c r="C613" s="5"/>
+      <c r="D613" s="5"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="C614" s="1"/>
-      <c r="D614" s="1"/>
+      <c r="C614" s="5"/>
+      <c r="D614" s="5"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="C615" s="1"/>
-      <c r="D615" s="1"/>
+      <c r="C615" s="5"/>
+      <c r="D615" s="5"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="1"/>
-      <c r="D616" s="1"/>
+      <c r="C616" s="5"/>
+      <c r="D616" s="5"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="1"/>
-      <c r="D617" s="1"/>
+      <c r="C617" s="5"/>
+      <c r="D617" s="5"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="1"/>
-      <c r="D618" s="1"/>
+      <c r="C618" s="5"/>
+      <c r="D618" s="5"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="C619" s="1"/>
-      <c r="D619" s="1"/>
+      <c r="C619" s="5"/>
+      <c r="D619" s="5"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="C620" s="1"/>
-      <c r="D620" s="1"/>
+      <c r="C620" s="5"/>
+      <c r="D620" s="5"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="C621" s="1"/>
-      <c r="D621" s="1"/>
+      <c r="C621" s="5"/>
+      <c r="D621" s="5"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="C622" s="1"/>
-      <c r="D622" s="1"/>
+      <c r="C622" s="5"/>
+      <c r="D622" s="5"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="C623" s="1"/>
-      <c r="D623" s="1"/>
+      <c r="C623" s="5"/>
+      <c r="D623" s="5"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="C624" s="1"/>
-      <c r="D624" s="1"/>
+      <c r="C624" s="5"/>
+      <c r="D624" s="5"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="C625" s="1"/>
-      <c r="D625" s="1"/>
+      <c r="C625" s="5"/>
+      <c r="D625" s="5"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="C626" s="1"/>
-      <c r="D626" s="1"/>
+      <c r="C626" s="5"/>
+      <c r="D626" s="5"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="C627" s="1"/>
-      <c r="D627" s="1"/>
+      <c r="C627" s="5"/>
+      <c r="D627" s="5"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="C628" s="1"/>
-      <c r="D628" s="1"/>
+      <c r="C628" s="5"/>
+      <c r="D628" s="5"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="C629" s="1"/>
-      <c r="D629" s="1"/>
+      <c r="C629" s="5"/>
+      <c r="D629" s="5"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="C630" s="1"/>
-      <c r="D630" s="1"/>
+      <c r="C630" s="5"/>
+      <c r="D630" s="5"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="C631" s="1"/>
-      <c r="D631" s="1"/>
+      <c r="C631" s="5"/>
+      <c r="D631" s="5"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="C632" s="1"/>
-      <c r="D632" s="1"/>
+      <c r="C632" s="5"/>
+      <c r="D632" s="5"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="C633" s="1"/>
-      <c r="D633" s="1"/>
+      <c r="C633" s="5"/>
+      <c r="D633" s="5"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="C634" s="1"/>
-      <c r="D634" s="1"/>
+      <c r="C634" s="5"/>
+      <c r="D634" s="5"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="C635" s="1"/>
-      <c r="D635" s="1"/>
+      <c r="C635" s="5"/>
+      <c r="D635" s="5"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="C636" s="1"/>
-      <c r="D636" s="1"/>
+      <c r="C636" s="5"/>
+      <c r="D636" s="5"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="C637" s="1"/>
-      <c r="D637" s="1"/>
+      <c r="C637" s="5"/>
+      <c r="D637" s="5"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="C638" s="1"/>
-      <c r="D638" s="1"/>
+      <c r="C638" s="5"/>
+      <c r="D638" s="5"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="C639" s="1"/>
-      <c r="D639" s="1"/>
+      <c r="C639" s="5"/>
+      <c r="D639" s="5"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="C640" s="1"/>
-      <c r="D640" s="1"/>
+      <c r="C640" s="5"/>
+      <c r="D640" s="5"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="C641" s="1"/>
-      <c r="D641" s="1"/>
+      <c r="C641" s="5"/>
+      <c r="D641" s="5"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="C642" s="1"/>
-      <c r="D642" s="1"/>
+      <c r="C642" s="5"/>
+      <c r="D642" s="5"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="C643" s="1"/>
-      <c r="D643" s="1"/>
+      <c r="C643" s="5"/>
+      <c r="D643" s="5"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="C644" s="1"/>
-      <c r="D644" s="1"/>
+      <c r="C644" s="5"/>
+      <c r="D644" s="5"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="C645" s="1"/>
-      <c r="D645" s="1"/>
+      <c r="C645" s="5"/>
+      <c r="D645" s="5"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="C646" s="1"/>
-      <c r="D646" s="1"/>
+      <c r="C646" s="5"/>
+      <c r="D646" s="5"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="C647" s="1"/>
-      <c r="D647" s="1"/>
+      <c r="C647" s="5"/>
+      <c r="D647" s="5"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="C648" s="1"/>
-      <c r="D648" s="1"/>
+      <c r="C648" s="5"/>
+      <c r="D648" s="5"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="C649" s="1"/>
-      <c r="D649" s="1"/>
+      <c r="C649" s="5"/>
+      <c r="D649" s="5"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="C650" s="1"/>
-      <c r="D650" s="1"/>
+      <c r="C650" s="5"/>
+      <c r="D650" s="5"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="C651" s="1"/>
-      <c r="D651" s="1"/>
+      <c r="C651" s="5"/>
+      <c r="D651" s="5"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="C652" s="1"/>
-      <c r="D652" s="1"/>
+      <c r="C652" s="5"/>
+      <c r="D652" s="5"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="C653" s="1"/>
-      <c r="D653" s="1"/>
+      <c r="C653" s="5"/>
+      <c r="D653" s="5"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="C654" s="1"/>
-      <c r="D654" s="1"/>
+      <c r="C654" s="5"/>
+      <c r="D654" s="5"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="C655" s="1"/>
-      <c r="D655" s="1"/>
+      <c r="C655" s="5"/>
+      <c r="D655" s="5"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="C656" s="1"/>
-      <c r="D656" s="1"/>
+      <c r="C656" s="5"/>
+      <c r="D656" s="5"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="C657" s="1"/>
-      <c r="D657" s="1"/>
+      <c r="C657" s="5"/>
+      <c r="D657" s="5"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="C658" s="1"/>
-      <c r="D658" s="1"/>
+      <c r="C658" s="5"/>
+      <c r="D658" s="5"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="C659" s="1"/>
-      <c r="D659" s="1"/>
+      <c r="C659" s="5"/>
+      <c r="D659" s="5"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="C660" s="1"/>
-      <c r="D660" s="1"/>
+      <c r="C660" s="5"/>
+      <c r="D660" s="5"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="C661" s="1"/>
-      <c r="D661" s="1"/>
+      <c r="C661" s="5"/>
+      <c r="D661" s="5"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="C662" s="1"/>
-      <c r="D662" s="1"/>
+      <c r="C662" s="5"/>
+      <c r="D662" s="5"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="C663" s="1"/>
-      <c r="D663" s="1"/>
+      <c r="C663" s="5"/>
+      <c r="D663" s="5"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="C664" s="1"/>
-      <c r="D664" s="1"/>
+      <c r="C664" s="5"/>
+      <c r="D664" s="5"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="C665" s="1"/>
-      <c r="D665" s="1"/>
+      <c r="C665" s="5"/>
+      <c r="D665" s="5"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="C666" s="1"/>
-      <c r="D666" s="1"/>
+      <c r="C666" s="5"/>
+      <c r="D666" s="5"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="C667" s="1"/>
-      <c r="D667" s="1"/>
+      <c r="C667" s="5"/>
+      <c r="D667" s="5"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="C668" s="1"/>
-      <c r="D668" s="1"/>
+      <c r="C668" s="5"/>
+      <c r="D668" s="5"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="C669" s="1"/>
-      <c r="D669" s="1"/>
+      <c r="C669" s="5"/>
+      <c r="D669" s="5"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="C670" s="1"/>
-      <c r="D670" s="1"/>
+      <c r="C670" s="5"/>
+      <c r="D670" s="5"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="C671" s="1"/>
-      <c r="D671" s="1"/>
+      <c r="C671" s="5"/>
+      <c r="D671" s="5"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="C672" s="1"/>
-      <c r="D672" s="1"/>
+      <c r="C672" s="5"/>
+      <c r="D672" s="5"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="C673" s="1"/>
-      <c r="D673" s="1"/>
+      <c r="C673" s="5"/>
+      <c r="D673" s="5"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="C674" s="1"/>
-      <c r="D674" s="1"/>
+      <c r="C674" s="5"/>
+      <c r="D674" s="5"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="C675" s="1"/>
-      <c r="D675" s="1"/>
+      <c r="C675" s="5"/>
+      <c r="D675" s="5"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="C676" s="1"/>
-      <c r="D676" s="1"/>
+      <c r="C676" s="5"/>
+      <c r="D676" s="5"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="C677" s="1"/>
-      <c r="D677" s="1"/>
+      <c r="C677" s="5"/>
+      <c r="D677" s="5"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="C678" s="1"/>
-      <c r="D678" s="1"/>
+      <c r="C678" s="5"/>
+      <c r="D678" s="5"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="C679" s="1"/>
-      <c r="D679" s="1"/>
+      <c r="C679" s="5"/>
+      <c r="D679" s="5"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="C680" s="1"/>
-      <c r="D680" s="1"/>
+      <c r="C680" s="5"/>
+      <c r="D680" s="5"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="C681" s="1"/>
-      <c r="D681" s="1"/>
+      <c r="C681" s="5"/>
+      <c r="D681" s="5"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="C682" s="1"/>
-      <c r="D682" s="1"/>
+      <c r="C682" s="5"/>
+      <c r="D682" s="5"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="C683" s="1"/>
-      <c r="D683" s="1"/>
+      <c r="C683" s="5"/>
+      <c r="D683" s="5"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="C684" s="1"/>
-      <c r="D684" s="1"/>
+      <c r="C684" s="5"/>
+      <c r="D684" s="5"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="C685" s="1"/>
-      <c r="D685" s="1"/>
+      <c r="C685" s="5"/>
+      <c r="D685" s="5"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="C686" s="1"/>
-      <c r="D686" s="1"/>
+      <c r="C686" s="5"/>
+      <c r="D686" s="5"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="C687" s="1"/>
-      <c r="D687" s="1"/>
+      <c r="C687" s="5"/>
+      <c r="D687" s="5"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="C688" s="1"/>
-      <c r="D688" s="1"/>
+      <c r="C688" s="5"/>
+      <c r="D688" s="5"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="C689" s="1"/>
-      <c r="D689" s="1"/>
+      <c r="C689" s="5"/>
+      <c r="D689" s="5"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="C690" s="1"/>
-      <c r="D690" s="1"/>
+      <c r="C690" s="5"/>
+      <c r="D690" s="5"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="C691" s="1"/>
-      <c r="D691" s="1"/>
+      <c r="C691" s="5"/>
+      <c r="D691" s="5"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="C692" s="1"/>
-      <c r="D692" s="1"/>
+      <c r="C692" s="5"/>
+      <c r="D692" s="5"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="C693" s="1"/>
-      <c r="D693" s="1"/>
+      <c r="C693" s="5"/>
+      <c r="D693" s="5"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="C694" s="1"/>
-      <c r="D694" s="1"/>
+      <c r="C694" s="5"/>
+      <c r="D694" s="5"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="C695" s="1"/>
-      <c r="D695" s="1"/>
+      <c r="C695" s="5"/>
+      <c r="D695" s="5"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="C696" s="1"/>
-      <c r="D696" s="1"/>
+      <c r="C696" s="5"/>
+      <c r="D696" s="5"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="C697" s="1"/>
-      <c r="D697" s="1"/>
+      <c r="C697" s="5"/>
+      <c r="D697" s="5"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="C698" s="1"/>
-      <c r="D698" s="1"/>
+      <c r="C698" s="5"/>
+      <c r="D698" s="5"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="C699" s="1"/>
-      <c r="D699" s="1"/>
+      <c r="C699" s="5"/>
+      <c r="D699" s="5"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="C700" s="1"/>
-      <c r="D700" s="1"/>
+      <c r="C700" s="5"/>
+      <c r="D700" s="5"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="C701" s="1"/>
-      <c r="D701" s="1"/>
+      <c r="C701" s="5"/>
+      <c r="D701" s="5"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="C702" s="1"/>
-      <c r="D702" s="1"/>
+      <c r="C702" s="5"/>
+      <c r="D702" s="5"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="C703" s="1"/>
-      <c r="D703" s="1"/>
+      <c r="C703" s="5"/>
+      <c r="D703" s="5"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="C704" s="1"/>
-      <c r="D704" s="1"/>
+      <c r="C704" s="5"/>
+      <c r="D704" s="5"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="C705" s="1"/>
-      <c r="D705" s="1"/>
+      <c r="C705" s="5"/>
+      <c r="D705" s="5"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="C706" s="1"/>
-      <c r="D706" s="1"/>
+      <c r="C706" s="5"/>
+      <c r="D706" s="5"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="C707" s="1"/>
-      <c r="D707" s="1"/>
+      <c r="C707" s="5"/>
+      <c r="D707" s="5"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="C708" s="1"/>
-      <c r="D708" s="1"/>
+      <c r="C708" s="5"/>
+      <c r="D708" s="5"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="C709" s="1"/>
-      <c r="D709" s="1"/>
+      <c r="C709" s="5"/>
+      <c r="D709" s="5"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="C710" s="1"/>
-      <c r="D710" s="1"/>
+      <c r="C710" s="5"/>
+      <c r="D710" s="5"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="C711" s="1"/>
-      <c r="D711" s="1"/>
+      <c r="C711" s="5"/>
+      <c r="D711" s="5"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="C712" s="1"/>
-      <c r="D712" s="1"/>
+      <c r="C712" s="5"/>
+      <c r="D712" s="5"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="C713" s="1"/>
-      <c r="D713" s="1"/>
+      <c r="C713" s="5"/>
+      <c r="D713" s="5"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="C714" s="1"/>
-      <c r="D714" s="1"/>
+      <c r="C714" s="5"/>
+      <c r="D714" s="5"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="C715" s="1"/>
-      <c r="D715" s="1"/>
+      <c r="C715" s="5"/>
+      <c r="D715" s="5"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="C716" s="1"/>
-      <c r="D716" s="1"/>
+      <c r="C716" s="5"/>
+      <c r="D716" s="5"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="C717" s="1"/>
-      <c r="D717" s="1"/>
+      <c r="C717" s="5"/>
+      <c r="D717" s="5"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="C718" s="1"/>
-      <c r="D718" s="1"/>
+      <c r="C718" s="5"/>
+      <c r="D718" s="5"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="C719" s="1"/>
-      <c r="D719" s="1"/>
+      <c r="C719" s="5"/>
+      <c r="D719" s="5"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="C720" s="1"/>
-      <c r="D720" s="1"/>
+      <c r="C720" s="5"/>
+      <c r="D720" s="5"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="C721" s="1"/>
-      <c r="D721" s="1"/>
+      <c r="C721" s="5"/>
+      <c r="D721" s="5"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="C722" s="1"/>
-      <c r="D722" s="1"/>
+      <c r="C722" s="5"/>
+      <c r="D722" s="5"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="C723" s="1"/>
-      <c r="D723" s="1"/>
+      <c r="C723" s="5"/>
+      <c r="D723" s="5"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="C724" s="1"/>
-      <c r="D724" s="1"/>
+      <c r="C724" s="5"/>
+      <c r="D724" s="5"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="C725" s="1"/>
-      <c r="D725" s="1"/>
+      <c r="C725" s="5"/>
+      <c r="D725" s="5"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="C726" s="1"/>
-      <c r="D726" s="1"/>
+      <c r="C726" s="5"/>
+      <c r="D726" s="5"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="C727" s="1"/>
-      <c r="D727" s="1"/>
+      <c r="C727" s="5"/>
+      <c r="D727" s="5"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="C728" s="1"/>
-      <c r="D728" s="1"/>
+      <c r="C728" s="5"/>
+      <c r="D728" s="5"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="C729" s="1"/>
-      <c r="D729" s="1"/>
+      <c r="C729" s="5"/>
+      <c r="D729" s="5"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="C730" s="1"/>
-      <c r="D730" s="1"/>
+      <c r="C730" s="5"/>
+      <c r="D730" s="5"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="C731" s="1"/>
-      <c r="D731" s="1"/>
+      <c r="C731" s="5"/>
+      <c r="D731" s="5"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="C732" s="1"/>
-      <c r="D732" s="1"/>
+      <c r="C732" s="5"/>
+      <c r="D732" s="5"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="C733" s="1"/>
-      <c r="D733" s="1"/>
+      <c r="C733" s="5"/>
+      <c r="D733" s="5"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="C734" s="1"/>
-      <c r="D734" s="1"/>
+      <c r="C734" s="5"/>
+      <c r="D734" s="5"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="C735" s="1"/>
-      <c r="D735" s="1"/>
+      <c r="C735" s="5"/>
+      <c r="D735" s="5"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="C736" s="1"/>
-      <c r="D736" s="1"/>
+      <c r="C736" s="5"/>
+      <c r="D736" s="5"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="C737" s="1"/>
-      <c r="D737" s="1"/>
+      <c r="C737" s="5"/>
+      <c r="D737" s="5"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="C738" s="1"/>
-      <c r="D738" s="1"/>
+      <c r="C738" s="5"/>
+      <c r="D738" s="5"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="C739" s="1"/>
-      <c r="D739" s="1"/>
+      <c r="C739" s="5"/>
+      <c r="D739" s="5"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="C740" s="1"/>
-      <c r="D740" s="1"/>
+      <c r="C740" s="5"/>
+      <c r="D740" s="5"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="C741" s="1"/>
-      <c r="D741" s="1"/>
+      <c r="C741" s="5"/>
+      <c r="D741" s="5"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="C742" s="1"/>
-      <c r="D742" s="1"/>
+      <c r="C742" s="5"/>
+      <c r="D742" s="5"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="C743" s="1"/>
-      <c r="D743" s="1"/>
+      <c r="C743" s="5"/>
+      <c r="D743" s="5"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="C744" s="1"/>
-      <c r="D744" s="1"/>
+      <c r="C744" s="5"/>
+      <c r="D744" s="5"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="C745" s="1"/>
-      <c r="D745" s="1"/>
+      <c r="C745" s="5"/>
+      <c r="D745" s="5"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="C746" s="1"/>
-      <c r="D746" s="1"/>
+      <c r="C746" s="5"/>
+      <c r="D746" s="5"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="C747" s="1"/>
-      <c r="D747" s="1"/>
+      <c r="C747" s="5"/>
+      <c r="D747" s="5"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="C748" s="1"/>
-      <c r="D748" s="1"/>
+      <c r="C748" s="5"/>
+      <c r="D748" s="5"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="C749" s="1"/>
-      <c r="D749" s="1"/>
+      <c r="C749" s="5"/>
+      <c r="D749" s="5"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="C750" s="1"/>
-      <c r="D750" s="1"/>
+      <c r="C750" s="5"/>
+      <c r="D750" s="5"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="C751" s="1"/>
-      <c r="D751" s="1"/>
+      <c r="C751" s="5"/>
+      <c r="D751" s="5"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="C752" s="1"/>
-      <c r="D752" s="1"/>
+      <c r="C752" s="5"/>
+      <c r="D752" s="5"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="C753" s="1"/>
-      <c r="D753" s="1"/>
+      <c r="C753" s="5"/>
+      <c r="D753" s="5"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="C754" s="1"/>
-      <c r="D754" s="1"/>
+      <c r="C754" s="5"/>
+      <c r="D754" s="5"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="C755" s="1"/>
-      <c r="D755" s="1"/>
+      <c r="C755" s="5"/>
+      <c r="D755" s="5"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="C756" s="1"/>
-      <c r="D756" s="1"/>
+      <c r="C756" s="5"/>
+      <c r="D756" s="5"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="C757" s="1"/>
-      <c r="D757" s="1"/>
+      <c r="C757" s="5"/>
+      <c r="D757" s="5"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="C758" s="1"/>
-      <c r="D758" s="1"/>
+      <c r="C758" s="5"/>
+      <c r="D758" s="5"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="C759" s="1"/>
-      <c r="D759" s="1"/>
+      <c r="C759" s="5"/>
+      <c r="D759" s="5"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="C760" s="1"/>
-      <c r="D760" s="1"/>
+      <c r="C760" s="5"/>
+      <c r="D760" s="5"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="C761" s="1"/>
-      <c r="D761" s="1"/>
+      <c r="C761" s="5"/>
+      <c r="D761" s="5"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="C762" s="1"/>
-      <c r="D762" s="1"/>
+      <c r="C762" s="5"/>
+      <c r="D762" s="5"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="C763" s="1"/>
-      <c r="D763" s="1"/>
+      <c r="C763" s="5"/>
+      <c r="D763" s="5"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="C764" s="1"/>
-      <c r="D764" s="1"/>
+      <c r="C764" s="5"/>
+      <c r="D764" s="5"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="C765" s="1"/>
-      <c r="D765" s="1"/>
+      <c r="C765" s="5"/>
+      <c r="D765" s="5"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="C766" s="1"/>
-      <c r="D766" s="1"/>
+      <c r="C766" s="5"/>
+      <c r="D766" s="5"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="C767" s="1"/>
-      <c r="D767" s="1"/>
+      <c r="C767" s="5"/>
+      <c r="D767" s="5"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="C768" s="1"/>
-      <c r="D768" s="1"/>
+      <c r="C768" s="5"/>
+      <c r="D768" s="5"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="C769" s="1"/>
-      <c r="D769" s="1"/>
+      <c r="C769" s="5"/>
+      <c r="D769" s="5"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="C770" s="1"/>
-      <c r="D770" s="1"/>
+      <c r="C770" s="5"/>
+      <c r="D770" s="5"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="C771" s="1"/>
-      <c r="D771" s="1"/>
+      <c r="C771" s="5"/>
+      <c r="D771" s="5"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="C772" s="1"/>
-      <c r="D772" s="1"/>
+      <c r="C772" s="5"/>
+      <c r="D772" s="5"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="C773" s="1"/>
-      <c r="D773" s="1"/>
+      <c r="C773" s="5"/>
+      <c r="D773" s="5"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="C774" s="1"/>
-      <c r="D774" s="1"/>
+      <c r="C774" s="5"/>
+      <c r="D774" s="5"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="C775" s="1"/>
-      <c r="D775" s="1"/>
+      <c r="C775" s="5"/>
+      <c r="D775" s="5"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="C776" s="1"/>
-      <c r="D776" s="1"/>
+      <c r="C776" s="5"/>
+      <c r="D776" s="5"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="C777" s="1"/>
-      <c r="D777" s="1"/>
+      <c r="C777" s="5"/>
+      <c r="D777" s="5"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="C778" s="1"/>
-      <c r="D778" s="1"/>
+      <c r="C778" s="5"/>
+      <c r="D778" s="5"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="C779" s="1"/>
-      <c r="D779" s="1"/>
+      <c r="C779" s="5"/>
+      <c r="D779" s="5"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="C780" s="1"/>
-      <c r="D780" s="1"/>
+      <c r="C780" s="5"/>
+      <c r="D780" s="5"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="C781" s="1"/>
-      <c r="D781" s="1"/>
+      <c r="C781" s="5"/>
+      <c r="D781" s="5"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="C782" s="1"/>
-      <c r="D782" s="1"/>
+      <c r="C782" s="5"/>
+      <c r="D782" s="5"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="C783" s="1"/>
-      <c r="D783" s="1"/>
+      <c r="C783" s="5"/>
+      <c r="D783" s="5"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="C784" s="1"/>
-      <c r="D784" s="1"/>
+      <c r="C784" s="5"/>
+      <c r="D784" s="5"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="C785" s="1"/>
-      <c r="D785" s="1"/>
+      <c r="C785" s="5"/>
+      <c r="D785" s="5"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="C786" s="1"/>
-      <c r="D786" s="1"/>
+      <c r="C786" s="5"/>
+      <c r="D786" s="5"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="C787" s="1"/>
-      <c r="D787" s="1"/>
+      <c r="C787" s="5"/>
+      <c r="D787" s="5"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="C788" s="1"/>
-      <c r="D788" s="1"/>
+      <c r="C788" s="5"/>
+      <c r="D788" s="5"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="C789" s="1"/>
-      <c r="D789" s="1"/>
+      <c r="C789" s="5"/>
+      <c r="D789" s="5"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="C790" s="1"/>
-      <c r="D790" s="1"/>
+      <c r="C790" s="5"/>
+      <c r="D790" s="5"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="C791" s="1"/>
-      <c r="D791" s="1"/>
+      <c r="C791" s="5"/>
+      <c r="D791" s="5"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="C792" s="1"/>
-      <c r="D792" s="1"/>
+      <c r="C792" s="5"/>
+      <c r="D792" s="5"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="C793" s="1"/>
-      <c r="D793" s="1"/>
+      <c r="C793" s="5"/>
+      <c r="D793" s="5"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="C794" s="1"/>
-      <c r="D794" s="1"/>
+      <c r="C794" s="5"/>
+      <c r="D794" s="5"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="C795" s="1"/>
-      <c r="D795" s="1"/>
+      <c r="C795" s="5"/>
+      <c r="D795" s="5"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="C796" s="1"/>
-      <c r="D796" s="1"/>
+      <c r="C796" s="5"/>
+      <c r="D796" s="5"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="C797" s="1"/>
-      <c r="D797" s="1"/>
+      <c r="C797" s="5"/>
+      <c r="D797" s="5"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="C798" s="1"/>
-      <c r="D798" s="1"/>
+      <c r="C798" s="5"/>
+      <c r="D798" s="5"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="C799" s="1"/>
-      <c r="D799" s="1"/>
+      <c r="C799" s="5"/>
+      <c r="D799" s="5"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="C800" s="1"/>
-      <c r="D800" s="1"/>
+      <c r="C800" s="5"/>
+      <c r="D800" s="5"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="C801" s="1"/>
-      <c r="D801" s="1"/>
+      <c r="C801" s="5"/>
+      <c r="D801" s="5"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="C802" s="1"/>
-      <c r="D802" s="1"/>
+      <c r="C802" s="5"/>
+      <c r="D802" s="5"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="C803" s="1"/>
-      <c r="D803" s="1"/>
+      <c r="C803" s="5"/>
+      <c r="D803" s="5"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="C804" s="1"/>
-      <c r="D804" s="1"/>
+      <c r="C804" s="5"/>
+      <c r="D804" s="5"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="C805" s="1"/>
-      <c r="D805" s="1"/>
+      <c r="C805" s="5"/>
+      <c r="D805" s="5"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="C806" s="1"/>
-      <c r="D806" s="1"/>
+      <c r="C806" s="5"/>
+      <c r="D806" s="5"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="C807" s="1"/>
-      <c r="D807" s="1"/>
+      <c r="C807" s="5"/>
+      <c r="D807" s="5"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="C808" s="1"/>
-      <c r="D808" s="1"/>
+      <c r="C808" s="5"/>
+      <c r="D808" s="5"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="C809" s="1"/>
-      <c r="D809" s="1"/>
+      <c r="C809" s="5"/>
+      <c r="D809" s="5"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="C810" s="1"/>
-      <c r="D810" s="1"/>
+      <c r="C810" s="5"/>
+      <c r="D810" s="5"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="C811" s="1"/>
-      <c r="D811" s="1"/>
+      <c r="C811" s="5"/>
+      <c r="D811" s="5"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="C812" s="1"/>
-      <c r="D812" s="1"/>
+      <c r="C812" s="5"/>
+      <c r="D812" s="5"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="C813" s="1"/>
-      <c r="D813" s="1"/>
+      <c r="C813" s="5"/>
+      <c r="D813" s="5"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="C814" s="1"/>
-      <c r="D814" s="1"/>
+      <c r="C814" s="5"/>
+      <c r="D814" s="5"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="C815" s="1"/>
-      <c r="D815" s="1"/>
+      <c r="C815" s="5"/>
+      <c r="D815" s="5"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="C816" s="1"/>
-      <c r="D816" s="1"/>
+      <c r="C816" s="5"/>
+      <c r="D816" s="5"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="C817" s="1"/>
-      <c r="D817" s="1"/>
+      <c r="C817" s="5"/>
+      <c r="D817" s="5"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="C818" s="1"/>
-      <c r="D818" s="1"/>
+      <c r="C818" s="5"/>
+      <c r="D818" s="5"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="C819" s="1"/>
-      <c r="D819" s="1"/>
+      <c r="C819" s="5"/>
+      <c r="D819" s="5"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="C820" s="1"/>
-      <c r="D820" s="1"/>
+      <c r="C820" s="5"/>
+      <c r="D820" s="5"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="C821" s="1"/>
-      <c r="D821" s="1"/>
+      <c r="C821" s="5"/>
+      <c r="D821" s="5"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="C822" s="1"/>
-      <c r="D822" s="1"/>
+      <c r="C822" s="5"/>
+      <c r="D822" s="5"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="C823" s="1"/>
-      <c r="D823" s="1"/>
+      <c r="C823" s="5"/>
+      <c r="D823" s="5"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="C824" s="1"/>
-      <c r="D824" s="1"/>
+      <c r="C824" s="5"/>
+      <c r="D824" s="5"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="C825" s="1"/>
-      <c r="D825" s="1"/>
+      <c r="C825" s="5"/>
+      <c r="D825" s="5"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="C826" s="1"/>
-      <c r="D826" s="1"/>
+      <c r="C826" s="5"/>
+      <c r="D826" s="5"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="C827" s="1"/>
-      <c r="D827" s="1"/>
+      <c r="C827" s="5"/>
+      <c r="D827" s="5"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="C828" s="1"/>
-      <c r="D828" s="1"/>
+      <c r="C828" s="5"/>
+      <c r="D828" s="5"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="C829" s="1"/>
-      <c r="D829" s="1"/>
+      <c r="C829" s="5"/>
+      <c r="D829" s="5"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="C830" s="1"/>
-      <c r="D830" s="1"/>
+      <c r="C830" s="5"/>
+      <c r="D830" s="5"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="C831" s="1"/>
-      <c r="D831" s="1"/>
+      <c r="C831" s="5"/>
+      <c r="D831" s="5"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="C832" s="1"/>
-      <c r="D832" s="1"/>
+      <c r="C832" s="5"/>
+      <c r="D832" s="5"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="C833" s="1"/>
-      <c r="D833" s="1"/>
+      <c r="C833" s="5"/>
+      <c r="D833" s="5"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="C834" s="1"/>
-      <c r="D834" s="1"/>
+      <c r="C834" s="5"/>
+      <c r="D834" s="5"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="C835" s="1"/>
-      <c r="D835" s="1"/>
+      <c r="C835" s="5"/>
+      <c r="D835" s="5"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="C836" s="1"/>
-      <c r="D836" s="1"/>
+      <c r="C836" s="5"/>
+      <c r="D836" s="5"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="C837" s="1"/>
-      <c r="D837" s="1"/>
+      <c r="C837" s="5"/>
+      <c r="D837" s="5"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="C838" s="1"/>
-      <c r="D838" s="1"/>
+      <c r="C838" s="5"/>
+      <c r="D838" s="5"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="C839" s="1"/>
-      <c r="D839" s="1"/>
+      <c r="C839" s="5"/>
+      <c r="D839" s="5"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="C840" s="1"/>
-      <c r="D840" s="1"/>
+      <c r="C840" s="5"/>
+      <c r="D840" s="5"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="C841" s="1"/>
-      <c r="D841" s="1"/>
+      <c r="C841" s="5"/>
+      <c r="D841" s="5"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="C842" s="1"/>
-      <c r="D842" s="1"/>
+      <c r="C842" s="5"/>
+      <c r="D842" s="5"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="C843" s="1"/>
-      <c r="D843" s="1"/>
+      <c r="C843" s="5"/>
+      <c r="D843" s="5"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="C844" s="1"/>
-      <c r="D844" s="1"/>
+      <c r="C844" s="5"/>
+      <c r="D844" s="5"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="C845" s="1"/>
-      <c r="D845" s="1"/>
+      <c r="C845" s="5"/>
+      <c r="D845" s="5"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="C846" s="1"/>
-      <c r="D846" s="1"/>
+      <c r="C846" s="5"/>
+      <c r="D846" s="5"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="C847" s="1"/>
-      <c r="D847" s="1"/>
+      <c r="C847" s="5"/>
+      <c r="D847" s="5"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="C848" s="1"/>
-      <c r="D848" s="1"/>
+      <c r="C848" s="5"/>
+      <c r="D848" s="5"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="C849" s="1"/>
-      <c r="D849" s="1"/>
+      <c r="C849" s="5"/>
+      <c r="D849" s="5"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="C850" s="1"/>
-      <c r="D850" s="1"/>
+      <c r="C850" s="5"/>
+      <c r="D850" s="5"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="C851" s="1"/>
-      <c r="D851" s="1"/>
+      <c r="C851" s="5"/>
+      <c r="D851" s="5"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="C852" s="1"/>
-      <c r="D852" s="1"/>
+      <c r="C852" s="5"/>
+      <c r="D852" s="5"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="C853" s="1"/>
-      <c r="D853" s="1"/>
+      <c r="C853" s="5"/>
+      <c r="D853" s="5"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="C854" s="1"/>
-      <c r="D854" s="1"/>
+      <c r="C854" s="5"/>
+      <c r="D854" s="5"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="C855" s="1"/>
-      <c r="D855" s="1"/>
+      <c r="C855" s="5"/>
+      <c r="D855" s="5"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="C856" s="1"/>
-      <c r="D856" s="1"/>
+      <c r="C856" s="5"/>
+      <c r="D856" s="5"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="C857" s="1"/>
-      <c r="D857" s="1"/>
+      <c r="C857" s="5"/>
+      <c r="D857" s="5"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="C858" s="1"/>
-      <c r="D858" s="1"/>
+      <c r="C858" s="5"/>
+      <c r="D858" s="5"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="C859" s="1"/>
-      <c r="D859" s="1"/>
+      <c r="C859" s="5"/>
+      <c r="D859" s="5"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="C860" s="1"/>
-      <c r="D860" s="1"/>
+      <c r="C860" s="5"/>
+      <c r="D860" s="5"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="C861" s="1"/>
-      <c r="D861" s="1"/>
+      <c r="C861" s="5"/>
+      <c r="D861" s="5"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="C862" s="1"/>
-      <c r="D862" s="1"/>
+      <c r="C862" s="5"/>
+      <c r="D862" s="5"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="C863" s="1"/>
-      <c r="D863" s="1"/>
+      <c r="C863" s="5"/>
+      <c r="D863" s="5"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="C864" s="1"/>
-      <c r="D864" s="1"/>
+      <c r="C864" s="5"/>
+      <c r="D864" s="5"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="C865" s="1"/>
-      <c r="D865" s="1"/>
+      <c r="C865" s="5"/>
+      <c r="D865" s="5"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="C866" s="1"/>
-      <c r="D866" s="1"/>
+      <c r="C866" s="5"/>
+      <c r="D866" s="5"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="C867" s="1"/>
-      <c r="D867" s="1"/>
+      <c r="C867" s="5"/>
+      <c r="D867" s="5"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="C868" s="1"/>
-      <c r="D868" s="1"/>
+      <c r="C868" s="5"/>
+      <c r="D868" s="5"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="C869" s="1"/>
-      <c r="D869" s="1"/>
+      <c r="C869" s="5"/>
+      <c r="D869" s="5"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="C870" s="1"/>
-      <c r="D870" s="1"/>
+      <c r="C870" s="5"/>
+      <c r="D870" s="5"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="C871" s="1"/>
-      <c r="D871" s="1"/>
+      <c r="C871" s="5"/>
+      <c r="D871" s="5"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="C872" s="1"/>
-      <c r="D872" s="1"/>
+      <c r="C872" s="5"/>
+      <c r="D872" s="5"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="C873" s="1"/>
-      <c r="D873" s="1"/>
+      <c r="C873" s="5"/>
+      <c r="D873" s="5"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="C874" s="1"/>
-      <c r="D874" s="1"/>
+      <c r="C874" s="5"/>
+      <c r="D874" s="5"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="C875" s="1"/>
-      <c r="D875" s="1"/>
+      <c r="C875" s="5"/>
+      <c r="D875" s="5"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="C876" s="1"/>
-      <c r="D876" s="1"/>
+      <c r="C876" s="5"/>
+      <c r="D876" s="5"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="C877" s="1"/>
-      <c r="D877" s="1"/>
+      <c r="C877" s="5"/>
+      <c r="D877" s="5"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="C878" s="1"/>
-      <c r="D878" s="1"/>
+      <c r="C878" s="5"/>
+      <c r="D878" s="5"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="C879" s="1"/>
-      <c r="D879" s="1"/>
+      <c r="C879" s="5"/>
+      <c r="D879" s="5"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="C880" s="1"/>
-      <c r="D880" s="1"/>
+      <c r="C880" s="5"/>
+      <c r="D880" s="5"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="C881" s="1"/>
-      <c r="D881" s="1"/>
+      <c r="C881" s="5"/>
+      <c r="D881" s="5"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="C882" s="1"/>
-      <c r="D882" s="1"/>
+      <c r="C882" s="5"/>
+      <c r="D882" s="5"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="C883" s="1"/>
-      <c r="D883" s="1"/>
+      <c r="C883" s="5"/>
+      <c r="D883" s="5"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="C884" s="1"/>
-      <c r="D884" s="1"/>
+      <c r="C884" s="5"/>
+      <c r="D884" s="5"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="C885" s="1"/>
-      <c r="D885" s="1"/>
+      <c r="C885" s="5"/>
+      <c r="D885" s="5"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="C886" s="1"/>
-      <c r="D886" s="1"/>
+      <c r="C886" s="5"/>
+      <c r="D886" s="5"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="C887" s="1"/>
-      <c r="D887" s="1"/>
+      <c r="C887" s="5"/>
+      <c r="D887" s="5"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="C888" s="1"/>
-      <c r="D888" s="1"/>
+      <c r="C888" s="5"/>
+      <c r="D888" s="5"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="C889" s="1"/>
-      <c r="D889" s="1"/>
+      <c r="C889" s="5"/>
+      <c r="D889" s="5"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="C890" s="1"/>
-      <c r="D890" s="1"/>
+      <c r="C890" s="5"/>
+      <c r="D890" s="5"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="C891" s="1"/>
-      <c r="D891" s="1"/>
+      <c r="C891" s="5"/>
+      <c r="D891" s="5"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="C892" s="1"/>
-      <c r="D892" s="1"/>
+      <c r="C892" s="5"/>
+      <c r="D892" s="5"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="C893" s="1"/>
-      <c r="D893" s="1"/>
+      <c r="C893" s="5"/>
+      <c r="D893" s="5"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="C894" s="1"/>
-      <c r="D894" s="1"/>
+      <c r="C894" s="5"/>
+      <c r="D894" s="5"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="C895" s="1"/>
-      <c r="D895" s="1"/>
+      <c r="C895" s="5"/>
+      <c r="D895" s="5"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="C896" s="1"/>
-      <c r="D896" s="1"/>
+      <c r="C896" s="5"/>
+      <c r="D896" s="5"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="C897" s="1"/>
-      <c r="D897" s="1"/>
+      <c r="C897" s="5"/>
+      <c r="D897" s="5"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="C898" s="1"/>
-      <c r="D898" s="1"/>
+      <c r="C898" s="5"/>
+      <c r="D898" s="5"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="C899" s="1"/>
-      <c r="D899" s="1"/>
+      <c r="C899" s="5"/>
+      <c r="D899" s="5"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="C900" s="1"/>
-      <c r="D900" s="1"/>
+      <c r="C900" s="5"/>
+      <c r="D900" s="5"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="C901" s="1"/>
-      <c r="D901" s="1"/>
+      <c r="C901" s="5"/>
+      <c r="D901" s="5"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="C902" s="1"/>
-      <c r="D902" s="1"/>
+      <c r="C902" s="5"/>
+      <c r="D902" s="5"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="C903" s="1"/>
-      <c r="D903" s="1"/>
+      <c r="C903" s="5"/>
+      <c r="D903" s="5"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="C904" s="1"/>
-      <c r="D904" s="1"/>
+      <c r="C904" s="5"/>
+      <c r="D904" s="5"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="C905" s="1"/>
-      <c r="D905" s="1"/>
+      <c r="C905" s="5"/>
+      <c r="D905" s="5"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="C906" s="1"/>
-      <c r="D906" s="1"/>
+      <c r="C906" s="5"/>
+      <c r="D906" s="5"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="C907" s="1"/>
-      <c r="D907" s="1"/>
+      <c r="C907" s="5"/>
+      <c r="D907" s="5"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="C908" s="1"/>
-      <c r="D908" s="1"/>
+      <c r="C908" s="5"/>
+      <c r="D908" s="5"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="C909" s="1"/>
-      <c r="D909" s="1"/>
+      <c r="C909" s="5"/>
+      <c r="D909" s="5"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="C910" s="1"/>
-      <c r="D910" s="1"/>
+      <c r="C910" s="5"/>
+      <c r="D910" s="5"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="C911" s="1"/>
-      <c r="D911" s="1"/>
+      <c r="C911" s="5"/>
+      <c r="D911" s="5"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="C912" s="1"/>
-      <c r="D912" s="1"/>
+      <c r="C912" s="5"/>
+      <c r="D912" s="5"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="C913" s="1"/>
-      <c r="D913" s="1"/>
+      <c r="C913" s="5"/>
+      <c r="D913" s="5"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="C914" s="1"/>
-      <c r="D914" s="1"/>
+      <c r="C914" s="5"/>
+      <c r="D914" s="5"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="C915" s="1"/>
-      <c r="D915" s="1"/>
+      <c r="C915" s="5"/>
+      <c r="D915" s="5"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="C916" s="1"/>
-      <c r="D916" s="1"/>
+      <c r="C916" s="5"/>
+      <c r="D916" s="5"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="C917" s="1"/>
-      <c r="D917" s="1"/>
+      <c r="C917" s="5"/>
+      <c r="D917" s="5"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="C918" s="1"/>
-      <c r="D918" s="1"/>
+      <c r="C918" s="5"/>
+      <c r="D918" s="5"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="C919" s="1"/>
-      <c r="D919" s="1"/>
+      <c r="C919" s="5"/>
+      <c r="D919" s="5"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="C920" s="1"/>
-      <c r="D920" s="1"/>
+      <c r="C920" s="5"/>
+      <c r="D920" s="5"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="C921" s="1"/>
-      <c r="D921" s="1"/>
+      <c r="C921" s="5"/>
+      <c r="D921" s="5"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="C922" s="1"/>
-      <c r="D922" s="1"/>
+      <c r="C922" s="5"/>
+      <c r="D922" s="5"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="C923" s="1"/>
-      <c r="D923" s="1"/>
+      <c r="C923" s="5"/>
+      <c r="D923" s="5"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="C924" s="1"/>
-      <c r="D924" s="1"/>
+      <c r="C924" s="5"/>
+      <c r="D924" s="5"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="C925" s="1"/>
-      <c r="D925" s="1"/>
+      <c r="C925" s="5"/>
+      <c r="D925" s="5"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="C926" s="1"/>
-      <c r="D926" s="1"/>
+      <c r="C926" s="5"/>
+      <c r="D926" s="5"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="C927" s="1"/>
-      <c r="D927" s="1"/>
+      <c r="C927" s="5"/>
+      <c r="D927" s="5"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="C928" s="1"/>
-      <c r="D928" s="1"/>
+      <c r="C928" s="5"/>
+      <c r="D928" s="5"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="C929" s="1"/>
-      <c r="D929" s="1"/>
+      <c r="C929" s="5"/>
+      <c r="D929" s="5"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="C930" s="1"/>
-      <c r="D930" s="1"/>
+      <c r="C930" s="5"/>
+      <c r="D930" s="5"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="C931" s="1"/>
-      <c r="D931" s="1"/>
+      <c r="C931" s="5"/>
+      <c r="D931" s="5"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="C932" s="1"/>
-      <c r="D932" s="1"/>
+      <c r="C932" s="5"/>
+      <c r="D932" s="5"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="C933" s="1"/>
-      <c r="D933" s="1"/>
+      <c r="C933" s="5"/>
+      <c r="D933" s="5"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="C934" s="1"/>
-      <c r="D934" s="1"/>
+      <c r="C934" s="5"/>
+      <c r="D934" s="5"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="C935" s="1"/>
-      <c r="D935" s="1"/>
+      <c r="C935" s="5"/>
+      <c r="D935" s="5"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="C936" s="1"/>
-      <c r="D936" s="1"/>
+      <c r="C936" s="5"/>
+      <c r="D936" s="5"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="C937" s="1"/>
-      <c r="D937" s="1"/>
+      <c r="C937" s="5"/>
+      <c r="D937" s="5"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="C938" s="1"/>
-      <c r="D938" s="1"/>
+      <c r="C938" s="5"/>
+      <c r="D938" s="5"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="C939" s="1"/>
-      <c r="D939" s="1"/>
+      <c r="C939" s="5"/>
+      <c r="D939" s="5"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="C940" s="1"/>
-      <c r="D940" s="1"/>
+      <c r="C940" s="5"/>
+      <c r="D940" s="5"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="C941" s="1"/>
-      <c r="D941" s="1"/>
+      <c r="C941" s="5"/>
+      <c r="D941" s="5"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="C942" s="1"/>
-      <c r="D942" s="1"/>
+      <c r="C942" s="5"/>
+      <c r="D942" s="5"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="C943" s="1"/>
-      <c r="D943" s="1"/>
+      <c r="C943" s="5"/>
+      <c r="D943" s="5"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="C944" s="1"/>
-      <c r="D944" s="1"/>
+      <c r="C944" s="5"/>
+      <c r="D944" s="5"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="C945" s="1"/>
-      <c r="D945" s="1"/>
+      <c r="C945" s="5"/>
+      <c r="D945" s="5"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="C946" s="1"/>
-      <c r="D946" s="1"/>
+      <c r="C946" s="5"/>
+      <c r="D946" s="5"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="C947" s="1"/>
-      <c r="D947" s="1"/>
+      <c r="C947" s="5"/>
+      <c r="D947" s="5"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="C948" s="1"/>
-      <c r="D948" s="1"/>
+      <c r="C948" s="5"/>
+      <c r="D948" s="5"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="C949" s="1"/>
-      <c r="D949" s="1"/>
+      <c r="C949" s="5"/>
+      <c r="D949" s="5"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="C950" s="1"/>
-      <c r="D950" s="1"/>
+      <c r="C950" s="5"/>
+      <c r="D950" s="5"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="C951" s="1"/>
-      <c r="D951" s="1"/>
+      <c r="C951" s="5"/>
+      <c r="D951" s="5"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="C952" s="1"/>
-      <c r="D952" s="1"/>
+      <c r="C952" s="5"/>
+      <c r="D952" s="5"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="C953" s="1"/>
-      <c r="D953" s="1"/>
+      <c r="C953" s="5"/>
+      <c r="D953" s="5"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="C954" s="1"/>
-      <c r="D954" s="1"/>
+      <c r="C954" s="5"/>
+      <c r="D954" s="5"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="C955" s="1"/>
-      <c r="D955" s="1"/>
+      <c r="C955" s="5"/>
+      <c r="D955" s="5"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="C956" s="1"/>
-      <c r="D956" s="1"/>
+      <c r="C956" s="5"/>
+      <c r="D956" s="5"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="C957" s="1"/>
-      <c r="D957" s="1"/>
+      <c r="C957" s="5"/>
+      <c r="D957" s="5"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="C958" s="1"/>
-      <c r="D958" s="1"/>
+      <c r="C958" s="5"/>
+      <c r="D958" s="5"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="C959" s="1"/>
-      <c r="D959" s="1"/>
+      <c r="C959" s="5"/>
+      <c r="D959" s="5"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="C960" s="1"/>
-      <c r="D960" s="1"/>
+      <c r="C960" s="5"/>
+      <c r="D960" s="5"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="C961" s="1"/>
-      <c r="D961" s="1"/>
+      <c r="C961" s="5"/>
+      <c r="D961" s="5"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="C962" s="1"/>
-      <c r="D962" s="1"/>
+      <c r="C962" s="5"/>
+      <c r="D962" s="5"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="C963" s="1"/>
-      <c r="D963" s="1"/>
+      <c r="C963" s="5"/>
+      <c r="D963" s="5"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="C964" s="1"/>
-      <c r="D964" s="1"/>
+      <c r="C964" s="5"/>
+      <c r="D964" s="5"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="C965" s="1"/>
-      <c r="D965" s="1"/>
+      <c r="C965" s="5"/>
+      <c r="D965" s="5"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="C966" s="1"/>
-      <c r="D966" s="1"/>
+      <c r="C966" s="5"/>
+      <c r="D966" s="5"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="C967" s="1"/>
-      <c r="D967" s="1"/>
+      <c r="C967" s="5"/>
+      <c r="D967" s="5"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="C968" s="1"/>
-      <c r="D968" s="1"/>
+      <c r="C968" s="5"/>
+      <c r="D968" s="5"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="C969" s="1"/>
-      <c r="D969" s="1"/>
+      <c r="C969" s="5"/>
+      <c r="D969" s="5"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="C970" s="1"/>
-      <c r="D970" s="1"/>
+      <c r="C970" s="5"/>
+      <c r="D970" s="5"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="C971" s="1"/>
-      <c r="D971" s="1"/>
+      <c r="C971" s="5"/>
+      <c r="D971" s="5"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="C972" s="1"/>
-      <c r="D972" s="1"/>
+      <c r="C972" s="5"/>
+      <c r="D972" s="5"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="C973" s="1"/>
-      <c r="D973" s="1"/>
+      <c r="C973" s="5"/>
+      <c r="D973" s="5"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="C974" s="1"/>
-      <c r="D974" s="1"/>
+      <c r="C974" s="5"/>
+      <c r="D974" s="5"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="C975" s="1"/>
-      <c r="D975" s="1"/>
+      <c r="C975" s="5"/>
+      <c r="D975" s="5"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="C976" s="1"/>
-      <c r="D976" s="1"/>
+      <c r="C976" s="5"/>
+      <c r="D976" s="5"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="C977" s="1"/>
-      <c r="D977" s="1"/>
+      <c r="C977" s="5"/>
+      <c r="D977" s="5"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="C978" s="1"/>
-      <c r="D978" s="1"/>
+      <c r="C978" s="5"/>
+      <c r="D978" s="5"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="C979" s="1"/>
-      <c r="D979" s="1"/>
+      <c r="C979" s="5"/>
+      <c r="D979" s="5"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="C980" s="1"/>
-      <c r="D980" s="1"/>
+      <c r="C980" s="5"/>
+      <c r="D980" s="5"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="C981" s="1"/>
-      <c r="D981" s="1"/>
+      <c r="C981" s="5"/>
+      <c r="D981" s="5"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="C982" s="1"/>
-      <c r="D982" s="1"/>
+      <c r="C982" s="5"/>
+      <c r="D982" s="5"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="C983" s="1"/>
-      <c r="D983" s="1"/>
+      <c r="C983" s="5"/>
+      <c r="D983" s="5"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="C984" s="1"/>
-      <c r="D984" s="1"/>
+      <c r="C984" s="5"/>
+      <c r="D984" s="5"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="C985" s="1"/>
-      <c r="D985" s="1"/>
+      <c r="C985" s="5"/>
+      <c r="D985" s="5"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="C986" s="1"/>
-      <c r="D986" s="1"/>
+      <c r="C986" s="5"/>
+      <c r="D986" s="5"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="C987" s="1"/>
-      <c r="D987" s="1"/>
+      <c r="C987" s="5"/>
+      <c r="D987" s="5"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="C988" s="1"/>
-      <c r="D988" s="1"/>
+      <c r="C988" s="5"/>
+      <c r="D988" s="5"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="C989" s="1"/>
-      <c r="D989" s="1"/>
+      <c r="C989" s="5"/>
+      <c r="D989" s="5"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="C990" s="1"/>
-      <c r="D990" s="1"/>
+      <c r="C990" s="5"/>
+      <c r="D990" s="5"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="C991" s="1"/>
-      <c r="D991" s="1"/>
+      <c r="C991" s="5"/>
+      <c r="D991" s="5"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="C992" s="1"/>
-      <c r="D992" s="1"/>
+      <c r="C992" s="5"/>
+      <c r="D992" s="5"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="C993" s="1"/>
-      <c r="D993" s="1"/>
+      <c r="C993" s="5"/>
+      <c r="D993" s="5"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="C994" s="1"/>
-      <c r="D994" s="1"/>
+      <c r="C994" s="5"/>
+      <c r="D994" s="5"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
+      <c r="C995" s="5"/>
+      <c r="D995" s="5"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
+      <c r="C996" s="5"/>
+      <c r="D996" s="5"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
+      <c r="C997" s="5"/>
+      <c r="D997" s="5"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
+      <c r="C998" s="5"/>
+      <c r="D998" s="5"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
+      <c r="C999" s="5"/>
+      <c r="D999" s="5"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
+      <c r="C1000" s="5"/>
+      <c r="D1000" s="5"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="C1001" s="1"/>
-      <c r="D1001" s="1"/>
+      <c r="C1001" s="5"/>
+      <c r="D1001" s="5"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
-      <c r="C1002" s="1"/>
-      <c r="D1002" s="1"/>
+      <c r="C1002" s="5"/>
+      <c r="D1002" s="5"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
-      <c r="C1003" s="1"/>
-      <c r="D1003" s="1"/>
+      <c r="C1003" s="5"/>
+      <c r="D1003" s="5"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
-      <c r="C1004" s="1"/>
-      <c r="D1004" s="1"/>
+      <c r="C1004" s="5"/>
+      <c r="D1004" s="5"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
-      <c r="C1005" s="1"/>
-      <c r="D1005" s="1"/>
+      <c r="C1005" s="5"/>
+      <c r="D1005" s="5"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
-      <c r="C1006" s="1"/>
-      <c r="D1006" s="1"/>
+      <c r="C1006" s="5"/>
+      <c r="D1006" s="5"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
-      <c r="C1007" s="1"/>
-      <c r="D1007" s="1"/>
+      <c r="C1007" s="5"/>
+      <c r="D1007" s="5"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
-      <c r="C1008" s="1"/>
-      <c r="D1008" s="1"/>
+      <c r="C1008" s="5"/>
+      <c r="D1008" s="5"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
-      <c r="C1009" s="1"/>
-      <c r="D1009" s="1"/>
+      <c r="C1009" s="5"/>
+      <c r="D1009" s="5"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
-      <c r="C1010" s="1"/>
-      <c r="D1010" s="1"/>
+      <c r="C1010" s="5"/>
+      <c r="D1010" s="5"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
-      <c r="C1011" s="1"/>
-      <c r="D1011" s="1"/>
+      <c r="C1011" s="5"/>
+      <c r="D1011" s="5"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
-      <c r="C1012" s="1"/>
-      <c r="D1012" s="1"/>
+      <c r="C1012" s="5"/>
+      <c r="D1012" s="5"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
-      <c r="C1013" s="1"/>
-      <c r="D1013" s="1"/>
+      <c r="C1013" s="5"/>
+      <c r="D1013" s="5"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
-      <c r="C1014" s="1"/>
-      <c r="D1014" s="1"/>
+      <c r="C1014" s="5"/>
+      <c r="D1014" s="5"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
-      <c r="C1015" s="1"/>
-      <c r="D1015" s="1"/>
+      <c r="C1015" s="5"/>
+      <c r="D1015" s="5"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
-      <c r="C1016" s="1"/>
-      <c r="D1016" s="1"/>
+      <c r="C1016" s="5"/>
+      <c r="D1016" s="5"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
-      <c r="C1017" s="1"/>
-      <c r="D1017" s="1"/>
+      <c r="C1017" s="5"/>
+      <c r="D1017" s="5"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
-      <c r="C1018" s="1"/>
-      <c r="D1018" s="1"/>
+      <c r="C1018" s="5"/>
+      <c r="D1018" s="5"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
-      <c r="C1019" s="1"/>
-      <c r="D1019" s="1"/>
+      <c r="C1019" s="5"/>
+      <c r="D1019" s="5"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
-      <c r="C1020" s="1"/>
-      <c r="D1020" s="1"/>
+      <c r="C1020" s="5"/>
+      <c r="D1020" s="5"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
-      <c r="C1021" s="1"/>
-      <c r="D1021" s="1"/>
+      <c r="C1021" s="5"/>
+      <c r="D1021" s="5"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
-      <c r="C1022" s="1"/>
-      <c r="D1022" s="1"/>
+      <c r="C1022" s="5"/>
+      <c r="D1022" s="5"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
-      <c r="C1023" s="1"/>
-      <c r="D1023" s="1"/>
+      <c r="C1023" s="5"/>
+      <c r="D1023" s="5"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
-      <c r="C1024" s="1"/>
-      <c r="D1024" s="1"/>
+      <c r="C1024" s="5"/>
+      <c r="D1024" s="5"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
-      <c r="C1025" s="1"/>
-      <c r="D1025" s="1"/>
+      <c r="C1025" s="5"/>
+      <c r="D1025" s="5"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1">
-      <c r="C1026" s="1"/>
-      <c r="D1026" s="1"/>
+      <c r="C1026" s="5"/>
+      <c r="D1026" s="5"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1">
-      <c r="C1027" s="1"/>
-      <c r="D1027" s="1"/>
+      <c r="C1027" s="5"/>
+      <c r="D1027" s="5"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5843,185 +5843,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D11" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C12" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>62</v>
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7031,40 +7031,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>39</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="4">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>65</v>
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="239">
   <si>
     <t>form_title</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -39,12 +45,6 @@
     <t>referral_follow_up</t>
   </si>
   <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -87,51 +87,123 @@
     <t>Sina pesa</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>did_not_want</t>
   </si>
   <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
     <t>I did not want to go</t>
   </si>
   <si>
+    <t>read_only</t>
+  </si>
+  <si>
     <t>Sikutaka kwenda</t>
   </si>
   <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
     <t>no_permission</t>
   </si>
   <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
     <t>I did not have permission to go</t>
   </si>
   <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
     <t>Sikupewa ruhusa ya kwenda</t>
   </si>
   <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
     <t>other</t>
   </si>
   <si>
+    <t>inputs</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
     <t>Nyenginezo</t>
   </si>
   <si>
+    <t>pages</t>
+  </si>
+  <si>
     <t>reason_didnt_get_svc</t>
   </si>
   <si>
-    <t>pages</t>
+    <t>./source = 'user'</t>
   </si>
   <si>
     <t>data</t>
   </si>
   <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>source_form</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
     <t>too_many_people</t>
   </si>
   <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
     <t>There were too many people</t>
   </si>
   <si>
     <t>Kulikuwa na watu wengi</t>
   </si>
   <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
     <t>services_not_offered</t>
   </si>
   <si>
@@ -141,25 +213,22 @@
     <t>Huduma nilizotaka hazikuwepo.</t>
   </si>
   <si>
+    <t>refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
     <t>no_service_provider_available</t>
   </si>
   <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
     <t>No service providers were available</t>
   </si>
   <si>
     <t>Hakukuwa na mtoa huduma</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
+    <t>refer_muac_flag</t>
   </si>
   <si>
     <t>was_asked_to_pay</t>
@@ -168,84 +237,18 @@
     <t>I was asked to pay for services</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
     <t>Walitaka nilipie huduma</t>
   </si>
   <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
     <t>was_treated_badly</t>
   </si>
   <si>
-    <t>hint::en</t>
-  </si>
-  <si>
     <t>Health workers treated me badly</t>
   </si>
   <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
     <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>source_form</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>last_visit_date</t>
-  </si>
-  <si>
-    <t>refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t>refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_muac_flag</t>
-  </si>
-  <si>
     <t>refer_palm_pallor_flag</t>
   </si>
   <si>
@@ -337,6 +340,9 @@
   </si>
   <si>
     <t>../inputs/refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_secondary_neonatal_danger_sign_flag</t>
   </si>
   <si>
     <t>../inputs/refer_child_danger_sign_flag</t>
@@ -523,6 +529,18 @@
   </si>
   <si>
     <t>../../inputs/refer_neonatal_danger_sign_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address a neonatal danger sign.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za mtoto mchanga.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_secondary_neonatal_danger_sign_flag = 1</t>
   </si>
   <si>
     <t>reason_refer_child_danger_sign_flag</t>
@@ -737,10 +755,10 @@
       <sz val="10.0"/>
       <name val="Arial"/>
     </font>
+    <font/>
     <font>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
@@ -778,28 +796,28 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -838,4990 +856,5034 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="17" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="14.43"/>
+    <col customWidth="1" min="2" max="2" width="43.57"/>
+    <col customWidth="1" min="3" max="17" width="14.43"/>
     <col customWidth="1" min="18" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="D2" s="2"/>
+      <c r="F2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="5" t="s">
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="F2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="5"/>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="5"/>
+      <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="5"/>
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="5"/>
+      <c r="C13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="5"/>
+      <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="5"/>
+      <c r="C15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="5"/>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="G21" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="5"/>
+      <c r="C23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="5"/>
+      <c r="C24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="L27" s="5" t="s">
+      <c r="B28" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="L28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="L28" s="5" t="s">
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="L29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="L29" s="5" t="s">
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="L30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="L30" s="5" t="s">
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="L31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="L31" s="7" t="s">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="L32" t="s">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="L32" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="A33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
       <c r="L33" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
       <c r="L34" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="L35" t="s">
+      <c r="A35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="L35" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="A36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
       <c r="L36" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="A37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
       <c r="L37" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+      <c r="A38" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
       <c r="L38" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="A39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="L39" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="L39" s="5" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="L40" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="L40" s="5" t="s">
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="L41" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="8"/>
-      <c r="D41" s="9"/>
-      <c r="L41" s="4" t="s">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="L42" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="L42" s="4" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
-      <c r="L43" s="4" t="s">
-        <v>120</v>
+      <c r="L43" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>121</v>
+      <c r="A44" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="9"/>
-      <c r="L44" s="10" t="s">
-        <v>122</v>
+      <c r="L44" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>123</v>
+      <c r="A45" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
-      <c r="L45" s="11" t="s">
-        <v>124</v>
+      <c r="L45" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>125</v>
+      <c r="A46" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9"/>
-      <c r="L46" s="11" t="s">
-        <v>126</v>
+      <c r="L46" s="10" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>127</v>
+      <c r="A47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9"/>
       <c r="L47" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>129</v>
+      <c r="A48" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9"/>
-      <c r="L48" s="14" t="s">
-        <v>130</v>
+      <c r="L48" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>131</v>
+      <c r="A49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
-      <c r="L49" s="14" t="s">
-        <v>132</v>
+      <c r="L49" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>95</v>
+      <c r="A50" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
       <c r="L50" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="4" t="s">
-        <v>95</v>
+      <c r="A51" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
       <c r="L51" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9"/>
+      <c r="L52" s="14" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" s="4" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
+      <c r="L53" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="9" t="s">
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="C54" s="8" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="4" t="s">
+      <c r="D54" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C53" s="4" t="s">
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="B55" s="6" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B54" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D55" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="4" t="s">
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="4" t="s">
+      <c r="C56" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D56" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D55" s="4" t="s">
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B56" s="4" t="s">
+      <c r="C57" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D57" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D56" s="4" t="s">
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="A59" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="D60" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="G60" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="C61" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D61" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D60" s="7" t="s">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F60" t="s">
+      <c r="C62" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B61" s="5" t="s">
+      <c r="D62" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="F62" t="s">
         <v>164</v>
       </c>
-      <c r="D61" s="7" t="s">
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F61" t="s">
+      <c r="C63" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="D63" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="F63" t="s">
         <v>168</v>
       </c>
-      <c r="D62" s="7" t="s">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F62" t="s">
+      <c r="C64" s="6" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="D64" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D63" s="7" t="s">
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F63" t="s">
+      <c r="C65" s="7" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" s="5" t="s">
+      <c r="D65" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="F65" t="s">
         <v>176</v>
       </c>
-      <c r="D64" s="7" t="s">
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F64" t="s">
+      <c r="C66" s="7" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="D66" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="F66" t="s">
         <v>180</v>
       </c>
-      <c r="D65" s="7" t="s">
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F65" t="s">
+      <c r="C67" s="7" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="D67" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="F67" t="s">
         <v>184</v>
       </c>
-      <c r="D66" s="7" t="s">
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F66" t="s">
+      <c r="C68" s="7" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="5" t="s">
+      <c r="D68" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="F68" t="s">
         <v>188</v>
       </c>
-      <c r="C67" s="7" t="s">
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="D69" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F69" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F69" s="5"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="5"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C72" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="D72" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="C73" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C72" s="7" t="s">
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="B74" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5" t="s">
+      <c r="D74" s="7" t="s">
         <v>208</v>
       </c>
+      <c r="E74" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F75" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B75" s="5" t="s">
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E75" s="5" t="s">
+      <c r="C78" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C76" s="7" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D76" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>223</v>
-      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="L81" s="7" t="s">
+      <c r="D82" s="7" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B82" s="7" t="s">
+      <c r="E82" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C83" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D83" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E82" s="7"/>
-      <c r="F82" t="s">
+      <c r="F83" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-    </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" t="s">
-        <v>95</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="A84" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="L85" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="L84" s="7" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B86" s="5" t="s">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="L86">
+      <c r="C85" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E85" s="7"/>
+      <c r="F85" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" ht="12.75" customHeight="1">
+      <c r="A88" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="L88" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" ht="12.75" customHeight="1">
+      <c r="A89" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="L89">
         <v>3.0</v>
       </c>
     </row>
-    <row r="87" ht="12.75" customHeight="1">
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-    </row>
-    <row r="88" ht="12.75" customHeight="1">
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-    </row>
-    <row r="89" ht="12.75" customHeight="1">
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-    </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="5"/>
-      <c r="D125" s="5"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="5"/>
-      <c r="D128" s="5"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="5"/>
-      <c r="D130" s="5"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="C131" s="5"/>
-      <c r="D131" s="5"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="C132" s="5"/>
-      <c r="D132" s="5"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="5"/>
-      <c r="D133" s="5"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="C134" s="5"/>
-      <c r="D134" s="5"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="C135" s="5"/>
-      <c r="D135" s="5"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="5"/>
-      <c r="D136" s="5"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="5"/>
-      <c r="D137" s="5"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="5"/>
-      <c r="D138" s="5"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="C139" s="5"/>
-      <c r="D139" s="5"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="5"/>
-      <c r="D141" s="5"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="5"/>
-      <c r="D142" s="5"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="C143" s="5"/>
-      <c r="D143" s="5"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="5"/>
-      <c r="D144" s="5"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="C145" s="5"/>
-      <c r="D145" s="5"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="5"/>
-      <c r="D146" s="5"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="C147" s="5"/>
-      <c r="D147" s="5"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="C151" s="5"/>
-      <c r="D151" s="5"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="C153" s="5"/>
-      <c r="D153" s="5"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="5"/>
-      <c r="D154" s="5"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="C157" s="5"/>
-      <c r="D157" s="5"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="5"/>
-      <c r="D158" s="5"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="C159" s="5"/>
-      <c r="D159" s="5"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="5"/>
-      <c r="D160" s="5"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="C161" s="5"/>
-      <c r="D161" s="5"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="5"/>
-      <c r="D162" s="5"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="C163" s="5"/>
-      <c r="D163" s="5"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="5"/>
-      <c r="D164" s="5"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="5"/>
-      <c r="D165" s="5"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="5"/>
-      <c r="D166" s="5"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="C167" s="5"/>
-      <c r="D167" s="5"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="C168" s="5"/>
-      <c r="D168" s="5"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="5"/>
-      <c r="D169" s="5"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="5"/>
-      <c r="D170" s="5"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="C171" s="5"/>
-      <c r="D171" s="5"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="5"/>
-      <c r="D172" s="5"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="5"/>
-      <c r="D173" s="5"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="C174" s="5"/>
-      <c r="D174" s="5"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="C177" s="5"/>
-      <c r="D177" s="5"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="5"/>
-      <c r="D178" s="5"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="C179" s="5"/>
-      <c r="D179" s="5"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="C180" s="5"/>
-      <c r="D180" s="5"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="5"/>
-      <c r="D181" s="5"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="5"/>
-      <c r="D182" s="5"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="C183" s="5"/>
-      <c r="D183" s="5"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="5"/>
-      <c r="D184" s="5"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="C185" s="5"/>
-      <c r="D185" s="5"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="5"/>
-      <c r="D186" s="5"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="C187" s="5"/>
-      <c r="D187" s="5"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="5"/>
-      <c r="D188" s="5"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="5"/>
-      <c r="D189" s="5"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="5"/>
-      <c r="D190" s="5"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="C191" s="5"/>
-      <c r="D191" s="5"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="C192" s="5"/>
-      <c r="D192" s="5"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="5"/>
-      <c r="D193" s="5"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="5"/>
-      <c r="D194" s="5"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="C195" s="5"/>
-      <c r="D195" s="5"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="5"/>
-      <c r="D196" s="5"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="5"/>
-      <c r="D197" s="5"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="5"/>
-      <c r="D198" s="5"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="C199" s="5"/>
-      <c r="D199" s="5"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="5"/>
-      <c r="D200" s="5"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="5"/>
-      <c r="D201" s="5"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="C202" s="5"/>
-      <c r="D202" s="5"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="C206" s="5"/>
-      <c r="D206" s="5"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="C207" s="5"/>
-      <c r="D207" s="5"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="C209" s="5"/>
-      <c r="D209" s="5"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="C210" s="5"/>
-      <c r="D210" s="5"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="C212" s="5"/>
-      <c r="D212" s="5"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="C213" s="5"/>
-      <c r="D213" s="5"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="C215" s="5"/>
-      <c r="D215" s="5"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="5"/>
-      <c r="D216" s="5"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="5"/>
-      <c r="D217" s="5"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="C218" s="5"/>
-      <c r="D218" s="5"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="5"/>
-      <c r="D221" s="5"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="C222" s="5"/>
-      <c r="D222" s="5"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="C225" s="5"/>
-      <c r="D225" s="5"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="C227" s="5"/>
-      <c r="D227" s="5"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="C229" s="5"/>
-      <c r="D229" s="5"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="C230" s="5"/>
-      <c r="D230" s="5"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="C231" s="5"/>
-      <c r="D231" s="5"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="C233" s="5"/>
-      <c r="D233" s="5"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="C234" s="5"/>
-      <c r="D234" s="5"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="C235" s="5"/>
-      <c r="D235" s="5"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="C236" s="5"/>
-      <c r="D236" s="5"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="C237" s="5"/>
-      <c r="D237" s="5"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="C239" s="5"/>
-      <c r="D239" s="5"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="C241" s="5"/>
-      <c r="D241" s="5"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="C242" s="5"/>
-      <c r="D242" s="5"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="C243" s="5"/>
-      <c r="D243" s="5"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="C244" s="5"/>
-      <c r="D244" s="5"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="C245" s="5"/>
-      <c r="D245" s="5"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="C246" s="5"/>
-      <c r="D246" s="5"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="C247" s="5"/>
-      <c r="D247" s="5"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="C248" s="5"/>
-      <c r="D248" s="5"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="C249" s="5"/>
-      <c r="D249" s="5"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="C250" s="5"/>
-      <c r="D250" s="5"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="C251" s="5"/>
-      <c r="D251" s="5"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="C252" s="5"/>
-      <c r="D252" s="5"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="C253" s="5"/>
-      <c r="D253" s="5"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="C255" s="5"/>
-      <c r="D255" s="5"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="C256" s="5"/>
-      <c r="D256" s="5"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="C257" s="5"/>
-      <c r="D257" s="5"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="C258" s="5"/>
-      <c r="D258" s="5"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="C259" s="5"/>
-      <c r="D259" s="5"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="C260" s="5"/>
-      <c r="D260" s="5"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="C261" s="5"/>
-      <c r="D261" s="5"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="C262" s="5"/>
-      <c r="D262" s="5"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="C263" s="5"/>
-      <c r="D263" s="5"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="C264" s="5"/>
-      <c r="D264" s="5"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="C265" s="5"/>
-      <c r="D265" s="5"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="C266" s="5"/>
-      <c r="D266" s="5"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="C267" s="5"/>
-      <c r="D267" s="5"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="C268" s="5"/>
-      <c r="D268" s="5"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="C269" s="5"/>
-      <c r="D269" s="5"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="C270" s="5"/>
-      <c r="D270" s="5"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="C271" s="5"/>
-      <c r="D271" s="5"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="C272" s="5"/>
-      <c r="D272" s="5"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="C273" s="5"/>
-      <c r="D273" s="5"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="C274" s="5"/>
-      <c r="D274" s="5"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="C275" s="5"/>
-      <c r="D275" s="5"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="C276" s="5"/>
-      <c r="D276" s="5"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="C277" s="5"/>
-      <c r="D277" s="5"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="C278" s="5"/>
-      <c r="D278" s="5"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="C279" s="5"/>
-      <c r="D279" s="5"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="C280" s="5"/>
-      <c r="D280" s="5"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="C281" s="5"/>
-      <c r="D281" s="5"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="C282" s="5"/>
-      <c r="D282" s="5"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="C283" s="5"/>
-      <c r="D283" s="5"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="C284" s="5"/>
-      <c r="D284" s="5"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="C285" s="5"/>
-      <c r="D285" s="5"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="C286" s="5"/>
-      <c r="D286" s="5"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="C287" s="5"/>
-      <c r="D287" s="5"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="C288" s="5"/>
-      <c r="D288" s="5"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="C289" s="5"/>
-      <c r="D289" s="5"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="C290" s="5"/>
-      <c r="D290" s="5"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="C291" s="5"/>
-      <c r="D291" s="5"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="C292" s="5"/>
-      <c r="D292" s="5"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="C293" s="5"/>
-      <c r="D293" s="5"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="5"/>
-      <c r="D294" s="5"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="C295" s="5"/>
-      <c r="D295" s="5"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="C296" s="5"/>
-      <c r="D296" s="5"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="C297" s="5"/>
-      <c r="D297" s="5"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="C298" s="5"/>
-      <c r="D298" s="5"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="C299" s="5"/>
-      <c r="D299" s="5"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="C300" s="5"/>
-      <c r="D300" s="5"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="C301" s="5"/>
-      <c r="D301" s="5"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="C302" s="5"/>
-      <c r="D302" s="5"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="C303" s="5"/>
-      <c r="D303" s="5"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="C304" s="5"/>
-      <c r="D304" s="5"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="C305" s="5"/>
-      <c r="D305" s="5"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="C306" s="5"/>
-      <c r="D306" s="5"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="C307" s="5"/>
-      <c r="D307" s="5"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="C308" s="5"/>
-      <c r="D308" s="5"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="5"/>
-      <c r="D309" s="5"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="C310" s="5"/>
-      <c r="D310" s="5"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="C311" s="5"/>
-      <c r="D311" s="5"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="C312" s="5"/>
-      <c r="D312" s="5"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="C313" s="5"/>
-      <c r="D313" s="5"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="C314" s="5"/>
-      <c r="D314" s="5"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="C315" s="5"/>
-      <c r="D315" s="5"/>
+      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="C316" s="5"/>
-      <c r="D316" s="5"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="C317" s="5"/>
-      <c r="D317" s="5"/>
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="C318" s="5"/>
-      <c r="D318" s="5"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="C319" s="5"/>
-      <c r="D319" s="5"/>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="C320" s="5"/>
-      <c r="D320" s="5"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="C321" s="5"/>
-      <c r="D321" s="5"/>
+      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="C322" s="5"/>
-      <c r="D322" s="5"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="C323" s="5"/>
-      <c r="D323" s="5"/>
+      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="C324" s="5"/>
-      <c r="D324" s="5"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="C325" s="5"/>
-      <c r="D325" s="5"/>
+      <c r="C325" s="2"/>
+      <c r="D325" s="2"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="C326" s="5"/>
-      <c r="D326" s="5"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="C327" s="5"/>
-      <c r="D327" s="5"/>
+      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="C328" s="5"/>
-      <c r="D328" s="5"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="C329" s="5"/>
-      <c r="D329" s="5"/>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="C330" s="5"/>
-      <c r="D330" s="5"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="C331" s="5"/>
-      <c r="D331" s="5"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="C332" s="5"/>
-      <c r="D332" s="5"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="C333" s="5"/>
-      <c r="D333" s="5"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="C334" s="5"/>
-      <c r="D334" s="5"/>
+      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="C335" s="5"/>
-      <c r="D335" s="5"/>
+      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="C336" s="5"/>
-      <c r="D336" s="5"/>
+      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="C337" s="5"/>
-      <c r="D337" s="5"/>
+      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="C338" s="5"/>
-      <c r="D338" s="5"/>
+      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="C339" s="5"/>
-      <c r="D339" s="5"/>
+      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="C340" s="5"/>
-      <c r="D340" s="5"/>
+      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="C341" s="5"/>
-      <c r="D341" s="5"/>
+      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="C342" s="5"/>
-      <c r="D342" s="5"/>
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="C343" s="5"/>
-      <c r="D343" s="5"/>
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="C344" s="5"/>
-      <c r="D344" s="5"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="C345" s="5"/>
-      <c r="D345" s="5"/>
+      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="C346" s="5"/>
-      <c r="D346" s="5"/>
+      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="C347" s="5"/>
-      <c r="D347" s="5"/>
+      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="C348" s="5"/>
-      <c r="D348" s="5"/>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="C349" s="5"/>
-      <c r="D349" s="5"/>
+      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="C350" s="5"/>
-      <c r="D350" s="5"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="C351" s="5"/>
-      <c r="D351" s="5"/>
+      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="C352" s="5"/>
-      <c r="D352" s="5"/>
+      <c r="C352" s="2"/>
+      <c r="D352" s="2"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="C353" s="5"/>
-      <c r="D353" s="5"/>
+      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="C354" s="5"/>
-      <c r="D354" s="5"/>
+      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="C355" s="5"/>
-      <c r="D355" s="5"/>
+      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="C356" s="5"/>
-      <c r="D356" s="5"/>
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="C357" s="5"/>
-      <c r="D357" s="5"/>
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="C358" s="5"/>
-      <c r="D358" s="5"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="C359" s="5"/>
-      <c r="D359" s="5"/>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="C360" s="5"/>
-      <c r="D360" s="5"/>
+      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="C361" s="5"/>
-      <c r="D361" s="5"/>
+      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="C362" s="5"/>
-      <c r="D362" s="5"/>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="C363" s="5"/>
-      <c r="D363" s="5"/>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="C364" s="5"/>
-      <c r="D364" s="5"/>
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="C365" s="5"/>
-      <c r="D365" s="5"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="C366" s="5"/>
-      <c r="D366" s="5"/>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="C367" s="5"/>
-      <c r="D367" s="5"/>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="C368" s="5"/>
-      <c r="D368" s="5"/>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="C369" s="5"/>
-      <c r="D369" s="5"/>
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="C370" s="5"/>
-      <c r="D370" s="5"/>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="C371" s="5"/>
-      <c r="D371" s="5"/>
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="C372" s="5"/>
-      <c r="D372" s="5"/>
+      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="C373" s="5"/>
-      <c r="D373" s="5"/>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="C374" s="5"/>
-      <c r="D374" s="5"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="C375" s="5"/>
-      <c r="D375" s="5"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="C376" s="5"/>
-      <c r="D376" s="5"/>
+      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="C377" s="5"/>
-      <c r="D377" s="5"/>
+      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="C378" s="5"/>
-      <c r="D378" s="5"/>
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="C379" s="5"/>
-      <c r="D379" s="5"/>
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="C380" s="5"/>
-      <c r="D380" s="5"/>
+      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="C381" s="5"/>
-      <c r="D381" s="5"/>
+      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="C382" s="5"/>
-      <c r="D382" s="5"/>
+      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="C383" s="5"/>
-      <c r="D383" s="5"/>
+      <c r="C383" s="2"/>
+      <c r="D383" s="2"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="C384" s="5"/>
-      <c r="D384" s="5"/>
+      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="C385" s="5"/>
-      <c r="D385" s="5"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="C386" s="5"/>
-      <c r="D386" s="5"/>
+      <c r="C386" s="2"/>
+      <c r="D386" s="2"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="5"/>
-      <c r="D387" s="5"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="2"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="C388" s="5"/>
-      <c r="D388" s="5"/>
+      <c r="C388" s="2"/>
+      <c r="D388" s="2"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="C389" s="5"/>
-      <c r="D389" s="5"/>
+      <c r="C389" s="2"/>
+      <c r="D389" s="2"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="C390" s="5"/>
-      <c r="D390" s="5"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="C391" s="5"/>
-      <c r="D391" s="5"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="C392" s="5"/>
-      <c r="D392" s="5"/>
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="C393" s="5"/>
-      <c r="D393" s="5"/>
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="C394" s="5"/>
-      <c r="D394" s="5"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="C395" s="5"/>
-      <c r="D395" s="5"/>
+      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="C396" s="5"/>
-      <c r="D396" s="5"/>
+      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="C397" s="5"/>
-      <c r="D397" s="5"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="C398" s="5"/>
-      <c r="D398" s="5"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="C399" s="5"/>
-      <c r="D399" s="5"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="C400" s="5"/>
-      <c r="D400" s="5"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="C401" s="5"/>
-      <c r="D401" s="5"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="C402" s="5"/>
-      <c r="D402" s="5"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="C403" s="5"/>
-      <c r="D403" s="5"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="C404" s="5"/>
-      <c r="D404" s="5"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="C405" s="5"/>
-      <c r="D405" s="5"/>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="C406" s="5"/>
-      <c r="D406" s="5"/>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="C407" s="5"/>
-      <c r="D407" s="5"/>
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="C408" s="5"/>
-      <c r="D408" s="5"/>
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="C409" s="5"/>
-      <c r="D409" s="5"/>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="C410" s="5"/>
-      <c r="D410" s="5"/>
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="C411" s="5"/>
-      <c r="D411" s="5"/>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="C412" s="5"/>
-      <c r="D412" s="5"/>
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="C413" s="5"/>
-      <c r="D413" s="5"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="C414" s="5"/>
-      <c r="D414" s="5"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="C415" s="5"/>
-      <c r="D415" s="5"/>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="C416" s="5"/>
-      <c r="D416" s="5"/>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="C417" s="5"/>
-      <c r="D417" s="5"/>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="C418" s="5"/>
-      <c r="D418" s="5"/>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="C419" s="5"/>
-      <c r="D419" s="5"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="C420" s="5"/>
-      <c r="D420" s="5"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="C421" s="5"/>
-      <c r="D421" s="5"/>
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="C422" s="5"/>
-      <c r="D422" s="5"/>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="C423" s="5"/>
-      <c r="D423" s="5"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="C424" s="5"/>
-      <c r="D424" s="5"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="C425" s="5"/>
-      <c r="D425" s="5"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="C426" s="5"/>
-      <c r="D426" s="5"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="C427" s="5"/>
-      <c r="D427" s="5"/>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="C428" s="5"/>
-      <c r="D428" s="5"/>
+      <c r="C428" s="2"/>
+      <c r="D428" s="2"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="C429" s="5"/>
-      <c r="D429" s="5"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="2"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="C430" s="5"/>
-      <c r="D430" s="5"/>
+      <c r="C430" s="2"/>
+      <c r="D430" s="2"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="C431" s="5"/>
-      <c r="D431" s="5"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="C432" s="5"/>
-      <c r="D432" s="5"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="C433" s="5"/>
-      <c r="D433" s="5"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="C434" s="5"/>
-      <c r="D434" s="5"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="C435" s="5"/>
-      <c r="D435" s="5"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="C436" s="5"/>
-      <c r="D436" s="5"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="C437" s="5"/>
-      <c r="D437" s="5"/>
+      <c r="C437" s="2"/>
+      <c r="D437" s="2"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="C438" s="5"/>
-      <c r="D438" s="5"/>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="C439" s="5"/>
-      <c r="D439" s="5"/>
+      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="C440" s="5"/>
-      <c r="D440" s="5"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="C441" s="5"/>
-      <c r="D441" s="5"/>
+      <c r="C441" s="2"/>
+      <c r="D441" s="2"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="C442" s="5"/>
-      <c r="D442" s="5"/>
+      <c r="C442" s="2"/>
+      <c r="D442" s="2"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="C443" s="5"/>
-      <c r="D443" s="5"/>
+      <c r="C443" s="2"/>
+      <c r="D443" s="2"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="C444" s="5"/>
-      <c r="D444" s="5"/>
+      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="C445" s="5"/>
-      <c r="D445" s="5"/>
+      <c r="C445" s="2"/>
+      <c r="D445" s="2"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="C446" s="5"/>
-      <c r="D446" s="5"/>
+      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="C447" s="5"/>
-      <c r="D447" s="5"/>
+      <c r="C447" s="2"/>
+      <c r="D447" s="2"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="C448" s="5"/>
-      <c r="D448" s="5"/>
+      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="C449" s="5"/>
-      <c r="D449" s="5"/>
+      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="C450" s="5"/>
-      <c r="D450" s="5"/>
+      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="C451" s="5"/>
-      <c r="D451" s="5"/>
+      <c r="C451" s="2"/>
+      <c r="D451" s="2"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="C452" s="5"/>
-      <c r="D452" s="5"/>
+      <c r="C452" s="2"/>
+      <c r="D452" s="2"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="C453" s="5"/>
-      <c r="D453" s="5"/>
+      <c r="C453" s="2"/>
+      <c r="D453" s="2"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="C454" s="5"/>
-      <c r="D454" s="5"/>
+      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="C455" s="5"/>
-      <c r="D455" s="5"/>
+      <c r="C455" s="2"/>
+      <c r="D455" s="2"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="C456" s="5"/>
-      <c r="D456" s="5"/>
+      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="C457" s="5"/>
-      <c r="D457" s="5"/>
+      <c r="C457" s="2"/>
+      <c r="D457" s="2"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="C458" s="5"/>
-      <c r="D458" s="5"/>
+      <c r="C458" s="2"/>
+      <c r="D458" s="2"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="C459" s="5"/>
-      <c r="D459" s="5"/>
+      <c r="C459" s="2"/>
+      <c r="D459" s="2"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="C460" s="5"/>
-      <c r="D460" s="5"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="2"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="C461" s="5"/>
-      <c r="D461" s="5"/>
+      <c r="C461" s="2"/>
+      <c r="D461" s="2"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="C462" s="5"/>
-      <c r="D462" s="5"/>
+      <c r="C462" s="2"/>
+      <c r="D462" s="2"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="C463" s="5"/>
-      <c r="D463" s="5"/>
+      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="C464" s="5"/>
-      <c r="D464" s="5"/>
+      <c r="C464" s="2"/>
+      <c r="D464" s="2"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="C465" s="5"/>
-      <c r="D465" s="5"/>
+      <c r="C465" s="2"/>
+      <c r="D465" s="2"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="C466" s="5"/>
-      <c r="D466" s="5"/>
+      <c r="C466" s="2"/>
+      <c r="D466" s="2"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="C467" s="5"/>
-      <c r="D467" s="5"/>
+      <c r="C467" s="2"/>
+      <c r="D467" s="2"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="C468" s="5"/>
-      <c r="D468" s="5"/>
+      <c r="C468" s="2"/>
+      <c r="D468" s="2"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="C469" s="5"/>
-      <c r="D469" s="5"/>
+      <c r="C469" s="2"/>
+      <c r="D469" s="2"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="C470" s="5"/>
-      <c r="D470" s="5"/>
+      <c r="C470" s="2"/>
+      <c r="D470" s="2"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="C471" s="5"/>
-      <c r="D471" s="5"/>
+      <c r="C471" s="2"/>
+      <c r="D471" s="2"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="C472" s="5"/>
-      <c r="D472" s="5"/>
+      <c r="C472" s="2"/>
+      <c r="D472" s="2"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="C473" s="5"/>
-      <c r="D473" s="5"/>
+      <c r="C473" s="2"/>
+      <c r="D473" s="2"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="C474" s="5"/>
-      <c r="D474" s="5"/>
+      <c r="C474" s="2"/>
+      <c r="D474" s="2"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="C475" s="5"/>
-      <c r="D475" s="5"/>
+      <c r="C475" s="2"/>
+      <c r="D475" s="2"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="C476" s="5"/>
-      <c r="D476" s="5"/>
+      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="C477" s="5"/>
-      <c r="D477" s="5"/>
+      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="C478" s="5"/>
-      <c r="D478" s="5"/>
+      <c r="C478" s="2"/>
+      <c r="D478" s="2"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="C479" s="5"/>
-      <c r="D479" s="5"/>
+      <c r="C479" s="2"/>
+      <c r="D479" s="2"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="C480" s="5"/>
-      <c r="D480" s="5"/>
+      <c r="C480" s="2"/>
+      <c r="D480" s="2"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="C481" s="5"/>
-      <c r="D481" s="5"/>
+      <c r="C481" s="2"/>
+      <c r="D481" s="2"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="C482" s="5"/>
-      <c r="D482" s="5"/>
+      <c r="C482" s="2"/>
+      <c r="D482" s="2"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="C483" s="5"/>
-      <c r="D483" s="5"/>
+      <c r="C483" s="2"/>
+      <c r="D483" s="2"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="C484" s="5"/>
-      <c r="D484" s="5"/>
+      <c r="C484" s="2"/>
+      <c r="D484" s="2"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="C485" s="5"/>
-      <c r="D485" s="5"/>
+      <c r="C485" s="2"/>
+      <c r="D485" s="2"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="C486" s="5"/>
-      <c r="D486" s="5"/>
+      <c r="C486" s="2"/>
+      <c r="D486" s="2"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="C487" s="5"/>
-      <c r="D487" s="5"/>
+      <c r="C487" s="2"/>
+      <c r="D487" s="2"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="C488" s="5"/>
-      <c r="D488" s="5"/>
+      <c r="C488" s="2"/>
+      <c r="D488" s="2"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="C489" s="5"/>
-      <c r="D489" s="5"/>
+      <c r="C489" s="2"/>
+      <c r="D489" s="2"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="C490" s="5"/>
-      <c r="D490" s="5"/>
+      <c r="C490" s="2"/>
+      <c r="D490" s="2"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="C491" s="5"/>
-      <c r="D491" s="5"/>
+      <c r="C491" s="2"/>
+      <c r="D491" s="2"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="C492" s="5"/>
-      <c r="D492" s="5"/>
+      <c r="C492" s="2"/>
+      <c r="D492" s="2"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="C493" s="5"/>
-      <c r="D493" s="5"/>
+      <c r="C493" s="2"/>
+      <c r="D493" s="2"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="C494" s="5"/>
-      <c r="D494" s="5"/>
+      <c r="C494" s="2"/>
+      <c r="D494" s="2"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="C495" s="5"/>
-      <c r="D495" s="5"/>
+      <c r="C495" s="2"/>
+      <c r="D495" s="2"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="C496" s="5"/>
-      <c r="D496" s="5"/>
+      <c r="C496" s="2"/>
+      <c r="D496" s="2"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="C497" s="5"/>
-      <c r="D497" s="5"/>
+      <c r="C497" s="2"/>
+      <c r="D497" s="2"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="C498" s="5"/>
-      <c r="D498" s="5"/>
+      <c r="C498" s="2"/>
+      <c r="D498" s="2"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="C499" s="5"/>
-      <c r="D499" s="5"/>
+      <c r="C499" s="2"/>
+      <c r="D499" s="2"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="C500" s="5"/>
-      <c r="D500" s="5"/>
+      <c r="C500" s="2"/>
+      <c r="D500" s="2"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="C501" s="5"/>
-      <c r="D501" s="5"/>
+      <c r="C501" s="2"/>
+      <c r="D501" s="2"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="C502" s="5"/>
-      <c r="D502" s="5"/>
+      <c r="C502" s="2"/>
+      <c r="D502" s="2"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="C503" s="5"/>
-      <c r="D503" s="5"/>
+      <c r="C503" s="2"/>
+      <c r="D503" s="2"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="C504" s="5"/>
-      <c r="D504" s="5"/>
+      <c r="C504" s="2"/>
+      <c r="D504" s="2"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="C505" s="5"/>
-      <c r="D505" s="5"/>
+      <c r="C505" s="2"/>
+      <c r="D505" s="2"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="C506" s="5"/>
-      <c r="D506" s="5"/>
+      <c r="C506" s="2"/>
+      <c r="D506" s="2"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="C507" s="5"/>
-      <c r="D507" s="5"/>
+      <c r="C507" s="2"/>
+      <c r="D507" s="2"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="C508" s="5"/>
-      <c r="D508" s="5"/>
+      <c r="C508" s="2"/>
+      <c r="D508" s="2"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="C509" s="5"/>
-      <c r="D509" s="5"/>
+      <c r="C509" s="2"/>
+      <c r="D509" s="2"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="C510" s="5"/>
-      <c r="D510" s="5"/>
+      <c r="C510" s="2"/>
+      <c r="D510" s="2"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="C511" s="5"/>
-      <c r="D511" s="5"/>
+      <c r="C511" s="2"/>
+      <c r="D511" s="2"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="C512" s="5"/>
-      <c r="D512" s="5"/>
+      <c r="C512" s="2"/>
+      <c r="D512" s="2"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="C513" s="5"/>
-      <c r="D513" s="5"/>
+      <c r="C513" s="2"/>
+      <c r="D513" s="2"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="C514" s="5"/>
-      <c r="D514" s="5"/>
+      <c r="C514" s="2"/>
+      <c r="D514" s="2"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="C515" s="5"/>
-      <c r="D515" s="5"/>
+      <c r="C515" s="2"/>
+      <c r="D515" s="2"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="C516" s="5"/>
-      <c r="D516" s="5"/>
+      <c r="C516" s="2"/>
+      <c r="D516" s="2"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="C517" s="5"/>
-      <c r="D517" s="5"/>
+      <c r="C517" s="2"/>
+      <c r="D517" s="2"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="C518" s="5"/>
-      <c r="D518" s="5"/>
+      <c r="C518" s="2"/>
+      <c r="D518" s="2"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="C519" s="5"/>
-      <c r="D519" s="5"/>
+      <c r="C519" s="2"/>
+      <c r="D519" s="2"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="C520" s="5"/>
-      <c r="D520" s="5"/>
+      <c r="C520" s="2"/>
+      <c r="D520" s="2"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="C521" s="5"/>
-      <c r="D521" s="5"/>
+      <c r="C521" s="2"/>
+      <c r="D521" s="2"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="C522" s="5"/>
-      <c r="D522" s="5"/>
+      <c r="C522" s="2"/>
+      <c r="D522" s="2"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="C523" s="5"/>
-      <c r="D523" s="5"/>
+      <c r="C523" s="2"/>
+      <c r="D523" s="2"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="C524" s="5"/>
-      <c r="D524" s="5"/>
+      <c r="C524" s="2"/>
+      <c r="D524" s="2"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="C525" s="5"/>
-      <c r="D525" s="5"/>
+      <c r="C525" s="2"/>
+      <c r="D525" s="2"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="C526" s="5"/>
-      <c r="D526" s="5"/>
+      <c r="C526" s="2"/>
+      <c r="D526" s="2"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="C527" s="5"/>
-      <c r="D527" s="5"/>
+      <c r="C527" s="2"/>
+      <c r="D527" s="2"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="C528" s="5"/>
-      <c r="D528" s="5"/>
+      <c r="C528" s="2"/>
+      <c r="D528" s="2"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="C529" s="5"/>
-      <c r="D529" s="5"/>
+      <c r="C529" s="2"/>
+      <c r="D529" s="2"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="C530" s="5"/>
-      <c r="D530" s="5"/>
+      <c r="C530" s="2"/>
+      <c r="D530" s="2"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="C531" s="5"/>
-      <c r="D531" s="5"/>
+      <c r="C531" s="2"/>
+      <c r="D531" s="2"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="C532" s="5"/>
-      <c r="D532" s="5"/>
+      <c r="C532" s="2"/>
+      <c r="D532" s="2"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="C533" s="5"/>
-      <c r="D533" s="5"/>
+      <c r="C533" s="2"/>
+      <c r="D533" s="2"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="C534" s="5"/>
-      <c r="D534" s="5"/>
+      <c r="C534" s="2"/>
+      <c r="D534" s="2"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="C535" s="5"/>
-      <c r="D535" s="5"/>
+      <c r="C535" s="2"/>
+      <c r="D535" s="2"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="C536" s="5"/>
-      <c r="D536" s="5"/>
+      <c r="C536" s="2"/>
+      <c r="D536" s="2"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="C537" s="5"/>
-      <c r="D537" s="5"/>
+      <c r="C537" s="2"/>
+      <c r="D537" s="2"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="C538" s="5"/>
-      <c r="D538" s="5"/>
+      <c r="C538" s="2"/>
+      <c r="D538" s="2"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="C539" s="5"/>
-      <c r="D539" s="5"/>
+      <c r="C539" s="2"/>
+      <c r="D539" s="2"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="C540" s="5"/>
-      <c r="D540" s="5"/>
+      <c r="C540" s="2"/>
+      <c r="D540" s="2"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="C541" s="5"/>
-      <c r="D541" s="5"/>
+      <c r="C541" s="2"/>
+      <c r="D541" s="2"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="C542" s="5"/>
-      <c r="D542" s="5"/>
+      <c r="C542" s="2"/>
+      <c r="D542" s="2"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="C543" s="5"/>
-      <c r="D543" s="5"/>
+      <c r="C543" s="2"/>
+      <c r="D543" s="2"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="C544" s="5"/>
-      <c r="D544" s="5"/>
+      <c r="C544" s="2"/>
+      <c r="D544" s="2"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="C545" s="5"/>
-      <c r="D545" s="5"/>
+      <c r="C545" s="2"/>
+      <c r="D545" s="2"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="C546" s="5"/>
-      <c r="D546" s="5"/>
+      <c r="C546" s="2"/>
+      <c r="D546" s="2"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="C547" s="5"/>
-      <c r="D547" s="5"/>
+      <c r="C547" s="2"/>
+      <c r="D547" s="2"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="C548" s="5"/>
-      <c r="D548" s="5"/>
+      <c r="C548" s="2"/>
+      <c r="D548" s="2"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="C549" s="5"/>
-      <c r="D549" s="5"/>
+      <c r="C549" s="2"/>
+      <c r="D549" s="2"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="C550" s="5"/>
-      <c r="D550" s="5"/>
+      <c r="C550" s="2"/>
+      <c r="D550" s="2"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="C551" s="5"/>
-      <c r="D551" s="5"/>
+      <c r="C551" s="2"/>
+      <c r="D551" s="2"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="C552" s="5"/>
-      <c r="D552" s="5"/>
+      <c r="C552" s="2"/>
+      <c r="D552" s="2"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="C553" s="5"/>
-      <c r="D553" s="5"/>
+      <c r="C553" s="2"/>
+      <c r="D553" s="2"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="C554" s="5"/>
-      <c r="D554" s="5"/>
+      <c r="C554" s="2"/>
+      <c r="D554" s="2"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="C555" s="5"/>
-      <c r="D555" s="5"/>
+      <c r="C555" s="2"/>
+      <c r="D555" s="2"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="C556" s="5"/>
-      <c r="D556" s="5"/>
+      <c r="C556" s="2"/>
+      <c r="D556" s="2"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="C557" s="5"/>
-      <c r="D557" s="5"/>
+      <c r="C557" s="2"/>
+      <c r="D557" s="2"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="C558" s="5"/>
-      <c r="D558" s="5"/>
+      <c r="C558" s="2"/>
+      <c r="D558" s="2"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="C559" s="5"/>
-      <c r="D559" s="5"/>
+      <c r="C559" s="2"/>
+      <c r="D559" s="2"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="C560" s="5"/>
-      <c r="D560" s="5"/>
+      <c r="C560" s="2"/>
+      <c r="D560" s="2"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="C561" s="5"/>
-      <c r="D561" s="5"/>
+      <c r="C561" s="2"/>
+      <c r="D561" s="2"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="C562" s="5"/>
-      <c r="D562" s="5"/>
+      <c r="C562" s="2"/>
+      <c r="D562" s="2"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="C563" s="5"/>
-      <c r="D563" s="5"/>
+      <c r="C563" s="2"/>
+      <c r="D563" s="2"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="C564" s="5"/>
-      <c r="D564" s="5"/>
+      <c r="C564" s="2"/>
+      <c r="D564" s="2"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="C565" s="5"/>
-      <c r="D565" s="5"/>
+      <c r="C565" s="2"/>
+      <c r="D565" s="2"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="C566" s="5"/>
-      <c r="D566" s="5"/>
+      <c r="C566" s="2"/>
+      <c r="D566" s="2"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="C567" s="5"/>
-      <c r="D567" s="5"/>
+      <c r="C567" s="2"/>
+      <c r="D567" s="2"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="C568" s="5"/>
-      <c r="D568" s="5"/>
+      <c r="C568" s="2"/>
+      <c r="D568" s="2"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="C569" s="5"/>
-      <c r="D569" s="5"/>
+      <c r="C569" s="2"/>
+      <c r="D569" s="2"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="C570" s="5"/>
-      <c r="D570" s="5"/>
+      <c r="C570" s="2"/>
+      <c r="D570" s="2"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="C571" s="5"/>
-      <c r="D571" s="5"/>
+      <c r="C571" s="2"/>
+      <c r="D571" s="2"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="C572" s="5"/>
-      <c r="D572" s="5"/>
+      <c r="C572" s="2"/>
+      <c r="D572" s="2"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="C573" s="5"/>
-      <c r="D573" s="5"/>
+      <c r="C573" s="2"/>
+      <c r="D573" s="2"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="C574" s="5"/>
-      <c r="D574" s="5"/>
+      <c r="C574" s="2"/>
+      <c r="D574" s="2"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="C575" s="5"/>
-      <c r="D575" s="5"/>
+      <c r="C575" s="2"/>
+      <c r="D575" s="2"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="C576" s="5"/>
-      <c r="D576" s="5"/>
+      <c r="C576" s="2"/>
+      <c r="D576" s="2"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="C577" s="5"/>
-      <c r="D577" s="5"/>
+      <c r="C577" s="2"/>
+      <c r="D577" s="2"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="C578" s="5"/>
-      <c r="D578" s="5"/>
+      <c r="C578" s="2"/>
+      <c r="D578" s="2"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="C579" s="5"/>
-      <c r="D579" s="5"/>
+      <c r="C579" s="2"/>
+      <c r="D579" s="2"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="C580" s="5"/>
-      <c r="D580" s="5"/>
+      <c r="C580" s="2"/>
+      <c r="D580" s="2"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="C581" s="5"/>
-      <c r="D581" s="5"/>
+      <c r="C581" s="2"/>
+      <c r="D581" s="2"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="C582" s="5"/>
-      <c r="D582" s="5"/>
+      <c r="C582" s="2"/>
+      <c r="D582" s="2"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="C583" s="5"/>
-      <c r="D583" s="5"/>
+      <c r="C583" s="2"/>
+      <c r="D583" s="2"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="5"/>
-      <c r="D584" s="5"/>
+      <c r="C584" s="2"/>
+      <c r="D584" s="2"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="5"/>
-      <c r="D585" s="5"/>
+      <c r="C585" s="2"/>
+      <c r="D585" s="2"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="5"/>
-      <c r="D586" s="5"/>
+      <c r="C586" s="2"/>
+      <c r="D586" s="2"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="C587" s="5"/>
-      <c r="D587" s="5"/>
+      <c r="C587" s="2"/>
+      <c r="D587" s="2"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="C588" s="5"/>
-      <c r="D588" s="5"/>
+      <c r="C588" s="2"/>
+      <c r="D588" s="2"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="C589" s="5"/>
-      <c r="D589" s="5"/>
+      <c r="C589" s="2"/>
+      <c r="D589" s="2"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="C590" s="5"/>
-      <c r="D590" s="5"/>
+      <c r="C590" s="2"/>
+      <c r="D590" s="2"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="C591" s="5"/>
-      <c r="D591" s="5"/>
+      <c r="C591" s="2"/>
+      <c r="D591" s="2"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="C592" s="5"/>
-      <c r="D592" s="5"/>
+      <c r="C592" s="2"/>
+      <c r="D592" s="2"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="C593" s="5"/>
-      <c r="D593" s="5"/>
+      <c r="C593" s="2"/>
+      <c r="D593" s="2"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="C594" s="5"/>
-      <c r="D594" s="5"/>
+      <c r="C594" s="2"/>
+      <c r="D594" s="2"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="C595" s="5"/>
-      <c r="D595" s="5"/>
+      <c r="C595" s="2"/>
+      <c r="D595" s="2"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="C596" s="5"/>
-      <c r="D596" s="5"/>
+      <c r="C596" s="2"/>
+      <c r="D596" s="2"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="C597" s="5"/>
-      <c r="D597" s="5"/>
+      <c r="C597" s="2"/>
+      <c r="D597" s="2"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="C598" s="5"/>
-      <c r="D598" s="5"/>
+      <c r="C598" s="2"/>
+      <c r="D598" s="2"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="C599" s="5"/>
-      <c r="D599" s="5"/>
+      <c r="C599" s="2"/>
+      <c r="D599" s="2"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="5"/>
-      <c r="D600" s="5"/>
+      <c r="C600" s="2"/>
+      <c r="D600" s="2"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="5"/>
-      <c r="D601" s="5"/>
+      <c r="C601" s="2"/>
+      <c r="D601" s="2"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="5"/>
-      <c r="D602" s="5"/>
+      <c r="C602" s="2"/>
+      <c r="D602" s="2"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="C603" s="5"/>
-      <c r="D603" s="5"/>
+      <c r="C603" s="2"/>
+      <c r="D603" s="2"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="C604" s="5"/>
-      <c r="D604" s="5"/>
+      <c r="C604" s="2"/>
+      <c r="D604" s="2"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="C605" s="5"/>
-      <c r="D605" s="5"/>
+      <c r="C605" s="2"/>
+      <c r="D605" s="2"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="C606" s="5"/>
-      <c r="D606" s="5"/>
+      <c r="C606" s="2"/>
+      <c r="D606" s="2"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="C607" s="5"/>
-      <c r="D607" s="5"/>
+      <c r="C607" s="2"/>
+      <c r="D607" s="2"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="C608" s="5"/>
-      <c r="D608" s="5"/>
+      <c r="C608" s="2"/>
+      <c r="D608" s="2"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="C609" s="5"/>
-      <c r="D609" s="5"/>
+      <c r="C609" s="2"/>
+      <c r="D609" s="2"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="C610" s="5"/>
-      <c r="D610" s="5"/>
+      <c r="C610" s="2"/>
+      <c r="D610" s="2"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="C611" s="5"/>
-      <c r="D611" s="5"/>
+      <c r="C611" s="2"/>
+      <c r="D611" s="2"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="C612" s="5"/>
-      <c r="D612" s="5"/>
+      <c r="C612" s="2"/>
+      <c r="D612" s="2"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="C613" s="5"/>
-      <c r="D613" s="5"/>
+      <c r="C613" s="2"/>
+      <c r="D613" s="2"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="C614" s="5"/>
-      <c r="D614" s="5"/>
+      <c r="C614" s="2"/>
+      <c r="D614" s="2"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="C615" s="5"/>
-      <c r="D615" s="5"/>
+      <c r="C615" s="2"/>
+      <c r="D615" s="2"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="5"/>
-      <c r="D616" s="5"/>
+      <c r="C616" s="2"/>
+      <c r="D616" s="2"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="5"/>
-      <c r="D617" s="5"/>
+      <c r="C617" s="2"/>
+      <c r="D617" s="2"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="5"/>
-      <c r="D618" s="5"/>
+      <c r="C618" s="2"/>
+      <c r="D618" s="2"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="C619" s="5"/>
-      <c r="D619" s="5"/>
+      <c r="C619" s="2"/>
+      <c r="D619" s="2"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="C620" s="5"/>
-      <c r="D620" s="5"/>
+      <c r="C620" s="2"/>
+      <c r="D620" s="2"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="C621" s="5"/>
-      <c r="D621" s="5"/>
+      <c r="C621" s="2"/>
+      <c r="D621" s="2"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="C622" s="5"/>
-      <c r="D622" s="5"/>
+      <c r="C622" s="2"/>
+      <c r="D622" s="2"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="C623" s="5"/>
-      <c r="D623" s="5"/>
+      <c r="C623" s="2"/>
+      <c r="D623" s="2"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="C624" s="5"/>
-      <c r="D624" s="5"/>
+      <c r="C624" s="2"/>
+      <c r="D624" s="2"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="C625" s="5"/>
-      <c r="D625" s="5"/>
+      <c r="C625" s="2"/>
+      <c r="D625" s="2"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="C626" s="5"/>
-      <c r="D626" s="5"/>
+      <c r="C626" s="2"/>
+      <c r="D626" s="2"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="C627" s="5"/>
-      <c r="D627" s="5"/>
+      <c r="C627" s="2"/>
+      <c r="D627" s="2"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="C628" s="5"/>
-      <c r="D628" s="5"/>
+      <c r="C628" s="2"/>
+      <c r="D628" s="2"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="C629" s="5"/>
-      <c r="D629" s="5"/>
+      <c r="C629" s="2"/>
+      <c r="D629" s="2"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="C630" s="5"/>
-      <c r="D630" s="5"/>
+      <c r="C630" s="2"/>
+      <c r="D630" s="2"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="C631" s="5"/>
-      <c r="D631" s="5"/>
+      <c r="C631" s="2"/>
+      <c r="D631" s="2"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="C632" s="5"/>
-      <c r="D632" s="5"/>
+      <c r="C632" s="2"/>
+      <c r="D632" s="2"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="C633" s="5"/>
-      <c r="D633" s="5"/>
+      <c r="C633" s="2"/>
+      <c r="D633" s="2"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="C634" s="5"/>
-      <c r="D634" s="5"/>
+      <c r="C634" s="2"/>
+      <c r="D634" s="2"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="C635" s="5"/>
-      <c r="D635" s="5"/>
+      <c r="C635" s="2"/>
+      <c r="D635" s="2"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="C636" s="5"/>
-      <c r="D636" s="5"/>
+      <c r="C636" s="2"/>
+      <c r="D636" s="2"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="C637" s="5"/>
-      <c r="D637" s="5"/>
+      <c r="C637" s="2"/>
+      <c r="D637" s="2"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="C638" s="5"/>
-      <c r="D638" s="5"/>
+      <c r="C638" s="2"/>
+      <c r="D638" s="2"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="C639" s="5"/>
-      <c r="D639" s="5"/>
+      <c r="C639" s="2"/>
+      <c r="D639" s="2"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="C640" s="5"/>
-      <c r="D640" s="5"/>
+      <c r="C640" s="2"/>
+      <c r="D640" s="2"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="C641" s="5"/>
-      <c r="D641" s="5"/>
+      <c r="C641" s="2"/>
+      <c r="D641" s="2"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="C642" s="5"/>
-      <c r="D642" s="5"/>
+      <c r="C642" s="2"/>
+      <c r="D642" s="2"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="C643" s="5"/>
-      <c r="D643" s="5"/>
+      <c r="C643" s="2"/>
+      <c r="D643" s="2"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="C644" s="5"/>
-      <c r="D644" s="5"/>
+      <c r="C644" s="2"/>
+      <c r="D644" s="2"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="C645" s="5"/>
-      <c r="D645" s="5"/>
+      <c r="C645" s="2"/>
+      <c r="D645" s="2"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="C646" s="5"/>
-      <c r="D646" s="5"/>
+      <c r="C646" s="2"/>
+      <c r="D646" s="2"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="C647" s="5"/>
-      <c r="D647" s="5"/>
+      <c r="C647" s="2"/>
+      <c r="D647" s="2"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="C648" s="5"/>
-      <c r="D648" s="5"/>
+      <c r="C648" s="2"/>
+      <c r="D648" s="2"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="C649" s="5"/>
-      <c r="D649" s="5"/>
+      <c r="C649" s="2"/>
+      <c r="D649" s="2"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="C650" s="5"/>
-      <c r="D650" s="5"/>
+      <c r="C650" s="2"/>
+      <c r="D650" s="2"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="C651" s="5"/>
-      <c r="D651" s="5"/>
+      <c r="C651" s="2"/>
+      <c r="D651" s="2"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="C652" s="5"/>
-      <c r="D652" s="5"/>
+      <c r="C652" s="2"/>
+      <c r="D652" s="2"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="C653" s="5"/>
-      <c r="D653" s="5"/>
+      <c r="C653" s="2"/>
+      <c r="D653" s="2"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="C654" s="5"/>
-      <c r="D654" s="5"/>
+      <c r="C654" s="2"/>
+      <c r="D654" s="2"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="C655" s="5"/>
-      <c r="D655" s="5"/>
+      <c r="C655" s="2"/>
+      <c r="D655" s="2"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="C656" s="5"/>
-      <c r="D656" s="5"/>
+      <c r="C656" s="2"/>
+      <c r="D656" s="2"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="C657" s="5"/>
-      <c r="D657" s="5"/>
+      <c r="C657" s="2"/>
+      <c r="D657" s="2"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="C658" s="5"/>
-      <c r="D658" s="5"/>
+      <c r="C658" s="2"/>
+      <c r="D658" s="2"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="C659" s="5"/>
-      <c r="D659" s="5"/>
+      <c r="C659" s="2"/>
+      <c r="D659" s="2"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="C660" s="5"/>
-      <c r="D660" s="5"/>
+      <c r="C660" s="2"/>
+      <c r="D660" s="2"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="C661" s="5"/>
-      <c r="D661" s="5"/>
+      <c r="C661" s="2"/>
+      <c r="D661" s="2"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="C662" s="5"/>
-      <c r="D662" s="5"/>
+      <c r="C662" s="2"/>
+      <c r="D662" s="2"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="C663" s="5"/>
-      <c r="D663" s="5"/>
+      <c r="C663" s="2"/>
+      <c r="D663" s="2"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="C664" s="5"/>
-      <c r="D664" s="5"/>
+      <c r="C664" s="2"/>
+      <c r="D664" s="2"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="C665" s="5"/>
-      <c r="D665" s="5"/>
+      <c r="C665" s="2"/>
+      <c r="D665" s="2"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="C666" s="5"/>
-      <c r="D666" s="5"/>
+      <c r="C666" s="2"/>
+      <c r="D666" s="2"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="C667" s="5"/>
-      <c r="D667" s="5"/>
+      <c r="C667" s="2"/>
+      <c r="D667" s="2"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="C668" s="5"/>
-      <c r="D668" s="5"/>
+      <c r="C668" s="2"/>
+      <c r="D668" s="2"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="C669" s="5"/>
-      <c r="D669" s="5"/>
+      <c r="C669" s="2"/>
+      <c r="D669" s="2"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="C670" s="5"/>
-      <c r="D670" s="5"/>
+      <c r="C670" s="2"/>
+      <c r="D670" s="2"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="C671" s="5"/>
-      <c r="D671" s="5"/>
+      <c r="C671" s="2"/>
+      <c r="D671" s="2"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="C672" s="5"/>
-      <c r="D672" s="5"/>
+      <c r="C672" s="2"/>
+      <c r="D672" s="2"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="C673" s="5"/>
-      <c r="D673" s="5"/>
+      <c r="C673" s="2"/>
+      <c r="D673" s="2"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="C674" s="5"/>
-      <c r="D674" s="5"/>
+      <c r="C674" s="2"/>
+      <c r="D674" s="2"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="C675" s="5"/>
-      <c r="D675" s="5"/>
+      <c r="C675" s="2"/>
+      <c r="D675" s="2"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="C676" s="5"/>
-      <c r="D676" s="5"/>
+      <c r="C676" s="2"/>
+      <c r="D676" s="2"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="C677" s="5"/>
-      <c r="D677" s="5"/>
+      <c r="C677" s="2"/>
+      <c r="D677" s="2"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="C678" s="5"/>
-      <c r="D678" s="5"/>
+      <c r="C678" s="2"/>
+      <c r="D678" s="2"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="C679" s="5"/>
-      <c r="D679" s="5"/>
+      <c r="C679" s="2"/>
+      <c r="D679" s="2"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="C680" s="5"/>
-      <c r="D680" s="5"/>
+      <c r="C680" s="2"/>
+      <c r="D680" s="2"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="C681" s="5"/>
-      <c r="D681" s="5"/>
+      <c r="C681" s="2"/>
+      <c r="D681" s="2"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="C682" s="5"/>
-      <c r="D682" s="5"/>
+      <c r="C682" s="2"/>
+      <c r="D682" s="2"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="C683" s="5"/>
-      <c r="D683" s="5"/>
+      <c r="C683" s="2"/>
+      <c r="D683" s="2"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="C684" s="5"/>
-      <c r="D684" s="5"/>
+      <c r="C684" s="2"/>
+      <c r="D684" s="2"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="C685" s="5"/>
-      <c r="D685" s="5"/>
+      <c r="C685" s="2"/>
+      <c r="D685" s="2"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="C686" s="5"/>
-      <c r="D686" s="5"/>
+      <c r="C686" s="2"/>
+      <c r="D686" s="2"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="C687" s="5"/>
-      <c r="D687" s="5"/>
+      <c r="C687" s="2"/>
+      <c r="D687" s="2"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="C688" s="5"/>
-      <c r="D688" s="5"/>
+      <c r="C688" s="2"/>
+      <c r="D688" s="2"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="C689" s="5"/>
-      <c r="D689" s="5"/>
+      <c r="C689" s="2"/>
+      <c r="D689" s="2"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="C690" s="5"/>
-      <c r="D690" s="5"/>
+      <c r="C690" s="2"/>
+      <c r="D690" s="2"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="C691" s="5"/>
-      <c r="D691" s="5"/>
+      <c r="C691" s="2"/>
+      <c r="D691" s="2"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="C692" s="5"/>
-      <c r="D692" s="5"/>
+      <c r="C692" s="2"/>
+      <c r="D692" s="2"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="C693" s="5"/>
-      <c r="D693" s="5"/>
+      <c r="C693" s="2"/>
+      <c r="D693" s="2"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="C694" s="5"/>
-      <c r="D694" s="5"/>
+      <c r="C694" s="2"/>
+      <c r="D694" s="2"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="C695" s="5"/>
-      <c r="D695" s="5"/>
+      <c r="C695" s="2"/>
+      <c r="D695" s="2"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="C696" s="5"/>
-      <c r="D696" s="5"/>
+      <c r="C696" s="2"/>
+      <c r="D696" s="2"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="C697" s="5"/>
-      <c r="D697" s="5"/>
+      <c r="C697" s="2"/>
+      <c r="D697" s="2"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="C698" s="5"/>
-      <c r="D698" s="5"/>
+      <c r="C698" s="2"/>
+      <c r="D698" s="2"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="C699" s="5"/>
-      <c r="D699" s="5"/>
+      <c r="C699" s="2"/>
+      <c r="D699" s="2"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="C700" s="5"/>
-      <c r="D700" s="5"/>
+      <c r="C700" s="2"/>
+      <c r="D700" s="2"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="C701" s="5"/>
-      <c r="D701" s="5"/>
+      <c r="C701" s="2"/>
+      <c r="D701" s="2"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="C702" s="5"/>
-      <c r="D702" s="5"/>
+      <c r="C702" s="2"/>
+      <c r="D702" s="2"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="C703" s="5"/>
-      <c r="D703" s="5"/>
+      <c r="C703" s="2"/>
+      <c r="D703" s="2"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="C704" s="5"/>
-      <c r="D704" s="5"/>
+      <c r="C704" s="2"/>
+      <c r="D704" s="2"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="C705" s="5"/>
-      <c r="D705" s="5"/>
+      <c r="C705" s="2"/>
+      <c r="D705" s="2"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="C706" s="5"/>
-      <c r="D706" s="5"/>
+      <c r="C706" s="2"/>
+      <c r="D706" s="2"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="C707" s="5"/>
-      <c r="D707" s="5"/>
+      <c r="C707" s="2"/>
+      <c r="D707" s="2"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="C708" s="5"/>
-      <c r="D708" s="5"/>
+      <c r="C708" s="2"/>
+      <c r="D708" s="2"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="C709" s="5"/>
-      <c r="D709" s="5"/>
+      <c r="C709" s="2"/>
+      <c r="D709" s="2"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="C710" s="5"/>
-      <c r="D710" s="5"/>
+      <c r="C710" s="2"/>
+      <c r="D710" s="2"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="C711" s="5"/>
-      <c r="D711" s="5"/>
+      <c r="C711" s="2"/>
+      <c r="D711" s="2"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="C712" s="5"/>
-      <c r="D712" s="5"/>
+      <c r="C712" s="2"/>
+      <c r="D712" s="2"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="C713" s="5"/>
-      <c r="D713" s="5"/>
+      <c r="C713" s="2"/>
+      <c r="D713" s="2"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="C714" s="5"/>
-      <c r="D714" s="5"/>
+      <c r="C714" s="2"/>
+      <c r="D714" s="2"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="C715" s="5"/>
-      <c r="D715" s="5"/>
+      <c r="C715" s="2"/>
+      <c r="D715" s="2"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="C716" s="5"/>
-      <c r="D716" s="5"/>
+      <c r="C716" s="2"/>
+      <c r="D716" s="2"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="C717" s="5"/>
-      <c r="D717" s="5"/>
+      <c r="C717" s="2"/>
+      <c r="D717" s="2"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="C718" s="5"/>
-      <c r="D718" s="5"/>
+      <c r="C718" s="2"/>
+      <c r="D718" s="2"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="C719" s="5"/>
-      <c r="D719" s="5"/>
+      <c r="C719" s="2"/>
+      <c r="D719" s="2"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="C720" s="5"/>
-      <c r="D720" s="5"/>
+      <c r="C720" s="2"/>
+      <c r="D720" s="2"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="C721" s="5"/>
-      <c r="D721" s="5"/>
+      <c r="C721" s="2"/>
+      <c r="D721" s="2"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="C722" s="5"/>
-      <c r="D722" s="5"/>
+      <c r="C722" s="2"/>
+      <c r="D722" s="2"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="C723" s="5"/>
-      <c r="D723" s="5"/>
+      <c r="C723" s="2"/>
+      <c r="D723" s="2"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="C724" s="5"/>
-      <c r="D724" s="5"/>
+      <c r="C724" s="2"/>
+      <c r="D724" s="2"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="C725" s="5"/>
-      <c r="D725" s="5"/>
+      <c r="C725" s="2"/>
+      <c r="D725" s="2"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="C726" s="5"/>
-      <c r="D726" s="5"/>
+      <c r="C726" s="2"/>
+      <c r="D726" s="2"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="C727" s="5"/>
-      <c r="D727" s="5"/>
+      <c r="C727" s="2"/>
+      <c r="D727" s="2"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="C728" s="5"/>
-      <c r="D728" s="5"/>
+      <c r="C728" s="2"/>
+      <c r="D728" s="2"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="C729" s="5"/>
-      <c r="D729" s="5"/>
+      <c r="C729" s="2"/>
+      <c r="D729" s="2"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="C730" s="5"/>
-      <c r="D730" s="5"/>
+      <c r="C730" s="2"/>
+      <c r="D730" s="2"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="C731" s="5"/>
-      <c r="D731" s="5"/>
+      <c r="C731" s="2"/>
+      <c r="D731" s="2"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="C732" s="5"/>
-      <c r="D732" s="5"/>
+      <c r="C732" s="2"/>
+      <c r="D732" s="2"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="C733" s="5"/>
-      <c r="D733" s="5"/>
+      <c r="C733" s="2"/>
+      <c r="D733" s="2"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="C734" s="5"/>
-      <c r="D734" s="5"/>
+      <c r="C734" s="2"/>
+      <c r="D734" s="2"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="C735" s="5"/>
-      <c r="D735" s="5"/>
+      <c r="C735" s="2"/>
+      <c r="D735" s="2"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="C736" s="5"/>
-      <c r="D736" s="5"/>
+      <c r="C736" s="2"/>
+      <c r="D736" s="2"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="C737" s="5"/>
-      <c r="D737" s="5"/>
+      <c r="C737" s="2"/>
+      <c r="D737" s="2"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="C738" s="5"/>
-      <c r="D738" s="5"/>
+      <c r="C738" s="2"/>
+      <c r="D738" s="2"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="C739" s="5"/>
-      <c r="D739" s="5"/>
+      <c r="C739" s="2"/>
+      <c r="D739" s="2"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="C740" s="5"/>
-      <c r="D740" s="5"/>
+      <c r="C740" s="2"/>
+      <c r="D740" s="2"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="C741" s="5"/>
-      <c r="D741" s="5"/>
+      <c r="C741" s="2"/>
+      <c r="D741" s="2"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="C742" s="5"/>
-      <c r="D742" s="5"/>
+      <c r="C742" s="2"/>
+      <c r="D742" s="2"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="C743" s="5"/>
-      <c r="D743" s="5"/>
+      <c r="C743" s="2"/>
+      <c r="D743" s="2"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="C744" s="5"/>
-      <c r="D744" s="5"/>
+      <c r="C744" s="2"/>
+      <c r="D744" s="2"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="C745" s="5"/>
-      <c r="D745" s="5"/>
+      <c r="C745" s="2"/>
+      <c r="D745" s="2"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="C746" s="5"/>
-      <c r="D746" s="5"/>
+      <c r="C746" s="2"/>
+      <c r="D746" s="2"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="C747" s="5"/>
-      <c r="D747" s="5"/>
+      <c r="C747" s="2"/>
+      <c r="D747" s="2"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="C748" s="5"/>
-      <c r="D748" s="5"/>
+      <c r="C748" s="2"/>
+      <c r="D748" s="2"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="C749" s="5"/>
-      <c r="D749" s="5"/>
+      <c r="C749" s="2"/>
+      <c r="D749" s="2"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="C750" s="5"/>
-      <c r="D750" s="5"/>
+      <c r="C750" s="2"/>
+      <c r="D750" s="2"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="C751" s="5"/>
-      <c r="D751" s="5"/>
+      <c r="C751" s="2"/>
+      <c r="D751" s="2"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="C752" s="5"/>
-      <c r="D752" s="5"/>
+      <c r="C752" s="2"/>
+      <c r="D752" s="2"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="C753" s="5"/>
-      <c r="D753" s="5"/>
+      <c r="C753" s="2"/>
+      <c r="D753" s="2"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="C754" s="5"/>
-      <c r="D754" s="5"/>
+      <c r="C754" s="2"/>
+      <c r="D754" s="2"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="C755" s="5"/>
-      <c r="D755" s="5"/>
+      <c r="C755" s="2"/>
+      <c r="D755" s="2"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="C756" s="5"/>
-      <c r="D756" s="5"/>
+      <c r="C756" s="2"/>
+      <c r="D756" s="2"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="C757" s="5"/>
-      <c r="D757" s="5"/>
+      <c r="C757" s="2"/>
+      <c r="D757" s="2"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="C758" s="5"/>
-      <c r="D758" s="5"/>
+      <c r="C758" s="2"/>
+      <c r="D758" s="2"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="C759" s="5"/>
-      <c r="D759" s="5"/>
+      <c r="C759" s="2"/>
+      <c r="D759" s="2"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="C760" s="5"/>
-      <c r="D760" s="5"/>
+      <c r="C760" s="2"/>
+      <c r="D760" s="2"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="C761" s="5"/>
-      <c r="D761" s="5"/>
+      <c r="C761" s="2"/>
+      <c r="D761" s="2"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="C762" s="5"/>
-      <c r="D762" s="5"/>
+      <c r="C762" s="2"/>
+      <c r="D762" s="2"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="C763" s="5"/>
-      <c r="D763" s="5"/>
+      <c r="C763" s="2"/>
+      <c r="D763" s="2"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="C764" s="5"/>
-      <c r="D764" s="5"/>
+      <c r="C764" s="2"/>
+      <c r="D764" s="2"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="C765" s="5"/>
-      <c r="D765" s="5"/>
+      <c r="C765" s="2"/>
+      <c r="D765" s="2"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="C766" s="5"/>
-      <c r="D766" s="5"/>
+      <c r="C766" s="2"/>
+      <c r="D766" s="2"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="C767" s="5"/>
-      <c r="D767" s="5"/>
+      <c r="C767" s="2"/>
+      <c r="D767" s="2"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="C768" s="5"/>
-      <c r="D768" s="5"/>
+      <c r="C768" s="2"/>
+      <c r="D768" s="2"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="C769" s="5"/>
-      <c r="D769" s="5"/>
+      <c r="C769" s="2"/>
+      <c r="D769" s="2"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="C770" s="5"/>
-      <c r="D770" s="5"/>
+      <c r="C770" s="2"/>
+      <c r="D770" s="2"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="C771" s="5"/>
-      <c r="D771" s="5"/>
+      <c r="C771" s="2"/>
+      <c r="D771" s="2"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="C772" s="5"/>
-      <c r="D772" s="5"/>
+      <c r="C772" s="2"/>
+      <c r="D772" s="2"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="C773" s="5"/>
-      <c r="D773" s="5"/>
+      <c r="C773" s="2"/>
+      <c r="D773" s="2"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="C774" s="5"/>
-      <c r="D774" s="5"/>
+      <c r="C774" s="2"/>
+      <c r="D774" s="2"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="C775" s="5"/>
-      <c r="D775" s="5"/>
+      <c r="C775" s="2"/>
+      <c r="D775" s="2"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="C776" s="5"/>
-      <c r="D776" s="5"/>
+      <c r="C776" s="2"/>
+      <c r="D776" s="2"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="C777" s="5"/>
-      <c r="D777" s="5"/>
+      <c r="C777" s="2"/>
+      <c r="D777" s="2"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="C778" s="5"/>
-      <c r="D778" s="5"/>
+      <c r="C778" s="2"/>
+      <c r="D778" s="2"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="C779" s="5"/>
-      <c r="D779" s="5"/>
+      <c r="C779" s="2"/>
+      <c r="D779" s="2"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="C780" s="5"/>
-      <c r="D780" s="5"/>
+      <c r="C780" s="2"/>
+      <c r="D780" s="2"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="C781" s="5"/>
-      <c r="D781" s="5"/>
+      <c r="C781" s="2"/>
+      <c r="D781" s="2"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="C782" s="5"/>
-      <c r="D782" s="5"/>
+      <c r="C782" s="2"/>
+      <c r="D782" s="2"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="C783" s="5"/>
-      <c r="D783" s="5"/>
+      <c r="C783" s="2"/>
+      <c r="D783" s="2"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="C784" s="5"/>
-      <c r="D784" s="5"/>
+      <c r="C784" s="2"/>
+      <c r="D784" s="2"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="C785" s="5"/>
-      <c r="D785" s="5"/>
+      <c r="C785" s="2"/>
+      <c r="D785" s="2"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="C786" s="5"/>
-      <c r="D786" s="5"/>
+      <c r="C786" s="2"/>
+      <c r="D786" s="2"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="C787" s="5"/>
-      <c r="D787" s="5"/>
+      <c r="C787" s="2"/>
+      <c r="D787" s="2"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="C788" s="5"/>
-      <c r="D788" s="5"/>
+      <c r="C788" s="2"/>
+      <c r="D788" s="2"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="C789" s="5"/>
-      <c r="D789" s="5"/>
+      <c r="C789" s="2"/>
+      <c r="D789" s="2"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="C790" s="5"/>
-      <c r="D790" s="5"/>
+      <c r="C790" s="2"/>
+      <c r="D790" s="2"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="C791" s="5"/>
-      <c r="D791" s="5"/>
+      <c r="C791" s="2"/>
+      <c r="D791" s="2"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="C792" s="5"/>
-      <c r="D792" s="5"/>
+      <c r="C792" s="2"/>
+      <c r="D792" s="2"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="C793" s="5"/>
-      <c r="D793" s="5"/>
+      <c r="C793" s="2"/>
+      <c r="D793" s="2"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="C794" s="5"/>
-      <c r="D794" s="5"/>
+      <c r="C794" s="2"/>
+      <c r="D794" s="2"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="C795" s="5"/>
-      <c r="D795" s="5"/>
+      <c r="C795" s="2"/>
+      <c r="D795" s="2"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="C796" s="5"/>
-      <c r="D796" s="5"/>
+      <c r="C796" s="2"/>
+      <c r="D796" s="2"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="C797" s="5"/>
-      <c r="D797" s="5"/>
+      <c r="C797" s="2"/>
+      <c r="D797" s="2"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="C798" s="5"/>
-      <c r="D798" s="5"/>
+      <c r="C798" s="2"/>
+      <c r="D798" s="2"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="C799" s="5"/>
-      <c r="D799" s="5"/>
+      <c r="C799" s="2"/>
+      <c r="D799" s="2"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="C800" s="5"/>
-      <c r="D800" s="5"/>
+      <c r="C800" s="2"/>
+      <c r="D800" s="2"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="C801" s="5"/>
-      <c r="D801" s="5"/>
+      <c r="C801" s="2"/>
+      <c r="D801" s="2"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="C802" s="5"/>
-      <c r="D802" s="5"/>
+      <c r="C802" s="2"/>
+      <c r="D802" s="2"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="C803" s="5"/>
-      <c r="D803" s="5"/>
+      <c r="C803" s="2"/>
+      <c r="D803" s="2"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="C804" s="5"/>
-      <c r="D804" s="5"/>
+      <c r="C804" s="2"/>
+      <c r="D804" s="2"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="C805" s="5"/>
-      <c r="D805" s="5"/>
+      <c r="C805" s="2"/>
+      <c r="D805" s="2"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="C806" s="5"/>
-      <c r="D806" s="5"/>
+      <c r="C806" s="2"/>
+      <c r="D806" s="2"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="C807" s="5"/>
-      <c r="D807" s="5"/>
+      <c r="C807" s="2"/>
+      <c r="D807" s="2"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="C808" s="5"/>
-      <c r="D808" s="5"/>
+      <c r="C808" s="2"/>
+      <c r="D808" s="2"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="C809" s="5"/>
-      <c r="D809" s="5"/>
+      <c r="C809" s="2"/>
+      <c r="D809" s="2"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="C810" s="5"/>
-      <c r="D810" s="5"/>
+      <c r="C810" s="2"/>
+      <c r="D810" s="2"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="C811" s="5"/>
-      <c r="D811" s="5"/>
+      <c r="C811" s="2"/>
+      <c r="D811" s="2"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="C812" s="5"/>
-      <c r="D812" s="5"/>
+      <c r="C812" s="2"/>
+      <c r="D812" s="2"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="C813" s="5"/>
-      <c r="D813" s="5"/>
+      <c r="C813" s="2"/>
+      <c r="D813" s="2"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="C814" s="5"/>
-      <c r="D814" s="5"/>
+      <c r="C814" s="2"/>
+      <c r="D814" s="2"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="C815" s="5"/>
-      <c r="D815" s="5"/>
+      <c r="C815" s="2"/>
+      <c r="D815" s="2"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="C816" s="5"/>
-      <c r="D816" s="5"/>
+      <c r="C816" s="2"/>
+      <c r="D816" s="2"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="C817" s="5"/>
-      <c r="D817" s="5"/>
+      <c r="C817" s="2"/>
+      <c r="D817" s="2"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="C818" s="5"/>
-      <c r="D818" s="5"/>
+      <c r="C818" s="2"/>
+      <c r="D818" s="2"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="C819" s="5"/>
-      <c r="D819" s="5"/>
+      <c r="C819" s="2"/>
+      <c r="D819" s="2"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="C820" s="5"/>
-      <c r="D820" s="5"/>
+      <c r="C820" s="2"/>
+      <c r="D820" s="2"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="C821" s="5"/>
-      <c r="D821" s="5"/>
+      <c r="C821" s="2"/>
+      <c r="D821" s="2"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="C822" s="5"/>
-      <c r="D822" s="5"/>
+      <c r="C822" s="2"/>
+      <c r="D822" s="2"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="C823" s="5"/>
-      <c r="D823" s="5"/>
+      <c r="C823" s="2"/>
+      <c r="D823" s="2"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="C824" s="5"/>
-      <c r="D824" s="5"/>
+      <c r="C824" s="2"/>
+      <c r="D824" s="2"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="C825" s="5"/>
-      <c r="D825" s="5"/>
+      <c r="C825" s="2"/>
+      <c r="D825" s="2"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="C826" s="5"/>
-      <c r="D826" s="5"/>
+      <c r="C826" s="2"/>
+      <c r="D826" s="2"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="C827" s="5"/>
-      <c r="D827" s="5"/>
+      <c r="C827" s="2"/>
+      <c r="D827" s="2"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="C828" s="5"/>
-      <c r="D828" s="5"/>
+      <c r="C828" s="2"/>
+      <c r="D828" s="2"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="C829" s="5"/>
-      <c r="D829" s="5"/>
+      <c r="C829" s="2"/>
+      <c r="D829" s="2"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="C830" s="5"/>
-      <c r="D830" s="5"/>
+      <c r="C830" s="2"/>
+      <c r="D830" s="2"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="C831" s="5"/>
-      <c r="D831" s="5"/>
+      <c r="C831" s="2"/>
+      <c r="D831" s="2"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="C832" s="5"/>
-      <c r="D832" s="5"/>
+      <c r="C832" s="2"/>
+      <c r="D832" s="2"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="C833" s="5"/>
-      <c r="D833" s="5"/>
+      <c r="C833" s="2"/>
+      <c r="D833" s="2"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="C834" s="5"/>
-      <c r="D834" s="5"/>
+      <c r="C834" s="2"/>
+      <c r="D834" s="2"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="C835" s="5"/>
-      <c r="D835" s="5"/>
+      <c r="C835" s="2"/>
+      <c r="D835" s="2"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="C836" s="5"/>
-      <c r="D836" s="5"/>
+      <c r="C836" s="2"/>
+      <c r="D836" s="2"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="C837" s="5"/>
-      <c r="D837" s="5"/>
+      <c r="C837" s="2"/>
+      <c r="D837" s="2"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="C838" s="5"/>
-      <c r="D838" s="5"/>
+      <c r="C838" s="2"/>
+      <c r="D838" s="2"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="C839" s="5"/>
-      <c r="D839" s="5"/>
+      <c r="C839" s="2"/>
+      <c r="D839" s="2"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="C840" s="5"/>
-      <c r="D840" s="5"/>
+      <c r="C840" s="2"/>
+      <c r="D840" s="2"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="C841" s="5"/>
-      <c r="D841" s="5"/>
+      <c r="C841" s="2"/>
+      <c r="D841" s="2"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="C842" s="5"/>
-      <c r="D842" s="5"/>
+      <c r="C842" s="2"/>
+      <c r="D842" s="2"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="C843" s="5"/>
-      <c r="D843" s="5"/>
+      <c r="C843" s="2"/>
+      <c r="D843" s="2"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="C844" s="5"/>
-      <c r="D844" s="5"/>
+      <c r="C844" s="2"/>
+      <c r="D844" s="2"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="C845" s="5"/>
-      <c r="D845" s="5"/>
+      <c r="C845" s="2"/>
+      <c r="D845" s="2"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="C846" s="5"/>
-      <c r="D846" s="5"/>
+      <c r="C846" s="2"/>
+      <c r="D846" s="2"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="C847" s="5"/>
-      <c r="D847" s="5"/>
+      <c r="C847" s="2"/>
+      <c r="D847" s="2"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="C848" s="5"/>
-      <c r="D848" s="5"/>
+      <c r="C848" s="2"/>
+      <c r="D848" s="2"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="C849" s="5"/>
-      <c r="D849" s="5"/>
+      <c r="C849" s="2"/>
+      <c r="D849" s="2"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="C850" s="5"/>
-      <c r="D850" s="5"/>
+      <c r="C850" s="2"/>
+      <c r="D850" s="2"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="C851" s="5"/>
-      <c r="D851" s="5"/>
+      <c r="C851" s="2"/>
+      <c r="D851" s="2"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="C852" s="5"/>
-      <c r="D852" s="5"/>
+      <c r="C852" s="2"/>
+      <c r="D852" s="2"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="C853" s="5"/>
-      <c r="D853" s="5"/>
+      <c r="C853" s="2"/>
+      <c r="D853" s="2"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="C854" s="5"/>
-      <c r="D854" s="5"/>
+      <c r="C854" s="2"/>
+      <c r="D854" s="2"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="C855" s="5"/>
-      <c r="D855" s="5"/>
+      <c r="C855" s="2"/>
+      <c r="D855" s="2"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="C856" s="5"/>
-      <c r="D856" s="5"/>
+      <c r="C856" s="2"/>
+      <c r="D856" s="2"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="C857" s="5"/>
-      <c r="D857" s="5"/>
+      <c r="C857" s="2"/>
+      <c r="D857" s="2"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="C858" s="5"/>
-      <c r="D858" s="5"/>
+      <c r="C858" s="2"/>
+      <c r="D858" s="2"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="C859" s="5"/>
-      <c r="D859" s="5"/>
+      <c r="C859" s="2"/>
+      <c r="D859" s="2"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="C860" s="5"/>
-      <c r="D860" s="5"/>
+      <c r="C860" s="2"/>
+      <c r="D860" s="2"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="C861" s="5"/>
-      <c r="D861" s="5"/>
+      <c r="C861" s="2"/>
+      <c r="D861" s="2"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="C862" s="5"/>
-      <c r="D862" s="5"/>
+      <c r="C862" s="2"/>
+      <c r="D862" s="2"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="C863" s="5"/>
-      <c r="D863" s="5"/>
+      <c r="C863" s="2"/>
+      <c r="D863" s="2"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="C864" s="5"/>
-      <c r="D864" s="5"/>
+      <c r="C864" s="2"/>
+      <c r="D864" s="2"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="C865" s="5"/>
-      <c r="D865" s="5"/>
+      <c r="C865" s="2"/>
+      <c r="D865" s="2"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="C866" s="5"/>
-      <c r="D866" s="5"/>
+      <c r="C866" s="2"/>
+      <c r="D866" s="2"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="C867" s="5"/>
-      <c r="D867" s="5"/>
+      <c r="C867" s="2"/>
+      <c r="D867" s="2"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="C868" s="5"/>
-      <c r="D868" s="5"/>
+      <c r="C868" s="2"/>
+      <c r="D868" s="2"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="C869" s="5"/>
-      <c r="D869" s="5"/>
+      <c r="C869" s="2"/>
+      <c r="D869" s="2"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="C870" s="5"/>
-      <c r="D870" s="5"/>
+      <c r="C870" s="2"/>
+      <c r="D870" s="2"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="C871" s="5"/>
-      <c r="D871" s="5"/>
+      <c r="C871" s="2"/>
+      <c r="D871" s="2"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="C872" s="5"/>
-      <c r="D872" s="5"/>
+      <c r="C872" s="2"/>
+      <c r="D872" s="2"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="C873" s="5"/>
-      <c r="D873" s="5"/>
+      <c r="C873" s="2"/>
+      <c r="D873" s="2"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="C874" s="5"/>
-      <c r="D874" s="5"/>
+      <c r="C874" s="2"/>
+      <c r="D874" s="2"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="C875" s="5"/>
-      <c r="D875" s="5"/>
+      <c r="C875" s="2"/>
+      <c r="D875" s="2"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="C876" s="5"/>
-      <c r="D876" s="5"/>
+      <c r="C876" s="2"/>
+      <c r="D876" s="2"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="C877" s="5"/>
-      <c r="D877" s="5"/>
+      <c r="C877" s="2"/>
+      <c r="D877" s="2"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="C878" s="5"/>
-      <c r="D878" s="5"/>
+      <c r="C878" s="2"/>
+      <c r="D878" s="2"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="C879" s="5"/>
-      <c r="D879" s="5"/>
+      <c r="C879" s="2"/>
+      <c r="D879" s="2"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="C880" s="5"/>
-      <c r="D880" s="5"/>
+      <c r="C880" s="2"/>
+      <c r="D880" s="2"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="C881" s="5"/>
-      <c r="D881" s="5"/>
+      <c r="C881" s="2"/>
+      <c r="D881" s="2"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="C882" s="5"/>
-      <c r="D882" s="5"/>
+      <c r="C882" s="2"/>
+      <c r="D882" s="2"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="C883" s="5"/>
-      <c r="D883" s="5"/>
+      <c r="C883" s="2"/>
+      <c r="D883" s="2"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="C884" s="5"/>
-      <c r="D884" s="5"/>
+      <c r="C884" s="2"/>
+      <c r="D884" s="2"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="C885" s="5"/>
-      <c r="D885" s="5"/>
+      <c r="C885" s="2"/>
+      <c r="D885" s="2"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="C886" s="5"/>
-      <c r="D886" s="5"/>
+      <c r="C886" s="2"/>
+      <c r="D886" s="2"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="C887" s="5"/>
-      <c r="D887" s="5"/>
+      <c r="C887" s="2"/>
+      <c r="D887" s="2"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="C888" s="5"/>
-      <c r="D888" s="5"/>
+      <c r="C888" s="2"/>
+      <c r="D888" s="2"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="C889" s="5"/>
-      <c r="D889" s="5"/>
+      <c r="C889" s="2"/>
+      <c r="D889" s="2"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="C890" s="5"/>
-      <c r="D890" s="5"/>
+      <c r="C890" s="2"/>
+      <c r="D890" s="2"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="C891" s="5"/>
-      <c r="D891" s="5"/>
+      <c r="C891" s="2"/>
+      <c r="D891" s="2"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="C892" s="5"/>
-      <c r="D892" s="5"/>
+      <c r="C892" s="2"/>
+      <c r="D892" s="2"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="C893" s="5"/>
-      <c r="D893" s="5"/>
+      <c r="C893" s="2"/>
+      <c r="D893" s="2"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="C894" s="5"/>
-      <c r="D894" s="5"/>
+      <c r="C894" s="2"/>
+      <c r="D894" s="2"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="C895" s="5"/>
-      <c r="D895" s="5"/>
+      <c r="C895" s="2"/>
+      <c r="D895" s="2"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="C896" s="5"/>
-      <c r="D896" s="5"/>
+      <c r="C896" s="2"/>
+      <c r="D896" s="2"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="C897" s="5"/>
-      <c r="D897" s="5"/>
+      <c r="C897" s="2"/>
+      <c r="D897" s="2"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="C898" s="5"/>
-      <c r="D898" s="5"/>
+      <c r="C898" s="2"/>
+      <c r="D898" s="2"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="C899" s="5"/>
-      <c r="D899" s="5"/>
+      <c r="C899" s="2"/>
+      <c r="D899" s="2"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="C900" s="5"/>
-      <c r="D900" s="5"/>
+      <c r="C900" s="2"/>
+      <c r="D900" s="2"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="C901" s="5"/>
-      <c r="D901" s="5"/>
+      <c r="C901" s="2"/>
+      <c r="D901" s="2"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="C902" s="5"/>
-      <c r="D902" s="5"/>
+      <c r="C902" s="2"/>
+      <c r="D902" s="2"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="C903" s="5"/>
-      <c r="D903" s="5"/>
+      <c r="C903" s="2"/>
+      <c r="D903" s="2"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="C904" s="5"/>
-      <c r="D904" s="5"/>
+      <c r="C904" s="2"/>
+      <c r="D904" s="2"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="C905" s="5"/>
-      <c r="D905" s="5"/>
+      <c r="C905" s="2"/>
+      <c r="D905" s="2"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="C906" s="5"/>
-      <c r="D906" s="5"/>
+      <c r="C906" s="2"/>
+      <c r="D906" s="2"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="C907" s="5"/>
-      <c r="D907" s="5"/>
+      <c r="C907" s="2"/>
+      <c r="D907" s="2"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="C908" s="5"/>
-      <c r="D908" s="5"/>
+      <c r="C908" s="2"/>
+      <c r="D908" s="2"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="C909" s="5"/>
-      <c r="D909" s="5"/>
+      <c r="C909" s="2"/>
+      <c r="D909" s="2"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="C910" s="5"/>
-      <c r="D910" s="5"/>
+      <c r="C910" s="2"/>
+      <c r="D910" s="2"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="C911" s="5"/>
-      <c r="D911" s="5"/>
+      <c r="C911" s="2"/>
+      <c r="D911" s="2"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="C912" s="5"/>
-      <c r="D912" s="5"/>
+      <c r="C912" s="2"/>
+      <c r="D912" s="2"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="C913" s="5"/>
-      <c r="D913" s="5"/>
+      <c r="C913" s="2"/>
+      <c r="D913" s="2"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="C914" s="5"/>
-      <c r="D914" s="5"/>
+      <c r="C914" s="2"/>
+      <c r="D914" s="2"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="C915" s="5"/>
-      <c r="D915" s="5"/>
+      <c r="C915" s="2"/>
+      <c r="D915" s="2"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="C916" s="5"/>
-      <c r="D916" s="5"/>
+      <c r="C916" s="2"/>
+      <c r="D916" s="2"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="C917" s="5"/>
-      <c r="D917" s="5"/>
+      <c r="C917" s="2"/>
+      <c r="D917" s="2"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="C918" s="5"/>
-      <c r="D918" s="5"/>
+      <c r="C918" s="2"/>
+      <c r="D918" s="2"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="C919" s="5"/>
-      <c r="D919" s="5"/>
+      <c r="C919" s="2"/>
+      <c r="D919" s="2"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="C920" s="5"/>
-      <c r="D920" s="5"/>
+      <c r="C920" s="2"/>
+      <c r="D920" s="2"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="C921" s="5"/>
-      <c r="D921" s="5"/>
+      <c r="C921" s="2"/>
+      <c r="D921" s="2"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="C922" s="5"/>
-      <c r="D922" s="5"/>
+      <c r="C922" s="2"/>
+      <c r="D922" s="2"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="C923" s="5"/>
-      <c r="D923" s="5"/>
+      <c r="C923" s="2"/>
+      <c r="D923" s="2"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="C924" s="5"/>
-      <c r="D924" s="5"/>
+      <c r="C924" s="2"/>
+      <c r="D924" s="2"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="C925" s="5"/>
-      <c r="D925" s="5"/>
+      <c r="C925" s="2"/>
+      <c r="D925" s="2"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="C926" s="5"/>
-      <c r="D926" s="5"/>
+      <c r="C926" s="2"/>
+      <c r="D926" s="2"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="C927" s="5"/>
-      <c r="D927" s="5"/>
+      <c r="C927" s="2"/>
+      <c r="D927" s="2"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="C928" s="5"/>
-      <c r="D928" s="5"/>
+      <c r="C928" s="2"/>
+      <c r="D928" s="2"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="C929" s="5"/>
-      <c r="D929" s="5"/>
+      <c r="C929" s="2"/>
+      <c r="D929" s="2"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="C930" s="5"/>
-      <c r="D930" s="5"/>
+      <c r="C930" s="2"/>
+      <c r="D930" s="2"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="C931" s="5"/>
-      <c r="D931" s="5"/>
+      <c r="C931" s="2"/>
+      <c r="D931" s="2"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="C932" s="5"/>
-      <c r="D932" s="5"/>
+      <c r="C932" s="2"/>
+      <c r="D932" s="2"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="C933" s="5"/>
-      <c r="D933" s="5"/>
+      <c r="C933" s="2"/>
+      <c r="D933" s="2"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="C934" s="5"/>
-      <c r="D934" s="5"/>
+      <c r="C934" s="2"/>
+      <c r="D934" s="2"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="C935" s="5"/>
-      <c r="D935" s="5"/>
+      <c r="C935" s="2"/>
+      <c r="D935" s="2"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="C936" s="5"/>
-      <c r="D936" s="5"/>
+      <c r="C936" s="2"/>
+      <c r="D936" s="2"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="C937" s="5"/>
-      <c r="D937" s="5"/>
+      <c r="C937" s="2"/>
+      <c r="D937" s="2"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="C938" s="5"/>
-      <c r="D938" s="5"/>
+      <c r="C938" s="2"/>
+      <c r="D938" s="2"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="C939" s="5"/>
-      <c r="D939" s="5"/>
+      <c r="C939" s="2"/>
+      <c r="D939" s="2"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="C940" s="5"/>
-      <c r="D940" s="5"/>
+      <c r="C940" s="2"/>
+      <c r="D940" s="2"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="C941" s="5"/>
-      <c r="D941" s="5"/>
+      <c r="C941" s="2"/>
+      <c r="D941" s="2"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="C942" s="5"/>
-      <c r="D942" s="5"/>
+      <c r="C942" s="2"/>
+      <c r="D942" s="2"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="C943" s="5"/>
-      <c r="D943" s="5"/>
+      <c r="C943" s="2"/>
+      <c r="D943" s="2"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="C944" s="5"/>
-      <c r="D944" s="5"/>
+      <c r="C944" s="2"/>
+      <c r="D944" s="2"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="C945" s="5"/>
-      <c r="D945" s="5"/>
+      <c r="C945" s="2"/>
+      <c r="D945" s="2"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="C946" s="5"/>
-      <c r="D946" s="5"/>
+      <c r="C946" s="2"/>
+      <c r="D946" s="2"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="C947" s="5"/>
-      <c r="D947" s="5"/>
+      <c r="C947" s="2"/>
+      <c r="D947" s="2"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="C948" s="5"/>
-      <c r="D948" s="5"/>
+      <c r="C948" s="2"/>
+      <c r="D948" s="2"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="C949" s="5"/>
-      <c r="D949" s="5"/>
+      <c r="C949" s="2"/>
+      <c r="D949" s="2"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="C950" s="5"/>
-      <c r="D950" s="5"/>
+      <c r="C950" s="2"/>
+      <c r="D950" s="2"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="C951" s="5"/>
-      <c r="D951" s="5"/>
+      <c r="C951" s="2"/>
+      <c r="D951" s="2"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="C952" s="5"/>
-      <c r="D952" s="5"/>
+      <c r="C952" s="2"/>
+      <c r="D952" s="2"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="C953" s="5"/>
-      <c r="D953" s="5"/>
+      <c r="C953" s="2"/>
+      <c r="D953" s="2"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="C954" s="5"/>
-      <c r="D954" s="5"/>
+      <c r="C954" s="2"/>
+      <c r="D954" s="2"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="C955" s="5"/>
-      <c r="D955" s="5"/>
+      <c r="C955" s="2"/>
+      <c r="D955" s="2"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="C956" s="5"/>
-      <c r="D956" s="5"/>
+      <c r="C956" s="2"/>
+      <c r="D956" s="2"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="C957" s="5"/>
-      <c r="D957" s="5"/>
+      <c r="C957" s="2"/>
+      <c r="D957" s="2"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="C958" s="5"/>
-      <c r="D958" s="5"/>
+      <c r="C958" s="2"/>
+      <c r="D958" s="2"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="C959" s="5"/>
-      <c r="D959" s="5"/>
+      <c r="C959" s="2"/>
+      <c r="D959" s="2"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="C960" s="5"/>
-      <c r="D960" s="5"/>
+      <c r="C960" s="2"/>
+      <c r="D960" s="2"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="C961" s="5"/>
-      <c r="D961" s="5"/>
+      <c r="C961" s="2"/>
+      <c r="D961" s="2"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="C962" s="5"/>
-      <c r="D962" s="5"/>
+      <c r="C962" s="2"/>
+      <c r="D962" s="2"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="C963" s="5"/>
-      <c r="D963" s="5"/>
+      <c r="C963" s="2"/>
+      <c r="D963" s="2"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="C964" s="5"/>
-      <c r="D964" s="5"/>
+      <c r="C964" s="2"/>
+      <c r="D964" s="2"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="C965" s="5"/>
-      <c r="D965" s="5"/>
+      <c r="C965" s="2"/>
+      <c r="D965" s="2"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="C966" s="5"/>
-      <c r="D966" s="5"/>
+      <c r="C966" s="2"/>
+      <c r="D966" s="2"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="C967" s="5"/>
-      <c r="D967" s="5"/>
+      <c r="C967" s="2"/>
+      <c r="D967" s="2"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="C968" s="5"/>
-      <c r="D968" s="5"/>
+      <c r="C968" s="2"/>
+      <c r="D968" s="2"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="C969" s="5"/>
-      <c r="D969" s="5"/>
+      <c r="C969" s="2"/>
+      <c r="D969" s="2"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="C970" s="5"/>
-      <c r="D970" s="5"/>
+      <c r="C970" s="2"/>
+      <c r="D970" s="2"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="C971" s="5"/>
-      <c r="D971" s="5"/>
+      <c r="C971" s="2"/>
+      <c r="D971" s="2"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="C972" s="5"/>
-      <c r="D972" s="5"/>
+      <c r="C972" s="2"/>
+      <c r="D972" s="2"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="C973" s="5"/>
-      <c r="D973" s="5"/>
+      <c r="C973" s="2"/>
+      <c r="D973" s="2"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="C974" s="5"/>
-      <c r="D974" s="5"/>
+      <c r="C974" s="2"/>
+      <c r="D974" s="2"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="C975" s="5"/>
-      <c r="D975" s="5"/>
+      <c r="C975" s="2"/>
+      <c r="D975" s="2"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="C976" s="5"/>
-      <c r="D976" s="5"/>
+      <c r="C976" s="2"/>
+      <c r="D976" s="2"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="C977" s="5"/>
-      <c r="D977" s="5"/>
+      <c r="C977" s="2"/>
+      <c r="D977" s="2"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="C978" s="5"/>
-      <c r="D978" s="5"/>
+      <c r="C978" s="2"/>
+      <c r="D978" s="2"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="C979" s="5"/>
-      <c r="D979" s="5"/>
+      <c r="C979" s="2"/>
+      <c r="D979" s="2"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="C980" s="5"/>
-      <c r="D980" s="5"/>
+      <c r="C980" s="2"/>
+      <c r="D980" s="2"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="C981" s="5"/>
-      <c r="D981" s="5"/>
+      <c r="C981" s="2"/>
+      <c r="D981" s="2"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="C982" s="5"/>
-      <c r="D982" s="5"/>
+      <c r="C982" s="2"/>
+      <c r="D982" s="2"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="C983" s="5"/>
-      <c r="D983" s="5"/>
+      <c r="C983" s="2"/>
+      <c r="D983" s="2"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="C984" s="5"/>
-      <c r="D984" s="5"/>
+      <c r="C984" s="2"/>
+      <c r="D984" s="2"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="C985" s="5"/>
-      <c r="D985" s="5"/>
+      <c r="C985" s="2"/>
+      <c r="D985" s="2"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="C986" s="5"/>
-      <c r="D986" s="5"/>
+      <c r="C986" s="2"/>
+      <c r="D986" s="2"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="C987" s="5"/>
-      <c r="D987" s="5"/>
+      <c r="C987" s="2"/>
+      <c r="D987" s="2"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="C988" s="5"/>
-      <c r="D988" s="5"/>
+      <c r="C988" s="2"/>
+      <c r="D988" s="2"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="C989" s="5"/>
-      <c r="D989" s="5"/>
+      <c r="C989" s="2"/>
+      <c r="D989" s="2"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="C990" s="5"/>
-      <c r="D990" s="5"/>
+      <c r="C990" s="2"/>
+      <c r="D990" s="2"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="C991" s="5"/>
-      <c r="D991" s="5"/>
+      <c r="C991" s="2"/>
+      <c r="D991" s="2"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="C992" s="5"/>
-      <c r="D992" s="5"/>
+      <c r="C992" s="2"/>
+      <c r="D992" s="2"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="C993" s="5"/>
-      <c r="D993" s="5"/>
+      <c r="C993" s="2"/>
+      <c r="D993" s="2"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="C994" s="5"/>
-      <c r="D994" s="5"/>
+      <c r="C994" s="2"/>
+      <c r="D994" s="2"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="C995" s="5"/>
-      <c r="D995" s="5"/>
+      <c r="C995" s="2"/>
+      <c r="D995" s="2"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="C996" s="5"/>
-      <c r="D996" s="5"/>
+      <c r="C996" s="2"/>
+      <c r="D996" s="2"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="C997" s="5"/>
-      <c r="D997" s="5"/>
+      <c r="C997" s="2"/>
+      <c r="D997" s="2"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="C998" s="5"/>
-      <c r="D998" s="5"/>
+      <c r="C998" s="2"/>
+      <c r="D998" s="2"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="C999" s="5"/>
-      <c r="D999" s="5"/>
+      <c r="C999" s="2"/>
+      <c r="D999" s="2"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="C1000" s="5"/>
-      <c r="D1000" s="5"/>
+      <c r="C1000" s="2"/>
+      <c r="D1000" s="2"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="C1001" s="5"/>
-      <c r="D1001" s="5"/>
+      <c r="C1001" s="2"/>
+      <c r="D1001" s="2"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
-      <c r="C1002" s="5"/>
-      <c r="D1002" s="5"/>
+      <c r="C1002" s="2"/>
+      <c r="D1002" s="2"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
-      <c r="C1003" s="5"/>
-      <c r="D1003" s="5"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
-      <c r="C1004" s="5"/>
-      <c r="D1004" s="5"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
-      <c r="C1005" s="5"/>
-      <c r="D1005" s="5"/>
+      <c r="C1005" s="2"/>
+      <c r="D1005" s="2"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
-      <c r="C1006" s="5"/>
-      <c r="D1006" s="5"/>
+      <c r="C1006" s="2"/>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
-      <c r="C1007" s="5"/>
-      <c r="D1007" s="5"/>
+      <c r="C1007" s="2"/>
+      <c r="D1007" s="2"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
-      <c r="C1008" s="5"/>
-      <c r="D1008" s="5"/>
+      <c r="C1008" s="2"/>
+      <c r="D1008" s="2"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
-      <c r="C1009" s="5"/>
-      <c r="D1009" s="5"/>
+      <c r="C1009" s="2"/>
+      <c r="D1009" s="2"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
-      <c r="C1010" s="5"/>
-      <c r="D1010" s="5"/>
+      <c r="C1010" s="2"/>
+      <c r="D1010" s="2"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
-      <c r="C1011" s="5"/>
-      <c r="D1011" s="5"/>
+      <c r="C1011" s="2"/>
+      <c r="D1011" s="2"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
-      <c r="C1012" s="5"/>
-      <c r="D1012" s="5"/>
+      <c r="C1012" s="2"/>
+      <c r="D1012" s="2"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
-      <c r="C1013" s="5"/>
-      <c r="D1013" s="5"/>
+      <c r="C1013" s="2"/>
+      <c r="D1013" s="2"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
-      <c r="C1014" s="5"/>
-      <c r="D1014" s="5"/>
+      <c r="C1014" s="2"/>
+      <c r="D1014" s="2"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
-      <c r="C1015" s="5"/>
-      <c r="D1015" s="5"/>
+      <c r="C1015" s="2"/>
+      <c r="D1015" s="2"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
-      <c r="C1016" s="5"/>
-      <c r="D1016" s="5"/>
+      <c r="C1016" s="2"/>
+      <c r="D1016" s="2"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
-      <c r="C1017" s="5"/>
-      <c r="D1017" s="5"/>
+      <c r="C1017" s="2"/>
+      <c r="D1017" s="2"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
-      <c r="C1018" s="5"/>
-      <c r="D1018" s="5"/>
+      <c r="C1018" s="2"/>
+      <c r="D1018" s="2"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
-      <c r="C1019" s="5"/>
-      <c r="D1019" s="5"/>
+      <c r="C1019" s="2"/>
+      <c r="D1019" s="2"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
-      <c r="C1020" s="5"/>
-      <c r="D1020" s="5"/>
+      <c r="C1020" s="2"/>
+      <c r="D1020" s="2"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
-      <c r="C1021" s="5"/>
-      <c r="D1021" s="5"/>
+      <c r="C1021" s="2"/>
+      <c r="D1021" s="2"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
-      <c r="C1022" s="5"/>
-      <c r="D1022" s="5"/>
+      <c r="C1022" s="2"/>
+      <c r="D1022" s="2"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
-      <c r="C1023" s="5"/>
-      <c r="D1023" s="5"/>
+      <c r="C1023" s="2"/>
+      <c r="D1023" s="2"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
-      <c r="C1024" s="5"/>
-      <c r="D1024" s="5"/>
+      <c r="C1024" s="2"/>
+      <c r="D1024" s="2"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
-      <c r="C1025" s="5"/>
-      <c r="D1025" s="5"/>
+      <c r="C1025" s="2"/>
+      <c r="D1025" s="2"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1">
-      <c r="C1026" s="5"/>
-      <c r="D1026" s="5"/>
+      <c r="C1026" s="2"/>
+      <c r="D1026" s="2"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1">
-      <c r="C1027" s="5"/>
-      <c r="D1027" s="5"/>
+      <c r="C1027" s="2"/>
+      <c r="D1027" s="2"/>
+    </row>
+    <row r="1028" ht="12.75" customHeight="1">
+      <c r="C1028" s="2"/>
+      <c r="D1028" s="2"/>
+    </row>
+    <row r="1029" ht="12.75" customHeight="1">
+      <c r="C1029" s="2"/>
+      <c r="D1029" s="2"/>
+    </row>
+    <row r="1030" ht="12.75" customHeight="1">
+      <c r="C1030" s="2"/>
+      <c r="D1030" s="2"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5844,7 +5906,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -5903,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -5917,13 +5979,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -5931,97 +5993,97 @@
         <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>38</v>
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>41</v>
+      <c r="A9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="A10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
+      <c r="C13" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7035,36 +7097,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>35</v>
+      <c r="D2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,17 +13,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="252">
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>Sina pesa</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
   <si>
     <t>form_title</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
     <t>form_id</t>
   </si>
   <si>
@@ -39,126 +81,87 @@
     <t>instance_name</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
     <t>Referral Follow-up</t>
   </si>
   <si>
+    <t>read_only</t>
+  </si>
+  <si>
     <t>referral_follow_up</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
-    <t>Sina pesa</t>
-  </si>
-  <si>
-    <t>required</t>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
   </si>
   <si>
     <t>did_not_want</t>
   </si>
   <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
+    <t>repeat_count</t>
   </si>
   <si>
     <t>I did not want to go</t>
   </si>
   <si>
-    <t>read_only</t>
-  </si>
-  <si>
     <t>Sikutaka kwenda</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
+    <t>begin group</t>
   </si>
   <si>
     <t>no_permission</t>
   </si>
   <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
     <t>I did not have permission to go</t>
   </si>
   <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
+    <t>inputs</t>
   </si>
   <si>
     <t>Sikupewa ruhusa ya kwenda</t>
   </si>
   <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>begin group</t>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
   </si>
   <si>
     <t>other</t>
   </si>
   <si>
-    <t>inputs</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
     <t>Nyenginezo</t>
   </si>
   <si>
@@ -168,93 +171,90 @@
     <t>reason_didnt_get_svc</t>
   </si>
   <si>
-    <t>./source = 'user'</t>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>source_form</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
+  </si>
+  <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>services_not_offered</t>
+  </si>
+  <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
+    <t>Huduma nilizotaka hazikuwepo.</t>
+  </si>
+  <si>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
+  </si>
+  <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
+    <t>Walitaka nilipie huduma</t>
+  </si>
+  <si>
+    <t>refer_muac_flag</t>
+  </si>
+  <si>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
+  </si>
+  <si>
+    <t>refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>refer_vaccines_flag</t>
   </si>
   <si>
     <t>data</t>
   </si>
   <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>source_form</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>last_visit_date</t>
-  </si>
-  <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
-    <t>refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
-  </si>
-  <si>
-    <t>refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
-    <t>refer_secondary_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
-    <t>refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
-    <t>refer_muac_flag</t>
-  </si>
-  <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
-  </si>
-  <si>
-    <t>refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t>refer_vaccines_flag</t>
-  </si>
-  <si>
     <t>refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
@@ -264,6 +264,15 @@
     <t>due_date_human_readable</t>
   </si>
   <si>
+    <t>refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
@@ -382,6 +391,15 @@
   </si>
   <si>
     <t>../inputs/due_date_human_readable</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>../refer_flag_pregnancy_complications</t>
   </si>
   <si>
     <t>age_days</t>
@@ -601,6 +619,27 @@
   </si>
   <si>
     <t>../../inputs/refer_slow_to_learn_specifics_flag = 1</t>
+  </si>
+  <si>
+    <t>reason_refer_pregnancy_emergency_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address urgent pregnancy danger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za dharura za mama mjamzito.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_emergency_danger_sign= 1</t>
+  </si>
+  <si>
+    <t>reason_refer_pregnancy_other_danger_signs</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address one or more pregnancy danger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_pregnancy_complications= 1 or ../../inputs/refer_flag_pregnancy_issues= 1</t>
   </si>
   <si>
     <t>select_one yes_no</t>
@@ -757,11 +796,11 @@
     </font>
     <font/>
     <font>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Roboto"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -791,33 +830,36 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -826,7 +868,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -858,490 +900,488 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="14.43"/>
     <col customWidth="1" min="2" max="2" width="43.57"/>
-    <col customWidth="1" min="3" max="17" width="14.43"/>
+    <col customWidth="1" min="3" max="3" width="37.29"/>
+    <col customWidth="1" min="4" max="17" width="14.43"/>
     <col customWidth="1" min="18" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="D2" s="2"/>
-      <c r="F2" s="5" t="s">
-        <v>51</v>
+      <c r="F2" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>54</v>
+      <c r="A8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>47</v>
+      <c r="C16" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>87</v>
+      <c r="C18" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="D22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>93</v>
-      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="D28" s="2"/>
-      <c r="L28" s="2" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="L29" s="2" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="L30" s="2" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="L31" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>105</v>
+      <c r="A32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="L32" s="7" t="s">
-        <v>106</v>
+      <c r="L32" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="L33" t="s">
-        <v>107</v>
+      <c r="L33" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="L34" t="s">
+      <c r="L34" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1351,10 +1391,10 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -1364,23 +1404,23 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="L38" t="s">
+      <c r="L38" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1390,10 +1430,10 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1403,755 +1443,837 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="L41" s="2" t="s">
-        <v>98</v>
+      <c r="L41" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="L42" s="2" t="s">
+      <c r="L42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="L43" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" s="6" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="9"/>
-      <c r="L43" s="6" t="s">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="L44" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="L44" s="6" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="L45" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="6" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="9"/>
-      <c r="L45" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="9"/>
-      <c r="L46" s="10" t="s">
-        <v>124</v>
+      <c r="L46" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>125</v>
+      <c r="A47" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="9"/>
-      <c r="L47" s="11" t="s">
-        <v>126</v>
+      <c r="L47" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>127</v>
+      <c r="A48" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="9"/>
-      <c r="L48" s="11" t="s">
-        <v>128</v>
+      <c r="L48" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>129</v>
+      <c r="A49" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
-      <c r="L49" s="11" t="s">
-        <v>130</v>
+      <c r="L49" s="10" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>131</v>
+      <c r="A50" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
-      <c r="L50" s="14" t="s">
-        <v>132</v>
+      <c r="L50" s="10" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>133</v>
+      <c r="A51" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
-      <c r="L51" s="14" t="s">
-        <v>134</v>
+      <c r="L51" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>135</v>
+      <c r="A52" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="9"/>
-      <c r="L52" s="14" t="s">
-        <v>136</v>
+      <c r="L52" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>137</v>
+      <c r="A53" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
-      <c r="L53" s="14" t="s">
+      <c r="L53" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
+      <c r="L54" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
+      <c r="L55" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
+      <c r="L56" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="6" t="s">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C57" s="8"/>
+      <c r="D57" s="9"/>
+      <c r="L57" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D54" s="9" t="s">
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="L58" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
+      <c r="L59" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C55" s="6" t="s">
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="C60" s="8" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" s="6" t="s">
+      <c r="D60" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="G60" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="6" t="s">
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C61" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D61" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B58" s="6" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C62" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D62" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="2" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="C63" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B61" s="2" t="s">
+      <c r="D63" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C61" s="7" t="s">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="C64" s="5" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="D64" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F62" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F63" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F65" t="s">
-        <v>176</v>
-      </c>
+      <c r="A65" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="7"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>178</v>
+        <v>27</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F66" t="s">
-        <v>180</v>
+        <v>163</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F67" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>186</v>
+        <v>167</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F68" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>190</v>
+        <v>171</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="F69" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>14</v>
+      <c r="A70" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>197</v>
+      <c r="A71" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>198</v>
+        <v>180</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F71" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="F72" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="2"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>209</v>
+      <c r="F74" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>210</v>
+        <v>149</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>209</v>
+        <v>197</v>
+      </c>
+      <c r="F75" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
+      <c r="A76" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>201</v>
+      </c>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="F76" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D77" s="2"/>
+      <c r="A77" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="E77" s="2"/>
-      <c r="F77" s="2" t="s">
-        <v>214</v>
+      <c r="F77" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>218</v>
+      <c r="A79" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>220</v>
+        <v>45</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
+      <c r="D80" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F80" s="2"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="7" t="s">
+      <c r="A81" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C81" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="7" t="s">
+      <c r="E82" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" s="7" t="s">
         <v>222</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="L84" s="7" t="s">
-        <v>231</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" t="s">
-        <v>235</v>
+      <c r="A85" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-    </row>
-    <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" t="s">
-        <v>236</v>
+        <v>231</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
-      <c r="L88" t="s">
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="2" t="s">
+      <c r="D90" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="L89">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="90" ht="12.75" customHeight="1">
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-    </row>
-    <row r="91" ht="12.75" customHeight="1">
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-    </row>
-    <row r="92" ht="12.75" customHeight="1">
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-    </row>
-    <row r="93" ht="12.75" customHeight="1">
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-    </row>
-    <row r="94" ht="12.75" customHeight="1">
+      <c r="E90" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="L92" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E93" s="7"/>
+      <c r="F93" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
+      <c r="A96" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96" t="s">
+        <v>249</v>
+      </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
+      <c r="L96" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="97" ht="12.75" customHeight="1">
+      <c r="A97" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
+      <c r="L97">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="98" ht="12.75" customHeight="1">
       <c r="C98" s="2"/>
@@ -5884,6 +6006,38 @@
     <row r="1030" ht="12.75" customHeight="1">
       <c r="C1030" s="2"/>
       <c r="D1030" s="2"/>
+    </row>
+    <row r="1031" ht="12.75" customHeight="1">
+      <c r="C1031" s="2"/>
+      <c r="D1031" s="2"/>
+    </row>
+    <row r="1032" ht="12.75" customHeight="1">
+      <c r="C1032" s="2"/>
+      <c r="D1032" s="2"/>
+    </row>
+    <row r="1033" ht="12.75" customHeight="1">
+      <c r="C1033" s="2"/>
+      <c r="D1033" s="2"/>
+    </row>
+    <row r="1034" ht="12.75" customHeight="1">
+      <c r="C1034" s="2"/>
+      <c r="D1034" s="2"/>
+    </row>
+    <row r="1035" ht="12.75" customHeight="1">
+      <c r="C1035" s="2"/>
+      <c r="D1035" s="2"/>
+    </row>
+    <row r="1036" ht="12.75" customHeight="1">
+      <c r="C1036" s="2"/>
+      <c r="D1036" s="2"/>
+    </row>
+    <row r="1037" ht="12.75" customHeight="1">
+      <c r="C1037" s="2"/>
+      <c r="D1037" s="2"/>
+    </row>
+    <row r="1038" ht="12.75" customHeight="1">
+      <c r="C1038" s="2"/>
+      <c r="D1038" s="2"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -5906,184 +6060,184 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7088,45 +7242,47 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="16.29"/>
+    <col customWidth="1" min="2" max="2" width="22.71"/>
+    <col customWidth="1" min="3" max="6" width="14.43"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>52</v>
+      <c r="D2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,20 +13,326 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="275">
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
+    <t>label::sw</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>source_form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string </t>
+  </si>
+  <si>
+    <t>original_source_form</t>
+  </si>
+  <si>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>refer_muac_flag</t>
+  </si>
+  <si>
+    <t>refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t>refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t>due_date</t>
+  </si>
+  <si>
+    <t>due_date_human_readable</t>
+  </si>
+  <si>
+    <t>refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>refer_flag_postpartum_danger_signs</t>
+  </si>
+  <si>
+    <t>refer_flag_postpartum_other_signs</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>db:person</t>
+  </si>
+  <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>db-object</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>../inputs/contact/_id</t>
+  </si>
+  <si>
+    <t>referral_source_form</t>
+  </si>
+  <si>
+    <t>../inputs/source_form</t>
+  </si>
+  <si>
+    <t>referral_original_source_form</t>
+  </si>
+  <si>
+    <t>../inputs/original_source_form</t>
+  </si>
+  <si>
+    <t>referral_source_id</t>
+  </si>
+  <si>
+    <t>../inputs/source_id</t>
+  </si>
+  <si>
+    <t>last_visit</t>
+  </si>
+  <si>
+    <t>../inputs/last_visit_date</t>
+  </si>
+  <si>
+    <t>last_visit_formatted</t>
+  </si>
+  <si>
+    <t>format-date-time(../inputs/last_visit_date div (1000*60*60*24), "%d/%m/%Y")</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_small_baby</t>
+  </si>
+  <si>
+    <t>../inputs/refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_child_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_muac_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_refer_palm_pallor_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_vaccines_flag</t>
+  </si>
+  <si>
+    <t>../inputs/refer_slow_to_learn_specifics_flag</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>../inputs/contact/name</t>
+  </si>
+  <si>
+    <t>client_date_of_birth</t>
+  </si>
+  <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>../inputs/due_date</t>
+  </si>
+  <si>
+    <t>due_date_pretty_print</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>../inputs/due_date_human_readable</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_emergency_danger_sign</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_pregnancy_issues</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_pregnancy_complications</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_postpartum_danger_signs</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_postpartum_other_signs</t>
+  </si>
+  <si>
+    <t>age_days</t>
+  </si>
+  <si>
+    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
+  </si>
+  <si>
+    <t>age_months</t>
+  </si>
+  <si>
+    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
+  </si>
+  <si>
+    <t>age_years</t>
+  </si>
   <si>
     <t>list_name</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
-  </si>
-  <si>
     <t>yes_no</t>
   </si>
   <si>
@@ -60,102 +366,24 @@
     <t>Sina pesa</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
     <t>did_not_want</t>
   </si>
   <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
     <t>I did not want to go</t>
   </si>
   <si>
     <t>Sikutaka kwenda</t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
     <t>no_permission</t>
   </si>
   <si>
     <t>I did not have permission to go</t>
   </si>
   <si>
-    <t>inputs</t>
-  </si>
-  <si>
     <t>Sikupewa ruhusa ya kwenda</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
@@ -165,42 +393,18 @@
     <t>Nyenginezo</t>
   </si>
   <si>
-    <t>pages</t>
-  </si>
-  <si>
     <t>reason_didnt_get_svc</t>
   </si>
   <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>source_form</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>last_visit_date</t>
-  </si>
-  <si>
     <t>too_many_people</t>
   </si>
   <si>
-    <t>refer_flag_small_baby</t>
-  </si>
-  <si>
     <t>There were too many people</t>
   </si>
   <si>
     <t>Kulikuwa na watu wengi</t>
   </si>
   <si>
-    <t>refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
     <t>services_not_offered</t>
   </si>
   <si>
@@ -213,18 +417,12 @@
     <t>no_service_provider_available</t>
   </si>
   <si>
-    <t>refer_secondary_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
     <t>No service providers were available</t>
   </si>
   <si>
     <t>Hakukuwa na mtoa huduma</t>
   </si>
   <si>
-    <t>refer_child_danger_sign_flag</t>
-  </si>
-  <si>
     <t>was_asked_to_pay</t>
   </si>
   <si>
@@ -234,9 +432,6 @@
     <t>Walitaka nilipie huduma</t>
   </si>
   <si>
-    <t>refer_muac_flag</t>
-  </si>
-  <si>
     <t>was_treated_badly</t>
   </si>
   <si>
@@ -244,177 +439,6 @@
   </si>
   <si>
     <t>Wahudumu wa afya hawakunihudumia vizuri</t>
-  </si>
-  <si>
-    <t>refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t>refer_vaccines_flag</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
-    <t>due_date</t>
-  </si>
-  <si>
-    <t>due_date_human_readable</t>
-  </si>
-  <si>
-    <t>refer_flag_emergency_danger_sign</t>
-  </si>
-  <si>
-    <t>refer_flag_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>refer_flag_pregnancy_complications</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
-    <t>end group</t>
-  </si>
-  <si>
-    <t>contact</t>
-  </si>
-  <si>
-    <t>db:person</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
-    <t>db-object</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>patient_id</t>
-  </si>
-  <si>
-    <t>../inputs/contact/_id</t>
-  </si>
-  <si>
-    <t>referral_source_form</t>
-  </si>
-  <si>
-    <t>../inputs/source_form</t>
-  </si>
-  <si>
-    <t>referral_source_id</t>
-  </si>
-  <si>
-    <t>../inputs/source_id</t>
-  </si>
-  <si>
-    <t>last_visit</t>
-  </si>
-  <si>
-    <t>../inputs/last_visit_date</t>
-  </si>
-  <si>
-    <t>last_visit_formatted</t>
-  </si>
-  <si>
-    <t>format-date-time(../inputs/last_visit_date div (1000*60*60*24), "%d/%m/%Y")</t>
-  </si>
-  <si>
-    <t>../inputs/refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t>../inputs/refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_secondary_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_muac_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_refer_palm_pallor_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_vaccines_flag</t>
-  </si>
-  <si>
-    <t>../inputs/refer_slow_to_learn_specifics_flag</t>
-  </si>
-  <si>
-    <t>client</t>
-  </si>
-  <si>
-    <t>client_name</t>
-  </si>
-  <si>
-    <t>../inputs/contact/name</t>
-  </si>
-  <si>
-    <t>client_date_of_birth</t>
-  </si>
-  <si>
-    <t>../inputs/contact/date_of_birth</t>
-  </si>
-  <si>
-    <t>../inputs/due_date</t>
-  </si>
-  <si>
-    <t>due_date_pretty_print</t>
-  </si>
-  <si>
-    <t>../inputs/due_date_human_readable</t>
-  </si>
-  <si>
-    <t>../inputs/refer_flag_emergency_danger_sign</t>
-  </si>
-  <si>
-    <t>../inputs/refer_flag_pregnancy_issues</t>
-  </si>
-  <si>
-    <t>../refer_flag_pregnancy_complications</t>
-  </si>
-  <si>
-    <t>age_days</t>
-  </si>
-  <si>
-    <t>int(decimal-date-time(now())-decimal-date-time(${client_date_of_birth}))</t>
-  </si>
-  <si>
-    <t>age_months</t>
-  </si>
-  <si>
-    <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
-  </si>
-  <si>
-    <t>age_years</t>
   </si>
   <si>
     <t>int(${age_days} div (30 *12),0)</t>
@@ -534,7 +558,7 @@
     <t>&lt;span style="display:block;padding-left:1em"&gt;Apate huduma maalum kwa ajili ya watoto wadogo.&lt;/span&gt;</t>
   </si>
   <si>
-    <t>../../refer_flag_small_baby = 1</t>
+    <t>./../inputs/refer_flag_small_baby = 1</t>
   </si>
   <si>
     <t>reason_refer_neonatal_danger_sign_flag</t>
@@ -639,9 +663,36 @@
     <t>&lt;span style="display:block;padding-left:1em"&gt;To address one or more pregnancy danger signs.&lt;/span&gt;</t>
   </si>
   <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za mama mjamzito.&lt;/span&gt;</t>
+  </si>
+  <si>
     <t>../../inputs/refer_flag_pregnancy_complications= 1 or ../../inputs/refer_flag_pregnancy_issues= 1</t>
   </si>
   <si>
+    <t>reason_refer_postpartum_danger_sings</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address one or more urgent postpartum danger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za dharura za mama aliyejifungua.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_postpartum_danger_signs= 1</t>
+  </si>
+  <si>
+    <t>reason_refer_postpartum_other_danger_signs</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address one or more postpartumdanger signs.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za mama aliyejifungua.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_postpartum_other_signs= 1</t>
+  </si>
+  <si>
     <t>select_one yes_no</t>
   </si>
   <si>
@@ -771,10 +822,28 @@
     <t>selected(${complete_referral},"no")</t>
   </si>
   <si>
-    <t>has_referral</t>
+    <t>should_visit_again</t>
   </si>
   <si>
     <t>if(selected(${complete_referral},"yes"),1,0)</t>
+  </si>
+  <si>
+    <t>has_pregnancy_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1 </t>
+  </si>
+  <si>
+    <t>has_infant_child_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">./../inputs/refer_flag_small_baby= 1 or ../../inputs/refer_neonatal_danger_sign_flag = 1 or ../../inputs/refer_secondary_neonatal_danger_sign_flag = 1 or ../../inputs/refer_child_danger_sign_flag = 1 or ../../inputs/refer_muac_flag= 1 or ../../inputs/refer_refer_palm_pallor_flag = 1 or  ../../inputs/refer_vaccines_flag = 1 or ../../inputs/refer_slow_to_learn_specifics_flag = 1 </t>
+  </si>
+  <si>
+    <t>has_postpartum_referral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">../inputs/refer_flag_postpartum_danger_signs = 1 or ../inputs/refer_flag_postpartum_other_signs = 1 </t>
   </si>
   <si>
     <t>referral_days</t>
@@ -790,16 +859,16 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="10.0"/>
-      <name val="Arial"/>
-    </font>
     <font/>
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -835,31 +904,31 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -868,7 +937,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -906,5138 +975,5289 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="L35" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="L36" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="L39" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="L40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="L41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="L42" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="L43" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="L44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="L45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="L46" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="L47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="L48" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="L49" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="7"/>
+      <c r="L50" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="7"/>
+      <c r="L51" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="7"/>
+      <c r="L52" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="7"/>
+      <c r="L53" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="7"/>
+      <c r="L54" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="F2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C55" s="5"/>
+      <c r="D55" s="7"/>
+      <c r="L55" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="B56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="7"/>
+      <c r="L56" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="7"/>
+      <c r="L57" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="7"/>
+      <c r="L58" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="7"/>
+      <c r="L59" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="7"/>
+      <c r="L60" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="7"/>
+      <c r="L61" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="7"/>
+      <c r="L62" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="7"/>
+      <c r="L63" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="7"/>
+      <c r="L64" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="7"/>
+      <c r="L65" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="L31" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="L32" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="L33" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="L34" s="2" t="s">
+      <c r="C72" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F75" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F77" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F78" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F80" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="L35" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="L36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="L37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="L38" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="L39" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="L40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="L41" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="L42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="L43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="L44" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="L45" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9"/>
-      <c r="L46" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="D47" s="9"/>
-      <c r="L47" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="9"/>
-      <c r="L48" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="9"/>
-      <c r="L49" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="L50" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
-      <c r="L51" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="L52" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="9"/>
-      <c r="L53" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="L54" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="9"/>
-      <c r="L55" s="12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="L56" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="9"/>
-      <c r="L57" s="15" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="9"/>
-      <c r="L58" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="9"/>
-      <c r="L59" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="C94" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="7"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F68" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F69" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F71" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F72" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F73" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F74" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F75" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F80" s="2"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="2"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="7" t="s">
+      <c r="B95" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C83" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="L92" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E93" s="7"/>
-      <c r="F93" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-    </row>
-    <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" t="s">
-        <v>249</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="L96" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" s="2" t="s">
+      <c r="B98" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="L100" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="L97">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+    </row>
+    <row r="104" ht="12.75" customHeight="1">
+      <c r="A104" t="s">
+        <v>56</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="L104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="105" ht="12.75" customHeight="1">
+      <c r="A105" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="L105" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" ht="12.75" customHeight="1">
+      <c r="A106" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="L106" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="107" ht="12.75" customHeight="1">
+      <c r="A107" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="L107" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" ht="12.75" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="L108">
         <v>3.0</v>
       </c>
     </row>
-    <row r="98" ht="12.75" customHeight="1">
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-    </row>
-    <row r="99" ht="12.75" customHeight="1">
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-    </row>
-    <row r="100" ht="12.75" customHeight="1">
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-    </row>
-    <row r="101" ht="12.75" customHeight="1">
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-    </row>
-    <row r="102" ht="12.75" customHeight="1">
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-    </row>
-    <row r="103" ht="12.75" customHeight="1">
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-    </row>
-    <row r="104" ht="12.75" customHeight="1">
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-    </row>
-    <row r="105" ht="12.75" customHeight="1">
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-    </row>
-    <row r="106" ht="12.75" customHeight="1">
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-    </row>
-    <row r="107" ht="12.75" customHeight="1">
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-    </row>
-    <row r="108" ht="12.75" customHeight="1">
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-    </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="C314" s="2"/>
-      <c r="D314" s="2"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="C354" s="2"/>
-      <c r="D354" s="2"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="C355" s="2"/>
-      <c r="D355" s="2"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="C356" s="2"/>
-      <c r="D356" s="2"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="C357" s="2"/>
-      <c r="D357" s="2"/>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="C358" s="2"/>
-      <c r="D358" s="2"/>
+      <c r="C358" s="1"/>
+      <c r="D358" s="1"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="C359" s="2"/>
-      <c r="D359" s="2"/>
+      <c r="C359" s="1"/>
+      <c r="D359" s="1"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="C360" s="2"/>
-      <c r="D360" s="2"/>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="C361" s="2"/>
-      <c r="D361" s="2"/>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="C362" s="2"/>
-      <c r="D362" s="2"/>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="C363" s="2"/>
-      <c r="D363" s="2"/>
+      <c r="C363" s="1"/>
+      <c r="D363" s="1"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="C364" s="2"/>
-      <c r="D364" s="2"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="C365" s="2"/>
-      <c r="D365" s="2"/>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
+      <c r="C366" s="1"/>
+      <c r="D366" s="1"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="C367" s="2"/>
-      <c r="D367" s="2"/>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="C368" s="2"/>
-      <c r="D368" s="2"/>
+      <c r="C368" s="1"/>
+      <c r="D368" s="1"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="C369" s="2"/>
-      <c r="D369" s="2"/>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="C370" s="2"/>
-      <c r="D370" s="2"/>
+      <c r="C370" s="1"/>
+      <c r="D370" s="1"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="C371" s="2"/>
-      <c r="D371" s="2"/>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="C372" s="2"/>
-      <c r="D372" s="2"/>
+      <c r="C372" s="1"/>
+      <c r="D372" s="1"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="C373" s="2"/>
-      <c r="D373" s="2"/>
+      <c r="C373" s="1"/>
+      <c r="D373" s="1"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="C374" s="2"/>
-      <c r="D374" s="2"/>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
+      <c r="C375" s="1"/>
+      <c r="D375" s="1"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="C376" s="2"/>
-      <c r="D376" s="2"/>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="C377" s="2"/>
-      <c r="D377" s="2"/>
+      <c r="C377" s="1"/>
+      <c r="D377" s="1"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="C378" s="2"/>
-      <c r="D378" s="2"/>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="C379" s="2"/>
-      <c r="D379" s="2"/>
+      <c r="C379" s="1"/>
+      <c r="D379" s="1"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="C380" s="2"/>
-      <c r="D380" s="2"/>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="C381" s="2"/>
-      <c r="D381" s="2"/>
+      <c r="C381" s="1"/>
+      <c r="D381" s="1"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="C382" s="2"/>
-      <c r="D382" s="2"/>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="C383" s="2"/>
-      <c r="D383" s="2"/>
+      <c r="C383" s="1"/>
+      <c r="D383" s="1"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="C384" s="2"/>
-      <c r="D384" s="2"/>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="C385" s="2"/>
-      <c r="D385" s="2"/>
+      <c r="C385" s="1"/>
+      <c r="D385" s="1"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="C386" s="2"/>
-      <c r="D386" s="2"/>
+      <c r="C386" s="1"/>
+      <c r="D386" s="1"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="2"/>
-      <c r="D387" s="2"/>
+      <c r="C387" s="1"/>
+      <c r="D387" s="1"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="C388" s="2"/>
-      <c r="D388" s="2"/>
+      <c r="C388" s="1"/>
+      <c r="D388" s="1"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="C389" s="2"/>
-      <c r="D389" s="2"/>
+      <c r="C389" s="1"/>
+      <c r="D389" s="1"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="C390" s="2"/>
-      <c r="D390" s="2"/>
+      <c r="C390" s="1"/>
+      <c r="D390" s="1"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="C391" s="2"/>
-      <c r="D391" s="2"/>
+      <c r="C391" s="1"/>
+      <c r="D391" s="1"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="C392" s="2"/>
-      <c r="D392" s="2"/>
+      <c r="C392" s="1"/>
+      <c r="D392" s="1"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="C393" s="2"/>
-      <c r="D393" s="2"/>
+      <c r="C393" s="1"/>
+      <c r="D393" s="1"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="C394" s="2"/>
-      <c r="D394" s="2"/>
+      <c r="C394" s="1"/>
+      <c r="D394" s="1"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
+      <c r="C395" s="1"/>
+      <c r="D395" s="1"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
+      <c r="C396" s="1"/>
+      <c r="D396" s="1"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="C397" s="2"/>
-      <c r="D397" s="2"/>
+      <c r="C397" s="1"/>
+      <c r="D397" s="1"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="C398" s="2"/>
-      <c r="D398" s="2"/>
+      <c r="C398" s="1"/>
+      <c r="D398" s="1"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="C399" s="2"/>
-      <c r="D399" s="2"/>
+      <c r="C399" s="1"/>
+      <c r="D399" s="1"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="C400" s="2"/>
-      <c r="D400" s="2"/>
+      <c r="C400" s="1"/>
+      <c r="D400" s="1"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="C401" s="2"/>
-      <c r="D401" s="2"/>
+      <c r="C401" s="1"/>
+      <c r="D401" s="1"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="C402" s="2"/>
-      <c r="D402" s="2"/>
+      <c r="C402" s="1"/>
+      <c r="D402" s="1"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="C403" s="2"/>
-      <c r="D403" s="2"/>
+      <c r="C403" s="1"/>
+      <c r="D403" s="1"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="C404" s="2"/>
-      <c r="D404" s="2"/>
+      <c r="C404" s="1"/>
+      <c r="D404" s="1"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="C405" s="2"/>
-      <c r="D405" s="2"/>
+      <c r="C405" s="1"/>
+      <c r="D405" s="1"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="C406" s="2"/>
-      <c r="D406" s="2"/>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="C407" s="2"/>
-      <c r="D407" s="2"/>
+      <c r="C407" s="1"/>
+      <c r="D407" s="1"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="C408" s="2"/>
-      <c r="D408" s="2"/>
+      <c r="C408" s="1"/>
+      <c r="D408" s="1"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="C409" s="2"/>
-      <c r="D409" s="2"/>
+      <c r="C409" s="1"/>
+      <c r="D409" s="1"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="C410" s="2"/>
-      <c r="D410" s="2"/>
+      <c r="C410" s="1"/>
+      <c r="D410" s="1"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="C411" s="2"/>
-      <c r="D411" s="2"/>
+      <c r="C411" s="1"/>
+      <c r="D411" s="1"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
+      <c r="C412" s="1"/>
+      <c r="D412" s="1"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="C413" s="2"/>
-      <c r="D413" s="2"/>
+      <c r="C413" s="1"/>
+      <c r="D413" s="1"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="C414" s="2"/>
-      <c r="D414" s="2"/>
+      <c r="C414" s="1"/>
+      <c r="D414" s="1"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="C415" s="2"/>
-      <c r="D415" s="2"/>
+      <c r="C415" s="1"/>
+      <c r="D415" s="1"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="C416" s="2"/>
-      <c r="D416" s="2"/>
+      <c r="C416" s="1"/>
+      <c r="D416" s="1"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="C417" s="2"/>
-      <c r="D417" s="2"/>
+      <c r="C417" s="1"/>
+      <c r="D417" s="1"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="C418" s="2"/>
-      <c r="D418" s="2"/>
+      <c r="C418" s="1"/>
+      <c r="D418" s="1"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="C419" s="2"/>
-      <c r="D419" s="2"/>
+      <c r="C419" s="1"/>
+      <c r="D419" s="1"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="C420" s="2"/>
-      <c r="D420" s="2"/>
+      <c r="C420" s="1"/>
+      <c r="D420" s="1"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="C421" s="2"/>
-      <c r="D421" s="2"/>
+      <c r="C421" s="1"/>
+      <c r="D421" s="1"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="C422" s="2"/>
-      <c r="D422" s="2"/>
+      <c r="C422" s="1"/>
+      <c r="D422" s="1"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="C423" s="2"/>
-      <c r="D423" s="2"/>
+      <c r="C423" s="1"/>
+      <c r="D423" s="1"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="C424" s="2"/>
-      <c r="D424" s="2"/>
+      <c r="C424" s="1"/>
+      <c r="D424" s="1"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="C425" s="2"/>
-      <c r="D425" s="2"/>
+      <c r="C425" s="1"/>
+      <c r="D425" s="1"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="C426" s="2"/>
-      <c r="D426" s="2"/>
+      <c r="C426" s="1"/>
+      <c r="D426" s="1"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="C427" s="2"/>
-      <c r="D427" s="2"/>
+      <c r="C427" s="1"/>
+      <c r="D427" s="1"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="C428" s="2"/>
-      <c r="D428" s="2"/>
+      <c r="C428" s="1"/>
+      <c r="D428" s="1"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="C429" s="2"/>
-      <c r="D429" s="2"/>
+      <c r="C429" s="1"/>
+      <c r="D429" s="1"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="C430" s="2"/>
-      <c r="D430" s="2"/>
+      <c r="C430" s="1"/>
+      <c r="D430" s="1"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="C431" s="2"/>
-      <c r="D431" s="2"/>
+      <c r="C431" s="1"/>
+      <c r="D431" s="1"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="C432" s="2"/>
-      <c r="D432" s="2"/>
+      <c r="C432" s="1"/>
+      <c r="D432" s="1"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="C433" s="2"/>
-      <c r="D433" s="2"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="C434" s="2"/>
-      <c r="D434" s="2"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="C435" s="2"/>
-      <c r="D435" s="2"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="C436" s="2"/>
-      <c r="D436" s="2"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="C437" s="2"/>
-      <c r="D437" s="2"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="C438" s="2"/>
-      <c r="D438" s="2"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="C439" s="2"/>
-      <c r="D439" s="2"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="C440" s="2"/>
-      <c r="D440" s="2"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="C441" s="2"/>
-      <c r="D441" s="2"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="C442" s="2"/>
-      <c r="D442" s="2"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="C443" s="2"/>
-      <c r="D443" s="2"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="C444" s="2"/>
-      <c r="D444" s="2"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="C445" s="2"/>
-      <c r="D445" s="2"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="C446" s="2"/>
-      <c r="D446" s="2"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="C447" s="2"/>
-      <c r="D447" s="2"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="C448" s="2"/>
-      <c r="D448" s="2"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="C449" s="2"/>
-      <c r="D449" s="2"/>
+      <c r="C449" s="1"/>
+      <c r="D449" s="1"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="C450" s="2"/>
-      <c r="D450" s="2"/>
+      <c r="C450" s="1"/>
+      <c r="D450" s="1"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="C451" s="2"/>
-      <c r="D451" s="2"/>
+      <c r="C451" s="1"/>
+      <c r="D451" s="1"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="C452" s="2"/>
-      <c r="D452" s="2"/>
+      <c r="C452" s="1"/>
+      <c r="D452" s="1"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="C453" s="2"/>
-      <c r="D453" s="2"/>
+      <c r="C453" s="1"/>
+      <c r="D453" s="1"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="C454" s="2"/>
-      <c r="D454" s="2"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="C455" s="2"/>
-      <c r="D455" s="2"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="C456" s="2"/>
-      <c r="D456" s="2"/>
+      <c r="C456" s="1"/>
+      <c r="D456" s="1"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="C457" s="2"/>
-      <c r="D457" s="2"/>
+      <c r="C457" s="1"/>
+      <c r="D457" s="1"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="C458" s="2"/>
-      <c r="D458" s="2"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="C459" s="2"/>
-      <c r="D459" s="2"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="C460" s="2"/>
-      <c r="D460" s="2"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="C461" s="2"/>
-      <c r="D461" s="2"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="C462" s="2"/>
-      <c r="D462" s="2"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="C463" s="2"/>
-      <c r="D463" s="2"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="C464" s="2"/>
-      <c r="D464" s="2"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="C465" s="2"/>
-      <c r="D465" s="2"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="C466" s="2"/>
-      <c r="D466" s="2"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="C467" s="2"/>
-      <c r="D467" s="2"/>
+      <c r="C467" s="1"/>
+      <c r="D467" s="1"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="C468" s="2"/>
-      <c r="D468" s="2"/>
+      <c r="C468" s="1"/>
+      <c r="D468" s="1"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="C469" s="2"/>
-      <c r="D469" s="2"/>
+      <c r="C469" s="1"/>
+      <c r="D469" s="1"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="C470" s="2"/>
-      <c r="D470" s="2"/>
+      <c r="C470" s="1"/>
+      <c r="D470" s="1"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="C471" s="2"/>
-      <c r="D471" s="2"/>
+      <c r="C471" s="1"/>
+      <c r="D471" s="1"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="C472" s="2"/>
-      <c r="D472" s="2"/>
+      <c r="C472" s="1"/>
+      <c r="D472" s="1"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="C473" s="2"/>
-      <c r="D473" s="2"/>
+      <c r="C473" s="1"/>
+      <c r="D473" s="1"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="C474" s="2"/>
-      <c r="D474" s="2"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="C475" s="2"/>
-      <c r="D475" s="2"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="C476" s="2"/>
-      <c r="D476" s="2"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="C477" s="2"/>
-      <c r="D477" s="2"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="C478" s="2"/>
-      <c r="D478" s="2"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="C479" s="2"/>
-      <c r="D479" s="2"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="C480" s="2"/>
-      <c r="D480" s="2"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="C481" s="2"/>
-      <c r="D481" s="2"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="C482" s="2"/>
-      <c r="D482" s="2"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="C483" s="2"/>
-      <c r="D483" s="2"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="C484" s="2"/>
-      <c r="D484" s="2"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="C485" s="2"/>
-      <c r="D485" s="2"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="C486" s="2"/>
-      <c r="D486" s="2"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
+      <c r="C488" s="1"/>
+      <c r="D488" s="1"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
+      <c r="C489" s="1"/>
+      <c r="D489" s="1"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
+      <c r="C490" s="1"/>
+      <c r="D490" s="1"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
+      <c r="C491" s="1"/>
+      <c r="D491" s="1"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
+      <c r="C492" s="1"/>
+      <c r="D492" s="1"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
+      <c r="C493" s="1"/>
+      <c r="D493" s="1"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
+      <c r="C494" s="1"/>
+      <c r="D494" s="1"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
+      <c r="C495" s="1"/>
+      <c r="D495" s="1"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
+      <c r="C496" s="1"/>
+      <c r="D496" s="1"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
+      <c r="C497" s="1"/>
+      <c r="D497" s="1"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
+      <c r="C498" s="1"/>
+      <c r="D498" s="1"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
+      <c r="C499" s="1"/>
+      <c r="D499" s="1"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
+      <c r="C500" s="1"/>
+      <c r="D500" s="1"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="C501" s="2"/>
-      <c r="D501" s="2"/>
+      <c r="C501" s="1"/>
+      <c r="D501" s="1"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="C502" s="2"/>
-      <c r="D502" s="2"/>
+      <c r="C502" s="1"/>
+      <c r="D502" s="1"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="C503" s="2"/>
-      <c r="D503" s="2"/>
+      <c r="C503" s="1"/>
+      <c r="D503" s="1"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="C504" s="2"/>
-      <c r="D504" s="2"/>
+      <c r="C504" s="1"/>
+      <c r="D504" s="1"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="C505" s="2"/>
-      <c r="D505" s="2"/>
+      <c r="C505" s="1"/>
+      <c r="D505" s="1"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="C506" s="2"/>
-      <c r="D506" s="2"/>
+      <c r="C506" s="1"/>
+      <c r="D506" s="1"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="C507" s="2"/>
-      <c r="D507" s="2"/>
+      <c r="C507" s="1"/>
+      <c r="D507" s="1"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="C508" s="2"/>
-      <c r="D508" s="2"/>
+      <c r="C508" s="1"/>
+      <c r="D508" s="1"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="C509" s="2"/>
-      <c r="D509" s="2"/>
+      <c r="C509" s="1"/>
+      <c r="D509" s="1"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="C510" s="2"/>
-      <c r="D510" s="2"/>
+      <c r="C510" s="1"/>
+      <c r="D510" s="1"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
+      <c r="C511" s="1"/>
+      <c r="D511" s="1"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
+      <c r="C512" s="1"/>
+      <c r="D512" s="1"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
+      <c r="C513" s="1"/>
+      <c r="D513" s="1"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
+      <c r="C514" s="1"/>
+      <c r="D514" s="1"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
+      <c r="C515" s="1"/>
+      <c r="D515" s="1"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
+      <c r="C516" s="1"/>
+      <c r="D516" s="1"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
+      <c r="C517" s="1"/>
+      <c r="D517" s="1"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
+      <c r="C518" s="1"/>
+      <c r="D518" s="1"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
+      <c r="C519" s="1"/>
+      <c r="D519" s="1"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
+      <c r="C520" s="1"/>
+      <c r="D520" s="1"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
+      <c r="C521" s="1"/>
+      <c r="D521" s="1"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
+      <c r="C522" s="1"/>
+      <c r="D522" s="1"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
+      <c r="C523" s="1"/>
+      <c r="D523" s="1"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
+      <c r="C524" s="1"/>
+      <c r="D524" s="1"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="C525" s="2"/>
-      <c r="D525" s="2"/>
+      <c r="C525" s="1"/>
+      <c r="D525" s="1"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="C526" s="2"/>
-      <c r="D526" s="2"/>
+      <c r="C526" s="1"/>
+      <c r="D526" s="1"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="C527" s="2"/>
-      <c r="D527" s="2"/>
+      <c r="C527" s="1"/>
+      <c r="D527" s="1"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="C528" s="2"/>
-      <c r="D528" s="2"/>
+      <c r="C528" s="1"/>
+      <c r="D528" s="1"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="C529" s="2"/>
-      <c r="D529" s="2"/>
+      <c r="C529" s="1"/>
+      <c r="D529" s="1"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="C530" s="2"/>
-      <c r="D530" s="2"/>
+      <c r="C530" s="1"/>
+      <c r="D530" s="1"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="C531" s="2"/>
-      <c r="D531" s="2"/>
+      <c r="C531" s="1"/>
+      <c r="D531" s="1"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="C532" s="2"/>
-      <c r="D532" s="2"/>
+      <c r="C532" s="1"/>
+      <c r="D532" s="1"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="C533" s="2"/>
-      <c r="D533" s="2"/>
+      <c r="C533" s="1"/>
+      <c r="D533" s="1"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="C534" s="2"/>
-      <c r="D534" s="2"/>
+      <c r="C534" s="1"/>
+      <c r="D534" s="1"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="C535" s="2"/>
-      <c r="D535" s="2"/>
+      <c r="C535" s="1"/>
+      <c r="D535" s="1"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="C536" s="2"/>
-      <c r="D536" s="2"/>
+      <c r="C536" s="1"/>
+      <c r="D536" s="1"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="C537" s="2"/>
-      <c r="D537" s="2"/>
+      <c r="C537" s="1"/>
+      <c r="D537" s="1"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="C538" s="2"/>
-      <c r="D538" s="2"/>
+      <c r="C538" s="1"/>
+      <c r="D538" s="1"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="C539" s="2"/>
-      <c r="D539" s="2"/>
+      <c r="C539" s="1"/>
+      <c r="D539" s="1"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="C540" s="2"/>
-      <c r="D540" s="2"/>
+      <c r="C540" s="1"/>
+      <c r="D540" s="1"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="C541" s="2"/>
-      <c r="D541" s="2"/>
+      <c r="C541" s="1"/>
+      <c r="D541" s="1"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="C542" s="2"/>
-      <c r="D542" s="2"/>
+      <c r="C542" s="1"/>
+      <c r="D542" s="1"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="C543" s="2"/>
-      <c r="D543" s="2"/>
+      <c r="C543" s="1"/>
+      <c r="D543" s="1"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="C544" s="2"/>
-      <c r="D544" s="2"/>
+      <c r="C544" s="1"/>
+      <c r="D544" s="1"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="C545" s="2"/>
-      <c r="D545" s="2"/>
+      <c r="C545" s="1"/>
+      <c r="D545" s="1"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="C546" s="2"/>
-      <c r="D546" s="2"/>
+      <c r="C546" s="1"/>
+      <c r="D546" s="1"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="C547" s="2"/>
-      <c r="D547" s="2"/>
+      <c r="C547" s="1"/>
+      <c r="D547" s="1"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="C548" s="2"/>
-      <c r="D548" s="2"/>
+      <c r="C548" s="1"/>
+      <c r="D548" s="1"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="C549" s="2"/>
-      <c r="D549" s="2"/>
+      <c r="C549" s="1"/>
+      <c r="D549" s="1"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="C550" s="2"/>
-      <c r="D550" s="2"/>
+      <c r="C550" s="1"/>
+      <c r="D550" s="1"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="C551" s="2"/>
-      <c r="D551" s="2"/>
+      <c r="C551" s="1"/>
+      <c r="D551" s="1"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
+      <c r="C552" s="1"/>
+      <c r="D552" s="1"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
+      <c r="C553" s="1"/>
+      <c r="D553" s="1"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="C554" s="2"/>
-      <c r="D554" s="2"/>
+      <c r="C554" s="1"/>
+      <c r="D554" s="1"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="C555" s="2"/>
-      <c r="D555" s="2"/>
+      <c r="C555" s="1"/>
+      <c r="D555" s="1"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="C556" s="2"/>
-      <c r="D556" s="2"/>
+      <c r="C556" s="1"/>
+      <c r="D556" s="1"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="C557" s="2"/>
-      <c r="D557" s="2"/>
+      <c r="C557" s="1"/>
+      <c r="D557" s="1"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="C558" s="2"/>
-      <c r="D558" s="2"/>
+      <c r="C558" s="1"/>
+      <c r="D558" s="1"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="C559" s="2"/>
-      <c r="D559" s="2"/>
+      <c r="C559" s="1"/>
+      <c r="D559" s="1"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="C560" s="2"/>
-      <c r="D560" s="2"/>
+      <c r="C560" s="1"/>
+      <c r="D560" s="1"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="C561" s="2"/>
-      <c r="D561" s="2"/>
+      <c r="C561" s="1"/>
+      <c r="D561" s="1"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="C562" s="2"/>
-      <c r="D562" s="2"/>
+      <c r="C562" s="1"/>
+      <c r="D562" s="1"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="C563" s="2"/>
-      <c r="D563" s="2"/>
+      <c r="C563" s="1"/>
+      <c r="D563" s="1"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="C564" s="2"/>
-      <c r="D564" s="2"/>
+      <c r="C564" s="1"/>
+      <c r="D564" s="1"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="C565" s="2"/>
-      <c r="D565" s="2"/>
+      <c r="C565" s="1"/>
+      <c r="D565" s="1"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
+      <c r="C566" s="1"/>
+      <c r="D566" s="1"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="C567" s="2"/>
-      <c r="D567" s="2"/>
+      <c r="C567" s="1"/>
+      <c r="D567" s="1"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="C568" s="2"/>
-      <c r="D568" s="2"/>
+      <c r="C568" s="1"/>
+      <c r="D568" s="1"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="C569" s="2"/>
-      <c r="D569" s="2"/>
+      <c r="C569" s="1"/>
+      <c r="D569" s="1"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="C570" s="2"/>
-      <c r="D570" s="2"/>
+      <c r="C570" s="1"/>
+      <c r="D570" s="1"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="C571" s="2"/>
-      <c r="D571" s="2"/>
+      <c r="C571" s="1"/>
+      <c r="D571" s="1"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="C572" s="2"/>
-      <c r="D572" s="2"/>
+      <c r="C572" s="1"/>
+      <c r="D572" s="1"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="C573" s="2"/>
-      <c r="D573" s="2"/>
+      <c r="C573" s="1"/>
+      <c r="D573" s="1"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="C574" s="2"/>
-      <c r="D574" s="2"/>
+      <c r="C574" s="1"/>
+      <c r="D574" s="1"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="C575" s="2"/>
-      <c r="D575" s="2"/>
+      <c r="C575" s="1"/>
+      <c r="D575" s="1"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="C576" s="2"/>
-      <c r="D576" s="2"/>
+      <c r="C576" s="1"/>
+      <c r="D576" s="1"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="C577" s="2"/>
-      <c r="D577" s="2"/>
+      <c r="C577" s="1"/>
+      <c r="D577" s="1"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="C578" s="2"/>
-      <c r="D578" s="2"/>
+      <c r="C578" s="1"/>
+      <c r="D578" s="1"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="C579" s="2"/>
-      <c r="D579" s="2"/>
+      <c r="C579" s="1"/>
+      <c r="D579" s="1"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="C580" s="2"/>
-      <c r="D580" s="2"/>
+      <c r="C580" s="1"/>
+      <c r="D580" s="1"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="C581" s="2"/>
-      <c r="D581" s="2"/>
+      <c r="C581" s="1"/>
+      <c r="D581" s="1"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="C582" s="2"/>
-      <c r="D582" s="2"/>
+      <c r="C582" s="1"/>
+      <c r="D582" s="1"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="C583" s="2"/>
-      <c r="D583" s="2"/>
+      <c r="C583" s="1"/>
+      <c r="D583" s="1"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="2"/>
-      <c r="D584" s="2"/>
+      <c r="C584" s="1"/>
+      <c r="D584" s="1"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="2"/>
-      <c r="D585" s="2"/>
+      <c r="C585" s="1"/>
+      <c r="D585" s="1"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="2"/>
-      <c r="D586" s="2"/>
+      <c r="C586" s="1"/>
+      <c r="D586" s="1"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="C587" s="2"/>
-      <c r="D587" s="2"/>
+      <c r="C587" s="1"/>
+      <c r="D587" s="1"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="C588" s="2"/>
-      <c r="D588" s="2"/>
+      <c r="C588" s="1"/>
+      <c r="D588" s="1"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="C589" s="2"/>
-      <c r="D589" s="2"/>
+      <c r="C589" s="1"/>
+      <c r="D589" s="1"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="C590" s="2"/>
-      <c r="D590" s="2"/>
+      <c r="C590" s="1"/>
+      <c r="D590" s="1"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="C591" s="2"/>
-      <c r="D591" s="2"/>
+      <c r="C591" s="1"/>
+      <c r="D591" s="1"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="C592" s="2"/>
-      <c r="D592" s="2"/>
+      <c r="C592" s="1"/>
+      <c r="D592" s="1"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="C593" s="2"/>
-      <c r="D593" s="2"/>
+      <c r="C593" s="1"/>
+      <c r="D593" s="1"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="C594" s="2"/>
-      <c r="D594" s="2"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="1"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="C595" s="2"/>
-      <c r="D595" s="2"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="1"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="C596" s="2"/>
-      <c r="D596" s="2"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="1"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="C597" s="2"/>
-      <c r="D597" s="2"/>
+      <c r="C597" s="1"/>
+      <c r="D597" s="1"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="C598" s="2"/>
-      <c r="D598" s="2"/>
+      <c r="C598" s="1"/>
+      <c r="D598" s="1"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="C599" s="2"/>
-      <c r="D599" s="2"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="2"/>
-      <c r="D600" s="2"/>
+      <c r="C600" s="1"/>
+      <c r="D600" s="1"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="2"/>
-      <c r="D601" s="2"/>
+      <c r="C601" s="1"/>
+      <c r="D601" s="1"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="2"/>
-      <c r="D602" s="2"/>
+      <c r="C602" s="1"/>
+      <c r="D602" s="1"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="C603" s="2"/>
-      <c r="D603" s="2"/>
+      <c r="C603" s="1"/>
+      <c r="D603" s="1"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="C604" s="2"/>
-      <c r="D604" s="2"/>
+      <c r="C604" s="1"/>
+      <c r="D604" s="1"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="C605" s="2"/>
-      <c r="D605" s="2"/>
+      <c r="C605" s="1"/>
+      <c r="D605" s="1"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="C606" s="2"/>
-      <c r="D606" s="2"/>
+      <c r="C606" s="1"/>
+      <c r="D606" s="1"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="C607" s="2"/>
-      <c r="D607" s="2"/>
+      <c r="C607" s="1"/>
+      <c r="D607" s="1"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
+      <c r="C608" s="1"/>
+      <c r="D608" s="1"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="C609" s="2"/>
-      <c r="D609" s="2"/>
+      <c r="C609" s="1"/>
+      <c r="D609" s="1"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="C610" s="2"/>
-      <c r="D610" s="2"/>
+      <c r="C610" s="1"/>
+      <c r="D610" s="1"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="C611" s="2"/>
-      <c r="D611" s="2"/>
+      <c r="C611" s="1"/>
+      <c r="D611" s="1"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="C612" s="2"/>
-      <c r="D612" s="2"/>
+      <c r="C612" s="1"/>
+      <c r="D612" s="1"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="C613" s="2"/>
-      <c r="D613" s="2"/>
+      <c r="C613" s="1"/>
+      <c r="D613" s="1"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="C614" s="2"/>
-      <c r="D614" s="2"/>
+      <c r="C614" s="1"/>
+      <c r="D614" s="1"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
+      <c r="C615" s="1"/>
+      <c r="D615" s="1"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="2"/>
-      <c r="D616" s="2"/>
+      <c r="C616" s="1"/>
+      <c r="D616" s="1"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="2"/>
-      <c r="D617" s="2"/>
+      <c r="C617" s="1"/>
+      <c r="D617" s="1"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="2"/>
-      <c r="D618" s="2"/>
+      <c r="C618" s="1"/>
+      <c r="D618" s="1"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="C619" s="2"/>
-      <c r="D619" s="2"/>
+      <c r="C619" s="1"/>
+      <c r="D619" s="1"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="C620" s="2"/>
-      <c r="D620" s="2"/>
+      <c r="C620" s="1"/>
+      <c r="D620" s="1"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="C621" s="2"/>
-      <c r="D621" s="2"/>
+      <c r="C621" s="1"/>
+      <c r="D621" s="1"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
+      <c r="C622" s="1"/>
+      <c r="D622" s="1"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="C623" s="2"/>
-      <c r="D623" s="2"/>
+      <c r="C623" s="1"/>
+      <c r="D623" s="1"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
+      <c r="C624" s="1"/>
+      <c r="D624" s="1"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
+      <c r="C625" s="1"/>
+      <c r="D625" s="1"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
+      <c r="C626" s="1"/>
+      <c r="D626" s="1"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="C627" s="2"/>
-      <c r="D627" s="2"/>
+      <c r="C627" s="1"/>
+      <c r="D627" s="1"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="C628" s="2"/>
-      <c r="D628" s="2"/>
+      <c r="C628" s="1"/>
+      <c r="D628" s="1"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="C629" s="2"/>
-      <c r="D629" s="2"/>
+      <c r="C629" s="1"/>
+      <c r="D629" s="1"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="C630" s="2"/>
-      <c r="D630" s="2"/>
+      <c r="C630" s="1"/>
+      <c r="D630" s="1"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="C631" s="2"/>
-      <c r="D631" s="2"/>
+      <c r="C631" s="1"/>
+      <c r="D631" s="1"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="C632" s="2"/>
-      <c r="D632" s="2"/>
+      <c r="C632" s="1"/>
+      <c r="D632" s="1"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="C633" s="2"/>
-      <c r="D633" s="2"/>
+      <c r="C633" s="1"/>
+      <c r="D633" s="1"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
+      <c r="C634" s="1"/>
+      <c r="D634" s="1"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
+      <c r="C635" s="1"/>
+      <c r="D635" s="1"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
+      <c r="C636" s="1"/>
+      <c r="D636" s="1"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
+      <c r="C637" s="1"/>
+      <c r="D637" s="1"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="C638" s="2"/>
-      <c r="D638" s="2"/>
+      <c r="C638" s="1"/>
+      <c r="D638" s="1"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="C639" s="2"/>
-      <c r="D639" s="2"/>
+      <c r="C639" s="1"/>
+      <c r="D639" s="1"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="C640" s="2"/>
-      <c r="D640" s="2"/>
+      <c r="C640" s="1"/>
+      <c r="D640" s="1"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="C641" s="2"/>
-      <c r="D641" s="2"/>
+      <c r="C641" s="1"/>
+      <c r="D641" s="1"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
+      <c r="C642" s="1"/>
+      <c r="D642" s="1"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="C643" s="2"/>
-      <c r="D643" s="2"/>
+      <c r="C643" s="1"/>
+      <c r="D643" s="1"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="C644" s="2"/>
-      <c r="D644" s="2"/>
+      <c r="C644" s="1"/>
+      <c r="D644" s="1"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="C645" s="2"/>
-      <c r="D645" s="2"/>
+      <c r="C645" s="1"/>
+      <c r="D645" s="1"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="C646" s="2"/>
-      <c r="D646" s="2"/>
+      <c r="C646" s="1"/>
+      <c r="D646" s="1"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
+      <c r="C647" s="1"/>
+      <c r="D647" s="1"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="C648" s="2"/>
-      <c r="D648" s="2"/>
+      <c r="C648" s="1"/>
+      <c r="D648" s="1"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="C649" s="2"/>
-      <c r="D649" s="2"/>
+      <c r="C649" s="1"/>
+      <c r="D649" s="1"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="C650" s="2"/>
-      <c r="D650" s="2"/>
+      <c r="C650" s="1"/>
+      <c r="D650" s="1"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="C651" s="2"/>
-      <c r="D651" s="2"/>
+      <c r="C651" s="1"/>
+      <c r="D651" s="1"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="C652" s="2"/>
-      <c r="D652" s="2"/>
+      <c r="C652" s="1"/>
+      <c r="D652" s="1"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="C653" s="2"/>
-      <c r="D653" s="2"/>
+      <c r="C653" s="1"/>
+      <c r="D653" s="1"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="C654" s="2"/>
-      <c r="D654" s="2"/>
+      <c r="C654" s="1"/>
+      <c r="D654" s="1"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
+      <c r="C655" s="1"/>
+      <c r="D655" s="1"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
+      <c r="C656" s="1"/>
+      <c r="D656" s="1"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
+      <c r="C657" s="1"/>
+      <c r="D657" s="1"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
+      <c r="C658" s="1"/>
+      <c r="D658" s="1"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
+      <c r="C659" s="1"/>
+      <c r="D659" s="1"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
+      <c r="C660" s="1"/>
+      <c r="D660" s="1"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
+      <c r="C661" s="1"/>
+      <c r="D661" s="1"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
+      <c r="C662" s="1"/>
+      <c r="D662" s="1"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
+      <c r="C663" s="1"/>
+      <c r="D663" s="1"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
+      <c r="C664" s="1"/>
+      <c r="D664" s="1"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
+      <c r="C665" s="1"/>
+      <c r="D665" s="1"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
+      <c r="C666" s="1"/>
+      <c r="D666" s="1"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
+      <c r="C667" s="1"/>
+      <c r="D667" s="1"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
+      <c r="C668" s="1"/>
+      <c r="D668" s="1"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
+      <c r="C669" s="1"/>
+      <c r="D669" s="1"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
+      <c r="C670" s="1"/>
+      <c r="D670" s="1"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
+      <c r="C671" s="1"/>
+      <c r="D671" s="1"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
+      <c r="C672" s="1"/>
+      <c r="D672" s="1"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
+      <c r="C673" s="1"/>
+      <c r="D673" s="1"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
+      <c r="C674" s="1"/>
+      <c r="D674" s="1"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
+      <c r="C675" s="1"/>
+      <c r="D675" s="1"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
+      <c r="C676" s="1"/>
+      <c r="D676" s="1"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
+      <c r="C677" s="1"/>
+      <c r="D677" s="1"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
+      <c r="C678" s="1"/>
+      <c r="D678" s="1"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
+      <c r="C679" s="1"/>
+      <c r="D679" s="1"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
+      <c r="C680" s="1"/>
+      <c r="D680" s="1"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
+      <c r="C681" s="1"/>
+      <c r="D681" s="1"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="C682" s="2"/>
-      <c r="D682" s="2"/>
+      <c r="C682" s="1"/>
+      <c r="D682" s="1"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="C683" s="2"/>
-      <c r="D683" s="2"/>
+      <c r="C683" s="1"/>
+      <c r="D683" s="1"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="C684" s="2"/>
-      <c r="D684" s="2"/>
+      <c r="C684" s="1"/>
+      <c r="D684" s="1"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="C685" s="2"/>
-      <c r="D685" s="2"/>
+      <c r="C685" s="1"/>
+      <c r="D685" s="1"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="C686" s="2"/>
-      <c r="D686" s="2"/>
+      <c r="C686" s="1"/>
+      <c r="D686" s="1"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="C687" s="2"/>
-      <c r="D687" s="2"/>
+      <c r="C687" s="1"/>
+      <c r="D687" s="1"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="C688" s="2"/>
-      <c r="D688" s="2"/>
+      <c r="C688" s="1"/>
+      <c r="D688" s="1"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="C689" s="2"/>
-      <c r="D689" s="2"/>
+      <c r="C689" s="1"/>
+      <c r="D689" s="1"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="C690" s="2"/>
-      <c r="D690" s="2"/>
+      <c r="C690" s="1"/>
+      <c r="D690" s="1"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="C691" s="2"/>
-      <c r="D691" s="2"/>
+      <c r="C691" s="1"/>
+      <c r="D691" s="1"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="C692" s="2"/>
-      <c r="D692" s="2"/>
+      <c r="C692" s="1"/>
+      <c r="D692" s="1"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="C693" s="2"/>
-      <c r="D693" s="2"/>
+      <c r="C693" s="1"/>
+      <c r="D693" s="1"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
+      <c r="C694" s="1"/>
+      <c r="D694" s="1"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
+      <c r="C695" s="1"/>
+      <c r="D695" s="1"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
+      <c r="C696" s="1"/>
+      <c r="D696" s="1"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="C697" s="2"/>
-      <c r="D697" s="2"/>
+      <c r="C697" s="1"/>
+      <c r="D697" s="1"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="C698" s="2"/>
-      <c r="D698" s="2"/>
+      <c r="C698" s="1"/>
+      <c r="D698" s="1"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="C699" s="2"/>
-      <c r="D699" s="2"/>
+      <c r="C699" s="1"/>
+      <c r="D699" s="1"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="C700" s="2"/>
-      <c r="D700" s="2"/>
+      <c r="C700" s="1"/>
+      <c r="D700" s="1"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
+      <c r="C701" s="1"/>
+      <c r="D701" s="1"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
+      <c r="C702" s="1"/>
+      <c r="D702" s="1"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
+      <c r="C703" s="1"/>
+      <c r="D703" s="1"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
+      <c r="C704" s="1"/>
+      <c r="D704" s="1"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
+      <c r="C705" s="1"/>
+      <c r="D705" s="1"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
+      <c r="C706" s="1"/>
+      <c r="D706" s="1"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
+      <c r="C707" s="1"/>
+      <c r="D707" s="1"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
+      <c r="C708" s="1"/>
+      <c r="D708" s="1"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
+      <c r="C709" s="1"/>
+      <c r="D709" s="1"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
+      <c r="C710" s="1"/>
+      <c r="D710" s="1"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
+      <c r="C711" s="1"/>
+      <c r="D711" s="1"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
+      <c r="C712" s="1"/>
+      <c r="D712" s="1"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
+      <c r="C713" s="1"/>
+      <c r="D713" s="1"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
+      <c r="C714" s="1"/>
+      <c r="D714" s="1"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="C715" s="2"/>
-      <c r="D715" s="2"/>
+      <c r="C715" s="1"/>
+      <c r="D715" s="1"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="C716" s="2"/>
-      <c r="D716" s="2"/>
+      <c r="C716" s="1"/>
+      <c r="D716" s="1"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="C717" s="2"/>
-      <c r="D717" s="2"/>
+      <c r="C717" s="1"/>
+      <c r="D717" s="1"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="C718" s="2"/>
-      <c r="D718" s="2"/>
+      <c r="C718" s="1"/>
+      <c r="D718" s="1"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="C719" s="2"/>
-      <c r="D719" s="2"/>
+      <c r="C719" s="1"/>
+      <c r="D719" s="1"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="C720" s="2"/>
-      <c r="D720" s="2"/>
+      <c r="C720" s="1"/>
+      <c r="D720" s="1"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="C721" s="2"/>
-      <c r="D721" s="2"/>
+      <c r="C721" s="1"/>
+      <c r="D721" s="1"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="C722" s="2"/>
-      <c r="D722" s="2"/>
+      <c r="C722" s="1"/>
+      <c r="D722" s="1"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="C723" s="2"/>
-      <c r="D723" s="2"/>
+      <c r="C723" s="1"/>
+      <c r="D723" s="1"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="C724" s="2"/>
-      <c r="D724" s="2"/>
+      <c r="C724" s="1"/>
+      <c r="D724" s="1"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="C725" s="2"/>
-      <c r="D725" s="2"/>
+      <c r="C725" s="1"/>
+      <c r="D725" s="1"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="C726" s="2"/>
-      <c r="D726" s="2"/>
+      <c r="C726" s="1"/>
+      <c r="D726" s="1"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="C727" s="2"/>
-      <c r="D727" s="2"/>
+      <c r="C727" s="1"/>
+      <c r="D727" s="1"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="C728" s="2"/>
-      <c r="D728" s="2"/>
+      <c r="C728" s="1"/>
+      <c r="D728" s="1"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="C729" s="2"/>
-      <c r="D729" s="2"/>
+      <c r="C729" s="1"/>
+      <c r="D729" s="1"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="C730" s="2"/>
-      <c r="D730" s="2"/>
+      <c r="C730" s="1"/>
+      <c r="D730" s="1"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="C731" s="2"/>
-      <c r="D731" s="2"/>
+      <c r="C731" s="1"/>
+      <c r="D731" s="1"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="C732" s="2"/>
-      <c r="D732" s="2"/>
+      <c r="C732" s="1"/>
+      <c r="D732" s="1"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="C733" s="2"/>
-      <c r="D733" s="2"/>
+      <c r="C733" s="1"/>
+      <c r="D733" s="1"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="C734" s="2"/>
-      <c r="D734" s="2"/>
+      <c r="C734" s="1"/>
+      <c r="D734" s="1"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="C735" s="2"/>
-      <c r="D735" s="2"/>
+      <c r="C735" s="1"/>
+      <c r="D735" s="1"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="C736" s="2"/>
-      <c r="D736" s="2"/>
+      <c r="C736" s="1"/>
+      <c r="D736" s="1"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="C737" s="2"/>
-      <c r="D737" s="2"/>
+      <c r="C737" s="1"/>
+      <c r="D737" s="1"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="C738" s="2"/>
-      <c r="D738" s="2"/>
+      <c r="C738" s="1"/>
+      <c r="D738" s="1"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="C739" s="2"/>
-      <c r="D739" s="2"/>
+      <c r="C739" s="1"/>
+      <c r="D739" s="1"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="C740" s="2"/>
-      <c r="D740" s="2"/>
+      <c r="C740" s="1"/>
+      <c r="D740" s="1"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="C741" s="2"/>
-      <c r="D741" s="2"/>
+      <c r="C741" s="1"/>
+      <c r="D741" s="1"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="C742" s="2"/>
-      <c r="D742" s="2"/>
+      <c r="C742" s="1"/>
+      <c r="D742" s="1"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="C743" s="2"/>
-      <c r="D743" s="2"/>
+      <c r="C743" s="1"/>
+      <c r="D743" s="1"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="C744" s="2"/>
-      <c r="D744" s="2"/>
+      <c r="C744" s="1"/>
+      <c r="D744" s="1"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="C745" s="2"/>
-      <c r="D745" s="2"/>
+      <c r="C745" s="1"/>
+      <c r="D745" s="1"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="C746" s="2"/>
-      <c r="D746" s="2"/>
+      <c r="C746" s="1"/>
+      <c r="D746" s="1"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="C747" s="2"/>
-      <c r="D747" s="2"/>
+      <c r="C747" s="1"/>
+      <c r="D747" s="1"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="C748" s="2"/>
-      <c r="D748" s="2"/>
+      <c r="C748" s="1"/>
+      <c r="D748" s="1"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="C749" s="2"/>
-      <c r="D749" s="2"/>
+      <c r="C749" s="1"/>
+      <c r="D749" s="1"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="C750" s="2"/>
-      <c r="D750" s="2"/>
+      <c r="C750" s="1"/>
+      <c r="D750" s="1"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="C751" s="2"/>
-      <c r="D751" s="2"/>
+      <c r="C751" s="1"/>
+      <c r="D751" s="1"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="C752" s="2"/>
-      <c r="D752" s="2"/>
+      <c r="C752" s="1"/>
+      <c r="D752" s="1"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="C753" s="2"/>
-      <c r="D753" s="2"/>
+      <c r="C753" s="1"/>
+      <c r="D753" s="1"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="C754" s="2"/>
-      <c r="D754" s="2"/>
+      <c r="C754" s="1"/>
+      <c r="D754" s="1"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="C755" s="2"/>
-      <c r="D755" s="2"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="C756" s="2"/>
-      <c r="D756" s="2"/>
+      <c r="C756" s="1"/>
+      <c r="D756" s="1"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="C757" s="2"/>
-      <c r="D757" s="2"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="C758" s="2"/>
-      <c r="D758" s="2"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="C759" s="2"/>
-      <c r="D759" s="2"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="C760" s="2"/>
-      <c r="D760" s="2"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="C761" s="2"/>
-      <c r="D761" s="2"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="C762" s="2"/>
-      <c r="D762" s="2"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="C763" s="2"/>
-      <c r="D763" s="2"/>
+      <c r="C763" s="1"/>
+      <c r="D763" s="1"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="C764" s="2"/>
-      <c r="D764" s="2"/>
+      <c r="C764" s="1"/>
+      <c r="D764" s="1"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="C765" s="2"/>
-      <c r="D765" s="2"/>
+      <c r="C765" s="1"/>
+      <c r="D765" s="1"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="C766" s="2"/>
-      <c r="D766" s="2"/>
+      <c r="C766" s="1"/>
+      <c r="D766" s="1"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
+      <c r="C767" s="1"/>
+      <c r="D767" s="1"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="C768" s="2"/>
-      <c r="D768" s="2"/>
+      <c r="C768" s="1"/>
+      <c r="D768" s="1"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="C769" s="2"/>
-      <c r="D769" s="2"/>
+      <c r="C769" s="1"/>
+      <c r="D769" s="1"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="C770" s="2"/>
-      <c r="D770" s="2"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="C771" s="2"/>
-      <c r="D771" s="2"/>
+      <c r="C771" s="1"/>
+      <c r="D771" s="1"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="C772" s="2"/>
-      <c r="D772" s="2"/>
+      <c r="C772" s="1"/>
+      <c r="D772" s="1"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
+      <c r="C773" s="1"/>
+      <c r="D773" s="1"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
+      <c r="C774" s="1"/>
+      <c r="D774" s="1"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
+      <c r="C775" s="1"/>
+      <c r="D775" s="1"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
+      <c r="C776" s="1"/>
+      <c r="D776" s="1"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="C777" s="2"/>
-      <c r="D777" s="2"/>
+      <c r="C777" s="1"/>
+      <c r="D777" s="1"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="C778" s="2"/>
-      <c r="D778" s="2"/>
+      <c r="C778" s="1"/>
+      <c r="D778" s="1"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="C779" s="2"/>
-      <c r="D779" s="2"/>
+      <c r="C779" s="1"/>
+      <c r="D779" s="1"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="C780" s="2"/>
-      <c r="D780" s="2"/>
+      <c r="C780" s="1"/>
+      <c r="D780" s="1"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="C781" s="2"/>
-      <c r="D781" s="2"/>
+      <c r="C781" s="1"/>
+      <c r="D781" s="1"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="C782" s="2"/>
-      <c r="D782" s="2"/>
+      <c r="C782" s="1"/>
+      <c r="D782" s="1"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="C783" s="2"/>
-      <c r="D783" s="2"/>
+      <c r="C783" s="1"/>
+      <c r="D783" s="1"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="C784" s="2"/>
-      <c r="D784" s="2"/>
+      <c r="C784" s="1"/>
+      <c r="D784" s="1"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="C785" s="2"/>
-      <c r="D785" s="2"/>
+      <c r="C785" s="1"/>
+      <c r="D785" s="1"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="C786" s="2"/>
-      <c r="D786" s="2"/>
+      <c r="C786" s="1"/>
+      <c r="D786" s="1"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="C787" s="2"/>
-      <c r="D787" s="2"/>
+      <c r="C787" s="1"/>
+      <c r="D787" s="1"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="C788" s="2"/>
-      <c r="D788" s="2"/>
+      <c r="C788" s="1"/>
+      <c r="D788" s="1"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="C789" s="2"/>
-      <c r="D789" s="2"/>
+      <c r="C789" s="1"/>
+      <c r="D789" s="1"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="C790" s="2"/>
-      <c r="D790" s="2"/>
+      <c r="C790" s="1"/>
+      <c r="D790" s="1"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="C791" s="2"/>
-      <c r="D791" s="2"/>
+      <c r="C791" s="1"/>
+      <c r="D791" s="1"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="C792" s="2"/>
-      <c r="D792" s="2"/>
+      <c r="C792" s="1"/>
+      <c r="D792" s="1"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="C793" s="2"/>
-      <c r="D793" s="2"/>
+      <c r="C793" s="1"/>
+      <c r="D793" s="1"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="C794" s="2"/>
-      <c r="D794" s="2"/>
+      <c r="C794" s="1"/>
+      <c r="D794" s="1"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="C795" s="2"/>
-      <c r="D795" s="2"/>
+      <c r="C795" s="1"/>
+      <c r="D795" s="1"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="C796" s="2"/>
-      <c r="D796" s="2"/>
+      <c r="C796" s="1"/>
+      <c r="D796" s="1"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="C797" s="2"/>
-      <c r="D797" s="2"/>
+      <c r="C797" s="1"/>
+      <c r="D797" s="1"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="C798" s="2"/>
-      <c r="D798" s="2"/>
+      <c r="C798" s="1"/>
+      <c r="D798" s="1"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="C799" s="2"/>
-      <c r="D799" s="2"/>
+      <c r="C799" s="1"/>
+      <c r="D799" s="1"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="C800" s="2"/>
-      <c r="D800" s="2"/>
+      <c r="C800" s="1"/>
+      <c r="D800" s="1"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="C801" s="2"/>
-      <c r="D801" s="2"/>
+      <c r="C801" s="1"/>
+      <c r="D801" s="1"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="C802" s="2"/>
-      <c r="D802" s="2"/>
+      <c r="C802" s="1"/>
+      <c r="D802" s="1"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="C803" s="2"/>
-      <c r="D803" s="2"/>
+      <c r="C803" s="1"/>
+      <c r="D803" s="1"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="C804" s="2"/>
-      <c r="D804" s="2"/>
+      <c r="C804" s="1"/>
+      <c r="D804" s="1"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="C805" s="2"/>
-      <c r="D805" s="2"/>
+      <c r="C805" s="1"/>
+      <c r="D805" s="1"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="C806" s="2"/>
-      <c r="D806" s="2"/>
+      <c r="C806" s="1"/>
+      <c r="D806" s="1"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="C807" s="2"/>
-      <c r="D807" s="2"/>
+      <c r="C807" s="1"/>
+      <c r="D807" s="1"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="C808" s="2"/>
-      <c r="D808" s="2"/>
+      <c r="C808" s="1"/>
+      <c r="D808" s="1"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="C809" s="2"/>
-      <c r="D809" s="2"/>
+      <c r="C809" s="1"/>
+      <c r="D809" s="1"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="C810" s="2"/>
-      <c r="D810" s="2"/>
+      <c r="C810" s="1"/>
+      <c r="D810" s="1"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="C811" s="2"/>
-      <c r="D811" s="2"/>
+      <c r="C811" s="1"/>
+      <c r="D811" s="1"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="C812" s="2"/>
-      <c r="D812" s="2"/>
+      <c r="C812" s="1"/>
+      <c r="D812" s="1"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="C813" s="2"/>
-      <c r="D813" s="2"/>
+      <c r="C813" s="1"/>
+      <c r="D813" s="1"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="C814" s="2"/>
-      <c r="D814" s="2"/>
+      <c r="C814" s="1"/>
+      <c r="D814" s="1"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="C815" s="2"/>
-      <c r="D815" s="2"/>
+      <c r="C815" s="1"/>
+      <c r="D815" s="1"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="C816" s="2"/>
-      <c r="D816" s="2"/>
+      <c r="C816" s="1"/>
+      <c r="D816" s="1"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="C817" s="2"/>
-      <c r="D817" s="2"/>
+      <c r="C817" s="1"/>
+      <c r="D817" s="1"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="C818" s="2"/>
-      <c r="D818" s="2"/>
+      <c r="C818" s="1"/>
+      <c r="D818" s="1"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="C819" s="2"/>
-      <c r="D819" s="2"/>
+      <c r="C819" s="1"/>
+      <c r="D819" s="1"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="C820" s="2"/>
-      <c r="D820" s="2"/>
+      <c r="C820" s="1"/>
+      <c r="D820" s="1"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="C821" s="2"/>
-      <c r="D821" s="2"/>
+      <c r="C821" s="1"/>
+      <c r="D821" s="1"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="C822" s="2"/>
-      <c r="D822" s="2"/>
+      <c r="C822" s="1"/>
+      <c r="D822" s="1"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="C823" s="2"/>
-      <c r="D823" s="2"/>
+      <c r="C823" s="1"/>
+      <c r="D823" s="1"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="C824" s="2"/>
-      <c r="D824" s="2"/>
+      <c r="C824" s="1"/>
+      <c r="D824" s="1"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="C825" s="2"/>
-      <c r="D825" s="2"/>
+      <c r="C825" s="1"/>
+      <c r="D825" s="1"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="C826" s="2"/>
-      <c r="D826" s="2"/>
+      <c r="C826" s="1"/>
+      <c r="D826" s="1"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="C827" s="2"/>
-      <c r="D827" s="2"/>
+      <c r="C827" s="1"/>
+      <c r="D827" s="1"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="C828" s="2"/>
-      <c r="D828" s="2"/>
+      <c r="C828" s="1"/>
+      <c r="D828" s="1"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="C829" s="2"/>
-      <c r="D829" s="2"/>
+      <c r="C829" s="1"/>
+      <c r="D829" s="1"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="C830" s="2"/>
-      <c r="D830" s="2"/>
+      <c r="C830" s="1"/>
+      <c r="D830" s="1"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="C831" s="2"/>
-      <c r="D831" s="2"/>
+      <c r="C831" s="1"/>
+      <c r="D831" s="1"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="C832" s="2"/>
-      <c r="D832" s="2"/>
+      <c r="C832" s="1"/>
+      <c r="D832" s="1"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="C833" s="2"/>
-      <c r="D833" s="2"/>
+      <c r="C833" s="1"/>
+      <c r="D833" s="1"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="C834" s="2"/>
-      <c r="D834" s="2"/>
+      <c r="C834" s="1"/>
+      <c r="D834" s="1"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="C835" s="2"/>
-      <c r="D835" s="2"/>
+      <c r="C835" s="1"/>
+      <c r="D835" s="1"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="C836" s="2"/>
-      <c r="D836" s="2"/>
+      <c r="C836" s="1"/>
+      <c r="D836" s="1"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="C837" s="2"/>
-      <c r="D837" s="2"/>
+      <c r="C837" s="1"/>
+      <c r="D837" s="1"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="C838" s="2"/>
-      <c r="D838" s="2"/>
+      <c r="C838" s="1"/>
+      <c r="D838" s="1"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="C839" s="2"/>
-      <c r="D839" s="2"/>
+      <c r="C839" s="1"/>
+      <c r="D839" s="1"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="C840" s="2"/>
-      <c r="D840" s="2"/>
+      <c r="C840" s="1"/>
+      <c r="D840" s="1"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="C841" s="2"/>
-      <c r="D841" s="2"/>
+      <c r="C841" s="1"/>
+      <c r="D841" s="1"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="C842" s="2"/>
-      <c r="D842" s="2"/>
+      <c r="C842" s="1"/>
+      <c r="D842" s="1"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="C843" s="2"/>
-      <c r="D843" s="2"/>
+      <c r="C843" s="1"/>
+      <c r="D843" s="1"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="C844" s="2"/>
-      <c r="D844" s="2"/>
+      <c r="C844" s="1"/>
+      <c r="D844" s="1"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="C845" s="2"/>
-      <c r="D845" s="2"/>
+      <c r="C845" s="1"/>
+      <c r="D845" s="1"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="C846" s="2"/>
-      <c r="D846" s="2"/>
+      <c r="C846" s="1"/>
+      <c r="D846" s="1"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="C847" s="2"/>
-      <c r="D847" s="2"/>
+      <c r="C847" s="1"/>
+      <c r="D847" s="1"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="C848" s="2"/>
-      <c r="D848" s="2"/>
+      <c r="C848" s="1"/>
+      <c r="D848" s="1"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="C849" s="2"/>
-      <c r="D849" s="2"/>
+      <c r="C849" s="1"/>
+      <c r="D849" s="1"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="C850" s="2"/>
-      <c r="D850" s="2"/>
+      <c r="C850" s="1"/>
+      <c r="D850" s="1"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="C851" s="2"/>
-      <c r="D851" s="2"/>
+      <c r="C851" s="1"/>
+      <c r="D851" s="1"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="C852" s="2"/>
-      <c r="D852" s="2"/>
+      <c r="C852" s="1"/>
+      <c r="D852" s="1"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="C853" s="2"/>
-      <c r="D853" s="2"/>
+      <c r="C853" s="1"/>
+      <c r="D853" s="1"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="C854" s="2"/>
-      <c r="D854" s="2"/>
+      <c r="C854" s="1"/>
+      <c r="D854" s="1"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="C855" s="2"/>
-      <c r="D855" s="2"/>
+      <c r="C855" s="1"/>
+      <c r="D855" s="1"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="C856" s="2"/>
-      <c r="D856" s="2"/>
+      <c r="C856" s="1"/>
+      <c r="D856" s="1"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="C857" s="2"/>
-      <c r="D857" s="2"/>
+      <c r="C857" s="1"/>
+      <c r="D857" s="1"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="C858" s="2"/>
-      <c r="D858" s="2"/>
+      <c r="C858" s="1"/>
+      <c r="D858" s="1"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="C859" s="2"/>
-      <c r="D859" s="2"/>
+      <c r="C859" s="1"/>
+      <c r="D859" s="1"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="C860" s="2"/>
-      <c r="D860" s="2"/>
+      <c r="C860" s="1"/>
+      <c r="D860" s="1"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="C861" s="2"/>
-      <c r="D861" s="2"/>
+      <c r="C861" s="1"/>
+      <c r="D861" s="1"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="C862" s="2"/>
-      <c r="D862" s="2"/>
+      <c r="C862" s="1"/>
+      <c r="D862" s="1"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="C863" s="2"/>
-      <c r="D863" s="2"/>
+      <c r="C863" s="1"/>
+      <c r="D863" s="1"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="C864" s="2"/>
-      <c r="D864" s="2"/>
+      <c r="C864" s="1"/>
+      <c r="D864" s="1"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="C865" s="2"/>
-      <c r="D865" s="2"/>
+      <c r="C865" s="1"/>
+      <c r="D865" s="1"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="C866" s="2"/>
-      <c r="D866" s="2"/>
+      <c r="C866" s="1"/>
+      <c r="D866" s="1"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="C867" s="2"/>
-      <c r="D867" s="2"/>
+      <c r="C867" s="1"/>
+      <c r="D867" s="1"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="C868" s="2"/>
-      <c r="D868" s="2"/>
+      <c r="C868" s="1"/>
+      <c r="D868" s="1"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="C869" s="2"/>
-      <c r="D869" s="2"/>
+      <c r="C869" s="1"/>
+      <c r="D869" s="1"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="C870" s="2"/>
-      <c r="D870" s="2"/>
+      <c r="C870" s="1"/>
+      <c r="D870" s="1"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="C871" s="2"/>
-      <c r="D871" s="2"/>
+      <c r="C871" s="1"/>
+      <c r="D871" s="1"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="C872" s="2"/>
-      <c r="D872" s="2"/>
+      <c r="C872" s="1"/>
+      <c r="D872" s="1"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="C873" s="2"/>
-      <c r="D873" s="2"/>
+      <c r="C873" s="1"/>
+      <c r="D873" s="1"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="C874" s="2"/>
-      <c r="D874" s="2"/>
+      <c r="C874" s="1"/>
+      <c r="D874" s="1"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="C875" s="2"/>
-      <c r="D875" s="2"/>
+      <c r="C875" s="1"/>
+      <c r="D875" s="1"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="C876" s="2"/>
-      <c r="D876" s="2"/>
+      <c r="C876" s="1"/>
+      <c r="D876" s="1"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="C877" s="2"/>
-      <c r="D877" s="2"/>
+      <c r="C877" s="1"/>
+      <c r="D877" s="1"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="C878" s="2"/>
-      <c r="D878" s="2"/>
+      <c r="C878" s="1"/>
+      <c r="D878" s="1"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="C879" s="2"/>
-      <c r="D879" s="2"/>
+      <c r="C879" s="1"/>
+      <c r="D879" s="1"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="C880" s="2"/>
-      <c r="D880" s="2"/>
+      <c r="C880" s="1"/>
+      <c r="D880" s="1"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="C881" s="2"/>
-      <c r="D881" s="2"/>
+      <c r="C881" s="1"/>
+      <c r="D881" s="1"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="C882" s="2"/>
-      <c r="D882" s="2"/>
+      <c r="C882" s="1"/>
+      <c r="D882" s="1"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="C883" s="2"/>
-      <c r="D883" s="2"/>
+      <c r="C883" s="1"/>
+      <c r="D883" s="1"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="C884" s="2"/>
-      <c r="D884" s="2"/>
+      <c r="C884" s="1"/>
+      <c r="D884" s="1"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="C885" s="2"/>
-      <c r="D885" s="2"/>
+      <c r="C885" s="1"/>
+      <c r="D885" s="1"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="C886" s="2"/>
-      <c r="D886" s="2"/>
+      <c r="C886" s="1"/>
+      <c r="D886" s="1"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="C887" s="2"/>
-      <c r="D887" s="2"/>
+      <c r="C887" s="1"/>
+      <c r="D887" s="1"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="C888" s="2"/>
-      <c r="D888" s="2"/>
+      <c r="C888" s="1"/>
+      <c r="D888" s="1"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="C889" s="2"/>
-      <c r="D889" s="2"/>
+      <c r="C889" s="1"/>
+      <c r="D889" s="1"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="C890" s="2"/>
-      <c r="D890" s="2"/>
+      <c r="C890" s="1"/>
+      <c r="D890" s="1"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="C891" s="2"/>
-      <c r="D891" s="2"/>
+      <c r="C891" s="1"/>
+      <c r="D891" s="1"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="C892" s="2"/>
-      <c r="D892" s="2"/>
+      <c r="C892" s="1"/>
+      <c r="D892" s="1"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="C893" s="2"/>
-      <c r="D893" s="2"/>
+      <c r="C893" s="1"/>
+      <c r="D893" s="1"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="C894" s="2"/>
-      <c r="D894" s="2"/>
+      <c r="C894" s="1"/>
+      <c r="D894" s="1"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="C895" s="2"/>
-      <c r="D895" s="2"/>
+      <c r="C895" s="1"/>
+      <c r="D895" s="1"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="C896" s="2"/>
-      <c r="D896" s="2"/>
+      <c r="C896" s="1"/>
+      <c r="D896" s="1"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="C897" s="2"/>
-      <c r="D897" s="2"/>
+      <c r="C897" s="1"/>
+      <c r="D897" s="1"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="C898" s="2"/>
-      <c r="D898" s="2"/>
+      <c r="C898" s="1"/>
+      <c r="D898" s="1"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="C899" s="2"/>
-      <c r="D899" s="2"/>
+      <c r="C899" s="1"/>
+      <c r="D899" s="1"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="C900" s="2"/>
-      <c r="D900" s="2"/>
+      <c r="C900" s="1"/>
+      <c r="D900" s="1"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="C901" s="2"/>
-      <c r="D901" s="2"/>
+      <c r="C901" s="1"/>
+      <c r="D901" s="1"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="C902" s="2"/>
-      <c r="D902" s="2"/>
+      <c r="C902" s="1"/>
+      <c r="D902" s="1"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="C903" s="2"/>
-      <c r="D903" s="2"/>
+      <c r="C903" s="1"/>
+      <c r="D903" s="1"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="C904" s="2"/>
-      <c r="D904" s="2"/>
+      <c r="C904" s="1"/>
+      <c r="D904" s="1"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="C905" s="2"/>
-      <c r="D905" s="2"/>
+      <c r="C905" s="1"/>
+      <c r="D905" s="1"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="C906" s="2"/>
-      <c r="D906" s="2"/>
+      <c r="C906" s="1"/>
+      <c r="D906" s="1"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="C907" s="2"/>
-      <c r="D907" s="2"/>
+      <c r="C907" s="1"/>
+      <c r="D907" s="1"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="C908" s="2"/>
-      <c r="D908" s="2"/>
+      <c r="C908" s="1"/>
+      <c r="D908" s="1"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="C909" s="2"/>
-      <c r="D909" s="2"/>
+      <c r="C909" s="1"/>
+      <c r="D909" s="1"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="C910" s="2"/>
-      <c r="D910" s="2"/>
+      <c r="C910" s="1"/>
+      <c r="D910" s="1"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="C911" s="2"/>
-      <c r="D911" s="2"/>
+      <c r="C911" s="1"/>
+      <c r="D911" s="1"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="C912" s="2"/>
-      <c r="D912" s="2"/>
+      <c r="C912" s="1"/>
+      <c r="D912" s="1"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="C913" s="2"/>
-      <c r="D913" s="2"/>
+      <c r="C913" s="1"/>
+      <c r="D913" s="1"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="C914" s="2"/>
-      <c r="D914" s="2"/>
+      <c r="C914" s="1"/>
+      <c r="D914" s="1"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="C915" s="2"/>
-      <c r="D915" s="2"/>
+      <c r="C915" s="1"/>
+      <c r="D915" s="1"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="C916" s="2"/>
-      <c r="D916" s="2"/>
+      <c r="C916" s="1"/>
+      <c r="D916" s="1"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="C917" s="2"/>
-      <c r="D917" s="2"/>
+      <c r="C917" s="1"/>
+      <c r="D917" s="1"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="C918" s="2"/>
-      <c r="D918" s="2"/>
+      <c r="C918" s="1"/>
+      <c r="D918" s="1"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="C919" s="2"/>
-      <c r="D919" s="2"/>
+      <c r="C919" s="1"/>
+      <c r="D919" s="1"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="C920" s="2"/>
-      <c r="D920" s="2"/>
+      <c r="C920" s="1"/>
+      <c r="D920" s="1"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="C921" s="2"/>
-      <c r="D921" s="2"/>
+      <c r="C921" s="1"/>
+      <c r="D921" s="1"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="C922" s="2"/>
-      <c r="D922" s="2"/>
+      <c r="C922" s="1"/>
+      <c r="D922" s="1"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="C923" s="2"/>
-      <c r="D923" s="2"/>
+      <c r="C923" s="1"/>
+      <c r="D923" s="1"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="C924" s="2"/>
-      <c r="D924" s="2"/>
+      <c r="C924" s="1"/>
+      <c r="D924" s="1"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="C925" s="2"/>
-      <c r="D925" s="2"/>
+      <c r="C925" s="1"/>
+      <c r="D925" s="1"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="C926" s="2"/>
-      <c r="D926" s="2"/>
+      <c r="C926" s="1"/>
+      <c r="D926" s="1"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="C927" s="2"/>
-      <c r="D927" s="2"/>
+      <c r="C927" s="1"/>
+      <c r="D927" s="1"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="C928" s="2"/>
-      <c r="D928" s="2"/>
+      <c r="C928" s="1"/>
+      <c r="D928" s="1"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="C929" s="2"/>
-      <c r="D929" s="2"/>
+      <c r="C929" s="1"/>
+      <c r="D929" s="1"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="C930" s="2"/>
-      <c r="D930" s="2"/>
+      <c r="C930" s="1"/>
+      <c r="D930" s="1"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="C931" s="2"/>
-      <c r="D931" s="2"/>
+      <c r="C931" s="1"/>
+      <c r="D931" s="1"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="C932" s="2"/>
-      <c r="D932" s="2"/>
+      <c r="C932" s="1"/>
+      <c r="D932" s="1"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="C933" s="2"/>
-      <c r="D933" s="2"/>
+      <c r="C933" s="1"/>
+      <c r="D933" s="1"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="C934" s="2"/>
-      <c r="D934" s="2"/>
+      <c r="C934" s="1"/>
+      <c r="D934" s="1"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="C935" s="2"/>
-      <c r="D935" s="2"/>
+      <c r="C935" s="1"/>
+      <c r="D935" s="1"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="C936" s="2"/>
-      <c r="D936" s="2"/>
+      <c r="C936" s="1"/>
+      <c r="D936" s="1"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="C937" s="2"/>
-      <c r="D937" s="2"/>
+      <c r="C937" s="1"/>
+      <c r="D937" s="1"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="C938" s="2"/>
-      <c r="D938" s="2"/>
+      <c r="C938" s="1"/>
+      <c r="D938" s="1"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="C939" s="2"/>
-      <c r="D939" s="2"/>
+      <c r="C939" s="1"/>
+      <c r="D939" s="1"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="C940" s="2"/>
-      <c r="D940" s="2"/>
+      <c r="C940" s="1"/>
+      <c r="D940" s="1"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="C941" s="2"/>
-      <c r="D941" s="2"/>
+      <c r="C941" s="1"/>
+      <c r="D941" s="1"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="C942" s="2"/>
-      <c r="D942" s="2"/>
+      <c r="C942" s="1"/>
+      <c r="D942" s="1"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="C943" s="2"/>
-      <c r="D943" s="2"/>
+      <c r="C943" s="1"/>
+      <c r="D943" s="1"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="C944" s="2"/>
-      <c r="D944" s="2"/>
+      <c r="C944" s="1"/>
+      <c r="D944" s="1"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="C945" s="2"/>
-      <c r="D945" s="2"/>
+      <c r="C945" s="1"/>
+      <c r="D945" s="1"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="C946" s="2"/>
-      <c r="D946" s="2"/>
+      <c r="C946" s="1"/>
+      <c r="D946" s="1"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="C947" s="2"/>
-      <c r="D947" s="2"/>
+      <c r="C947" s="1"/>
+      <c r="D947" s="1"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="C948" s="2"/>
-      <c r="D948" s="2"/>
+      <c r="C948" s="1"/>
+      <c r="D948" s="1"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="C949" s="2"/>
-      <c r="D949" s="2"/>
+      <c r="C949" s="1"/>
+      <c r="D949" s="1"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="C950" s="2"/>
-      <c r="D950" s="2"/>
+      <c r="C950" s="1"/>
+      <c r="D950" s="1"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="C951" s="2"/>
-      <c r="D951" s="2"/>
+      <c r="C951" s="1"/>
+      <c r="D951" s="1"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
+      <c r="C952" s="1"/>
+      <c r="D952" s="1"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
+      <c r="C953" s="1"/>
+      <c r="D953" s="1"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
+      <c r="C954" s="1"/>
+      <c r="D954" s="1"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
+      <c r="C955" s="1"/>
+      <c r="D955" s="1"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
+      <c r="C956" s="1"/>
+      <c r="D956" s="1"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
+      <c r="C957" s="1"/>
+      <c r="D957" s="1"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
+      <c r="C958" s="1"/>
+      <c r="D958" s="1"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
+      <c r="C959" s="1"/>
+      <c r="D959" s="1"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
+      <c r="C960" s="1"/>
+      <c r="D960" s="1"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
+      <c r="C961" s="1"/>
+      <c r="D961" s="1"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
+      <c r="C962" s="1"/>
+      <c r="D962" s="1"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
+      <c r="C963" s="1"/>
+      <c r="D963" s="1"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
+      <c r="C964" s="1"/>
+      <c r="D964" s="1"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
+      <c r="C965" s="1"/>
+      <c r="D965" s="1"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
+      <c r="C966" s="1"/>
+      <c r="D966" s="1"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
+      <c r="C967" s="1"/>
+      <c r="D967" s="1"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
+      <c r="C968" s="1"/>
+      <c r="D968" s="1"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
+      <c r="C969" s="1"/>
+      <c r="D969" s="1"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
+      <c r="C970" s="1"/>
+      <c r="D970" s="1"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
+      <c r="C971" s="1"/>
+      <c r="D971" s="1"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
+      <c r="C972" s="1"/>
+      <c r="D972" s="1"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
+      <c r="C973" s="1"/>
+      <c r="D973" s="1"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
+      <c r="C974" s="1"/>
+      <c r="D974" s="1"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
+      <c r="C975" s="1"/>
+      <c r="D975" s="1"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
+      <c r="C976" s="1"/>
+      <c r="D976" s="1"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
+      <c r="C977" s="1"/>
+      <c r="D977" s="1"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
+      <c r="C978" s="1"/>
+      <c r="D978" s="1"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
+      <c r="C979" s="1"/>
+      <c r="D979" s="1"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
+      <c r="C980" s="1"/>
+      <c r="D980" s="1"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
+      <c r="C981" s="1"/>
+      <c r="D981" s="1"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
+      <c r="C982" s="1"/>
+      <c r="D982" s="1"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
+      <c r="C983" s="1"/>
+      <c r="D983" s="1"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
+      <c r="C984" s="1"/>
+      <c r="D984" s="1"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
+      <c r="C985" s="1"/>
+      <c r="D985" s="1"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
+      <c r="C986" s="1"/>
+      <c r="D986" s="1"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
+      <c r="C987" s="1"/>
+      <c r="D987" s="1"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
+      <c r="C988" s="1"/>
+      <c r="D988" s="1"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
+      <c r="C989" s="1"/>
+      <c r="D989" s="1"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
+      <c r="C990" s="1"/>
+      <c r="D990" s="1"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
+      <c r="C991" s="1"/>
+      <c r="D991" s="1"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
+      <c r="C992" s="1"/>
+      <c r="D992" s="1"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
+      <c r="C993" s="1"/>
+      <c r="D993" s="1"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
+      <c r="C994" s="1"/>
+      <c r="D994" s="1"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
+      <c r="C995" s="1"/>
+      <c r="D995" s="1"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
+      <c r="C996" s="1"/>
+      <c r="D996" s="1"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
+      <c r="C997" s="1"/>
+      <c r="D997" s="1"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
+      <c r="C998" s="1"/>
+      <c r="D998" s="1"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
+      <c r="C999" s="1"/>
+      <c r="D999" s="1"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
+      <c r="C1000" s="1"/>
+      <c r="D1000" s="1"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="C1001" s="2"/>
-      <c r="D1001" s="2"/>
+      <c r="C1001" s="1"/>
+      <c r="D1001" s="1"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
-      <c r="C1002" s="2"/>
-      <c r="D1002" s="2"/>
+      <c r="C1002" s="1"/>
+      <c r="D1002" s="1"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
-      <c r="C1003" s="2"/>
-      <c r="D1003" s="2"/>
+      <c r="C1003" s="1"/>
+      <c r="D1003" s="1"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
-      <c r="C1004" s="2"/>
-      <c r="D1004" s="2"/>
+      <c r="C1004" s="1"/>
+      <c r="D1004" s="1"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
-      <c r="C1005" s="2"/>
-      <c r="D1005" s="2"/>
+      <c r="C1005" s="1"/>
+      <c r="D1005" s="1"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
-      <c r="C1006" s="2"/>
-      <c r="D1006" s="2"/>
+      <c r="C1006" s="1"/>
+      <c r="D1006" s="1"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
-      <c r="C1007" s="2"/>
-      <c r="D1007" s="2"/>
+      <c r="C1007" s="1"/>
+      <c r="D1007" s="1"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
-      <c r="C1008" s="2"/>
-      <c r="D1008" s="2"/>
+      <c r="C1008" s="1"/>
+      <c r="D1008" s="1"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
-      <c r="C1009" s="2"/>
-      <c r="D1009" s="2"/>
+      <c r="C1009" s="1"/>
+      <c r="D1009" s="1"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
-      <c r="C1010" s="2"/>
-      <c r="D1010" s="2"/>
+      <c r="C1010" s="1"/>
+      <c r="D1010" s="1"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
-      <c r="C1011" s="2"/>
-      <c r="D1011" s="2"/>
+      <c r="C1011" s="1"/>
+      <c r="D1011" s="1"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
-      <c r="C1012" s="2"/>
-      <c r="D1012" s="2"/>
+      <c r="C1012" s="1"/>
+      <c r="D1012" s="1"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
-      <c r="C1013" s="2"/>
-      <c r="D1013" s="2"/>
+      <c r="C1013" s="1"/>
+      <c r="D1013" s="1"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
-      <c r="C1014" s="2"/>
-      <c r="D1014" s="2"/>
+      <c r="C1014" s="1"/>
+      <c r="D1014" s="1"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
-      <c r="C1015" s="2"/>
-      <c r="D1015" s="2"/>
+      <c r="C1015" s="1"/>
+      <c r="D1015" s="1"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
-      <c r="C1016" s="2"/>
-      <c r="D1016" s="2"/>
+      <c r="C1016" s="1"/>
+      <c r="D1016" s="1"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
-      <c r="C1017" s="2"/>
-      <c r="D1017" s="2"/>
+      <c r="C1017" s="1"/>
+      <c r="D1017" s="1"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
-      <c r="C1018" s="2"/>
-      <c r="D1018" s="2"/>
+      <c r="C1018" s="1"/>
+      <c r="D1018" s="1"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
-      <c r="C1019" s="2"/>
-      <c r="D1019" s="2"/>
+      <c r="C1019" s="1"/>
+      <c r="D1019" s="1"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
-      <c r="C1020" s="2"/>
-      <c r="D1020" s="2"/>
+      <c r="C1020" s="1"/>
+      <c r="D1020" s="1"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
-      <c r="C1021" s="2"/>
-      <c r="D1021" s="2"/>
+      <c r="C1021" s="1"/>
+      <c r="D1021" s="1"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
-      <c r="C1022" s="2"/>
-      <c r="D1022" s="2"/>
+      <c r="C1022" s="1"/>
+      <c r="D1022" s="1"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
-      <c r="C1023" s="2"/>
-      <c r="D1023" s="2"/>
+      <c r="C1023" s="1"/>
+      <c r="D1023" s="1"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
-      <c r="C1024" s="2"/>
-      <c r="D1024" s="2"/>
+      <c r="C1024" s="1"/>
+      <c r="D1024" s="1"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
-      <c r="C1025" s="2"/>
-      <c r="D1025" s="2"/>
+      <c r="C1025" s="1"/>
+      <c r="D1025" s="1"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1">
-      <c r="C1026" s="2"/>
-      <c r="D1026" s="2"/>
+      <c r="C1026" s="1"/>
+      <c r="D1026" s="1"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1">
-      <c r="C1027" s="2"/>
-      <c r="D1027" s="2"/>
+      <c r="C1027" s="1"/>
+      <c r="D1027" s="1"/>
     </row>
     <row r="1028" ht="12.75" customHeight="1">
-      <c r="C1028" s="2"/>
-      <c r="D1028" s="2"/>
+      <c r="C1028" s="1"/>
+      <c r="D1028" s="1"/>
     </row>
     <row r="1029" ht="12.75" customHeight="1">
-      <c r="C1029" s="2"/>
-      <c r="D1029" s="2"/>
+      <c r="C1029" s="1"/>
+      <c r="D1029" s="1"/>
     </row>
     <row r="1030" ht="12.75" customHeight="1">
-      <c r="C1030" s="2"/>
-      <c r="D1030" s="2"/>
+      <c r="C1030" s="1"/>
+      <c r="D1030" s="1"/>
     </row>
     <row r="1031" ht="12.75" customHeight="1">
-      <c r="C1031" s="2"/>
-      <c r="D1031" s="2"/>
+      <c r="C1031" s="1"/>
+      <c r="D1031" s="1"/>
     </row>
     <row r="1032" ht="12.75" customHeight="1">
-      <c r="C1032" s="2"/>
-      <c r="D1032" s="2"/>
+      <c r="C1032" s="1"/>
+      <c r="D1032" s="1"/>
     </row>
     <row r="1033" ht="12.75" customHeight="1">
-      <c r="C1033" s="2"/>
-      <c r="D1033" s="2"/>
+      <c r="C1033" s="1"/>
+      <c r="D1033" s="1"/>
     </row>
     <row r="1034" ht="12.75" customHeight="1">
-      <c r="C1034" s="2"/>
-      <c r="D1034" s="2"/>
+      <c r="C1034" s="1"/>
+      <c r="D1034" s="1"/>
     </row>
     <row r="1035" ht="12.75" customHeight="1">
-      <c r="C1035" s="2"/>
-      <c r="D1035" s="2"/>
+      <c r="C1035" s="1"/>
+      <c r="D1035" s="1"/>
     </row>
     <row r="1036" ht="12.75" customHeight="1">
-      <c r="C1036" s="2"/>
-      <c r="D1036" s="2"/>
+      <c r="C1036" s="1"/>
+      <c r="D1036" s="1"/>
     </row>
     <row r="1037" ht="12.75" customHeight="1">
-      <c r="C1037" s="2"/>
-      <c r="D1037" s="2"/>
+      <c r="C1037" s="1"/>
+      <c r="D1037" s="1"/>
     </row>
     <row r="1038" ht="12.75" customHeight="1">
-      <c r="C1038" s="2"/>
-      <c r="D1038" s="2"/>
+      <c r="C1038" s="1"/>
+      <c r="D1038" s="1"/>
+    </row>
+    <row r="1039" ht="12.75" customHeight="1">
+      <c r="C1039" s="1"/>
+      <c r="D1039" s="1"/>
+    </row>
+    <row r="1040" ht="12.75" customHeight="1">
+      <c r="C1040" s="1"/>
+      <c r="D1040" s="1"/>
+    </row>
+    <row r="1041" ht="12.75" customHeight="1">
+      <c r="C1041" s="1"/>
+      <c r="D1041" s="1"/>
+    </row>
+    <row r="1042" ht="12.75" customHeight="1">
+      <c r="C1042" s="1"/>
+      <c r="D1042" s="1"/>
+    </row>
+    <row r="1043" ht="12.75" customHeight="1">
+      <c r="C1043" s="1"/>
+      <c r="D1043" s="1"/>
+    </row>
+    <row r="1044" ht="12.75" customHeight="1">
+      <c r="C1044" s="1"/>
+      <c r="D1044" s="1"/>
+    </row>
+    <row r="1045" ht="12.75" customHeight="1">
+      <c r="C1045" s="1"/>
+      <c r="D1045" s="1"/>
+    </row>
+    <row r="1046" ht="12.75" customHeight="1">
+      <c r="C1046" s="1"/>
+      <c r="D1046" s="1"/>
+    </row>
+    <row r="1047" ht="12.75" customHeight="1">
+      <c r="C1047" s="1"/>
+      <c r="D1047" s="1"/>
+    </row>
+    <row r="1048" ht="12.75" customHeight="1">
+      <c r="C1048" s="1"/>
+      <c r="D1048" s="1"/>
+    </row>
+    <row r="1049" ht="12.75" customHeight="1">
+      <c r="C1049" s="1"/>
+      <c r="D1049" s="1"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -6054,190 +6274,192 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="14.43"/>
+    <col customWidth="1" min="1" max="2" width="14.43"/>
+    <col customWidth="1" min="3" max="3" width="43.71"/>
+    <col customWidth="1" min="4" max="6" width="14.43"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+      <c r="A2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
+      <c r="A3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>38</v>
+      <c r="A5" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>42</v>
+      <c r="A6" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>48</v>
+      <c r="A7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>60</v>
+      <c r="A8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>64</v>
+      <c r="A9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>68</v>
+      <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>72</v>
+      <c r="A11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>76</v>
+      <c r="A12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>48</v>
+      <c r="A13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7249,40 +7471,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
+      <c r="A1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3">
+        <v>88</v>
+      </c>
+      <c r="C2" s="8">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>79</v>
+      <c r="D2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="281">
   <si>
     <t>type</t>
   </si>
@@ -144,6 +144,9 @@
     <t>refer_flag_postpartum_other_signs</t>
   </si>
   <si>
+    <t>refer_flag_anc_visit_6m_or_more</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
@@ -204,6 +207,12 @@
     <t>../inputs/original_source_form</t>
   </si>
   <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
     <t>referral_source_id</t>
   </si>
   <si>
@@ -216,21 +225,48 @@
     <t>../inputs/last_visit_date</t>
   </si>
   <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
     <t>last_visit_formatted</t>
   </si>
   <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
     <t>format-date-time(../inputs/last_visit_date div (1000*60*60*24), "%d/%m/%Y")</t>
   </si>
   <si>
     <t>../inputs/refer_flag_small_baby</t>
   </si>
   <si>
+    <t>pages</t>
+  </si>
+  <si>
     <t>../inputs/refer_neonatal_danger_sign_flag</t>
   </si>
   <si>
     <t>../inputs/refer_secondary_neonatal_danger_sign_flag</t>
   </si>
   <si>
+    <t>data</t>
+  </si>
+  <si>
     <t>../inputs/refer_child_danger_sign_flag</t>
   </si>
   <si>
@@ -240,69 +276,147 @@
     <t>../inputs/refer_refer_palm_pallor_flag</t>
   </si>
   <si>
+    <t>yes_no</t>
+  </si>
+  <si>
     <t>../inputs/refer_vaccines_flag</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
     <t>../inputs/refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
     <t>client</t>
   </si>
   <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
     <t>client_name</t>
   </si>
   <si>
+    <t>Sina pesa</t>
+  </si>
+  <si>
     <t>../inputs/contact/name</t>
   </si>
   <si>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
     <t>client_date_of_birth</t>
   </si>
   <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
-    <t>referral_follow_up</t>
+    <t>Sikutaka kwenda</t>
+  </si>
+  <si>
+    <t>no_permission</t>
+  </si>
+  <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
+    <t>reason_didnt_get_svc</t>
+  </si>
+  <si>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
   </si>
   <si>
     <t>../inputs/contact/date_of_birth</t>
   </si>
   <si>
-    <t>pages</t>
+    <t>services_not_offered</t>
+  </si>
+  <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
+    <t>Huduma nilizotaka hazikuwepo.</t>
   </si>
   <si>
     <t>../inputs/due_date</t>
   </si>
   <si>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
+  </si>
+  <si>
     <t>due_date_pretty_print</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>../inputs/due_date_human_readable</t>
   </si>
   <si>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
+    <t>Walitaka nilipie huduma</t>
+  </si>
+  <si>
     <t>../inputs/refer_flag_emergency_danger_sign</t>
   </si>
   <si>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
+  </si>
+  <si>
     <t>../inputs/refer_flag_pregnancy_issues</t>
   </si>
   <si>
@@ -315,6 +429,9 @@
     <t>../inputs/refer_flag_postpartum_other_signs</t>
   </si>
   <si>
+    <t>../inputs/refer_flag_anc_visit_6m_or_more</t>
+  </si>
+  <si>
     <t>age_days</t>
   </si>
   <si>
@@ -328,117 +445,6 @@
   </si>
   <si>
     <t>age_years</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
-    <t>Sina pesa</t>
-  </si>
-  <si>
-    <t>did_not_want</t>
-  </si>
-  <si>
-    <t>I did not want to go</t>
-  </si>
-  <si>
-    <t>Sikutaka kwenda</t>
-  </si>
-  <si>
-    <t>no_permission</t>
-  </si>
-  <si>
-    <t>I did not have permission to go</t>
-  </si>
-  <si>
-    <t>Sikupewa ruhusa ya kwenda</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Nyenginezo</t>
-  </si>
-  <si>
-    <t>reason_didnt_get_svc</t>
-  </si>
-  <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
-  </si>
-  <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
     <t>int(${age_days} div (30 *12),0)</t>
@@ -693,6 +699,18 @@
     <t>../../inputs/refer_flag_postpartum_other_signs= 1</t>
   </si>
   <si>
+    <t>reason_refer_flag_anc_visit_6m_or_more</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To get ANC services since your pregnancy is 6 months or more.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kupatiwa huduma za mama mjamzito kwa vile mimba yako ni miezi sita au zaidi.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_anc_visit_6m_or_more= 1</t>
+  </si>
+  <si>
     <t>select_one yes_no</t>
   </si>
   <si>
@@ -831,7 +849,7 @@
     <t>has_pregnancy_referral</t>
   </si>
   <si>
-    <t xml:space="preserve">../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1 </t>
+    <t>../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1 or ../inputs/refer_flag_anc_visit_6m_or_more = 1</t>
   </si>
   <si>
     <t>has_infant_child_referral</t>
@@ -865,10 +883,10 @@
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10.0"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -910,16 +928,16 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -928,7 +946,7 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1277,26 +1295,26 @@
       <c r="D21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1"/>
     </row>
@@ -1305,10 +1323,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -1317,7 +1335,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>48</v>
@@ -1326,59 +1344,59 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="1"/>
       <c r="D26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C27" s="1"/>
       <c r="D27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="1"/>
-      <c r="G28" s="1" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
@@ -1399,1113 +1417,1144 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="L35" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="L36" s="3" t="s">
+      <c r="L36" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="L37" s="1" t="s">
-        <v>64</v>
+      <c r="L37" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>67</v>
+      <c r="A39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="L39" s="4" t="s">
-        <v>68</v>
+      <c r="L39" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>28</v>
+      <c r="A40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="L40" t="s">
-        <v>69</v>
+      <c r="L40" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="L41" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="L42" s="3" t="s">
-        <v>71</v>
+      <c r="L42" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="L43" t="s">
-        <v>72</v>
+      <c r="L43" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="L44" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="L45" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="L46" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="L48" s="1" t="s">
-        <v>58</v>
+      <c r="L48" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="L49" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="7"/>
-      <c r="L50" s="3" t="s">
-        <v>89</v>
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="L50" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9"/>
       <c r="L51" s="3" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9"/>
       <c r="L52" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="7"/>
-      <c r="L53" s="10" t="s">
-        <v>95</v>
+        <v>125</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9"/>
+      <c r="L53" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
       <c r="L54" s="10" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
       <c r="L55" s="10" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="7"/>
+        <v>40</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
       <c r="L56" s="10" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9"/>
       <c r="L57" s="10" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="7"/>
-      <c r="L58" s="11" t="s">
-        <v>101</v>
+        <v>42</v>
+      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="L58" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="5"/>
-      <c r="D59" s="7"/>
-      <c r="L59" s="12" t="s">
-        <v>103</v>
+        <v>43</v>
+      </c>
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
+      <c r="L59" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="7"/>
-      <c r="L60" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
+      </c>
+      <c r="C60" s="8"/>
+      <c r="D60" s="9"/>
+      <c r="L60" s="11" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="9"/>
       <c r="L61" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="7"/>
-      <c r="L62" s="15" t="s">
-        <v>146</v>
+        <v>57</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="8"/>
+      <c r="D62" s="9"/>
+      <c r="L62" s="12" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="7"/>
-      <c r="L63" s="15" t="s">
-        <v>148</v>
+        <v>57</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="9"/>
+      <c r="L63" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C64" s="5"/>
-      <c r="D64" s="7"/>
+        <v>147</v>
+      </c>
+      <c r="C64" s="8"/>
+      <c r="D64" s="9"/>
       <c r="L64" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B65" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="7"/>
+        <v>149</v>
+      </c>
+      <c r="C65" s="8"/>
+      <c r="D65" s="9"/>
       <c r="L65" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>156</v>
+        <v>57</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="8"/>
+      <c r="D66" s="9"/>
+      <c r="L66" s="15" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>160</v>
+        <v>57</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="8"/>
+      <c r="D67" s="9"/>
+      <c r="L67" s="15" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>163</v>
+      <c r="G68" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="4"/>
+        <v>166</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="A72" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>174</v>
-      </c>
+      <c r="A73" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D76" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="F76" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F75" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F77" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="F78" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F77" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="F78" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="F79" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>201</v>
+        <v>193</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="F80" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D82" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="F82" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="4" t="s">
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F81" t="s">
+      <c r="C83" s="5" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="D83" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="F83" t="s">
         <v>208</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="E84" s="1"/>
-      <c r="F84" s="3" t="s">
-        <v>218</v>
+      <c r="F84" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>221</v>
+        <v>214</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="1" t="s">
+      <c r="D87" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="E87" s="1"/>
+      <c r="F87" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C86" s="4" t="s">
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="C88" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B87" s="4" t="s">
+      <c r="D88" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1" t="s">
+      <c r="E88" s="1"/>
+      <c r="F88" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F88" s="1"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="E89" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="C90" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F89" s="1"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B91" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="E92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="B93" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
+      <c r="D93" s="5" t="s">
         <v>244</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>250</v>
-      </c>
+      <c r="A95" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C96" s="1"/>
+        <v>249</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
+      <c r="F96" s="1" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B97" s="4" t="s">
+      <c r="A97" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="4" t="s">
+      <c r="B97" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>252</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C98" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="C98" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>107</v>
+      <c r="D98" s="5" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C99" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="C100" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="F99" s="1" t="s">
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B100" s="4" t="s">
+      <c r="C101" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="L100" s="4" t="s">
+      <c r="D101" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E101" s="4"/>
-      <c r="F101" t="s">
-        <v>265</v>
+      <c r="E101" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-    </row>
-    <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" t="s">
-        <v>56</v>
-      </c>
-      <c r="B104" s="3" t="s">
+      <c r="A103" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="L104" t="s">
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="L103" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B105" s="3" t="s">
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>268</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E104" s="5"/>
+      <c r="F104" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="L105" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>270</v>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="L106" s="2" t="s">
-        <v>271</v>
-      </c>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="3" t="s">
-        <v>56</v>
+      <c r="A107" t="s">
+        <v>57</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
-      <c r="L107" s="3" t="s">
+      <c r="L107" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B108" s="1" t="s">
+      <c r="A108" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>274</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
-      <c r="L108">
-        <v>3.0</v>
+      <c r="L108" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="109" ht="12.75" customHeight="1">
+      <c r="A109" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
+      <c r="L109" s="2" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="110" ht="12.75" customHeight="1">
+      <c r="A110" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
+      <c r="L110" s="3" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="111" ht="12.75" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
+      <c r="L111">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="C112" s="1"/>
@@ -6258,6 +6307,18 @@
     <row r="1049" ht="12.75" customHeight="1">
       <c r="C1049" s="1"/>
       <c r="D1049" s="1"/>
+    </row>
+    <row r="1050" ht="12.75" customHeight="1">
+      <c r="C1050" s="1"/>
+      <c r="D1050" s="1"/>
+    </row>
+    <row r="1051" ht="12.75" customHeight="1">
+      <c r="C1051" s="1"/>
+      <c r="D1051" s="1"/>
+    </row>
+    <row r="1052" ht="12.75" customHeight="1">
+      <c r="C1052" s="1"/>
+      <c r="D1052" s="1"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -6281,185 +6342,185 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D7" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7471,40 +7532,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>86</v>
+      <c r="A1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="8">
+        <v>77</v>
+      </c>
+      <c r="C2" s="6">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>93</v>
+      <c r="D2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,11 +13,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="295">
+  <si>
+    <t>list_name</t>
+  </si>
   <si>
     <t>type</t>
   </si>
   <si>
+    <t>form_title</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -27,18 +33,102 @@
     <t>label::sw</t>
   </si>
   <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>Sina pesa</t>
+  </si>
+  <si>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
+    <t>Sikutaka kwenda</t>
+  </si>
+  <si>
+    <t>no_permission</t>
+  </si>
+  <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>relevant</t>
   </si>
   <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
     <t>appearance</t>
   </si>
   <si>
     <t>read_only</t>
   </si>
   <si>
+    <t>reason_didnt_get_svc</t>
+  </si>
+  <si>
     <t>constraint</t>
   </si>
   <si>
@@ -78,6 +168,54 @@
     <t>./source = 'user'</t>
   </si>
   <si>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
+  </si>
+  <si>
+    <t>services_not_offered</t>
+  </si>
+  <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
+    <t>Huduma nilizotaka hazikuwepo.</t>
+  </si>
+  <si>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
+  </si>
+  <si>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
+    <t>Walitaka nilipie huduma</t>
+  </si>
+  <si>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
     <t>hidden</t>
   </si>
   <si>
@@ -93,6 +231,9 @@
     <t>original_source_form</t>
   </si>
   <si>
+    <t>data</t>
+  </si>
+  <si>
     <t>source_id</t>
   </si>
   <si>
@@ -111,6 +252,9 @@
     <t>refer_child_danger_sign_flag</t>
   </si>
   <si>
+    <t>refer_child_other_danger_sign_flag</t>
+  </si>
+  <si>
     <t>refer_muac_flag</t>
   </si>
   <si>
@@ -207,12 +351,6 @@
     <t>../inputs/original_source_form</t>
   </si>
   <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
     <t>referral_source_id</t>
   </si>
   <si>
@@ -225,198 +363,66 @@
     <t>../inputs/last_visit_date</t>
   </si>
   <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
     <t>last_visit_formatted</t>
   </si>
   <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
     <t>format-date-time(../inputs/last_visit_date div (1000*60*60*24), "%d/%m/%Y")</t>
   </si>
   <si>
     <t>../inputs/refer_flag_small_baby</t>
   </si>
   <si>
-    <t>pages</t>
-  </si>
-  <si>
     <t>../inputs/refer_neonatal_danger_sign_flag</t>
   </si>
   <si>
     <t>../inputs/refer_secondary_neonatal_danger_sign_flag</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>../inputs/refer_child_danger_sign_flag</t>
   </si>
   <si>
+    <t>../inputs/refer_child_other_danger_sign_flag</t>
+  </si>
+  <si>
     <t>../inputs/refer_muac_flag</t>
   </si>
   <si>
     <t>../inputs/refer_refer_palm_pallor_flag</t>
   </si>
   <si>
-    <t>yes_no</t>
-  </si>
-  <si>
     <t>../inputs/refer_vaccines_flag</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
-  </si>
-  <si>
     <t>../inputs/refer_slow_to_learn_specifics_flag</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Hapana</t>
-  </si>
-  <si>
     <t>client</t>
   </si>
   <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
     <t>client_name</t>
   </si>
   <si>
-    <t>Sina pesa</t>
-  </si>
-  <si>
     <t>../inputs/contact/name</t>
   </si>
   <si>
-    <t>did_not_want</t>
-  </si>
-  <si>
-    <t>I did not want to go</t>
-  </si>
-  <si>
     <t>client_date_of_birth</t>
   </si>
   <si>
-    <t>Sikutaka kwenda</t>
-  </si>
-  <si>
-    <t>no_permission</t>
-  </si>
-  <si>
-    <t>I did not have permission to go</t>
-  </si>
-  <si>
-    <t>Sikupewa ruhusa ya kwenda</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Nyenginezo</t>
-  </si>
-  <si>
-    <t>reason_didnt_get_svc</t>
-  </si>
-  <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
-  </si>
-  <si>
     <t>../inputs/contact/date_of_birth</t>
   </si>
   <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
     <t>../inputs/due_date</t>
   </si>
   <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
     <t>due_date_pretty_print</t>
   </si>
   <si>
     <t>../inputs/due_date_human_readable</t>
   </si>
   <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
     <t>../inputs/refer_flag_emergency_danger_sign</t>
   </si>
   <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
-  </si>
-  <si>
     <t>../inputs/refer_flag_pregnancy_issues</t>
   </si>
   <si>
@@ -480,6 +486,49 @@
     <t>instance('contact-summary')/context/phone</t>
   </si>
   <si>
+    <t xml:space="preserve">begin group </t>
+  </si>
+  <si>
+    <t>covid19_intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precautionary measures when visiting a client  </t>
+  </si>
+  <si>
+    <t>Hatua za kuchukua pindi unapoenda kumtembelea mteja wako</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>covid19_intro_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Corona virus to one another. Therefore, make sure you consider the following while you conduct the visits:  
+•        Wash your hands with soap/sanitizer as many time as you can while at home, once you are at the client’s house and when you leave.
+•        Keep a 2 meters distance while talking to your clients.
+•        Don’t shake hands with your clients. 
+•        Avoid group gatherings.
+•        Provide the service at the open space and if it should be inside, make sure the windows and doors are open. 
+•        Cover your mouth with a towel or elbow when you sneeze or cough. 
+•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama mhudumu wa afya ya jamii, una jukumu la kuhakikisha unatoa elimu ya afya ya jamii na huduma huku ukijikinga ili kuepusha kusambaa kwa maambukizi ya korona kutoka kwa mtu mmoja kwenda kwa mwengine. Hivyo hakikisha unazingatia yafuatayo wakati ukiwa unatoa huduma:
+•        Osha mikono yako kwa maji na sabuni au kutumia vitakasa mikono mara nyingi kadiri unavyoweza ukiwa nyumbani kwako,nyumbani kwa mteja wako na pindi ukimaliza kutoa huduma. 
+•        Hakikisha kuna umbali wa mita mbili kati yako na mteja wako unayeenda kumtembelea 
+•        Pindi ukiongea na wateja wako , usishikane mikono. 
+•        Epuka mikusanyiko. 
+•        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
+•        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end group </t>
+  </si>
+  <si>
     <t>client_information</t>
   </si>
   <si>
@@ -490,9 +539,6 @@
   </si>
   <si>
     <t>field-list</t>
-  </si>
-  <si>
-    <t>note</t>
   </si>
   <si>
     <t>intro_note</t>
@@ -603,6 +649,18 @@
     <t>../../inputs/refer_child_danger_sign_flag = 1</t>
   </si>
   <si>
+    <t>reason_refer_child_other_danger_sign_flag</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To address child danger sign.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kushughulikia dalili za hatari za mtoto.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_child_other_danger_sign_flag = 1</t>
+  </si>
+  <si>
     <t>reason_refer_muac_flag</t>
   </si>
   <si>
@@ -855,7 +913,7 @@
     <t>has_infant_child_referral</t>
   </si>
   <si>
-    <t xml:space="preserve">./../inputs/refer_flag_small_baby= 1 or ../../inputs/refer_neonatal_danger_sign_flag = 1 or ../../inputs/refer_secondary_neonatal_danger_sign_flag = 1 or ../../inputs/refer_child_danger_sign_flag = 1 or ../../inputs/refer_muac_flag= 1 or ../../inputs/refer_refer_palm_pallor_flag = 1 or  ../../inputs/refer_vaccines_flag = 1 or ../../inputs/refer_slow_to_learn_specifics_flag = 1 </t>
+    <t xml:space="preserve">../inputs/refer_flag_small_baby= 1 or ../inputs/refer_neonatal_danger_sign_flag = 1 or ../inputs/refer_secondary_neonatal_danger_sign_flag = 1 or ../inputs/refer_child_danger_sign_flag = 1 or ../inputs/refer_child_other_danger_sign_flag = 1 or ../inputs/refer_muac_flag= 1 or ../inputs/refer_refer_palm_pallor_flag = 1 or  ../inputs/refer_vaccines_flag = 1 or ../inputs/refer_slow_to_learn_specifics_flag = 1 </t>
   </si>
   <si>
     <t>has_postpartum_referral</t>
@@ -871,10 +929,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
       <name val="Arial"/>
     </font>
     <font/>
@@ -883,18 +945,18 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color rgb="FF1D1C1D"/>
+      <name val="Slack-Lato"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -907,6 +969,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -917,33 +985,33 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -955,8 +1023,20 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,7 +1065,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="40.0"/>
     <col customWidth="1" min="2" max="2" width="43.57"/>
     <col customWidth="1" min="3" max="3" width="37.29"/>
     <col customWidth="1" min="4" max="17" width="14.43"/>
@@ -993,739 +1073,738 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
+      <c r="E1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
+      <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="F2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="G4" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="A5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1"/>
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1"/>
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1"/>
+      <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1"/>
+      <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1"/>
+      <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1"/>
+      <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1"/>
+      <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1"/>
+      <c r="A15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
+      <c r="A16" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>22</v>
+      <c r="A17" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1"/>
+      <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="1"/>
+      <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1"/>
-      <c r="G29" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="L35" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="L36" s="1" t="s">
-        <v>61</v>
+      <c r="A36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="L36" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="L37" s="3" t="s">
-        <v>63</v>
+      <c r="A37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="L37" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="L38" s="1" t="s">
-        <v>67</v>
+      <c r="A38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="L38" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>69</v>
+      <c r="A39" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="A40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="L40" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="L41" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="L42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="L40" s="5" t="s">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="L43" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="L44" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="L41" t="s">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="L45" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="L42" t="s">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="L46" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="L47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="L43" s="3" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="L48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="L44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="L45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="L46" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="L47" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="L48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="L49" s="1" t="s">
-        <v>59</v>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="L49" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="L50" s="1" t="s">
-        <v>102</v>
+      <c r="A50" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="L50" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="9"/>
-      <c r="L51" s="3" t="s">
-        <v>117</v>
+      <c r="B51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="L51" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="9"/>
-      <c r="L52" s="3" t="s">
-        <v>121</v>
+      <c r="A52" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="L52" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
       <c r="L53" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="9"/>
-      <c r="L54" s="10" t="s">
-        <v>130</v>
+      <c r="L54" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
-      <c r="L55" s="10" t="s">
+      <c r="L55" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="9"/>
@@ -1735,10 +1814,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
@@ -1748,10 +1827,10 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="9"/>
@@ -1761,10 +1840,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="9"/>
@@ -1774,4551 +1853,4677 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="9"/>
-      <c r="L60" s="11" t="s">
-        <v>140</v>
+      <c r="L60" s="10" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="9"/>
-      <c r="L61" s="12" t="s">
-        <v>142</v>
+      <c r="L61" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="9"/>
-      <c r="L62" s="12" t="s">
-        <v>144</v>
+      <c r="L62" s="11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>145</v>
+        <v>105</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="9"/>
       <c r="L63" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>147</v>
+        <v>105</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>145</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="9"/>
-      <c r="L64" s="15" t="s">
-        <v>148</v>
+      <c r="L64" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>149</v>
+        <v>105</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="9"/>
-      <c r="L65" s="15" t="s">
-        <v>150</v>
+      <c r="L65" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B66" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="9"/>
       <c r="L66" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B67" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="9"/>
       <c r="L67" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>158</v>
+        <v>105</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="8"/>
+      <c r="D68" s="9"/>
+      <c r="L68" s="15" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="9"/>
+      <c r="L69" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="D70" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" s="19"/>
+      <c r="O70" s="19"/>
+      <c r="P70" s="19"/>
+      <c r="Q70" s="19"/>
+      <c r="R70" s="19"/>
+      <c r="S70" s="19"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="B71" s="16" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="C71" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D71" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+      <c r="M71" s="19"/>
+      <c r="N71" s="19"/>
+      <c r="O71" s="19"/>
+      <c r="P71" s="19"/>
+      <c r="Q71" s="19"/>
+      <c r="R71" s="19"/>
+      <c r="S71" s="19"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="B72" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C72" s="17"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="19"/>
+      <c r="Q72" s="19"/>
+      <c r="R72" s="19"/>
+      <c r="S72" s="19"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="5"/>
+        <v>166</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="A74" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D74" s="5" t="s">
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="D75" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D75" s="5" t="s">
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D76" s="5" t="s">
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B77" s="1" t="s">
+      <c r="D77" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F77" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D80" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D78" s="3" t="s">
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B79" s="1" t="s">
+      <c r="D81" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="F81" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D79" s="5" t="s">
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F79" t="s">
+      <c r="C82" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B80" s="1" t="s">
+      <c r="D82" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="F82" t="s">
         <v>194</v>
       </c>
-      <c r="D80" s="5" t="s">
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F80" t="s">
+      <c r="C83" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B81" s="1" t="s">
+      <c r="D83" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="F83" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D81" s="5" t="s">
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F81" t="s">
+      <c r="C84" s="7" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B82" s="1" t="s">
+      <c r="D84" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="F84" t="s">
         <v>202</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F83" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E84" s="1"/>
-      <c r="F84" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F86" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="F87" t="s">
         <v>214</v>
       </c>
-      <c r="D85" s="3" t="s">
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="3" t="s">
+      <c r="C88" s="7" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B86" s="3" t="s">
+      <c r="D88" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="F88" t="s">
         <v>218</v>
       </c>
-      <c r="D86" s="2" t="s">
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="3" t="s">
+      <c r="C89" s="7" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B87" s="3" t="s">
+      <c r="D89" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="F89" t="s">
         <v>222</v>
       </c>
-      <c r="D87" s="2" t="s">
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E87" s="1"/>
-      <c r="F87" s="3" t="s">
+      <c r="C90" s="5" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B88" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="E90" s="2"/>
+      <c r="F90" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D88" s="2" t="s">
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="2" t="s">
+      <c r="C91" s="5" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="1" t="s">
+      <c r="D91" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="E91" s="2"/>
+      <c r="F91" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C89" s="5" t="s">
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B90" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="E92" s="2"/>
+      <c r="F92" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F91" s="1"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F92" s="1"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C93" s="5" t="s">
+      <c r="C103" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D93" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="L103" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E104" s="5"/>
-      <c r="F104" t="s">
+      <c r="B107" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="L109" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E110" s="7"/>
+      <c r="F110" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B111" s="7" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-    </row>
-    <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" t="s">
-        <v>57</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="L107" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="L108" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="L109" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="L110" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="L111">
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+    </row>
+    <row r="113" ht="12.75" customHeight="1">
+      <c r="A113" t="s">
+        <v>105</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="L113" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="114" ht="12.75" customHeight="1">
+      <c r="A114" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="L114" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="115" ht="12.75" customHeight="1">
+      <c r="A115" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="L115" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="116" ht="12.75" customHeight="1">
+      <c r="A116" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="L116" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="117" ht="12.75" customHeight="1">
+      <c r="A117" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="L117">
         <v>3.0</v>
       </c>
     </row>
-    <row r="112" ht="12.75" customHeight="1">
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-    </row>
-    <row r="113" ht="12.75" customHeight="1">
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-    </row>
-    <row r="114" ht="12.75" customHeight="1">
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-    </row>
-    <row r="115" ht="12.75" customHeight="1">
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-    </row>
-    <row r="116" ht="12.75" customHeight="1">
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-    </row>
-    <row r="117" ht="12.75" customHeight="1">
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-    </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="2"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="2"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="C260" s="1"/>
-      <c r="D260" s="1"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="C261" s="1"/>
-      <c r="D261" s="1"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="C262" s="1"/>
-      <c r="D262" s="1"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="C263" s="1"/>
-      <c r="D263" s="1"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="C265" s="1"/>
-      <c r="D265" s="1"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="C266" s="1"/>
-      <c r="D266" s="1"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="C267" s="1"/>
-      <c r="D267" s="1"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="C268" s="1"/>
-      <c r="D268" s="1"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="C269" s="1"/>
-      <c r="D269" s="1"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="C283" s="1"/>
-      <c r="D283" s="1"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="C284" s="1"/>
-      <c r="D284" s="1"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="C285" s="1"/>
-      <c r="D285" s="1"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="C286" s="1"/>
-      <c r="D286" s="1"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="C287" s="1"/>
-      <c r="D287" s="1"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="C288" s="1"/>
-      <c r="D288" s="1"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="C289" s="1"/>
-      <c r="D289" s="1"/>
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="C290" s="1"/>
-      <c r="D290" s="1"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="C291" s="1"/>
-      <c r="D291" s="1"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="C292" s="1"/>
-      <c r="D292" s="1"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="C293" s="1"/>
-      <c r="D293" s="1"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="C295" s="1"/>
-      <c r="D295" s="1"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="C296" s="1"/>
-      <c r="D296" s="1"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="C298" s="1"/>
-      <c r="D298" s="1"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="C299" s="1"/>
-      <c r="D299" s="1"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="C300" s="1"/>
-      <c r="D300" s="1"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="C301" s="1"/>
-      <c r="D301" s="1"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="C302" s="1"/>
-      <c r="D302" s="1"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="C303" s="1"/>
-      <c r="D303" s="1"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="C304" s="1"/>
-      <c r="D304" s="1"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="C305" s="1"/>
-      <c r="D305" s="1"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="C306" s="1"/>
-      <c r="D306" s="1"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="C307" s="1"/>
-      <c r="D307" s="1"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="C308" s="1"/>
-      <c r="D308" s="1"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="C309" s="1"/>
-      <c r="D309" s="1"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="C310" s="1"/>
-      <c r="D310" s="1"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="C311" s="1"/>
-      <c r="D311" s="1"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="C312" s="1"/>
-      <c r="D312" s="1"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="C314" s="1"/>
-      <c r="D314" s="1"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="C315" s="1"/>
-      <c r="D315" s="1"/>
+      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="C316" s="1"/>
-      <c r="D316" s="1"/>
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
+      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="C323" s="1"/>
-      <c r="D323" s="1"/>
+      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="C324" s="1"/>
-      <c r="D324" s="1"/>
+      <c r="C324" s="2"/>
+      <c r="D324" s="2"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="C325" s="1"/>
-      <c r="D325" s="1"/>
+      <c r="C325" s="2"/>
+      <c r="D325" s="2"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="C326" s="1"/>
-      <c r="D326" s="1"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="C327" s="1"/>
-      <c r="D327" s="1"/>
+      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="C328" s="1"/>
-      <c r="D328" s="1"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="C329" s="1"/>
-      <c r="D329" s="1"/>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="C330" s="1"/>
-      <c r="D330" s="1"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="C331" s="1"/>
-      <c r="D331" s="1"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="C332" s="1"/>
-      <c r="D332" s="1"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="C333" s="1"/>
-      <c r="D333" s="1"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="C334" s="1"/>
-      <c r="D334" s="1"/>
+      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="C335" s="1"/>
-      <c r="D335" s="1"/>
+      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="C336" s="1"/>
-      <c r="D336" s="1"/>
+      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="C337" s="1"/>
-      <c r="D337" s="1"/>
+      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
+      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
+      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
+      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
+      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
+      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
+      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
+      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="C348" s="1"/>
-      <c r="D348" s="1"/>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="C349" s="1"/>
-      <c r="D349" s="1"/>
+      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="C350" s="1"/>
-      <c r="D350" s="1"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="C351" s="1"/>
-      <c r="D351" s="1"/>
+      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="C352" s="1"/>
-      <c r="D352" s="1"/>
+      <c r="C352" s="2"/>
+      <c r="D352" s="2"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="C353" s="1"/>
-      <c r="D353" s="1"/>
+      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="C354" s="1"/>
-      <c r="D354" s="1"/>
+      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="C355" s="1"/>
-      <c r="D355" s="1"/>
+      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="C356" s="1"/>
-      <c r="D356" s="1"/>
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="C357" s="1"/>
-      <c r="D357" s="1"/>
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="C358" s="1"/>
-      <c r="D358" s="1"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="C359" s="1"/>
-      <c r="D359" s="1"/>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="C360" s="1"/>
-      <c r="D360" s="1"/>
+      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="C361" s="1"/>
-      <c r="D361" s="1"/>
+      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="C362" s="1"/>
-      <c r="D362" s="1"/>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="C363" s="1"/>
-      <c r="D363" s="1"/>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="C364" s="1"/>
-      <c r="D364" s="1"/>
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="C365" s="1"/>
-      <c r="D365" s="1"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="C366" s="1"/>
-      <c r="D366" s="1"/>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="C367" s="1"/>
-      <c r="D367" s="1"/>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="C368" s="1"/>
-      <c r="D368" s="1"/>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="C369" s="1"/>
-      <c r="D369" s="1"/>
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="C370" s="1"/>
-      <c r="D370" s="1"/>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="C372" s="1"/>
-      <c r="D372" s="1"/>
+      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="C373" s="1"/>
-      <c r="D373" s="1"/>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="C374" s="1"/>
-      <c r="D374" s="1"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="C375" s="1"/>
-      <c r="D375" s="1"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="C376" s="1"/>
-      <c r="D376" s="1"/>
+      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="C377" s="1"/>
-      <c r="D377" s="1"/>
+      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="C378" s="1"/>
-      <c r="D378" s="1"/>
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="C379" s="1"/>
-      <c r="D379" s="1"/>
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="C380" s="1"/>
-      <c r="D380" s="1"/>
+      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="C381" s="1"/>
-      <c r="D381" s="1"/>
+      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="C382" s="1"/>
-      <c r="D382" s="1"/>
+      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="C383" s="1"/>
-      <c r="D383" s="1"/>
+      <c r="C383" s="2"/>
+      <c r="D383" s="2"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="C384" s="1"/>
-      <c r="D384" s="1"/>
+      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="C385" s="1"/>
-      <c r="D385" s="1"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="C386" s="1"/>
-      <c r="D386" s="1"/>
+      <c r="C386" s="2"/>
+      <c r="D386" s="2"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="C387" s="1"/>
-      <c r="D387" s="1"/>
+      <c r="C387" s="2"/>
+      <c r="D387" s="2"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="C388" s="1"/>
-      <c r="D388" s="1"/>
+      <c r="C388" s="2"/>
+      <c r="D388" s="2"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="C389" s="1"/>
-      <c r="D389" s="1"/>
+      <c r="C389" s="2"/>
+      <c r="D389" s="2"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="C390" s="1"/>
-      <c r="D390" s="1"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="C391" s="1"/>
-      <c r="D391" s="1"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="C392" s="1"/>
-      <c r="D392" s="1"/>
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="C393" s="1"/>
-      <c r="D393" s="1"/>
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="C394" s="1"/>
-      <c r="D394" s="1"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="C395" s="1"/>
-      <c r="D395" s="1"/>
+      <c r="C395" s="2"/>
+      <c r="D395" s="2"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="C396" s="1"/>
-      <c r="D396" s="1"/>
+      <c r="C396" s="2"/>
+      <c r="D396" s="2"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="C397" s="1"/>
-      <c r="D397" s="1"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="C398" s="1"/>
-      <c r="D398" s="1"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="C399" s="1"/>
-      <c r="D399" s="1"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="C400" s="1"/>
-      <c r="D400" s="1"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="C401" s="1"/>
-      <c r="D401" s="1"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="C402" s="1"/>
-      <c r="D402" s="1"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="C403" s="1"/>
-      <c r="D403" s="1"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="C404" s="1"/>
-      <c r="D404" s="1"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="C405" s="1"/>
-      <c r="D405" s="1"/>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="C406" s="1"/>
-      <c r="D406" s="1"/>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="C407" s="1"/>
-      <c r="D407" s="1"/>
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="C408" s="1"/>
-      <c r="D408" s="1"/>
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="C409" s="1"/>
-      <c r="D409" s="1"/>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="C410" s="1"/>
-      <c r="D410" s="1"/>
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="C411" s="1"/>
-      <c r="D411" s="1"/>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="C412" s="1"/>
-      <c r="D412" s="1"/>
+      <c r="C412" s="2"/>
+      <c r="D412" s="2"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="C413" s="1"/>
-      <c r="D413" s="1"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="C414" s="1"/>
-      <c r="D414" s="1"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="C415" s="1"/>
-      <c r="D415" s="1"/>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="C416" s="1"/>
-      <c r="D416" s="1"/>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="C417" s="1"/>
-      <c r="D417" s="1"/>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="C418" s="1"/>
-      <c r="D418" s="1"/>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="C419" s="1"/>
-      <c r="D419" s="1"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="C420" s="1"/>
-      <c r="D420" s="1"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="C421" s="1"/>
-      <c r="D421" s="1"/>
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="C422" s="1"/>
-      <c r="D422" s="1"/>
+      <c r="C422" s="2"/>
+      <c r="D422" s="2"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="C423" s="1"/>
-      <c r="D423" s="1"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="C424" s="1"/>
-      <c r="D424" s="1"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="C425" s="1"/>
-      <c r="D425" s="1"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="C426" s="1"/>
-      <c r="D426" s="1"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="C427" s="1"/>
-      <c r="D427" s="1"/>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="C428" s="1"/>
-      <c r="D428" s="1"/>
+      <c r="C428" s="2"/>
+      <c r="D428" s="2"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="C429" s="1"/>
-      <c r="D429" s="1"/>
+      <c r="C429" s="2"/>
+      <c r="D429" s="2"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="C430" s="1"/>
-      <c r="D430" s="1"/>
+      <c r="C430" s="2"/>
+      <c r="D430" s="2"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="C431" s="1"/>
-      <c r="D431" s="1"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="C432" s="1"/>
-      <c r="D432" s="1"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="C433" s="1"/>
-      <c r="D433" s="1"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="C434" s="1"/>
-      <c r="D434" s="1"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="C435" s="1"/>
-      <c r="D435" s="1"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="C436" s="1"/>
-      <c r="D436" s="1"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="C437" s="1"/>
-      <c r="D437" s="1"/>
+      <c r="C437" s="2"/>
+      <c r="D437" s="2"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="C438" s="1"/>
-      <c r="D438" s="1"/>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="C439" s="1"/>
-      <c r="D439" s="1"/>
+      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="C440" s="1"/>
-      <c r="D440" s="1"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="C441" s="1"/>
-      <c r="D441" s="1"/>
+      <c r="C441" s="2"/>
+      <c r="D441" s="2"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="C442" s="1"/>
-      <c r="D442" s="1"/>
+      <c r="C442" s="2"/>
+      <c r="D442" s="2"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="C443" s="1"/>
-      <c r="D443" s="1"/>
+      <c r="C443" s="2"/>
+      <c r="D443" s="2"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="C444" s="1"/>
-      <c r="D444" s="1"/>
+      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="C445" s="1"/>
-      <c r="D445" s="1"/>
+      <c r="C445" s="2"/>
+      <c r="D445" s="2"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="C446" s="1"/>
-      <c r="D446" s="1"/>
+      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="C447" s="1"/>
-      <c r="D447" s="1"/>
+      <c r="C447" s="2"/>
+      <c r="D447" s="2"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="C448" s="1"/>
-      <c r="D448" s="1"/>
+      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="C449" s="1"/>
-      <c r="D449" s="1"/>
+      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="C450" s="1"/>
-      <c r="D450" s="1"/>
+      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="C451" s="1"/>
-      <c r="D451" s="1"/>
+      <c r="C451" s="2"/>
+      <c r="D451" s="2"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="C452" s="1"/>
-      <c r="D452" s="1"/>
+      <c r="C452" s="2"/>
+      <c r="D452" s="2"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="C453" s="1"/>
-      <c r="D453" s="1"/>
+      <c r="C453" s="2"/>
+      <c r="D453" s="2"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="C454" s="1"/>
-      <c r="D454" s="1"/>
+      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="C455" s="1"/>
-      <c r="D455" s="1"/>
+      <c r="C455" s="2"/>
+      <c r="D455" s="2"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="C456" s="1"/>
-      <c r="D456" s="1"/>
+      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="C457" s="1"/>
-      <c r="D457" s="1"/>
+      <c r="C457" s="2"/>
+      <c r="D457" s="2"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="C458" s="1"/>
-      <c r="D458" s="1"/>
+      <c r="C458" s="2"/>
+      <c r="D458" s="2"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="C459" s="1"/>
-      <c r="D459" s="1"/>
+      <c r="C459" s="2"/>
+      <c r="D459" s="2"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="C460" s="1"/>
-      <c r="D460" s="1"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="2"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="C461" s="1"/>
-      <c r="D461" s="1"/>
+      <c r="C461" s="2"/>
+      <c r="D461" s="2"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="C462" s="1"/>
-      <c r="D462" s="1"/>
+      <c r="C462" s="2"/>
+      <c r="D462" s="2"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="C463" s="1"/>
-      <c r="D463" s="1"/>
+      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="C464" s="1"/>
-      <c r="D464" s="1"/>
+      <c r="C464" s="2"/>
+      <c r="D464" s="2"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="C465" s="1"/>
-      <c r="D465" s="1"/>
+      <c r="C465" s="2"/>
+      <c r="D465" s="2"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="C466" s="1"/>
-      <c r="D466" s="1"/>
+      <c r="C466" s="2"/>
+      <c r="D466" s="2"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="C467" s="1"/>
-      <c r="D467" s="1"/>
+      <c r="C467" s="2"/>
+      <c r="D467" s="2"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="C468" s="1"/>
-      <c r="D468" s="1"/>
+      <c r="C468" s="2"/>
+      <c r="D468" s="2"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="C469" s="1"/>
-      <c r="D469" s="1"/>
+      <c r="C469" s="2"/>
+      <c r="D469" s="2"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="C470" s="1"/>
-      <c r="D470" s="1"/>
+      <c r="C470" s="2"/>
+      <c r="D470" s="2"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="C471" s="1"/>
-      <c r="D471" s="1"/>
+      <c r="C471" s="2"/>
+      <c r="D471" s="2"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="C472" s="1"/>
-      <c r="D472" s="1"/>
+      <c r="C472" s="2"/>
+      <c r="D472" s="2"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="C473" s="1"/>
-      <c r="D473" s="1"/>
+      <c r="C473" s="2"/>
+      <c r="D473" s="2"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="C474" s="1"/>
-      <c r="D474" s="1"/>
+      <c r="C474" s="2"/>
+      <c r="D474" s="2"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="C475" s="1"/>
-      <c r="D475" s="1"/>
+      <c r="C475" s="2"/>
+      <c r="D475" s="2"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="C476" s="1"/>
-      <c r="D476" s="1"/>
+      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="C477" s="1"/>
-      <c r="D477" s="1"/>
+      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="C478" s="1"/>
-      <c r="D478" s="1"/>
+      <c r="C478" s="2"/>
+      <c r="D478" s="2"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="C479" s="1"/>
-      <c r="D479" s="1"/>
+      <c r="C479" s="2"/>
+      <c r="D479" s="2"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="C480" s="1"/>
-      <c r="D480" s="1"/>
+      <c r="C480" s="2"/>
+      <c r="D480" s="2"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="C481" s="1"/>
-      <c r="D481" s="1"/>
+      <c r="C481" s="2"/>
+      <c r="D481" s="2"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="C482" s="1"/>
-      <c r="D482" s="1"/>
+      <c r="C482" s="2"/>
+      <c r="D482" s="2"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="C483" s="1"/>
-      <c r="D483" s="1"/>
+      <c r="C483" s="2"/>
+      <c r="D483" s="2"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="C484" s="1"/>
-      <c r="D484" s="1"/>
+      <c r="C484" s="2"/>
+      <c r="D484" s="2"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="C485" s="1"/>
-      <c r="D485" s="1"/>
+      <c r="C485" s="2"/>
+      <c r="D485" s="2"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="C486" s="1"/>
-      <c r="D486" s="1"/>
+      <c r="C486" s="2"/>
+      <c r="D486" s="2"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="C487" s="1"/>
-      <c r="D487" s="1"/>
+      <c r="C487" s="2"/>
+      <c r="D487" s="2"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="C488" s="1"/>
-      <c r="D488" s="1"/>
+      <c r="C488" s="2"/>
+      <c r="D488" s="2"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="C489" s="1"/>
-      <c r="D489" s="1"/>
+      <c r="C489" s="2"/>
+      <c r="D489" s="2"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="C490" s="1"/>
-      <c r="D490" s="1"/>
+      <c r="C490" s="2"/>
+      <c r="D490" s="2"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="C491" s="1"/>
-      <c r="D491" s="1"/>
+      <c r="C491" s="2"/>
+      <c r="D491" s="2"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="C492" s="1"/>
-      <c r="D492" s="1"/>
+      <c r="C492" s="2"/>
+      <c r="D492" s="2"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="C493" s="1"/>
-      <c r="D493" s="1"/>
+      <c r="C493" s="2"/>
+      <c r="D493" s="2"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="C494" s="1"/>
-      <c r="D494" s="1"/>
+      <c r="C494" s="2"/>
+      <c r="D494" s="2"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="C495" s="1"/>
-      <c r="D495" s="1"/>
+      <c r="C495" s="2"/>
+      <c r="D495" s="2"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="C496" s="1"/>
-      <c r="D496" s="1"/>
+      <c r="C496" s="2"/>
+      <c r="D496" s="2"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="C497" s="1"/>
-      <c r="D497" s="1"/>
+      <c r="C497" s="2"/>
+      <c r="D497" s="2"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="C498" s="1"/>
-      <c r="D498" s="1"/>
+      <c r="C498" s="2"/>
+      <c r="D498" s="2"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="C499" s="1"/>
-      <c r="D499" s="1"/>
+      <c r="C499" s="2"/>
+      <c r="D499" s="2"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="C500" s="1"/>
-      <c r="D500" s="1"/>
+      <c r="C500" s="2"/>
+      <c r="D500" s="2"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="C501" s="1"/>
-      <c r="D501" s="1"/>
+      <c r="C501" s="2"/>
+      <c r="D501" s="2"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="C502" s="1"/>
-      <c r="D502" s="1"/>
+      <c r="C502" s="2"/>
+      <c r="D502" s="2"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="C503" s="1"/>
-      <c r="D503" s="1"/>
+      <c r="C503" s="2"/>
+      <c r="D503" s="2"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="C504" s="1"/>
-      <c r="D504" s="1"/>
+      <c r="C504" s="2"/>
+      <c r="D504" s="2"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="C505" s="1"/>
-      <c r="D505" s="1"/>
+      <c r="C505" s="2"/>
+      <c r="D505" s="2"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="C506" s="1"/>
-      <c r="D506" s="1"/>
+      <c r="C506" s="2"/>
+      <c r="D506" s="2"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="C507" s="1"/>
-      <c r="D507" s="1"/>
+      <c r="C507" s="2"/>
+      <c r="D507" s="2"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="C508" s="1"/>
-      <c r="D508" s="1"/>
+      <c r="C508" s="2"/>
+      <c r="D508" s="2"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="C509" s="1"/>
-      <c r="D509" s="1"/>
+      <c r="C509" s="2"/>
+      <c r="D509" s="2"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="C510" s="1"/>
-      <c r="D510" s="1"/>
+      <c r="C510" s="2"/>
+      <c r="D510" s="2"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="C511" s="1"/>
-      <c r="D511" s="1"/>
+      <c r="C511" s="2"/>
+      <c r="D511" s="2"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="C512" s="1"/>
-      <c r="D512" s="1"/>
+      <c r="C512" s="2"/>
+      <c r="D512" s="2"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="C513" s="1"/>
-      <c r="D513" s="1"/>
+      <c r="C513" s="2"/>
+      <c r="D513" s="2"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="C514" s="1"/>
-      <c r="D514" s="1"/>
+      <c r="C514" s="2"/>
+      <c r="D514" s="2"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="C515" s="1"/>
-      <c r="D515" s="1"/>
+      <c r="C515" s="2"/>
+      <c r="D515" s="2"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="C516" s="1"/>
-      <c r="D516" s="1"/>
+      <c r="C516" s="2"/>
+      <c r="D516" s="2"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="C517" s="1"/>
-      <c r="D517" s="1"/>
+      <c r="C517" s="2"/>
+      <c r="D517" s="2"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="C518" s="1"/>
-      <c r="D518" s="1"/>
+      <c r="C518" s="2"/>
+      <c r="D518" s="2"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="C519" s="1"/>
-      <c r="D519" s="1"/>
+      <c r="C519" s="2"/>
+      <c r="D519" s="2"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="C520" s="1"/>
-      <c r="D520" s="1"/>
+      <c r="C520" s="2"/>
+      <c r="D520" s="2"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="C521" s="1"/>
-      <c r="D521" s="1"/>
+      <c r="C521" s="2"/>
+      <c r="D521" s="2"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="C522" s="1"/>
-      <c r="D522" s="1"/>
+      <c r="C522" s="2"/>
+      <c r="D522" s="2"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="C523" s="1"/>
-      <c r="D523" s="1"/>
+      <c r="C523" s="2"/>
+      <c r="D523" s="2"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="C524" s="1"/>
-      <c r="D524" s="1"/>
+      <c r="C524" s="2"/>
+      <c r="D524" s="2"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="C525" s="1"/>
-      <c r="D525" s="1"/>
+      <c r="C525" s="2"/>
+      <c r="D525" s="2"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="C526" s="1"/>
-      <c r="D526" s="1"/>
+      <c r="C526" s="2"/>
+      <c r="D526" s="2"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="C527" s="1"/>
-      <c r="D527" s="1"/>
+      <c r="C527" s="2"/>
+      <c r="D527" s="2"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="C528" s="1"/>
-      <c r="D528" s="1"/>
+      <c r="C528" s="2"/>
+      <c r="D528" s="2"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="C529" s="1"/>
-      <c r="D529" s="1"/>
+      <c r="C529" s="2"/>
+      <c r="D529" s="2"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="C530" s="1"/>
-      <c r="D530" s="1"/>
+      <c r="C530" s="2"/>
+      <c r="D530" s="2"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="C531" s="1"/>
-      <c r="D531" s="1"/>
+      <c r="C531" s="2"/>
+      <c r="D531" s="2"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="C532" s="1"/>
-      <c r="D532" s="1"/>
+      <c r="C532" s="2"/>
+      <c r="D532" s="2"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="C533" s="1"/>
-      <c r="D533" s="1"/>
+      <c r="C533" s="2"/>
+      <c r="D533" s="2"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="C534" s="1"/>
-      <c r="D534" s="1"/>
+      <c r="C534" s="2"/>
+      <c r="D534" s="2"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="C535" s="1"/>
-      <c r="D535" s="1"/>
+      <c r="C535" s="2"/>
+      <c r="D535" s="2"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="C536" s="1"/>
-      <c r="D536" s="1"/>
+      <c r="C536" s="2"/>
+      <c r="D536" s="2"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="C537" s="1"/>
-      <c r="D537" s="1"/>
+      <c r="C537" s="2"/>
+      <c r="D537" s="2"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="C538" s="1"/>
-      <c r="D538" s="1"/>
+      <c r="C538" s="2"/>
+      <c r="D538" s="2"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="C539" s="1"/>
-      <c r="D539" s="1"/>
+      <c r="C539" s="2"/>
+      <c r="D539" s="2"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="C540" s="1"/>
-      <c r="D540" s="1"/>
+      <c r="C540" s="2"/>
+      <c r="D540" s="2"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="C541" s="1"/>
-      <c r="D541" s="1"/>
+      <c r="C541" s="2"/>
+      <c r="D541" s="2"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="C542" s="1"/>
-      <c r="D542" s="1"/>
+      <c r="C542" s="2"/>
+      <c r="D542" s="2"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="C543" s="1"/>
-      <c r="D543" s="1"/>
+      <c r="C543" s="2"/>
+      <c r="D543" s="2"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="C544" s="1"/>
-      <c r="D544" s="1"/>
+      <c r="C544" s="2"/>
+      <c r="D544" s="2"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="C545" s="1"/>
-      <c r="D545" s="1"/>
+      <c r="C545" s="2"/>
+      <c r="D545" s="2"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="C546" s="1"/>
-      <c r="D546" s="1"/>
+      <c r="C546" s="2"/>
+      <c r="D546" s="2"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="C547" s="1"/>
-      <c r="D547" s="1"/>
+      <c r="C547" s="2"/>
+      <c r="D547" s="2"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="C548" s="1"/>
-      <c r="D548" s="1"/>
+      <c r="C548" s="2"/>
+      <c r="D548" s="2"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="C549" s="1"/>
-      <c r="D549" s="1"/>
+      <c r="C549" s="2"/>
+      <c r="D549" s="2"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="C550" s="1"/>
-      <c r="D550" s="1"/>
+      <c r="C550" s="2"/>
+      <c r="D550" s="2"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="C551" s="1"/>
-      <c r="D551" s="1"/>
+      <c r="C551" s="2"/>
+      <c r="D551" s="2"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="C552" s="1"/>
-      <c r="D552" s="1"/>
+      <c r="C552" s="2"/>
+      <c r="D552" s="2"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="C553" s="1"/>
-      <c r="D553" s="1"/>
+      <c r="C553" s="2"/>
+      <c r="D553" s="2"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="C554" s="1"/>
-      <c r="D554" s="1"/>
+      <c r="C554" s="2"/>
+      <c r="D554" s="2"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="C555" s="1"/>
-      <c r="D555" s="1"/>
+      <c r="C555" s="2"/>
+      <c r="D555" s="2"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="C556" s="1"/>
-      <c r="D556" s="1"/>
+      <c r="C556" s="2"/>
+      <c r="D556" s="2"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="C557" s="1"/>
-      <c r="D557" s="1"/>
+      <c r="C557" s="2"/>
+      <c r="D557" s="2"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="C558" s="1"/>
-      <c r="D558" s="1"/>
+      <c r="C558" s="2"/>
+      <c r="D558" s="2"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="C559" s="1"/>
-      <c r="D559" s="1"/>
+      <c r="C559" s="2"/>
+      <c r="D559" s="2"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="C560" s="1"/>
-      <c r="D560" s="1"/>
+      <c r="C560" s="2"/>
+      <c r="D560" s="2"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="C561" s="1"/>
-      <c r="D561" s="1"/>
+      <c r="C561" s="2"/>
+      <c r="D561" s="2"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="C562" s="1"/>
-      <c r="D562" s="1"/>
+      <c r="C562" s="2"/>
+      <c r="D562" s="2"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="C563" s="1"/>
-      <c r="D563" s="1"/>
+      <c r="C563" s="2"/>
+      <c r="D563" s="2"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="C564" s="1"/>
-      <c r="D564" s="1"/>
+      <c r="C564" s="2"/>
+      <c r="D564" s="2"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="C565" s="1"/>
-      <c r="D565" s="1"/>
+      <c r="C565" s="2"/>
+      <c r="D565" s="2"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="C566" s="1"/>
-      <c r="D566" s="1"/>
+      <c r="C566" s="2"/>
+      <c r="D566" s="2"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="C567" s="1"/>
-      <c r="D567" s="1"/>
+      <c r="C567" s="2"/>
+      <c r="D567" s="2"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="C568" s="1"/>
-      <c r="D568" s="1"/>
+      <c r="C568" s="2"/>
+      <c r="D568" s="2"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="C569" s="1"/>
-      <c r="D569" s="1"/>
+      <c r="C569" s="2"/>
+      <c r="D569" s="2"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="C570" s="1"/>
-      <c r="D570" s="1"/>
+      <c r="C570" s="2"/>
+      <c r="D570" s="2"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="C571" s="1"/>
-      <c r="D571" s="1"/>
+      <c r="C571" s="2"/>
+      <c r="D571" s="2"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="C572" s="1"/>
-      <c r="D572" s="1"/>
+      <c r="C572" s="2"/>
+      <c r="D572" s="2"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="C573" s="1"/>
-      <c r="D573" s="1"/>
+      <c r="C573" s="2"/>
+      <c r="D573" s="2"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="C574" s="1"/>
-      <c r="D574" s="1"/>
+      <c r="C574" s="2"/>
+      <c r="D574" s="2"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="C575" s="1"/>
-      <c r="D575" s="1"/>
+      <c r="C575" s="2"/>
+      <c r="D575" s="2"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="C576" s="1"/>
-      <c r="D576" s="1"/>
+      <c r="C576" s="2"/>
+      <c r="D576" s="2"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="C577" s="1"/>
-      <c r="D577" s="1"/>
+      <c r="C577" s="2"/>
+      <c r="D577" s="2"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="C578" s="1"/>
-      <c r="D578" s="1"/>
+      <c r="C578" s="2"/>
+      <c r="D578" s="2"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="C579" s="1"/>
-      <c r="D579" s="1"/>
+      <c r="C579" s="2"/>
+      <c r="D579" s="2"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="C580" s="1"/>
-      <c r="D580" s="1"/>
+      <c r="C580" s="2"/>
+      <c r="D580" s="2"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="C581" s="1"/>
-      <c r="D581" s="1"/>
+      <c r="C581" s="2"/>
+      <c r="D581" s="2"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="C582" s="1"/>
-      <c r="D582" s="1"/>
+      <c r="C582" s="2"/>
+      <c r="D582" s="2"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="C583" s="1"/>
-      <c r="D583" s="1"/>
+      <c r="C583" s="2"/>
+      <c r="D583" s="2"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="C584" s="1"/>
-      <c r="D584" s="1"/>
+      <c r="C584" s="2"/>
+      <c r="D584" s="2"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="C585" s="1"/>
-      <c r="D585" s="1"/>
+      <c r="C585" s="2"/>
+      <c r="D585" s="2"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="C586" s="1"/>
-      <c r="D586" s="1"/>
+      <c r="C586" s="2"/>
+      <c r="D586" s="2"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="C587" s="1"/>
-      <c r="D587" s="1"/>
+      <c r="C587" s="2"/>
+      <c r="D587" s="2"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="C588" s="1"/>
-      <c r="D588" s="1"/>
+      <c r="C588" s="2"/>
+      <c r="D588" s="2"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="C589" s="1"/>
-      <c r="D589" s="1"/>
+      <c r="C589" s="2"/>
+      <c r="D589" s="2"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="C590" s="1"/>
-      <c r="D590" s="1"/>
+      <c r="C590" s="2"/>
+      <c r="D590" s="2"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="C591" s="1"/>
-      <c r="D591" s="1"/>
+      <c r="C591" s="2"/>
+      <c r="D591" s="2"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="C592" s="1"/>
-      <c r="D592" s="1"/>
+      <c r="C592" s="2"/>
+      <c r="D592" s="2"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="C593" s="1"/>
-      <c r="D593" s="1"/>
+      <c r="C593" s="2"/>
+      <c r="D593" s="2"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="C594" s="1"/>
-      <c r="D594" s="1"/>
+      <c r="C594" s="2"/>
+      <c r="D594" s="2"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="C595" s="1"/>
-      <c r="D595" s="1"/>
+      <c r="C595" s="2"/>
+      <c r="D595" s="2"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="C596" s="1"/>
-      <c r="D596" s="1"/>
+      <c r="C596" s="2"/>
+      <c r="D596" s="2"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="C597" s="1"/>
-      <c r="D597" s="1"/>
+      <c r="C597" s="2"/>
+      <c r="D597" s="2"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="C598" s="1"/>
-      <c r="D598" s="1"/>
+      <c r="C598" s="2"/>
+      <c r="D598" s="2"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="C599" s="1"/>
-      <c r="D599" s="1"/>
+      <c r="C599" s="2"/>
+      <c r="D599" s="2"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="C600" s="1"/>
-      <c r="D600" s="1"/>
+      <c r="C600" s="2"/>
+      <c r="D600" s="2"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="C601" s="1"/>
-      <c r="D601" s="1"/>
+      <c r="C601" s="2"/>
+      <c r="D601" s="2"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="C602" s="1"/>
-      <c r="D602" s="1"/>
+      <c r="C602" s="2"/>
+      <c r="D602" s="2"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="C603" s="1"/>
-      <c r="D603" s="1"/>
+      <c r="C603" s="2"/>
+      <c r="D603" s="2"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="C604" s="1"/>
-      <c r="D604" s="1"/>
+      <c r="C604" s="2"/>
+      <c r="D604" s="2"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="C605" s="1"/>
-      <c r="D605" s="1"/>
+      <c r="C605" s="2"/>
+      <c r="D605" s="2"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="C606" s="1"/>
-      <c r="D606" s="1"/>
+      <c r="C606" s="2"/>
+      <c r="D606" s="2"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="C607" s="1"/>
-      <c r="D607" s="1"/>
+      <c r="C607" s="2"/>
+      <c r="D607" s="2"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="C608" s="1"/>
-      <c r="D608" s="1"/>
+      <c r="C608" s="2"/>
+      <c r="D608" s="2"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="C609" s="1"/>
-      <c r="D609" s="1"/>
+      <c r="C609" s="2"/>
+      <c r="D609" s="2"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="C610" s="1"/>
-      <c r="D610" s="1"/>
+      <c r="C610" s="2"/>
+      <c r="D610" s="2"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="C611" s="1"/>
-      <c r="D611" s="1"/>
+      <c r="C611" s="2"/>
+      <c r="D611" s="2"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="C612" s="1"/>
-      <c r="D612" s="1"/>
+      <c r="C612" s="2"/>
+      <c r="D612" s="2"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="C613" s="1"/>
-      <c r="D613" s="1"/>
+      <c r="C613" s="2"/>
+      <c r="D613" s="2"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="C614" s="1"/>
-      <c r="D614" s="1"/>
+      <c r="C614" s="2"/>
+      <c r="D614" s="2"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="C615" s="1"/>
-      <c r="D615" s="1"/>
+      <c r="C615" s="2"/>
+      <c r="D615" s="2"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="C616" s="1"/>
-      <c r="D616" s="1"/>
+      <c r="C616" s="2"/>
+      <c r="D616" s="2"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="C617" s="1"/>
-      <c r="D617" s="1"/>
+      <c r="C617" s="2"/>
+      <c r="D617" s="2"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="C618" s="1"/>
-      <c r="D618" s="1"/>
+      <c r="C618" s="2"/>
+      <c r="D618" s="2"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="C619" s="1"/>
-      <c r="D619" s="1"/>
+      <c r="C619" s="2"/>
+      <c r="D619" s="2"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="C620" s="1"/>
-      <c r="D620" s="1"/>
+      <c r="C620" s="2"/>
+      <c r="D620" s="2"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="C621" s="1"/>
-      <c r="D621" s="1"/>
+      <c r="C621" s="2"/>
+      <c r="D621" s="2"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="C622" s="1"/>
-      <c r="D622" s="1"/>
+      <c r="C622" s="2"/>
+      <c r="D622" s="2"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="C623" s="1"/>
-      <c r="D623" s="1"/>
+      <c r="C623" s="2"/>
+      <c r="D623" s="2"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="C624" s="1"/>
-      <c r="D624" s="1"/>
+      <c r="C624" s="2"/>
+      <c r="D624" s="2"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="C625" s="1"/>
-      <c r="D625" s="1"/>
+      <c r="C625" s="2"/>
+      <c r="D625" s="2"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="C626" s="1"/>
-      <c r="D626" s="1"/>
+      <c r="C626" s="2"/>
+      <c r="D626" s="2"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="C627" s="1"/>
-      <c r="D627" s="1"/>
+      <c r="C627" s="2"/>
+      <c r="D627" s="2"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="C628" s="1"/>
-      <c r="D628" s="1"/>
+      <c r="C628" s="2"/>
+      <c r="D628" s="2"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="C629" s="1"/>
-      <c r="D629" s="1"/>
+      <c r="C629" s="2"/>
+      <c r="D629" s="2"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="C630" s="1"/>
-      <c r="D630" s="1"/>
+      <c r="C630" s="2"/>
+      <c r="D630" s="2"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="C631" s="1"/>
-      <c r="D631" s="1"/>
+      <c r="C631" s="2"/>
+      <c r="D631" s="2"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="C632" s="1"/>
-      <c r="D632" s="1"/>
+      <c r="C632" s="2"/>
+      <c r="D632" s="2"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="C633" s="1"/>
-      <c r="D633" s="1"/>
+      <c r="C633" s="2"/>
+      <c r="D633" s="2"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="C634" s="1"/>
-      <c r="D634" s="1"/>
+      <c r="C634" s="2"/>
+      <c r="D634" s="2"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="C635" s="1"/>
-      <c r="D635" s="1"/>
+      <c r="C635" s="2"/>
+      <c r="D635" s="2"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="C636" s="1"/>
-      <c r="D636" s="1"/>
+      <c r="C636" s="2"/>
+      <c r="D636" s="2"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="C637" s="1"/>
-      <c r="D637" s="1"/>
+      <c r="C637" s="2"/>
+      <c r="D637" s="2"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="C638" s="1"/>
-      <c r="D638" s="1"/>
+      <c r="C638" s="2"/>
+      <c r="D638" s="2"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="C639" s="1"/>
-      <c r="D639" s="1"/>
+      <c r="C639" s="2"/>
+      <c r="D639" s="2"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="C640" s="1"/>
-      <c r="D640" s="1"/>
+      <c r="C640" s="2"/>
+      <c r="D640" s="2"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="C641" s="1"/>
-      <c r="D641" s="1"/>
+      <c r="C641" s="2"/>
+      <c r="D641" s="2"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="C642" s="1"/>
-      <c r="D642" s="1"/>
+      <c r="C642" s="2"/>
+      <c r="D642" s="2"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="C643" s="1"/>
-      <c r="D643" s="1"/>
+      <c r="C643" s="2"/>
+      <c r="D643" s="2"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="C644" s="1"/>
-      <c r="D644" s="1"/>
+      <c r="C644" s="2"/>
+      <c r="D644" s="2"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="C645" s="1"/>
-      <c r="D645" s="1"/>
+      <c r="C645" s="2"/>
+      <c r="D645" s="2"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="C646" s="1"/>
-      <c r="D646" s="1"/>
+      <c r="C646" s="2"/>
+      <c r="D646" s="2"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="C647" s="1"/>
-      <c r="D647" s="1"/>
+      <c r="C647" s="2"/>
+      <c r="D647" s="2"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="C648" s="1"/>
-      <c r="D648" s="1"/>
+      <c r="C648" s="2"/>
+      <c r="D648" s="2"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="C649" s="1"/>
-      <c r="D649" s="1"/>
+      <c r="C649" s="2"/>
+      <c r="D649" s="2"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="C650" s="1"/>
-      <c r="D650" s="1"/>
+      <c r="C650" s="2"/>
+      <c r="D650" s="2"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="C651" s="1"/>
-      <c r="D651" s="1"/>
+      <c r="C651" s="2"/>
+      <c r="D651" s="2"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="C652" s="1"/>
-      <c r="D652" s="1"/>
+      <c r="C652" s="2"/>
+      <c r="D652" s="2"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="C653" s="1"/>
-      <c r="D653" s="1"/>
+      <c r="C653" s="2"/>
+      <c r="D653" s="2"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="C654" s="1"/>
-      <c r="D654" s="1"/>
+      <c r="C654" s="2"/>
+      <c r="D654" s="2"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="C655" s="1"/>
-      <c r="D655" s="1"/>
+      <c r="C655" s="2"/>
+      <c r="D655" s="2"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="C656" s="1"/>
-      <c r="D656" s="1"/>
+      <c r="C656" s="2"/>
+      <c r="D656" s="2"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="C657" s="1"/>
-      <c r="D657" s="1"/>
+      <c r="C657" s="2"/>
+      <c r="D657" s="2"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="C658" s="1"/>
-      <c r="D658" s="1"/>
+      <c r="C658" s="2"/>
+      <c r="D658" s="2"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="C659" s="1"/>
-      <c r="D659" s="1"/>
+      <c r="C659" s="2"/>
+      <c r="D659" s="2"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="C660" s="1"/>
-      <c r="D660" s="1"/>
+      <c r="C660" s="2"/>
+      <c r="D660" s="2"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="C661" s="1"/>
-      <c r="D661" s="1"/>
+      <c r="C661" s="2"/>
+      <c r="D661" s="2"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="C662" s="1"/>
-      <c r="D662" s="1"/>
+      <c r="C662" s="2"/>
+      <c r="D662" s="2"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="C663" s="1"/>
-      <c r="D663" s="1"/>
+      <c r="C663" s="2"/>
+      <c r="D663" s="2"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="C664" s="1"/>
-      <c r="D664" s="1"/>
+      <c r="C664" s="2"/>
+      <c r="D664" s="2"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="C665" s="1"/>
-      <c r="D665" s="1"/>
+      <c r="C665" s="2"/>
+      <c r="D665" s="2"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="C666" s="1"/>
-      <c r="D666" s="1"/>
+      <c r="C666" s="2"/>
+      <c r="D666" s="2"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="C667" s="1"/>
-      <c r="D667" s="1"/>
+      <c r="C667" s="2"/>
+      <c r="D667" s="2"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="C668" s="1"/>
-      <c r="D668" s="1"/>
+      <c r="C668" s="2"/>
+      <c r="D668" s="2"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="C669" s="1"/>
-      <c r="D669" s="1"/>
+      <c r="C669" s="2"/>
+      <c r="D669" s="2"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="C670" s="1"/>
-      <c r="D670" s="1"/>
+      <c r="C670" s="2"/>
+      <c r="D670" s="2"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="C671" s="1"/>
-      <c r="D671" s="1"/>
+      <c r="C671" s="2"/>
+      <c r="D671" s="2"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="C672" s="1"/>
-      <c r="D672" s="1"/>
+      <c r="C672" s="2"/>
+      <c r="D672" s="2"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="C673" s="1"/>
-      <c r="D673" s="1"/>
+      <c r="C673" s="2"/>
+      <c r="D673" s="2"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="C674" s="1"/>
-      <c r="D674" s="1"/>
+      <c r="C674" s="2"/>
+      <c r="D674" s="2"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="C675" s="1"/>
-      <c r="D675" s="1"/>
+      <c r="C675" s="2"/>
+      <c r="D675" s="2"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="C676" s="1"/>
-      <c r="D676" s="1"/>
+      <c r="C676" s="2"/>
+      <c r="D676" s="2"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="C677" s="1"/>
-      <c r="D677" s="1"/>
+      <c r="C677" s="2"/>
+      <c r="D677" s="2"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="C678" s="1"/>
-      <c r="D678" s="1"/>
+      <c r="C678" s="2"/>
+      <c r="D678" s="2"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="C679" s="1"/>
-      <c r="D679" s="1"/>
+      <c r="C679" s="2"/>
+      <c r="D679" s="2"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="C680" s="1"/>
-      <c r="D680" s="1"/>
+      <c r="C680" s="2"/>
+      <c r="D680" s="2"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="C681" s="1"/>
-      <c r="D681" s="1"/>
+      <c r="C681" s="2"/>
+      <c r="D681" s="2"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="C682" s="1"/>
-      <c r="D682" s="1"/>
+      <c r="C682" s="2"/>
+      <c r="D682" s="2"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="C683" s="1"/>
-      <c r="D683" s="1"/>
+      <c r="C683" s="2"/>
+      <c r="D683" s="2"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="C684" s="1"/>
-      <c r="D684" s="1"/>
+      <c r="C684" s="2"/>
+      <c r="D684" s="2"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="C685" s="1"/>
-      <c r="D685" s="1"/>
+      <c r="C685" s="2"/>
+      <c r="D685" s="2"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="C686" s="1"/>
-      <c r="D686" s="1"/>
+      <c r="C686" s="2"/>
+      <c r="D686" s="2"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="C687" s="1"/>
-      <c r="D687" s="1"/>
+      <c r="C687" s="2"/>
+      <c r="D687" s="2"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="C688" s="1"/>
-      <c r="D688" s="1"/>
+      <c r="C688" s="2"/>
+      <c r="D688" s="2"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="C689" s="1"/>
-      <c r="D689" s="1"/>
+      <c r="C689" s="2"/>
+      <c r="D689" s="2"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="C690" s="1"/>
-      <c r="D690" s="1"/>
+      <c r="C690" s="2"/>
+      <c r="D690" s="2"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="C691" s="1"/>
-      <c r="D691" s="1"/>
+      <c r="C691" s="2"/>
+      <c r="D691" s="2"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="C692" s="1"/>
-      <c r="D692" s="1"/>
+      <c r="C692" s="2"/>
+      <c r="D692" s="2"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="C693" s="1"/>
-      <c r="D693" s="1"/>
+      <c r="C693" s="2"/>
+      <c r="D693" s="2"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="C694" s="1"/>
-      <c r="D694" s="1"/>
+      <c r="C694" s="2"/>
+      <c r="D694" s="2"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="C695" s="1"/>
-      <c r="D695" s="1"/>
+      <c r="C695" s="2"/>
+      <c r="D695" s="2"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="C696" s="1"/>
-      <c r="D696" s="1"/>
+      <c r="C696" s="2"/>
+      <c r="D696" s="2"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="C697" s="1"/>
-      <c r="D697" s="1"/>
+      <c r="C697" s="2"/>
+      <c r="D697" s="2"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="C698" s="1"/>
-      <c r="D698" s="1"/>
+      <c r="C698" s="2"/>
+      <c r="D698" s="2"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="C699" s="1"/>
-      <c r="D699" s="1"/>
+      <c r="C699" s="2"/>
+      <c r="D699" s="2"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="C700" s="1"/>
-      <c r="D700" s="1"/>
+      <c r="C700" s="2"/>
+      <c r="D700" s="2"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="C701" s="1"/>
-      <c r="D701" s="1"/>
+      <c r="C701" s="2"/>
+      <c r="D701" s="2"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="C702" s="1"/>
-      <c r="D702" s="1"/>
+      <c r="C702" s="2"/>
+      <c r="D702" s="2"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="C703" s="1"/>
-      <c r="D703" s="1"/>
+      <c r="C703" s="2"/>
+      <c r="D703" s="2"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="C704" s="1"/>
-      <c r="D704" s="1"/>
+      <c r="C704" s="2"/>
+      <c r="D704" s="2"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="C705" s="1"/>
-      <c r="D705" s="1"/>
+      <c r="C705" s="2"/>
+      <c r="D705" s="2"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="C706" s="1"/>
-      <c r="D706" s="1"/>
+      <c r="C706" s="2"/>
+      <c r="D706" s="2"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="C707" s="1"/>
-      <c r="D707" s="1"/>
+      <c r="C707" s="2"/>
+      <c r="D707" s="2"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="C708" s="1"/>
-      <c r="D708" s="1"/>
+      <c r="C708" s="2"/>
+      <c r="D708" s="2"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="C709" s="1"/>
-      <c r="D709" s="1"/>
+      <c r="C709" s="2"/>
+      <c r="D709" s="2"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="C710" s="1"/>
-      <c r="D710" s="1"/>
+      <c r="C710" s="2"/>
+      <c r="D710" s="2"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="C711" s="1"/>
-      <c r="D711" s="1"/>
+      <c r="C711" s="2"/>
+      <c r="D711" s="2"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="C712" s="1"/>
-      <c r="D712" s="1"/>
+      <c r="C712" s="2"/>
+      <c r="D712" s="2"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="C713" s="1"/>
-      <c r="D713" s="1"/>
+      <c r="C713" s="2"/>
+      <c r="D713" s="2"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="C714" s="1"/>
-      <c r="D714" s="1"/>
+      <c r="C714" s="2"/>
+      <c r="D714" s="2"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="C715" s="1"/>
-      <c r="D715" s="1"/>
+      <c r="C715" s="2"/>
+      <c r="D715" s="2"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="C716" s="1"/>
-      <c r="D716" s="1"/>
+      <c r="C716" s="2"/>
+      <c r="D716" s="2"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="C717" s="1"/>
-      <c r="D717" s="1"/>
+      <c r="C717" s="2"/>
+      <c r="D717" s="2"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="C718" s="1"/>
-      <c r="D718" s="1"/>
+      <c r="C718" s="2"/>
+      <c r="D718" s="2"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="C719" s="1"/>
-      <c r="D719" s="1"/>
+      <c r="C719" s="2"/>
+      <c r="D719" s="2"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="C720" s="1"/>
-      <c r="D720" s="1"/>
+      <c r="C720" s="2"/>
+      <c r="D720" s="2"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="C721" s="1"/>
-      <c r="D721" s="1"/>
+      <c r="C721" s="2"/>
+      <c r="D721" s="2"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="C722" s="1"/>
-      <c r="D722" s="1"/>
+      <c r="C722" s="2"/>
+      <c r="D722" s="2"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="C723" s="1"/>
-      <c r="D723" s="1"/>
+      <c r="C723" s="2"/>
+      <c r="D723" s="2"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="C724" s="1"/>
-      <c r="D724" s="1"/>
+      <c r="C724" s="2"/>
+      <c r="D724" s="2"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="C725" s="1"/>
-      <c r="D725" s="1"/>
+      <c r="C725" s="2"/>
+      <c r="D725" s="2"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="C726" s="1"/>
-      <c r="D726" s="1"/>
+      <c r="C726" s="2"/>
+      <c r="D726" s="2"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="C727" s="1"/>
-      <c r="D727" s="1"/>
+      <c r="C727" s="2"/>
+      <c r="D727" s="2"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="C728" s="1"/>
-      <c r="D728" s="1"/>
+      <c r="C728" s="2"/>
+      <c r="D728" s="2"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="C729" s="1"/>
-      <c r="D729" s="1"/>
+      <c r="C729" s="2"/>
+      <c r="D729" s="2"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="C730" s="1"/>
-      <c r="D730" s="1"/>
+      <c r="C730" s="2"/>
+      <c r="D730" s="2"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="C731" s="1"/>
-      <c r="D731" s="1"/>
+      <c r="C731" s="2"/>
+      <c r="D731" s="2"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="C732" s="1"/>
-      <c r="D732" s="1"/>
+      <c r="C732" s="2"/>
+      <c r="D732" s="2"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="C733" s="1"/>
-      <c r="D733" s="1"/>
+      <c r="C733" s="2"/>
+      <c r="D733" s="2"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="C734" s="1"/>
-      <c r="D734" s="1"/>
+      <c r="C734" s="2"/>
+      <c r="D734" s="2"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="C735" s="1"/>
-      <c r="D735" s="1"/>
+      <c r="C735" s="2"/>
+      <c r="D735" s="2"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="C736" s="1"/>
-      <c r="D736" s="1"/>
+      <c r="C736" s="2"/>
+      <c r="D736" s="2"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="C737" s="1"/>
-      <c r="D737" s="1"/>
+      <c r="C737" s="2"/>
+      <c r="D737" s="2"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="C738" s="1"/>
-      <c r="D738" s="1"/>
+      <c r="C738" s="2"/>
+      <c r="D738" s="2"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="C739" s="1"/>
-      <c r="D739" s="1"/>
+      <c r="C739" s="2"/>
+      <c r="D739" s="2"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="C740" s="1"/>
-      <c r="D740" s="1"/>
+      <c r="C740" s="2"/>
+      <c r="D740" s="2"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="C741" s="1"/>
-      <c r="D741" s="1"/>
+      <c r="C741" s="2"/>
+      <c r="D741" s="2"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="C742" s="1"/>
-      <c r="D742" s="1"/>
+      <c r="C742" s="2"/>
+      <c r="D742" s="2"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="C743" s="1"/>
-      <c r="D743" s="1"/>
+      <c r="C743" s="2"/>
+      <c r="D743" s="2"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="C744" s="1"/>
-      <c r="D744" s="1"/>
+      <c r="C744" s="2"/>
+      <c r="D744" s="2"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="C745" s="1"/>
-      <c r="D745" s="1"/>
+      <c r="C745" s="2"/>
+      <c r="D745" s="2"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="C746" s="1"/>
-      <c r="D746" s="1"/>
+      <c r="C746" s="2"/>
+      <c r="D746" s="2"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="C747" s="1"/>
-      <c r="D747" s="1"/>
+      <c r="C747" s="2"/>
+      <c r="D747" s="2"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="C748" s="1"/>
-      <c r="D748" s="1"/>
+      <c r="C748" s="2"/>
+      <c r="D748" s="2"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="C749" s="1"/>
-      <c r="D749" s="1"/>
+      <c r="C749" s="2"/>
+      <c r="D749" s="2"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="C750" s="1"/>
-      <c r="D750" s="1"/>
+      <c r="C750" s="2"/>
+      <c r="D750" s="2"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="C751" s="1"/>
-      <c r="D751" s="1"/>
+      <c r="C751" s="2"/>
+      <c r="D751" s="2"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="C752" s="1"/>
-      <c r="D752" s="1"/>
+      <c r="C752" s="2"/>
+      <c r="D752" s="2"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="C753" s="1"/>
-      <c r="D753" s="1"/>
+      <c r="C753" s="2"/>
+      <c r="D753" s="2"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="C754" s="1"/>
-      <c r="D754" s="1"/>
+      <c r="C754" s="2"/>
+      <c r="D754" s="2"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="C755" s="1"/>
-      <c r="D755" s="1"/>
+      <c r="C755" s="2"/>
+      <c r="D755" s="2"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="C756" s="1"/>
-      <c r="D756" s="1"/>
+      <c r="C756" s="2"/>
+      <c r="D756" s="2"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="C757" s="1"/>
-      <c r="D757" s="1"/>
+      <c r="C757" s="2"/>
+      <c r="D757" s="2"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="C758" s="1"/>
-      <c r="D758" s="1"/>
+      <c r="C758" s="2"/>
+      <c r="D758" s="2"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="C759" s="1"/>
-      <c r="D759" s="1"/>
+      <c r="C759" s="2"/>
+      <c r="D759" s="2"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="C760" s="1"/>
-      <c r="D760" s="1"/>
+      <c r="C760" s="2"/>
+      <c r="D760" s="2"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="C761" s="1"/>
-      <c r="D761" s="1"/>
+      <c r="C761" s="2"/>
+      <c r="D761" s="2"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="C762" s="1"/>
-      <c r="D762" s="1"/>
+      <c r="C762" s="2"/>
+      <c r="D762" s="2"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="C763" s="1"/>
-      <c r="D763" s="1"/>
+      <c r="C763" s="2"/>
+      <c r="D763" s="2"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="C764" s="1"/>
-      <c r="D764" s="1"/>
+      <c r="C764" s="2"/>
+      <c r="D764" s="2"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="C765" s="1"/>
-      <c r="D765" s="1"/>
+      <c r="C765" s="2"/>
+      <c r="D765" s="2"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="C766" s="1"/>
-      <c r="D766" s="1"/>
+      <c r="C766" s="2"/>
+      <c r="D766" s="2"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="C767" s="1"/>
-      <c r="D767" s="1"/>
+      <c r="C767" s="2"/>
+      <c r="D767" s="2"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="C768" s="1"/>
-      <c r="D768" s="1"/>
+      <c r="C768" s="2"/>
+      <c r="D768" s="2"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="C769" s="1"/>
-      <c r="D769" s="1"/>
+      <c r="C769" s="2"/>
+      <c r="D769" s="2"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="C770" s="1"/>
-      <c r="D770" s="1"/>
+      <c r="C770" s="2"/>
+      <c r="D770" s="2"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="C771" s="1"/>
-      <c r="D771" s="1"/>
+      <c r="C771" s="2"/>
+      <c r="D771" s="2"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="C772" s="1"/>
-      <c r="D772" s="1"/>
+      <c r="C772" s="2"/>
+      <c r="D772" s="2"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="C773" s="1"/>
-      <c r="D773" s="1"/>
+      <c r="C773" s="2"/>
+      <c r="D773" s="2"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="C774" s="1"/>
-      <c r="D774" s="1"/>
+      <c r="C774" s="2"/>
+      <c r="D774" s="2"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="C775" s="1"/>
-      <c r="D775" s="1"/>
+      <c r="C775" s="2"/>
+      <c r="D775" s="2"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="C776" s="1"/>
-      <c r="D776" s="1"/>
+      <c r="C776" s="2"/>
+      <c r="D776" s="2"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="C777" s="1"/>
-      <c r="D777" s="1"/>
+      <c r="C777" s="2"/>
+      <c r="D777" s="2"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="C778" s="1"/>
-      <c r="D778" s="1"/>
+      <c r="C778" s="2"/>
+      <c r="D778" s="2"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="C779" s="1"/>
-      <c r="D779" s="1"/>
+      <c r="C779" s="2"/>
+      <c r="D779" s="2"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="C780" s="1"/>
-      <c r="D780" s="1"/>
+      <c r="C780" s="2"/>
+      <c r="D780" s="2"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="C781" s="1"/>
-      <c r="D781" s="1"/>
+      <c r="C781" s="2"/>
+      <c r="D781" s="2"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="C782" s="1"/>
-      <c r="D782" s="1"/>
+      <c r="C782" s="2"/>
+      <c r="D782" s="2"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="C783" s="1"/>
-      <c r="D783" s="1"/>
+      <c r="C783" s="2"/>
+      <c r="D783" s="2"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="C784" s="1"/>
-      <c r="D784" s="1"/>
+      <c r="C784" s="2"/>
+      <c r="D784" s="2"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="C785" s="1"/>
-      <c r="D785" s="1"/>
+      <c r="C785" s="2"/>
+      <c r="D785" s="2"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="C786" s="1"/>
-      <c r="D786" s="1"/>
+      <c r="C786" s="2"/>
+      <c r="D786" s="2"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="C787" s="1"/>
-      <c r="D787" s="1"/>
+      <c r="C787" s="2"/>
+      <c r="D787" s="2"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="C788" s="1"/>
-      <c r="D788" s="1"/>
+      <c r="C788" s="2"/>
+      <c r="D788" s="2"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="C789" s="1"/>
-      <c r="D789" s="1"/>
+      <c r="C789" s="2"/>
+      <c r="D789" s="2"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="C790" s="1"/>
-      <c r="D790" s="1"/>
+      <c r="C790" s="2"/>
+      <c r="D790" s="2"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="C791" s="1"/>
-      <c r="D791" s="1"/>
+      <c r="C791" s="2"/>
+      <c r="D791" s="2"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="C792" s="1"/>
-      <c r="D792" s="1"/>
+      <c r="C792" s="2"/>
+      <c r="D792" s="2"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="C793" s="1"/>
-      <c r="D793" s="1"/>
+      <c r="C793" s="2"/>
+      <c r="D793" s="2"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="C794" s="1"/>
-      <c r="D794" s="1"/>
+      <c r="C794" s="2"/>
+      <c r="D794" s="2"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="C795" s="1"/>
-      <c r="D795" s="1"/>
+      <c r="C795" s="2"/>
+      <c r="D795" s="2"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="C796" s="1"/>
-      <c r="D796" s="1"/>
+      <c r="C796" s="2"/>
+      <c r="D796" s="2"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="C797" s="1"/>
-      <c r="D797" s="1"/>
+      <c r="C797" s="2"/>
+      <c r="D797" s="2"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="C798" s="1"/>
-      <c r="D798" s="1"/>
+      <c r="C798" s="2"/>
+      <c r="D798" s="2"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="C799" s="1"/>
-      <c r="D799" s="1"/>
+      <c r="C799" s="2"/>
+      <c r="D799" s="2"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="C800" s="1"/>
-      <c r="D800" s="1"/>
+      <c r="C800" s="2"/>
+      <c r="D800" s="2"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="C801" s="1"/>
-      <c r="D801" s="1"/>
+      <c r="C801" s="2"/>
+      <c r="D801" s="2"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="C802" s="1"/>
-      <c r="D802" s="1"/>
+      <c r="C802" s="2"/>
+      <c r="D802" s="2"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="C803" s="1"/>
-      <c r="D803" s="1"/>
+      <c r="C803" s="2"/>
+      <c r="D803" s="2"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="C804" s="1"/>
-      <c r="D804" s="1"/>
+      <c r="C804" s="2"/>
+      <c r="D804" s="2"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="C805" s="1"/>
-      <c r="D805" s="1"/>
+      <c r="C805" s="2"/>
+      <c r="D805" s="2"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="C806" s="1"/>
-      <c r="D806" s="1"/>
+      <c r="C806" s="2"/>
+      <c r="D806" s="2"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="C807" s="1"/>
-      <c r="D807" s="1"/>
+      <c r="C807" s="2"/>
+      <c r="D807" s="2"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="C808" s="1"/>
-      <c r="D808" s="1"/>
+      <c r="C808" s="2"/>
+      <c r="D808" s="2"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="C809" s="1"/>
-      <c r="D809" s="1"/>
+      <c r="C809" s="2"/>
+      <c r="D809" s="2"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="C810" s="1"/>
-      <c r="D810" s="1"/>
+      <c r="C810" s="2"/>
+      <c r="D810" s="2"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="C811" s="1"/>
-      <c r="D811" s="1"/>
+      <c r="C811" s="2"/>
+      <c r="D811" s="2"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="C812" s="1"/>
-      <c r="D812" s="1"/>
+      <c r="C812" s="2"/>
+      <c r="D812" s="2"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="C813" s="1"/>
-      <c r="D813" s="1"/>
+      <c r="C813" s="2"/>
+      <c r="D813" s="2"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="C814" s="1"/>
-      <c r="D814" s="1"/>
+      <c r="C814" s="2"/>
+      <c r="D814" s="2"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="C815" s="1"/>
-      <c r="D815" s="1"/>
+      <c r="C815" s="2"/>
+      <c r="D815" s="2"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="C816" s="1"/>
-      <c r="D816" s="1"/>
+      <c r="C816" s="2"/>
+      <c r="D816" s="2"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="C817" s="1"/>
-      <c r="D817" s="1"/>
+      <c r="C817" s="2"/>
+      <c r="D817" s="2"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="C818" s="1"/>
-      <c r="D818" s="1"/>
+      <c r="C818" s="2"/>
+      <c r="D818" s="2"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="C819" s="1"/>
-      <c r="D819" s="1"/>
+      <c r="C819" s="2"/>
+      <c r="D819" s="2"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="C820" s="1"/>
-      <c r="D820" s="1"/>
+      <c r="C820" s="2"/>
+      <c r="D820" s="2"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="C821" s="1"/>
-      <c r="D821" s="1"/>
+      <c r="C821" s="2"/>
+      <c r="D821" s="2"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="C822" s="1"/>
-      <c r="D822" s="1"/>
+      <c r="C822" s="2"/>
+      <c r="D822" s="2"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="C823" s="1"/>
-      <c r="D823" s="1"/>
+      <c r="C823" s="2"/>
+      <c r="D823" s="2"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="C824" s="1"/>
-      <c r="D824" s="1"/>
+      <c r="C824" s="2"/>
+      <c r="D824" s="2"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="C825" s="1"/>
-      <c r="D825" s="1"/>
+      <c r="C825" s="2"/>
+      <c r="D825" s="2"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="C826" s="1"/>
-      <c r="D826" s="1"/>
+      <c r="C826" s="2"/>
+      <c r="D826" s="2"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="C827" s="1"/>
-      <c r="D827" s="1"/>
+      <c r="C827" s="2"/>
+      <c r="D827" s="2"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="C828" s="1"/>
-      <c r="D828" s="1"/>
+      <c r="C828" s="2"/>
+      <c r="D828" s="2"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="C829" s="1"/>
-      <c r="D829" s="1"/>
+      <c r="C829" s="2"/>
+      <c r="D829" s="2"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="C830" s="1"/>
-      <c r="D830" s="1"/>
+      <c r="C830" s="2"/>
+      <c r="D830" s="2"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="C831" s="1"/>
-      <c r="D831" s="1"/>
+      <c r="C831" s="2"/>
+      <c r="D831" s="2"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="C832" s="1"/>
-      <c r="D832" s="1"/>
+      <c r="C832" s="2"/>
+      <c r="D832" s="2"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="C833" s="1"/>
-      <c r="D833" s="1"/>
+      <c r="C833" s="2"/>
+      <c r="D833" s="2"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="C834" s="1"/>
-      <c r="D834" s="1"/>
+      <c r="C834" s="2"/>
+      <c r="D834" s="2"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="C835" s="1"/>
-      <c r="D835" s="1"/>
+      <c r="C835" s="2"/>
+      <c r="D835" s="2"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="C836" s="1"/>
-      <c r="D836" s="1"/>
+      <c r="C836" s="2"/>
+      <c r="D836" s="2"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="C837" s="1"/>
-      <c r="D837" s="1"/>
+      <c r="C837" s="2"/>
+      <c r="D837" s="2"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="C838" s="1"/>
-      <c r="D838" s="1"/>
+      <c r="C838" s="2"/>
+      <c r="D838" s="2"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="C839" s="1"/>
-      <c r="D839" s="1"/>
+      <c r="C839" s="2"/>
+      <c r="D839" s="2"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="C840" s="1"/>
-      <c r="D840" s="1"/>
+      <c r="C840" s="2"/>
+      <c r="D840" s="2"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="C841" s="1"/>
-      <c r="D841" s="1"/>
+      <c r="C841" s="2"/>
+      <c r="D841" s="2"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="C842" s="1"/>
-      <c r="D842" s="1"/>
+      <c r="C842" s="2"/>
+      <c r="D842" s="2"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="C843" s="1"/>
-      <c r="D843" s="1"/>
+      <c r="C843" s="2"/>
+      <c r="D843" s="2"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="C844" s="1"/>
-      <c r="D844" s="1"/>
+      <c r="C844" s="2"/>
+      <c r="D844" s="2"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="C845" s="1"/>
-      <c r="D845" s="1"/>
+      <c r="C845" s="2"/>
+      <c r="D845" s="2"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="C846" s="1"/>
-      <c r="D846" s="1"/>
+      <c r="C846" s="2"/>
+      <c r="D846" s="2"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="C847" s="1"/>
-      <c r="D847" s="1"/>
+      <c r="C847" s="2"/>
+      <c r="D847" s="2"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="C848" s="1"/>
-      <c r="D848" s="1"/>
+      <c r="C848" s="2"/>
+      <c r="D848" s="2"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="C849" s="1"/>
-      <c r="D849" s="1"/>
+      <c r="C849" s="2"/>
+      <c r="D849" s="2"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="C850" s="1"/>
-      <c r="D850" s="1"/>
+      <c r="C850" s="2"/>
+      <c r="D850" s="2"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="C851" s="1"/>
-      <c r="D851" s="1"/>
+      <c r="C851" s="2"/>
+      <c r="D851" s="2"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="C852" s="1"/>
-      <c r="D852" s="1"/>
+      <c r="C852" s="2"/>
+      <c r="D852" s="2"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="C853" s="1"/>
-      <c r="D853" s="1"/>
+      <c r="C853" s="2"/>
+      <c r="D853" s="2"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="C854" s="1"/>
-      <c r="D854" s="1"/>
+      <c r="C854" s="2"/>
+      <c r="D854" s="2"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="C855" s="1"/>
-      <c r="D855" s="1"/>
+      <c r="C855" s="2"/>
+      <c r="D855" s="2"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="C856" s="1"/>
-      <c r="D856" s="1"/>
+      <c r="C856" s="2"/>
+      <c r="D856" s="2"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="C857" s="1"/>
-      <c r="D857" s="1"/>
+      <c r="C857" s="2"/>
+      <c r="D857" s="2"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="C858" s="1"/>
-      <c r="D858" s="1"/>
+      <c r="C858" s="2"/>
+      <c r="D858" s="2"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="C859" s="1"/>
-      <c r="D859" s="1"/>
+      <c r="C859" s="2"/>
+      <c r="D859" s="2"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="C860" s="1"/>
-      <c r="D860" s="1"/>
+      <c r="C860" s="2"/>
+      <c r="D860" s="2"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="C861" s="1"/>
-      <c r="D861" s="1"/>
+      <c r="C861" s="2"/>
+      <c r="D861" s="2"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="C862" s="1"/>
-      <c r="D862" s="1"/>
+      <c r="C862" s="2"/>
+      <c r="D862" s="2"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="C863" s="1"/>
-      <c r="D863" s="1"/>
+      <c r="C863" s="2"/>
+      <c r="D863" s="2"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="C864" s="1"/>
-      <c r="D864" s="1"/>
+      <c r="C864" s="2"/>
+      <c r="D864" s="2"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="C865" s="1"/>
-      <c r="D865" s="1"/>
+      <c r="C865" s="2"/>
+      <c r="D865" s="2"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="C866" s="1"/>
-      <c r="D866" s="1"/>
+      <c r="C866" s="2"/>
+      <c r="D866" s="2"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="C867" s="1"/>
-      <c r="D867" s="1"/>
+      <c r="C867" s="2"/>
+      <c r="D867" s="2"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="C868" s="1"/>
-      <c r="D868" s="1"/>
+      <c r="C868" s="2"/>
+      <c r="D868" s="2"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="C869" s="1"/>
-      <c r="D869" s="1"/>
+      <c r="C869" s="2"/>
+      <c r="D869" s="2"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="C870" s="1"/>
-      <c r="D870" s="1"/>
+      <c r="C870" s="2"/>
+      <c r="D870" s="2"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="C871" s="1"/>
-      <c r="D871" s="1"/>
+      <c r="C871" s="2"/>
+      <c r="D871" s="2"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="C872" s="1"/>
-      <c r="D872" s="1"/>
+      <c r="C872" s="2"/>
+      <c r="D872" s="2"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="C873" s="1"/>
-      <c r="D873" s="1"/>
+      <c r="C873" s="2"/>
+      <c r="D873" s="2"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="C874" s="1"/>
-      <c r="D874" s="1"/>
+      <c r="C874" s="2"/>
+      <c r="D874" s="2"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="C875" s="1"/>
-      <c r="D875" s="1"/>
+      <c r="C875" s="2"/>
+      <c r="D875" s="2"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="C876" s="1"/>
-      <c r="D876" s="1"/>
+      <c r="C876" s="2"/>
+      <c r="D876" s="2"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="C877" s="1"/>
-      <c r="D877" s="1"/>
+      <c r="C877" s="2"/>
+      <c r="D877" s="2"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="C878" s="1"/>
-      <c r="D878" s="1"/>
+      <c r="C878" s="2"/>
+      <c r="D878" s="2"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="C879" s="1"/>
-      <c r="D879" s="1"/>
+      <c r="C879" s="2"/>
+      <c r="D879" s="2"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="C880" s="1"/>
-      <c r="D880" s="1"/>
+      <c r="C880" s="2"/>
+      <c r="D880" s="2"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="C881" s="1"/>
-      <c r="D881" s="1"/>
+      <c r="C881" s="2"/>
+      <c r="D881" s="2"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="C882" s="1"/>
-      <c r="D882" s="1"/>
+      <c r="C882" s="2"/>
+      <c r="D882" s="2"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="C883" s="1"/>
-      <c r="D883" s="1"/>
+      <c r="C883" s="2"/>
+      <c r="D883" s="2"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="C884" s="1"/>
-      <c r="D884" s="1"/>
+      <c r="C884" s="2"/>
+      <c r="D884" s="2"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="C885" s="1"/>
-      <c r="D885" s="1"/>
+      <c r="C885" s="2"/>
+      <c r="D885" s="2"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="C886" s="1"/>
-      <c r="D886" s="1"/>
+      <c r="C886" s="2"/>
+      <c r="D886" s="2"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="C887" s="1"/>
-      <c r="D887" s="1"/>
+      <c r="C887" s="2"/>
+      <c r="D887" s="2"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="C888" s="1"/>
-      <c r="D888" s="1"/>
+      <c r="C888" s="2"/>
+      <c r="D888" s="2"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="C889" s="1"/>
-      <c r="D889" s="1"/>
+      <c r="C889" s="2"/>
+      <c r="D889" s="2"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="C890" s="1"/>
-      <c r="D890" s="1"/>
+      <c r="C890" s="2"/>
+      <c r="D890" s="2"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="C891" s="1"/>
-      <c r="D891" s="1"/>
+      <c r="C891" s="2"/>
+      <c r="D891" s="2"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="C892" s="1"/>
-      <c r="D892" s="1"/>
+      <c r="C892" s="2"/>
+      <c r="D892" s="2"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="C893" s="1"/>
-      <c r="D893" s="1"/>
+      <c r="C893" s="2"/>
+      <c r="D893" s="2"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="C894" s="1"/>
-      <c r="D894" s="1"/>
+      <c r="C894" s="2"/>
+      <c r="D894" s="2"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="C895" s="1"/>
-      <c r="D895" s="1"/>
+      <c r="C895" s="2"/>
+      <c r="D895" s="2"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="C896" s="1"/>
-      <c r="D896" s="1"/>
+      <c r="C896" s="2"/>
+      <c r="D896" s="2"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="C897" s="1"/>
-      <c r="D897" s="1"/>
+      <c r="C897" s="2"/>
+      <c r="D897" s="2"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="C898" s="1"/>
-      <c r="D898" s="1"/>
+      <c r="C898" s="2"/>
+      <c r="D898" s="2"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="C899" s="1"/>
-      <c r="D899" s="1"/>
+      <c r="C899" s="2"/>
+      <c r="D899" s="2"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="C900" s="1"/>
-      <c r="D900" s="1"/>
+      <c r="C900" s="2"/>
+      <c r="D900" s="2"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="C901" s="1"/>
-      <c r="D901" s="1"/>
+      <c r="C901" s="2"/>
+      <c r="D901" s="2"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="C902" s="1"/>
-      <c r="D902" s="1"/>
+      <c r="C902" s="2"/>
+      <c r="D902" s="2"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="C903" s="1"/>
-      <c r="D903" s="1"/>
+      <c r="C903" s="2"/>
+      <c r="D903" s="2"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="C904" s="1"/>
-      <c r="D904" s="1"/>
+      <c r="C904" s="2"/>
+      <c r="D904" s="2"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="C905" s="1"/>
-      <c r="D905" s="1"/>
+      <c r="C905" s="2"/>
+      <c r="D905" s="2"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="C906" s="1"/>
-      <c r="D906" s="1"/>
+      <c r="C906" s="2"/>
+      <c r="D906" s="2"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="C907" s="1"/>
-      <c r="D907" s="1"/>
+      <c r="C907" s="2"/>
+      <c r="D907" s="2"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="C908" s="1"/>
-      <c r="D908" s="1"/>
+      <c r="C908" s="2"/>
+      <c r="D908" s="2"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="C909" s="1"/>
-      <c r="D909" s="1"/>
+      <c r="C909" s="2"/>
+      <c r="D909" s="2"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="C910" s="1"/>
-      <c r="D910" s="1"/>
+      <c r="C910" s="2"/>
+      <c r="D910" s="2"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="C911" s="1"/>
-      <c r="D911" s="1"/>
+      <c r="C911" s="2"/>
+      <c r="D911" s="2"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="C912" s="1"/>
-      <c r="D912" s="1"/>
+      <c r="C912" s="2"/>
+      <c r="D912" s="2"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="C913" s="1"/>
-      <c r="D913" s="1"/>
+      <c r="C913" s="2"/>
+      <c r="D913" s="2"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="C914" s="1"/>
-      <c r="D914" s="1"/>
+      <c r="C914" s="2"/>
+      <c r="D914" s="2"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="C915" s="1"/>
-      <c r="D915" s="1"/>
+      <c r="C915" s="2"/>
+      <c r="D915" s="2"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="C916" s="1"/>
-      <c r="D916" s="1"/>
+      <c r="C916" s="2"/>
+      <c r="D916" s="2"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="C917" s="1"/>
-      <c r="D917" s="1"/>
+      <c r="C917" s="2"/>
+      <c r="D917" s="2"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="C918" s="1"/>
-      <c r="D918" s="1"/>
+      <c r="C918" s="2"/>
+      <c r="D918" s="2"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="C919" s="1"/>
-      <c r="D919" s="1"/>
+      <c r="C919" s="2"/>
+      <c r="D919" s="2"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="C920" s="1"/>
-      <c r="D920" s="1"/>
+      <c r="C920" s="2"/>
+      <c r="D920" s="2"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="C921" s="1"/>
-      <c r="D921" s="1"/>
+      <c r="C921" s="2"/>
+      <c r="D921" s="2"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="C922" s="1"/>
-      <c r="D922" s="1"/>
+      <c r="C922" s="2"/>
+      <c r="D922" s="2"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="C923" s="1"/>
-      <c r="D923" s="1"/>
+      <c r="C923" s="2"/>
+      <c r="D923" s="2"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="C924" s="1"/>
-      <c r="D924" s="1"/>
+      <c r="C924" s="2"/>
+      <c r="D924" s="2"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="C925" s="1"/>
-      <c r="D925" s="1"/>
+      <c r="C925" s="2"/>
+      <c r="D925" s="2"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="C926" s="1"/>
-      <c r="D926" s="1"/>
+      <c r="C926" s="2"/>
+      <c r="D926" s="2"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="C927" s="1"/>
-      <c r="D927" s="1"/>
+      <c r="C927" s="2"/>
+      <c r="D927" s="2"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="C928" s="1"/>
-      <c r="D928" s="1"/>
+      <c r="C928" s="2"/>
+      <c r="D928" s="2"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="C929" s="1"/>
-      <c r="D929" s="1"/>
+      <c r="C929" s="2"/>
+      <c r="D929" s="2"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="C930" s="1"/>
-      <c r="D930" s="1"/>
+      <c r="C930" s="2"/>
+      <c r="D930" s="2"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="C931" s="1"/>
-      <c r="D931" s="1"/>
+      <c r="C931" s="2"/>
+      <c r="D931" s="2"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="C932" s="1"/>
-      <c r="D932" s="1"/>
+      <c r="C932" s="2"/>
+      <c r="D932" s="2"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="C933" s="1"/>
-      <c r="D933" s="1"/>
+      <c r="C933" s="2"/>
+      <c r="D933" s="2"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="C934" s="1"/>
-      <c r="D934" s="1"/>
+      <c r="C934" s="2"/>
+      <c r="D934" s="2"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="C935" s="1"/>
-      <c r="D935" s="1"/>
+      <c r="C935" s="2"/>
+      <c r="D935" s="2"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="C936" s="1"/>
-      <c r="D936" s="1"/>
+      <c r="C936" s="2"/>
+      <c r="D936" s="2"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="C937" s="1"/>
-      <c r="D937" s="1"/>
+      <c r="C937" s="2"/>
+      <c r="D937" s="2"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="C938" s="1"/>
-      <c r="D938" s="1"/>
+      <c r="C938" s="2"/>
+      <c r="D938" s="2"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="C939" s="1"/>
-      <c r="D939" s="1"/>
+      <c r="C939" s="2"/>
+      <c r="D939" s="2"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="C940" s="1"/>
-      <c r="D940" s="1"/>
+      <c r="C940" s="2"/>
+      <c r="D940" s="2"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="C941" s="1"/>
-      <c r="D941" s="1"/>
+      <c r="C941" s="2"/>
+      <c r="D941" s="2"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="C942" s="1"/>
-      <c r="D942" s="1"/>
+      <c r="C942" s="2"/>
+      <c r="D942" s="2"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="C943" s="1"/>
-      <c r="D943" s="1"/>
+      <c r="C943" s="2"/>
+      <c r="D943" s="2"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="C944" s="1"/>
-      <c r="D944" s="1"/>
+      <c r="C944" s="2"/>
+      <c r="D944" s="2"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="C945" s="1"/>
-      <c r="D945" s="1"/>
+      <c r="C945" s="2"/>
+      <c r="D945" s="2"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="C946" s="1"/>
-      <c r="D946" s="1"/>
+      <c r="C946" s="2"/>
+      <c r="D946" s="2"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="C947" s="1"/>
-      <c r="D947" s="1"/>
+      <c r="C947" s="2"/>
+      <c r="D947" s="2"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="C948" s="1"/>
-      <c r="D948" s="1"/>
+      <c r="C948" s="2"/>
+      <c r="D948" s="2"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="C949" s="1"/>
-      <c r="D949" s="1"/>
+      <c r="C949" s="2"/>
+      <c r="D949" s="2"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="C950" s="1"/>
-      <c r="D950" s="1"/>
+      <c r="C950" s="2"/>
+      <c r="D950" s="2"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="C951" s="1"/>
-      <c r="D951" s="1"/>
+      <c r="C951" s="2"/>
+      <c r="D951" s="2"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="C952" s="1"/>
-      <c r="D952" s="1"/>
+      <c r="C952" s="2"/>
+      <c r="D952" s="2"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="C953" s="1"/>
-      <c r="D953" s="1"/>
+      <c r="C953" s="2"/>
+      <c r="D953" s="2"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="C954" s="1"/>
-      <c r="D954" s="1"/>
+      <c r="C954" s="2"/>
+      <c r="D954" s="2"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="C955" s="1"/>
-      <c r="D955" s="1"/>
+      <c r="C955" s="2"/>
+      <c r="D955" s="2"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="C956" s="1"/>
-      <c r="D956" s="1"/>
+      <c r="C956" s="2"/>
+      <c r="D956" s="2"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="C957" s="1"/>
-      <c r="D957" s="1"/>
+      <c r="C957" s="2"/>
+      <c r="D957" s="2"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="C958" s="1"/>
-      <c r="D958" s="1"/>
+      <c r="C958" s="2"/>
+      <c r="D958" s="2"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="C959" s="1"/>
-      <c r="D959" s="1"/>
+      <c r="C959" s="2"/>
+      <c r="D959" s="2"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="C960" s="1"/>
-      <c r="D960" s="1"/>
+      <c r="C960" s="2"/>
+      <c r="D960" s="2"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="C961" s="1"/>
-      <c r="D961" s="1"/>
+      <c r="C961" s="2"/>
+      <c r="D961" s="2"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="C962" s="1"/>
-      <c r="D962" s="1"/>
+      <c r="C962" s="2"/>
+      <c r="D962" s="2"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="C963" s="1"/>
-      <c r="D963" s="1"/>
+      <c r="C963" s="2"/>
+      <c r="D963" s="2"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="C964" s="1"/>
-      <c r="D964" s="1"/>
+      <c r="C964" s="2"/>
+      <c r="D964" s="2"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="C965" s="1"/>
-      <c r="D965" s="1"/>
+      <c r="C965" s="2"/>
+      <c r="D965" s="2"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="C966" s="1"/>
-      <c r="D966" s="1"/>
+      <c r="C966" s="2"/>
+      <c r="D966" s="2"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="C967" s="1"/>
-      <c r="D967" s="1"/>
+      <c r="C967" s="2"/>
+      <c r="D967" s="2"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="C968" s="1"/>
-      <c r="D968" s="1"/>
+      <c r="C968" s="2"/>
+      <c r="D968" s="2"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="C969" s="1"/>
-      <c r="D969" s="1"/>
+      <c r="C969" s="2"/>
+      <c r="D969" s="2"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="C970" s="1"/>
-      <c r="D970" s="1"/>
+      <c r="C970" s="2"/>
+      <c r="D970" s="2"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="C971" s="1"/>
-      <c r="D971" s="1"/>
+      <c r="C971" s="2"/>
+      <c r="D971" s="2"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="C972" s="1"/>
-      <c r="D972" s="1"/>
+      <c r="C972" s="2"/>
+      <c r="D972" s="2"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="C973" s="1"/>
-      <c r="D973" s="1"/>
+      <c r="C973" s="2"/>
+      <c r="D973" s="2"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="C974" s="1"/>
-      <c r="D974" s="1"/>
+      <c r="C974" s="2"/>
+      <c r="D974" s="2"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="C975" s="1"/>
-      <c r="D975" s="1"/>
+      <c r="C975" s="2"/>
+      <c r="D975" s="2"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="C976" s="1"/>
-      <c r="D976" s="1"/>
+      <c r="C976" s="2"/>
+      <c r="D976" s="2"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="C977" s="1"/>
-      <c r="D977" s="1"/>
+      <c r="C977" s="2"/>
+      <c r="D977" s="2"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="C978" s="1"/>
-      <c r="D978" s="1"/>
+      <c r="C978" s="2"/>
+      <c r="D978" s="2"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="C979" s="1"/>
-      <c r="D979" s="1"/>
+      <c r="C979" s="2"/>
+      <c r="D979" s="2"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="C980" s="1"/>
-      <c r="D980" s="1"/>
+      <c r="C980" s="2"/>
+      <c r="D980" s="2"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="C981" s="1"/>
-      <c r="D981" s="1"/>
+      <c r="C981" s="2"/>
+      <c r="D981" s="2"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="C982" s="1"/>
-      <c r="D982" s="1"/>
+      <c r="C982" s="2"/>
+      <c r="D982" s="2"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="C983" s="1"/>
-      <c r="D983" s="1"/>
+      <c r="C983" s="2"/>
+      <c r="D983" s="2"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="C984" s="1"/>
-      <c r="D984" s="1"/>
+      <c r="C984" s="2"/>
+      <c r="D984" s="2"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="C985" s="1"/>
-      <c r="D985" s="1"/>
+      <c r="C985" s="2"/>
+      <c r="D985" s="2"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="C986" s="1"/>
-      <c r="D986" s="1"/>
+      <c r="C986" s="2"/>
+      <c r="D986" s="2"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="C987" s="1"/>
-      <c r="D987" s="1"/>
+      <c r="C987" s="2"/>
+      <c r="D987" s="2"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="C988" s="1"/>
-      <c r="D988" s="1"/>
+      <c r="C988" s="2"/>
+      <c r="D988" s="2"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="C989" s="1"/>
-      <c r="D989" s="1"/>
+      <c r="C989" s="2"/>
+      <c r="D989" s="2"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="C990" s="1"/>
-      <c r="D990" s="1"/>
+      <c r="C990" s="2"/>
+      <c r="D990" s="2"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="C991" s="1"/>
-      <c r="D991" s="1"/>
+      <c r="C991" s="2"/>
+      <c r="D991" s="2"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="C992" s="1"/>
-      <c r="D992" s="1"/>
+      <c r="C992" s="2"/>
+      <c r="D992" s="2"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="C993" s="1"/>
-      <c r="D993" s="1"/>
+      <c r="C993" s="2"/>
+      <c r="D993" s="2"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="C994" s="1"/>
-      <c r="D994" s="1"/>
+      <c r="C994" s="2"/>
+      <c r="D994" s="2"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
+      <c r="C995" s="2"/>
+      <c r="D995" s="2"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
+      <c r="C996" s="2"/>
+      <c r="D996" s="2"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
+      <c r="C997" s="2"/>
+      <c r="D997" s="2"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
+      <c r="C998" s="2"/>
+      <c r="D998" s="2"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
+      <c r="C999" s="2"/>
+      <c r="D999" s="2"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
+      <c r="C1000" s="2"/>
+      <c r="D1000" s="2"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="C1001" s="1"/>
-      <c r="D1001" s="1"/>
+      <c r="C1001" s="2"/>
+      <c r="D1001" s="2"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
-      <c r="C1002" s="1"/>
-      <c r="D1002" s="1"/>
+      <c r="C1002" s="2"/>
+      <c r="D1002" s="2"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
-      <c r="C1003" s="1"/>
-      <c r="D1003" s="1"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
-      <c r="C1004" s="1"/>
-      <c r="D1004" s="1"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
-      <c r="C1005" s="1"/>
-      <c r="D1005" s="1"/>
+      <c r="C1005" s="2"/>
+      <c r="D1005" s="2"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
-      <c r="C1006" s="1"/>
-      <c r="D1006" s="1"/>
+      <c r="C1006" s="2"/>
+      <c r="D1006" s="2"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
-      <c r="C1007" s="1"/>
-      <c r="D1007" s="1"/>
+      <c r="C1007" s="2"/>
+      <c r="D1007" s="2"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
-      <c r="C1008" s="1"/>
-      <c r="D1008" s="1"/>
+      <c r="C1008" s="2"/>
+      <c r="D1008" s="2"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
-      <c r="C1009" s="1"/>
-      <c r="D1009" s="1"/>
+      <c r="C1009" s="2"/>
+      <c r="D1009" s="2"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
-      <c r="C1010" s="1"/>
-      <c r="D1010" s="1"/>
+      <c r="C1010" s="2"/>
+      <c r="D1010" s="2"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
-      <c r="C1011" s="1"/>
-      <c r="D1011" s="1"/>
+      <c r="C1011" s="2"/>
+      <c r="D1011" s="2"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
-      <c r="C1012" s="1"/>
-      <c r="D1012" s="1"/>
+      <c r="C1012" s="2"/>
+      <c r="D1012" s="2"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
-      <c r="C1013" s="1"/>
-      <c r="D1013" s="1"/>
+      <c r="C1013" s="2"/>
+      <c r="D1013" s="2"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
-      <c r="C1014" s="1"/>
-      <c r="D1014" s="1"/>
+      <c r="C1014" s="2"/>
+      <c r="D1014" s="2"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
-      <c r="C1015" s="1"/>
-      <c r="D1015" s="1"/>
+      <c r="C1015" s="2"/>
+      <c r="D1015" s="2"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
-      <c r="C1016" s="1"/>
-      <c r="D1016" s="1"/>
+      <c r="C1016" s="2"/>
+      <c r="D1016" s="2"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
-      <c r="C1017" s="1"/>
-      <c r="D1017" s="1"/>
+      <c r="C1017" s="2"/>
+      <c r="D1017" s="2"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
-      <c r="C1018" s="1"/>
-      <c r="D1018" s="1"/>
+      <c r="C1018" s="2"/>
+      <c r="D1018" s="2"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
-      <c r="C1019" s="1"/>
-      <c r="D1019" s="1"/>
+      <c r="C1019" s="2"/>
+      <c r="D1019" s="2"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
-      <c r="C1020" s="1"/>
-      <c r="D1020" s="1"/>
+      <c r="C1020" s="2"/>
+      <c r="D1020" s="2"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
-      <c r="C1021" s="1"/>
-      <c r="D1021" s="1"/>
+      <c r="C1021" s="2"/>
+      <c r="D1021" s="2"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
-      <c r="C1022" s="1"/>
-      <c r="D1022" s="1"/>
+      <c r="C1022" s="2"/>
+      <c r="D1022" s="2"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
-      <c r="C1023" s="1"/>
-      <c r="D1023" s="1"/>
+      <c r="C1023" s="2"/>
+      <c r="D1023" s="2"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
-      <c r="C1024" s="1"/>
-      <c r="D1024" s="1"/>
+      <c r="C1024" s="2"/>
+      <c r="D1024" s="2"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
-      <c r="C1025" s="1"/>
-      <c r="D1025" s="1"/>
+      <c r="C1025" s="2"/>
+      <c r="D1025" s="2"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1">
-      <c r="C1026" s="1"/>
-      <c r="D1026" s="1"/>
+      <c r="C1026" s="2"/>
+      <c r="D1026" s="2"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1">
-      <c r="C1027" s="1"/>
-      <c r="D1027" s="1"/>
+      <c r="C1027" s="2"/>
+      <c r="D1027" s="2"/>
     </row>
     <row r="1028" ht="12.75" customHeight="1">
-      <c r="C1028" s="1"/>
-      <c r="D1028" s="1"/>
+      <c r="C1028" s="2"/>
+      <c r="D1028" s="2"/>
     </row>
     <row r="1029" ht="12.75" customHeight="1">
-      <c r="C1029" s="1"/>
-      <c r="D1029" s="1"/>
+      <c r="C1029" s="2"/>
+      <c r="D1029" s="2"/>
     </row>
     <row r="1030" ht="12.75" customHeight="1">
-      <c r="C1030" s="1"/>
-      <c r="D1030" s="1"/>
+      <c r="C1030" s="2"/>
+      <c r="D1030" s="2"/>
     </row>
     <row r="1031" ht="12.75" customHeight="1">
-      <c r="C1031" s="1"/>
-      <c r="D1031" s="1"/>
+      <c r="C1031" s="2"/>
+      <c r="D1031" s="2"/>
     </row>
     <row r="1032" ht="12.75" customHeight="1">
-      <c r="C1032" s="1"/>
-      <c r="D1032" s="1"/>
+      <c r="C1032" s="2"/>
+      <c r="D1032" s="2"/>
     </row>
     <row r="1033" ht="12.75" customHeight="1">
-      <c r="C1033" s="1"/>
-      <c r="D1033" s="1"/>
+      <c r="C1033" s="2"/>
+      <c r="D1033" s="2"/>
     </row>
     <row r="1034" ht="12.75" customHeight="1">
-      <c r="C1034" s="1"/>
-      <c r="D1034" s="1"/>
+      <c r="C1034" s="2"/>
+      <c r="D1034" s="2"/>
     </row>
     <row r="1035" ht="12.75" customHeight="1">
-      <c r="C1035" s="1"/>
-      <c r="D1035" s="1"/>
+      <c r="C1035" s="2"/>
+      <c r="D1035" s="2"/>
     </row>
     <row r="1036" ht="12.75" customHeight="1">
-      <c r="C1036" s="1"/>
-      <c r="D1036" s="1"/>
+      <c r="C1036" s="2"/>
+      <c r="D1036" s="2"/>
     </row>
     <row r="1037" ht="12.75" customHeight="1">
-      <c r="C1037" s="1"/>
-      <c r="D1037" s="1"/>
+      <c r="C1037" s="2"/>
+      <c r="D1037" s="2"/>
     </row>
     <row r="1038" ht="12.75" customHeight="1">
-      <c r="C1038" s="1"/>
-      <c r="D1038" s="1"/>
+      <c r="C1038" s="2"/>
+      <c r="D1038" s="2"/>
     </row>
     <row r="1039" ht="12.75" customHeight="1">
-      <c r="C1039" s="1"/>
-      <c r="D1039" s="1"/>
+      <c r="C1039" s="2"/>
+      <c r="D1039" s="2"/>
     </row>
     <row r="1040" ht="12.75" customHeight="1">
-      <c r="C1040" s="1"/>
-      <c r="D1040" s="1"/>
+      <c r="C1040" s="2"/>
+      <c r="D1040" s="2"/>
     </row>
     <row r="1041" ht="12.75" customHeight="1">
-      <c r="C1041" s="1"/>
-      <c r="D1041" s="1"/>
+      <c r="C1041" s="2"/>
+      <c r="D1041" s="2"/>
     </row>
     <row r="1042" ht="12.75" customHeight="1">
-      <c r="C1042" s="1"/>
-      <c r="D1042" s="1"/>
+      <c r="C1042" s="2"/>
+      <c r="D1042" s="2"/>
     </row>
     <row r="1043" ht="12.75" customHeight="1">
-      <c r="C1043" s="1"/>
-      <c r="D1043" s="1"/>
+      <c r="C1043" s="2"/>
+      <c r="D1043" s="2"/>
     </row>
     <row r="1044" ht="12.75" customHeight="1">
-      <c r="C1044" s="1"/>
-      <c r="D1044" s="1"/>
+      <c r="C1044" s="2"/>
+      <c r="D1044" s="2"/>
     </row>
     <row r="1045" ht="12.75" customHeight="1">
-      <c r="C1045" s="1"/>
-      <c r="D1045" s="1"/>
+      <c r="C1045" s="2"/>
+      <c r="D1045" s="2"/>
     </row>
     <row r="1046" ht="12.75" customHeight="1">
-      <c r="C1046" s="1"/>
-      <c r="D1046" s="1"/>
+      <c r="C1046" s="2"/>
+      <c r="D1046" s="2"/>
     </row>
     <row r="1047" ht="12.75" customHeight="1">
-      <c r="C1047" s="1"/>
-      <c r="D1047" s="1"/>
+      <c r="C1047" s="2"/>
+      <c r="D1047" s="2"/>
     </row>
     <row r="1048" ht="12.75" customHeight="1">
-      <c r="C1048" s="1"/>
-      <c r="D1048" s="1"/>
+      <c r="C1048" s="2"/>
+      <c r="D1048" s="2"/>
     </row>
     <row r="1049" ht="12.75" customHeight="1">
-      <c r="C1049" s="1"/>
-      <c r="D1049" s="1"/>
+      <c r="C1049" s="2"/>
+      <c r="D1049" s="2"/>
     </row>
     <row r="1050" ht="12.75" customHeight="1">
-      <c r="C1050" s="1"/>
-      <c r="D1050" s="1"/>
+      <c r="C1050" s="2"/>
+      <c r="D1050" s="2"/>
     </row>
     <row r="1051" ht="12.75" customHeight="1">
-      <c r="C1051" s="1"/>
-      <c r="D1051" s="1"/>
+      <c r="C1051" s="2"/>
+      <c r="D1051" s="2"/>
     </row>
     <row r="1052" ht="12.75" customHeight="1">
-      <c r="C1052" s="1"/>
-      <c r="D1052" s="1"/>
+      <c r="C1052" s="2"/>
+      <c r="D1052" s="2"/>
+    </row>
+    <row r="1053" ht="12.75" customHeight="1">
+      <c r="C1053" s="2"/>
+      <c r="D1053" s="2"/>
+    </row>
+    <row r="1054" ht="12.75" customHeight="1">
+      <c r="C1054" s="2"/>
+      <c r="D1054" s="2"/>
+    </row>
+    <row r="1055" ht="12.75" customHeight="1">
+      <c r="C1055" s="2"/>
+      <c r="D1055" s="2"/>
+    </row>
+    <row r="1056" ht="12.75" customHeight="1">
+      <c r="C1056" s="2"/>
+      <c r="D1056" s="2"/>
+    </row>
+    <row r="1057" ht="12.75" customHeight="1">
+      <c r="C1057" s="2"/>
+      <c r="D1057" s="2"/>
+    </row>
+    <row r="1058" ht="12.75" customHeight="1">
+      <c r="C1058" s="2"/>
+      <c r="D1058" s="2"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -6335,192 +6540,193 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="34.0"/>
+    <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="3" width="43.71"/>
     <col customWidth="1" min="4" max="6" width="14.43"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>91</v>
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>95</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>99</v>
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>104</v>
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>108</v>
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>111</v>
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7532,40 +7738,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>74</v>
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="6">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>83</v>
+      <c r="D2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -15,15 +15,33 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="295">
   <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t>Referral Follow-up</t>
+  </si>
+  <si>
     <t>list_name</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>form_title</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -33,51 +51,87 @@
     <t>label::sw</t>
   </si>
   <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
   </si>
   <si>
     <t>yes_no</t>
   </si>
   <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>instance_name</t>
-  </si>
-  <si>
     <t>Ndiyo</t>
   </si>
   <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>./source = 'user'</t>
+  </si>
+  <si>
     <t>no</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
+    <t>pages</t>
+  </si>
+  <si>
     <t>Hapana</t>
   </si>
   <si>
-    <t>Referral Follow-up</t>
-  </si>
-  <si>
     <t>reason_didnt_go</t>
   </si>
   <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
     <t>no_money</t>
   </si>
   <si>
@@ -93,9 +147,21 @@
     <t>I did not want to go</t>
   </si>
   <si>
+    <t>hidden</t>
+  </si>
+  <si>
     <t>Sikutaka kwenda</t>
   </si>
   <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>source_form</t>
+  </si>
+  <si>
     <t>no_permission</t>
   </si>
   <si>
@@ -105,78 +171,39 @@
     <t>Sikupewa ruhusa ya kwenda</t>
   </si>
   <si>
+    <t xml:space="preserve">string </t>
+  </si>
+  <si>
     <t>other</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>relevant</t>
-  </si>
-  <si>
     <t>Nyenginezo</t>
   </si>
   <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
+    <t>original_source_form</t>
   </si>
   <si>
     <t>reason_didnt_get_svc</t>
   </si>
   <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>./source = 'user'</t>
-  </si>
-  <si>
     <t>too_many_people</t>
   </si>
   <si>
+    <t>source_id</t>
+  </si>
+  <si>
     <t>There were too many people</t>
   </si>
   <si>
     <t>Kulikuwa na watu wengi</t>
   </si>
   <si>
+    <t>last_visit_date</t>
+  </si>
+  <si>
     <t>services_not_offered</t>
   </si>
   <si>
@@ -186,15 +213,24 @@
     <t>Huduma nilizotaka hazikuwepo.</t>
   </si>
   <si>
+    <t>refer_flag_small_baby</t>
+  </si>
+  <si>
     <t>no_service_provider_available</t>
   </si>
   <si>
+    <t>refer_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
     <t>No service providers were available</t>
   </si>
   <si>
     <t>Hakukuwa na mtoa huduma</t>
   </si>
   <si>
+    <t>refer_secondary_neonatal_danger_sign_flag</t>
+  </si>
+  <si>
     <t>was_asked_to_pay</t>
   </si>
   <si>
@@ -204,55 +240,19 @@
     <t>Walitaka nilipie huduma</t>
   </si>
   <si>
+    <t>refer_child_danger_sign_flag</t>
+  </si>
+  <si>
     <t>was_treated_badly</t>
   </si>
   <si>
+    <t>refer_child_other_danger_sign_flag</t>
+  </si>
+  <si>
     <t>Health workers treated me badly</t>
   </si>
   <si>
     <t>Wahudumu wa afya hawakunihudumia vizuri</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>source_form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string </t>
-  </si>
-  <si>
-    <t>original_source_form</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
-    <t>last_visit_date</t>
-  </si>
-  <si>
-    <t>refer_flag_small_baby</t>
-  </si>
-  <si>
-    <t>refer_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_secondary_neonatal_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_child_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>refer_child_other_danger_sign_flag</t>
   </si>
   <si>
     <t>refer_muac_flag</t>
@@ -991,15 +991,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1074,345 +1074,345 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="F2" s="5" t="s">
-        <v>50</v>
+      <c r="F2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>49</v>
+      <c r="A4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>68</v>
+      <c r="A9" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>49</v>
+      <c r="A11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>49</v>
+      <c r="C18" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
+      <c r="C19" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>49</v>
+      <c r="C20" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>49</v>
+      <c r="C21" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>49</v>
+      <c r="C22" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
+      <c r="C23" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>93</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>95</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>97</v>
@@ -1458,13 +1458,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -1476,7 +1476,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D30" s="2"/>
       <c r="G30" s="2" t="s">
@@ -1485,37 +1485,37 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -1534,7 +1534,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1566,15 +1566,15 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="6" t="s">
         <v>110</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="L38" s="3" t="s">
+      <c r="L38" s="6" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1621,8 +1621,8 @@
       <c r="A42" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>75</v>
+      <c r="B42" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1635,7 +1635,7 @@
         <v>105</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1648,11 +1648,11 @@
         <v>105</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="L44" s="3" t="s">
+      <c r="L44" s="6" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
         <v>105</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -1670,15 +1670,15 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>79</v>
+      <c r="B46" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="L46" s="3" t="s">
+      <c r="L46" s="6" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1761,49 +1761,49 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="6" t="s">
         <v>130</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
-      <c r="L53" s="3" t="s">
+      <c r="L53" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="9"/>
-      <c r="L54" s="3" t="s">
+      <c r="L54" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>133</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
-      <c r="L55" s="3" t="s">
+      <c r="L55" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C56" s="8"/>
@@ -1813,10 +1813,10 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C57" s="8"/>
@@ -1826,10 +1826,10 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C58" s="8"/>
@@ -1839,10 +1839,10 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C59" s="8"/>
@@ -1852,10 +1852,10 @@
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C60" s="8"/>
@@ -1865,10 +1865,10 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C61" s="8"/>
@@ -1878,10 +1878,10 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="6" t="s">
         <v>141</v>
       </c>
       <c r="C62" s="8"/>
@@ -1891,10 +1891,10 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="6" t="s">
         <v>143</v>
       </c>
       <c r="C63" s="8"/>
@@ -1904,10 +1904,10 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="6" t="s">
         <v>145</v>
       </c>
       <c r="C64" s="8"/>
@@ -1917,7 +1917,7 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B65" s="13" t="s">
@@ -1930,7 +1930,7 @@
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B66" s="14" t="s">
@@ -1943,7 +1943,7 @@
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -1956,7 +1956,7 @@
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B68" s="14" t="s">
@@ -1969,7 +1969,7 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B69" s="14" t="s">
@@ -2065,10 +2065,10 @@
       <c r="S72" s="19"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="A73" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>166</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -2077,71 +2077,71 @@
       <c r="D73" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="6" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="6" t="s">
         <v>166</v>
       </c>
       <c r="C78" s="2"/>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>182</v>
@@ -2160,7 +2160,7 @@
       <c r="D79" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="6" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       <c r="D81" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="6" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2213,19 +2213,19 @@
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="6" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2247,19 +2247,19 @@
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="6" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2332,92 +2332,92 @@
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="6" t="s">
         <v>225</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="5" t="s">
+      <c r="F90" s="4" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="6" t="s">
         <v>229</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="6" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D92" s="4" t="s">
         <v>233</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D93" s="4" t="s">
         <v>237</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="6" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D94" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="5" t="s">
+      <c r="F94" s="4" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2435,18 +2435,18 @@
         <v>246</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>247</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -2483,7 +2483,7 @@
         <v>254</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -2501,7 +2501,7 @@
         <v>258</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>259</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
@@ -2557,7 +2557,7 @@
         <v>265</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>266</v>
@@ -2566,7 +2566,7 @@
         <v>267</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -2596,13 +2596,13 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>271</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
@@ -2624,7 +2624,7 @@
         <v>275</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
@@ -2691,7 +2691,7 @@
         <v>98</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -2700,7 +2700,7 @@
       <c r="A113" t="s">
         <v>105</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="6" t="s">
         <v>286</v>
       </c>
       <c r="C113" s="2"/>
@@ -2710,41 +2710,41 @@
       </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="6" t="s">
         <v>288</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="L114" s="3" t="s">
+      <c r="L114" s="6" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="6" t="s">
         <v>290</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="L115" s="5" t="s">
+      <c r="L115" s="4" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="6" t="s">
         <v>292</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
-      <c r="L116" s="3" t="s">
+      <c r="L116" s="6" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6549,184 +6549,184 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="A8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D13" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7739,39 +7739,39 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="4">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3">
         <v>43584.0</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>72</v>
+      <c r="D2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -15,12 +15,27 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="295">
   <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>form_title</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label::en</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
+    <t>label::sw</t>
+  </si>
+  <si>
     <t>version</t>
   </si>
   <si>
@@ -33,22 +48,52 @@
     <t>instance_name</t>
   </si>
   <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Referral Follow-up</t>
   </si>
   <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label::en</t>
-  </si>
-  <si>
-    <t>label::sw</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>referral_follow_up</t>
+  </si>
+  <si>
+    <t>Ndiyo</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Hapana</t>
+  </si>
+  <si>
+    <t>reason_didnt_go</t>
+  </si>
+  <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t>I have no money</t>
+  </si>
+  <si>
+    <t>Sina pesa</t>
+  </si>
+  <si>
+    <t>did_not_want</t>
+  </si>
+  <si>
+    <t>I did not want to go</t>
+  </si>
+  <si>
+    <t>Sikutaka kwenda</t>
   </si>
   <si>
     <t>required</t>
@@ -57,24 +102,42 @@
     <t>relevant</t>
   </si>
   <si>
+    <t>no_permission</t>
+  </si>
+  <si>
     <t>appearance</t>
   </si>
   <si>
+    <t>I did not have permission to go</t>
+  </si>
+  <si>
+    <t>Sikupewa ruhusa ya kwenda</t>
+  </si>
+  <si>
     <t>read_only</t>
   </si>
   <si>
     <t>constraint</t>
   </si>
   <si>
+    <t>other</t>
+  </si>
+  <si>
     <t>constraint_message::en</t>
   </si>
   <si>
     <t>constraint_message::sw</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>calculation</t>
   </si>
   <si>
+    <t>Nyenginezo</t>
+  </si>
+  <si>
     <t>choice_filter</t>
   </si>
   <si>
@@ -84,25 +147,13 @@
     <t>hint::sw</t>
   </si>
   <si>
-    <t>yes_no</t>
-  </si>
-  <si>
     <t>default</t>
   </si>
   <si>
     <t>repeat_count</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>referral_follow_up</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Ndiyo</t>
+    <t>reason_didnt_get_svc</t>
   </si>
   <si>
     <t>begin group</t>
@@ -117,142 +168,91 @@
     <t>./source = 'user'</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>pages</t>
   </si>
   <si>
-    <t>Hapana</t>
-  </si>
-  <si>
-    <t>reason_didnt_go</t>
-  </si>
-  <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t>I have no money</t>
-  </si>
-  <si>
-    <t>Sina pesa</t>
-  </si>
-  <si>
-    <t>did_not_want</t>
-  </si>
-  <si>
-    <t>I did not want to go</t>
+    <t>too_many_people</t>
+  </si>
+  <si>
+    <t>There were too many people</t>
+  </si>
+  <si>
+    <t>Kulikuwa na watu wengi</t>
+  </si>
+  <si>
+    <t>services_not_offered</t>
+  </si>
+  <si>
+    <t>The services I needed were not offered when I went</t>
+  </si>
+  <si>
+    <t>Huduma nilizotaka hazikuwepo.</t>
+  </si>
+  <si>
+    <t>no_service_provider_available</t>
+  </si>
+  <si>
+    <t>No service providers were available</t>
+  </si>
+  <si>
+    <t>Hakukuwa na mtoa huduma</t>
+  </si>
+  <si>
+    <t>was_asked_to_pay</t>
+  </si>
+  <si>
+    <t>I was asked to pay for services</t>
+  </si>
+  <si>
+    <t>Walitaka nilipie huduma</t>
+  </si>
+  <si>
+    <t>was_treated_badly</t>
+  </si>
+  <si>
+    <t>Health workers treated me badly</t>
+  </si>
+  <si>
+    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
+  </si>
+  <si>
+    <t>data</t>
   </si>
   <si>
     <t>hidden</t>
   </si>
   <si>
-    <t>Sikutaka kwenda</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
     <t>source_form</t>
   </si>
   <si>
-    <t>no_permission</t>
-  </si>
-  <si>
-    <t>I did not have permission to go</t>
-  </si>
-  <si>
-    <t>Sikupewa ruhusa ya kwenda</t>
-  </si>
-  <si>
     <t xml:space="preserve">string </t>
   </si>
   <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Nyenginezo</t>
-  </si>
-  <si>
     <t>original_source_form</t>
   </si>
   <si>
-    <t>reason_didnt_get_svc</t>
-  </si>
-  <si>
-    <t>too_many_people</t>
-  </si>
-  <si>
     <t>source_id</t>
   </si>
   <si>
-    <t>There were too many people</t>
-  </si>
-  <si>
-    <t>Kulikuwa na watu wengi</t>
-  </si>
-  <si>
     <t>last_visit_date</t>
   </si>
   <si>
-    <t>services_not_offered</t>
-  </si>
-  <si>
-    <t>The services I needed were not offered when I went</t>
-  </si>
-  <si>
-    <t>Huduma nilizotaka hazikuwepo.</t>
-  </si>
-  <si>
     <t>refer_flag_small_baby</t>
   </si>
   <si>
-    <t>no_service_provider_available</t>
-  </si>
-  <si>
     <t>refer_neonatal_danger_sign_flag</t>
   </si>
   <si>
-    <t>No service providers were available</t>
-  </si>
-  <si>
-    <t>Hakukuwa na mtoa huduma</t>
-  </si>
-  <si>
     <t>refer_secondary_neonatal_danger_sign_flag</t>
   </si>
   <si>
-    <t>was_asked_to_pay</t>
-  </si>
-  <si>
-    <t>I was asked to pay for services</t>
-  </si>
-  <si>
-    <t>Walitaka nilipie huduma</t>
-  </si>
-  <si>
     <t>refer_child_danger_sign_flag</t>
   </si>
   <si>
-    <t>was_treated_badly</t>
-  </si>
-  <si>
     <t>refer_child_other_danger_sign_flag</t>
-  </si>
-  <si>
-    <t>Health workers treated me badly</t>
-  </si>
-  <si>
-    <t>Wahudumu wa afya hawakunihudumia vizuri</t>
   </si>
   <si>
     <t>refer_muac_flag</t>
@@ -511,7 +511,8 @@
 •        Avoid group gatherings.
 •        Provide the service at the open space and if it should be inside, make sure the windows and doors are open. 
 •        Cover your mouth with a towel or elbow when you sneeze or cough. 
-•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.
+•        Please remember to do the covid education visit before or after submitting this form. &lt;/span&gt;  
 </t>
   </si>
   <si>
@@ -522,7 +523,8 @@
 •        Epuka mikusanyiko. 
 •        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
 •        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
-•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
+•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.
+•        Tafadhali kumbuka kufungua fomu ya kuwaelimsiha wanakaya juu ya maambukizi ya korona na jinsi ya kuchukua tahadhari. Tembeleo kuhusu korona unaweza kulifanya kabla ya kuanza tembeleo lako au mara baada ya kumaliza tembeleo lako hili.&lt;/span&gt;
 </t>
   </si>
   <si>
@@ -941,11 +943,11 @@
     </font>
     <font/>
     <font>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -985,36 +987,36 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1023,20 +1025,23 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1074,345 +1079,345 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="F2" s="4" t="s">
-        <v>33</v>
+      <c r="F2" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>32</v>
+      <c r="A4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>47</v>
+      <c r="A9" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>32</v>
+      <c r="A11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>32</v>
+      <c r="C18" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>32</v>
+      <c r="C19" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>32</v>
+      <c r="C20" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>32</v>
+      <c r="C21" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>32</v>
+      <c r="C22" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>32</v>
+      <c r="C23" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>93</v>
@@ -1424,7 +1429,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>95</v>
@@ -1436,10 +1441,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>97</v>
@@ -1458,13 +1463,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -1476,7 +1481,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D30" s="2"/>
       <c r="G30" s="2" t="s">
@@ -1485,37 +1490,37 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -1534,7 +1539,7 @@
         <v>98</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1566,15 +1571,15 @@
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="4" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1621,8 +1626,8 @@
       <c r="A42" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>66</v>
+      <c r="B42" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -1635,7 +1640,7 @@
         <v>105</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1648,11 +1653,11 @@
         <v>105</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="4" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1661,7 +1666,7 @@
         <v>105</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -1670,15 +1675,15 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>77</v>
+      <c r="B46" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="L46" s="6" t="s">
+      <c r="L46" s="4" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1761,49 +1766,49 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="9"/>
-      <c r="L53" s="6" t="s">
+      <c r="L53" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="9"/>
-      <c r="L54" s="6" t="s">
+      <c r="L54" s="4" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
-      <c r="L55" s="6" t="s">
+      <c r="L55" s="4" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C56" s="8"/>
@@ -1813,10 +1818,10 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C57" s="8"/>
@@ -1826,10 +1831,10 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C58" s="8"/>
@@ -1839,10 +1844,10 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C59" s="8"/>
@@ -1852,10 +1857,10 @@
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C60" s="8"/>
@@ -1865,10 +1870,10 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C61" s="8"/>
@@ -1878,10 +1883,10 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="4" t="s">
         <v>141</v>
       </c>
       <c r="C62" s="8"/>
@@ -1891,10 +1896,10 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C63" s="8"/>
@@ -1904,10 +1909,10 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="4" t="s">
         <v>145</v>
       </c>
       <c r="C64" s="8"/>
@@ -1917,7 +1922,7 @@
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B65" s="13" t="s">
@@ -1930,7 +1935,7 @@
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B66" s="14" t="s">
@@ -1943,7 +1948,7 @@
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B67" s="14" t="s">
@@ -1956,7 +1961,7 @@
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B68" s="14" t="s">
@@ -1969,7 +1974,7 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B69" s="14" t="s">
@@ -2017,10 +2022,10 @@
       <c r="B71" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="20" t="s">
         <v>164</v>
       </c>
       <c r="E71" s="19"/>
@@ -2065,10 +2070,10 @@
       <c r="S72" s="19"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C73" s="8" t="s">
@@ -2077,71 +2082,71 @@
       <c r="D73" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="G73" s="6" t="s">
+      <c r="G73" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="4" t="s">
         <v>166</v>
       </c>
       <c r="C78" s="2"/>
@@ -2149,10 +2154,10 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>182</v>
@@ -2160,7 +2165,7 @@
       <c r="D79" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" s="4" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2191,7 +2196,7 @@
       <c r="D81" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="4" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2213,19 +2218,19 @@
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="4" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2247,19 +2252,19 @@
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="4" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2332,92 +2337,92 @@
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="4" t="s">
         <v>225</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="6" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="D91" s="4" t="s">
         <v>229</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="4" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="6" t="s">
         <v>233</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="6" t="s">
         <v>237</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="6" t="s">
         <v>241</v>
       </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="6" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2435,18 +2440,18 @@
         <v>246</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>247</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
@@ -2483,7 +2488,7 @@
         <v>254</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -2501,7 +2506,7 @@
         <v>258</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>259</v>
@@ -2538,13 +2543,13 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>263</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
@@ -2557,7 +2562,7 @@
         <v>265</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>266</v>
@@ -2566,7 +2571,7 @@
         <v>267</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -2596,13 +2601,13 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>271</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
@@ -2624,7 +2629,7 @@
         <v>275</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
@@ -2691,7 +2696,7 @@
         <v>98</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -2700,7 +2705,7 @@
       <c r="A113" t="s">
         <v>105</v>
       </c>
-      <c r="B113" s="6" t="s">
+      <c r="B113" s="4" t="s">
         <v>286</v>
       </c>
       <c r="C113" s="2"/>
@@ -2710,41 +2715,41 @@
       </c>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="4" t="s">
         <v>288</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="L114" s="6" t="s">
+      <c r="L114" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="4" t="s">
         <v>290</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="L115" s="4" t="s">
+      <c r="L115" s="6" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
-      <c r="L116" s="6" t="s">
+      <c r="L116" s="4" t="s">
         <v>293</v>
       </c>
     </row>
@@ -6549,184 +6554,184 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="C9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="6" t="s">
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="6" t="s">
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="C11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="6" t="s">
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>79</v>
+      <c r="D12" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>54</v>
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7739,39 +7744,39 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3">
         <v>43584.0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="299">
   <si>
     <t>type</t>
   </si>
@@ -796,6 +796,12 @@
   </si>
   <si>
     <t xml:space="preserve">../inputs/refer_flag_postpartum_danger_signs = 1 or ../inputs/refer_flag_postpartum_other_signs = 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_pregnancy_counselling_referral </t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1</t>
   </si>
   <si>
     <t>referral_days</t>
@@ -1082,7 +1088,9 @@
     <col customWidth="1" min="1" max="1" width="40.0"/>
     <col customWidth="1" min="2" max="2" width="43.57"/>
     <col customWidth="1" min="3" max="3" width="37.29"/>
-    <col customWidth="1" min="4" max="17" width="14.43"/>
+    <col customWidth="1" min="4" max="5" width="14.43"/>
+    <col customWidth="1" min="6" max="6" width="91.0"/>
+    <col customWidth="1" min="7" max="17" width="14.43"/>
     <col customWidth="1" min="18" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -2827,21 +2835,30 @@
       </c>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="3" t="s">
         <v>252</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
-      <c r="L119">
-        <v>3.0</v>
+      <c r="L119" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="120" ht="12.75" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
+      <c r="L120">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="C121" s="1"/>
@@ -6602,6 +6619,10 @@
     <row r="1060" ht="12.75" customHeight="1">
       <c r="C1060" s="1"/>
       <c r="D1060" s="1"/>
+    </row>
+    <row r="1061" ht="12.75" customHeight="1">
+      <c r="C1061" s="1"/>
+      <c r="D1061" s="1"/>
     </row>
   </sheetData>
   <printOptions/>
@@ -6627,7 +6648,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>1</v>
@@ -6641,30 +6662,30 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>203</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -6672,13 +6693,13 @@
         <v>223</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -6686,13 +6707,13 @@
         <v>223</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -6700,13 +6721,13 @@
         <v>223</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -6714,97 +6735,97 @@
         <v>223</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1"/>
@@ -7817,27 +7838,27 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
         <v>137</v>
@@ -7846,10 +7867,10 @@
         <v>43584.0</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20376"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314ACE0B-493E-49E8-8E84-6B4C3FE9A041}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -186,9 +195,6 @@
     <t>sex</t>
   </si>
   <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
@@ -265,9 +271,6 @@
   </si>
   <si>
     <t>client_date_of_birth</t>
-  </si>
-  <si>
-    <t>../inputs/contact/date_of_birth</t>
   </si>
   <si>
     <t>../inputs/due_date</t>
@@ -938,36 +941,53 @@
   <si>
     <t>data</t>
   </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>../inputs/contact/dob</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -975,7 +995,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -991,110 +1011,374 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
+      <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z1061"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.0"/>
-    <col customWidth="1" min="2" max="2" width="43.57"/>
-    <col customWidth="1" min="3" max="3" width="37.29"/>
-    <col customWidth="1" min="4" max="5" width="14.43"/>
-    <col customWidth="1" min="6" max="6" width="91.0"/>
-    <col customWidth="1" min="7" max="17" width="14.43"/>
-    <col customWidth="1" min="18" max="26" width="8.71"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" customWidth="1"/>
+    <col min="4" max="5" width="14.40625" customWidth="1"/>
+    <col min="6" max="6" width="91" customWidth="1"/>
+    <col min="7" max="17" width="14.40625" customWidth="1"/>
+    <col min="18" max="26" width="8.6796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1147,7 +1431,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1165,7 +1449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1178,7 +1462,7 @@
       <c r="D3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -1191,7 +1475,7 @@
       <c r="D4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1204,7 +1488,7 @@
       <c r="D5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1216,7 +1500,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1228,7 +1512,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -1240,7 +1524,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
@@ -1252,7 +1536,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1264,7 +1548,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1276,7 +1560,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1288,7 +1572,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1300,7 +1584,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1312,7 +1596,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1324,7 +1608,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1336,7 +1620,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1348,7 +1632,7 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -1360,7 +1644,7 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1372,7 +1656,7 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -1384,7 +1668,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1396,7 +1680,7 @@
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -1408,7 +1692,7 @@
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
@@ -1420,7 +1704,7 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1432,7 +1716,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>22</v>
       </c>
@@ -1444,7 +1728,7 @@
       </c>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>22</v>
       </c>
@@ -1456,7 +1740,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1468,7 +1752,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
@@ -1478,7 +1762,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>17</v>
       </c>
@@ -1490,7 +1774,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
@@ -1505,7 +1789,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>22</v>
       </c>
@@ -1517,7 +1801,7 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
@@ -1529,19 +1813,19 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:12" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>57</v>
+        <v>297</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>51</v>
       </c>
@@ -1551,7 +1835,7 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -1561,87 +1845,87 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:12" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="L36" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="L37" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="L38" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="L39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="L40" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="L41" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>28</v>
@@ -1649,12 +1933,12 @@
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="L42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>29</v>
@@ -1662,12 +1946,12 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="L43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>30</v>
@@ -1675,12 +1959,12 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="L44" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>31</v>
@@ -1688,12 +1972,12 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="L45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>32</v>
@@ -1701,12 +1985,12 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="L46" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>33</v>
@@ -1714,12 +1998,12 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="L47" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>34</v>
@@ -1727,12 +2011,12 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="L48" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>35</v>
@@ -1740,12 +2024,12 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="L49" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>36</v>
@@ -1753,51 +2037,51 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="L50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="L51" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="L52" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="6"/>
       <c r="L53" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>37</v>
@@ -1805,25 +2089,25 @@
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="L54" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
       <c r="L55" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -1831,12 +2115,12 @@
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
       <c r="L56" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>40</v>
@@ -1844,12 +2128,12 @@
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
       <c r="L57" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>41</v>
@@ -1857,12 +2141,12 @@
       <c r="C58" s="5"/>
       <c r="D58" s="6"/>
       <c r="L58" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>42</v>
@@ -1870,12 +2154,12 @@
       <c r="C59" s="5"/>
       <c r="D59" s="6"/>
       <c r="L59" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>43</v>
@@ -1883,12 +2167,12 @@
       <c r="C60" s="5"/>
       <c r="D60" s="6"/>
       <c r="L60" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>44</v>
@@ -1896,119 +2180,119 @@
       <c r="C61" s="5"/>
       <c r="D61" s="6"/>
       <c r="L61" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="6"/>
       <c r="L62" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="6"/>
       <c r="L63" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="6"/>
       <c r="L64" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="6"/>
       <c r="L65" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="6"/>
       <c r="L66" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="6"/>
       <c r="L67" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="6"/>
       <c r="L68" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="6"/>
       <c r="L69" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" ht="15.75" customHeight="1">
       <c r="A70" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C70" s="13"/>
       <c r="D70" s="14"/>
@@ -2035,12 +2319,12 @@
       <c r="Y70" s="15"/>
       <c r="Z70" s="15"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1">
       <c r="A71" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C71" s="13"/>
       <c r="D71" s="14"/>
@@ -2067,18 +2351,18 @@
       <c r="Y71" s="15"/>
       <c r="Z71" s="15"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1">
       <c r="A72" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="D72" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>115</v>
       </c>
       <c r="E72" s="15"/>
       <c r="F72" s="15"/>
@@ -2096,18 +2380,18 @@
       <c r="R72" s="15"/>
       <c r="S72" s="15"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1">
       <c r="A73" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="D73" s="18" t="s">
         <v>117</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>119</v>
       </c>
       <c r="E73" s="15"/>
       <c r="F73" s="15"/>
@@ -2125,12 +2409,12 @@
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C74" s="13"/>
       <c r="D74" s="14"/>
@@ -2150,386 +2434,386 @@
       <c r="R74" s="15"/>
       <c r="S74" s="15"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="G75" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="6" t="s">
+    </row>
+    <row r="76" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C76" s="3" t="s">
+    </row>
+    <row r="77" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A77" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C77" s="3" t="s">
+    </row>
+    <row r="78" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C78" s="3" t="s">
+    </row>
+    <row r="79" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A79" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
+    </row>
+    <row r="80" spans="1:26" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="4"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:7" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="G81" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="C82" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B82" s="1" t="s">
+      <c r="D82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C82" s="4" t="s">
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="C83" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B83" s="1" t="s">
+      <c r="D83" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="F83" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D83" s="4" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A84" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="C84" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B84" s="1" t="s">
+      <c r="D84" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="F84" t="s">
         <v>148</v>
       </c>
-      <c r="D84" s="4" t="s">
+    </row>
+    <row r="85" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A85" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F84" t="s">
+      <c r="C85" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="F85" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D85" s="3" t="s">
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="D86" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="F86" t="s">
         <v>156</v>
       </c>
-      <c r="D86" s="4" t="s">
+    </row>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A87" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F86" t="s">
+      <c r="C87" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="F87" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D87" s="3" t="s">
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="C88" s="4" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="D88" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="F88" t="s">
         <v>164</v>
       </c>
-      <c r="D88" s="4" t="s">
+    </row>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F88" t="s">
+      <c r="C89" s="4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="D89" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="F89" t="s">
         <v>168</v>
       </c>
-      <c r="D89" s="4" t="s">
+    </row>
+    <row r="90" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F89" t="s">
+      <c r="C90" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="D90" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="F90" t="s">
         <v>172</v>
       </c>
-      <c r="D90" s="4" t="s">
+    </row>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F90" t="s">
+      <c r="C91" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B91" s="1" t="s">
+      <c r="D91" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="F91" t="s">
         <v>176</v>
       </c>
-      <c r="D91" s="4" t="s">
+    </row>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F91" t="s">
+      <c r="C92" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A93" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B93" s="3" t="s">
+      <c r="D93" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A95" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A96" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="1" t="s">
+      <c r="C97" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="D97" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="E97" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
+    </row>
+    <row r="98" spans="1:12" ht="15.75" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>19</v>
@@ -2537,97 +2821,97 @@
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B99" s="1" t="s">
+      <c r="D99" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A100" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="C100" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="F99" s="1"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="D100" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="E100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A101" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="B101" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F100" s="1"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="4" t="s">
+      <c r="C101" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="D101" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="E101" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D101" s="4" t="s">
+    </row>
+    <row r="102" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B102" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E101" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F101" s="4" t="s">
+      <c r="C102" s="4" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B102" s="4" t="s">
+      <c r="D102" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="F102" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15.75" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:12" ht="15.75" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>19</v>
@@ -2635,57 +2919,57 @@
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="1" t="s">
+      <c r="C105" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="D105" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="E105" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="C106" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B106" s="1" t="s">
+      <c r="D106" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
+    </row>
+    <row r="107" spans="1:12" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:12" ht="15.75" customHeight="1">
       <c r="A108" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>19</v>
@@ -2693,3962 +2977,3958 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="D109" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="E109" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B110" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="C110" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B110" s="4" t="s">
+      <c r="D110" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="F110" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D110" s="1" t="s">
+    </row>
+    <row r="111" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A111" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B111" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="L111" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A112" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B112" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:12" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" ht="12.75" customHeight="1">
+    <row r="115" spans="1:12" ht="12.75" customHeight="1">
       <c r="A115" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="L115" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="116" ht="12.75" customHeight="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="12.75" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="L116" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="117" ht="12.75" customHeight="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="12.75" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="L117" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="118" ht="12.75" customHeight="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="12.75" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="L118" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="119" ht="12.75" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="12.75" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="L119" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="120" ht="12.75" customHeight="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="12.75" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="L120">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="121" ht="12.75" customHeight="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="12.75" customHeight="1">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
     </row>
-    <row r="122" ht="12.75" customHeight="1">
+    <row r="122" spans="1:12" ht="12.75" customHeight="1">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
     </row>
-    <row r="123" ht="12.75" customHeight="1">
+    <row r="123" spans="1:12" ht="12.75" customHeight="1">
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
     </row>
-    <row r="124" ht="12.75" customHeight="1">
+    <row r="124" spans="1:12" ht="12.75" customHeight="1">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
     </row>
-    <row r="125" ht="12.75" customHeight="1">
+    <row r="125" spans="1:12" ht="12.75" customHeight="1">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
     </row>
-    <row r="126" ht="12.75" customHeight="1">
+    <row r="126" spans="1:12" ht="12.75" customHeight="1">
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
     </row>
-    <row r="127" ht="12.75" customHeight="1">
+    <row r="127" spans="1:12" ht="12.75" customHeight="1">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
     </row>
-    <row r="128" ht="12.75" customHeight="1">
+    <row r="128" spans="1:12" ht="12.75" customHeight="1">
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
     </row>
-    <row r="129" ht="12.75" customHeight="1">
+    <row r="129" spans="3:4" ht="12.75" customHeight="1">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
     </row>
-    <row r="130" ht="12.75" customHeight="1">
+    <row r="130" spans="3:4" ht="12.75" customHeight="1">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
     </row>
-    <row r="131" ht="12.75" customHeight="1">
+    <row r="131" spans="3:4" ht="12.75" customHeight="1">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
     </row>
-    <row r="132" ht="12.75" customHeight="1">
+    <row r="132" spans="3:4" ht="12.75" customHeight="1">
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
     </row>
-    <row r="133" ht="12.75" customHeight="1">
+    <row r="133" spans="3:4" ht="12.75" customHeight="1">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
     </row>
-    <row r="134" ht="12.75" customHeight="1">
+    <row r="134" spans="3:4" ht="12.75" customHeight="1">
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
     </row>
-    <row r="135" ht="12.75" customHeight="1">
+    <row r="135" spans="3:4" ht="12.75" customHeight="1">
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
     </row>
-    <row r="136" ht="12.75" customHeight="1">
+    <row r="136" spans="3:4" ht="12.75" customHeight="1">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
     </row>
-    <row r="137" ht="12.75" customHeight="1">
+    <row r="137" spans="3:4" ht="12.75" customHeight="1">
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
     </row>
-    <row r="138" ht="12.75" customHeight="1">
+    <row r="138" spans="3:4" ht="12.75" customHeight="1">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
     </row>
-    <row r="139" ht="12.75" customHeight="1">
+    <row r="139" spans="3:4" ht="12.75" customHeight="1">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
     </row>
-    <row r="140" ht="12.75" customHeight="1">
+    <row r="140" spans="3:4" ht="12.75" customHeight="1">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
     </row>
-    <row r="141" ht="12.75" customHeight="1">
+    <row r="141" spans="3:4" ht="12.75" customHeight="1">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" ht="12.75" customHeight="1">
+    <row r="142" spans="3:4" ht="12.75" customHeight="1">
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
     </row>
-    <row r="143" ht="12.75" customHeight="1">
+    <row r="143" spans="3:4" ht="12.75" customHeight="1">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
     </row>
-    <row r="144" ht="12.75" customHeight="1">
+    <row r="144" spans="3:4" ht="12.75" customHeight="1">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
     </row>
-    <row r="145" ht="12.75" customHeight="1">
+    <row r="145" spans="3:4" ht="12.75" customHeight="1">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
     </row>
-    <row r="146" ht="12.75" customHeight="1">
+    <row r="146" spans="3:4" ht="12.75" customHeight="1">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
     </row>
-    <row r="147" ht="12.75" customHeight="1">
+    <row r="147" spans="3:4" ht="12.75" customHeight="1">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
     </row>
-    <row r="148" ht="12.75" customHeight="1">
+    <row r="148" spans="3:4" ht="12.75" customHeight="1">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
     </row>
-    <row r="149" ht="12.75" customHeight="1">
+    <row r="149" spans="3:4" ht="12.75" customHeight="1">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
     </row>
-    <row r="150" ht="12.75" customHeight="1">
+    <row r="150" spans="3:4" ht="12.75" customHeight="1">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
     </row>
-    <row r="151" ht="12.75" customHeight="1">
+    <row r="151" spans="3:4" ht="12.75" customHeight="1">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
     </row>
-    <row r="152" ht="12.75" customHeight="1">
+    <row r="152" spans="3:4" ht="12.75" customHeight="1">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
     </row>
-    <row r="153" ht="12.75" customHeight="1">
+    <row r="153" spans="3:4" ht="12.75" customHeight="1">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
     </row>
-    <row r="154" ht="12.75" customHeight="1">
+    <row r="154" spans="3:4" ht="12.75" customHeight="1">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
     </row>
-    <row r="155" ht="12.75" customHeight="1">
+    <row r="155" spans="3:4" ht="12.75" customHeight="1">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
     </row>
-    <row r="156" ht="12.75" customHeight="1">
+    <row r="156" spans="3:4" ht="12.75" customHeight="1">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
     </row>
-    <row r="157" ht="12.75" customHeight="1">
+    <row r="157" spans="3:4" ht="12.75" customHeight="1">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
     </row>
-    <row r="158" ht="12.75" customHeight="1">
+    <row r="158" spans="3:4" ht="12.75" customHeight="1">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
     </row>
-    <row r="159" ht="12.75" customHeight="1">
+    <row r="159" spans="3:4" ht="12.75" customHeight="1">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
     </row>
-    <row r="160" ht="12.75" customHeight="1">
+    <row r="160" spans="3:4" ht="12.75" customHeight="1">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
     </row>
-    <row r="161" ht="12.75" customHeight="1">
+    <row r="161" spans="3:4" ht="12.75" customHeight="1">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
     </row>
-    <row r="162" ht="12.75" customHeight="1">
+    <row r="162" spans="3:4" ht="12.75" customHeight="1">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
     </row>
-    <row r="163" ht="12.75" customHeight="1">
+    <row r="163" spans="3:4" ht="12.75" customHeight="1">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
     </row>
-    <row r="164" ht="12.75" customHeight="1">
+    <row r="164" spans="3:4" ht="12.75" customHeight="1">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
     </row>
-    <row r="165" ht="12.75" customHeight="1">
+    <row r="165" spans="3:4" ht="12.75" customHeight="1">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
     </row>
-    <row r="166" ht="12.75" customHeight="1">
+    <row r="166" spans="3:4" ht="12.75" customHeight="1">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
     </row>
-    <row r="167" ht="12.75" customHeight="1">
+    <row r="167" spans="3:4" ht="12.75" customHeight="1">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
     </row>
-    <row r="168" ht="12.75" customHeight="1">
+    <row r="168" spans="3:4" ht="12.75" customHeight="1">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
     </row>
-    <row r="169" ht="12.75" customHeight="1">
+    <row r="169" spans="3:4" ht="12.75" customHeight="1">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
     </row>
-    <row r="170" ht="12.75" customHeight="1">
+    <row r="170" spans="3:4" ht="12.75" customHeight="1">
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
     </row>
-    <row r="171" ht="12.75" customHeight="1">
+    <row r="171" spans="3:4" ht="12.75" customHeight="1">
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
     </row>
-    <row r="172" ht="12.75" customHeight="1">
+    <row r="172" spans="3:4" ht="12.75" customHeight="1">
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
     </row>
-    <row r="173" ht="12.75" customHeight="1">
+    <row r="173" spans="3:4" ht="12.75" customHeight="1">
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
     </row>
-    <row r="174" ht="12.75" customHeight="1">
+    <row r="174" spans="3:4" ht="12.75" customHeight="1">
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
     </row>
-    <row r="175" ht="12.75" customHeight="1">
+    <row r="175" spans="3:4" ht="12.75" customHeight="1">
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
     </row>
-    <row r="176" ht="12.75" customHeight="1">
+    <row r="176" spans="3:4" ht="12.75" customHeight="1">
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
     </row>
-    <row r="177" ht="12.75" customHeight="1">
+    <row r="177" spans="3:4" ht="12.75" customHeight="1">
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
     </row>
-    <row r="178" ht="12.75" customHeight="1">
+    <row r="178" spans="3:4" ht="12.75" customHeight="1">
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
     </row>
-    <row r="179" ht="12.75" customHeight="1">
+    <row r="179" spans="3:4" ht="12.75" customHeight="1">
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
     </row>
-    <row r="180" ht="12.75" customHeight="1">
+    <row r="180" spans="3:4" ht="12.75" customHeight="1">
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
     </row>
-    <row r="181" ht="12.75" customHeight="1">
+    <row r="181" spans="3:4" ht="12.75" customHeight="1">
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
     </row>
-    <row r="182" ht="12.75" customHeight="1">
+    <row r="182" spans="3:4" ht="12.75" customHeight="1">
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
     </row>
-    <row r="183" ht="12.75" customHeight="1">
+    <row r="183" spans="3:4" ht="12.75" customHeight="1">
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
     </row>
-    <row r="184" ht="12.75" customHeight="1">
+    <row r="184" spans="3:4" ht="12.75" customHeight="1">
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
     </row>
-    <row r="185" ht="12.75" customHeight="1">
+    <row r="185" spans="3:4" ht="12.75" customHeight="1">
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
     </row>
-    <row r="186" ht="12.75" customHeight="1">
+    <row r="186" spans="3:4" ht="12.75" customHeight="1">
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
     </row>
-    <row r="187" ht="12.75" customHeight="1">
+    <row r="187" spans="3:4" ht="12.75" customHeight="1">
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
     </row>
-    <row r="188" ht="12.75" customHeight="1">
+    <row r="188" spans="3:4" ht="12.75" customHeight="1">
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
     </row>
-    <row r="189" ht="12.75" customHeight="1">
+    <row r="189" spans="3:4" ht="12.75" customHeight="1">
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
     </row>
-    <row r="190" ht="12.75" customHeight="1">
+    <row r="190" spans="3:4" ht="12.75" customHeight="1">
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
     </row>
-    <row r="191" ht="12.75" customHeight="1">
+    <row r="191" spans="3:4" ht="12.75" customHeight="1">
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
     </row>
-    <row r="192" ht="12.75" customHeight="1">
+    <row r="192" spans="3:4" ht="12.75" customHeight="1">
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
     </row>
-    <row r="193" ht="12.75" customHeight="1">
+    <row r="193" spans="3:4" ht="12.75" customHeight="1">
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
     </row>
-    <row r="194" ht="12.75" customHeight="1">
+    <row r="194" spans="3:4" ht="12.75" customHeight="1">
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
     </row>
-    <row r="195" ht="12.75" customHeight="1">
+    <row r="195" spans="3:4" ht="12.75" customHeight="1">
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
     </row>
-    <row r="196" ht="12.75" customHeight="1">
+    <row r="196" spans="3:4" ht="12.75" customHeight="1">
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
     </row>
-    <row r="197" ht="12.75" customHeight="1">
+    <row r="197" spans="3:4" ht="12.75" customHeight="1">
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
     </row>
-    <row r="198" ht="12.75" customHeight="1">
+    <row r="198" spans="3:4" ht="12.75" customHeight="1">
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
     </row>
-    <row r="199" ht="12.75" customHeight="1">
+    <row r="199" spans="3:4" ht="12.75" customHeight="1">
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
     </row>
-    <row r="200" ht="12.75" customHeight="1">
+    <row r="200" spans="3:4" ht="12.75" customHeight="1">
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
     </row>
-    <row r="201" ht="12.75" customHeight="1">
+    <row r="201" spans="3:4" ht="12.75" customHeight="1">
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
     </row>
-    <row r="202" ht="12.75" customHeight="1">
+    <row r="202" spans="3:4" ht="12.75" customHeight="1">
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1">
+    <row r="203" spans="3:4" ht="12.75" customHeight="1">
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
     </row>
-    <row r="204" ht="12.75" customHeight="1">
+    <row r="204" spans="3:4" ht="12.75" customHeight="1">
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1">
+    <row r="205" spans="3:4" ht="12.75" customHeight="1">
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
     </row>
-    <row r="206" ht="12.75" customHeight="1">
+    <row r="206" spans="3:4" ht="12.75" customHeight="1">
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
     </row>
-    <row r="207" ht="12.75" customHeight="1">
+    <row r="207" spans="3:4" ht="12.75" customHeight="1">
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
     </row>
-    <row r="208" ht="12.75" customHeight="1">
+    <row r="208" spans="3:4" ht="12.75" customHeight="1">
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
     </row>
-    <row r="209" ht="12.75" customHeight="1">
+    <row r="209" spans="3:4" ht="12.75" customHeight="1">
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
     </row>
-    <row r="210" ht="12.75" customHeight="1">
+    <row r="210" spans="3:4" ht="12.75" customHeight="1">
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1">
+    <row r="211" spans="3:4" ht="12.75" customHeight="1">
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
     </row>
-    <row r="212" ht="12.75" customHeight="1">
+    <row r="212" spans="3:4" ht="12.75" customHeight="1">
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
     </row>
-    <row r="213" ht="12.75" customHeight="1">
+    <row r="213" spans="3:4" ht="12.75" customHeight="1">
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1">
+    <row r="214" spans="3:4" ht="12.75" customHeight="1">
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
     </row>
-    <row r="215" ht="12.75" customHeight="1">
+    <row r="215" spans="3:4" ht="12.75" customHeight="1">
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
     </row>
-    <row r="216" ht="12.75" customHeight="1">
+    <row r="216" spans="3:4" ht="12.75" customHeight="1">
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
     </row>
-    <row r="217" ht="12.75" customHeight="1">
+    <row r="217" spans="3:4" ht="12.75" customHeight="1">
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1">
+    <row r="218" spans="3:4" ht="12.75" customHeight="1">
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
     </row>
-    <row r="219" ht="12.75" customHeight="1">
+    <row r="219" spans="3:4" ht="12.75" customHeight="1">
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
     </row>
-    <row r="220" ht="12.75" customHeight="1">
+    <row r="220" spans="3:4" ht="12.75" customHeight="1">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
     </row>
-    <row r="221" ht="12.75" customHeight="1">
+    <row r="221" spans="3:4" ht="12.75" customHeight="1">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
     </row>
-    <row r="222" ht="12.75" customHeight="1">
+    <row r="222" spans="3:4" ht="12.75" customHeight="1">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
     </row>
-    <row r="223" ht="12.75" customHeight="1">
+    <row r="223" spans="3:4" ht="12.75" customHeight="1">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1">
+    <row r="224" spans="3:4" ht="12.75" customHeight="1">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
     </row>
-    <row r="225" ht="12.75" customHeight="1">
+    <row r="225" spans="3:4" ht="12.75" customHeight="1">
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
     </row>
-    <row r="226" ht="12.75" customHeight="1">
+    <row r="226" spans="3:4" ht="12.75" customHeight="1">
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
     </row>
-    <row r="227" ht="12.75" customHeight="1">
+    <row r="227" spans="3:4" ht="12.75" customHeight="1">
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1">
+    <row r="228" spans="3:4" ht="12.75" customHeight="1">
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
     </row>
-    <row r="229" ht="12.75" customHeight="1">
+    <row r="229" spans="3:4" ht="12.75" customHeight="1">
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
     </row>
-    <row r="230" ht="12.75" customHeight="1">
+    <row r="230" spans="3:4" ht="12.75" customHeight="1">
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
     </row>
-    <row r="231" ht="12.75" customHeight="1">
+    <row r="231" spans="3:4" ht="12.75" customHeight="1">
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
     </row>
-    <row r="232" ht="12.75" customHeight="1">
+    <row r="232" spans="3:4" ht="12.75" customHeight="1">
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
     </row>
-    <row r="233" ht="12.75" customHeight="1">
+    <row r="233" spans="3:4" ht="12.75" customHeight="1">
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
     </row>
-    <row r="234" ht="12.75" customHeight="1">
+    <row r="234" spans="3:4" ht="12.75" customHeight="1">
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
     </row>
-    <row r="235" ht="12.75" customHeight="1">
+    <row r="235" spans="3:4" ht="12.75" customHeight="1">
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
     </row>
-    <row r="236" ht="12.75" customHeight="1">
+    <row r="236" spans="3:4" ht="12.75" customHeight="1">
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1">
+    <row r="237" spans="3:4" ht="12.75" customHeight="1">
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
     </row>
-    <row r="238" ht="12.75" customHeight="1">
+    <row r="238" spans="3:4" ht="12.75" customHeight="1">
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
     </row>
-    <row r="239" ht="12.75" customHeight="1">
+    <row r="239" spans="3:4" ht="12.75" customHeight="1">
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
     </row>
-    <row r="240" ht="12.75" customHeight="1">
+    <row r="240" spans="3:4" ht="12.75" customHeight="1">
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
     </row>
-    <row r="241" ht="12.75" customHeight="1">
+    <row r="241" spans="3:4" ht="12.75" customHeight="1">
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
     </row>
-    <row r="242" ht="12.75" customHeight="1">
+    <row r="242" spans="3:4" ht="12.75" customHeight="1">
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
     </row>
-    <row r="243" ht="12.75" customHeight="1">
+    <row r="243" spans="3:4" ht="12.75" customHeight="1">
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
     </row>
-    <row r="244" ht="12.75" customHeight="1">
+    <row r="244" spans="3:4" ht="12.75" customHeight="1">
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
     </row>
-    <row r="245" ht="12.75" customHeight="1">
+    <row r="245" spans="3:4" ht="12.75" customHeight="1">
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
     </row>
-    <row r="246" ht="12.75" customHeight="1">
+    <row r="246" spans="3:4" ht="12.75" customHeight="1">
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
     </row>
-    <row r="247" ht="12.75" customHeight="1">
+    <row r="247" spans="3:4" ht="12.75" customHeight="1">
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
     </row>
-    <row r="248" ht="12.75" customHeight="1">
+    <row r="248" spans="3:4" ht="12.75" customHeight="1">
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
     </row>
-    <row r="249" ht="12.75" customHeight="1">
+    <row r="249" spans="3:4" ht="12.75" customHeight="1">
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1">
+    <row r="250" spans="3:4" ht="12.75" customHeight="1">
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
     </row>
-    <row r="251" ht="12.75" customHeight="1">
+    <row r="251" spans="3:4" ht="12.75" customHeight="1">
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
     </row>
-    <row r="252" ht="12.75" customHeight="1">
+    <row r="252" spans="3:4" ht="12.75" customHeight="1">
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
     </row>
-    <row r="253" ht="12.75" customHeight="1">
+    <row r="253" spans="3:4" ht="12.75" customHeight="1">
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
     </row>
-    <row r="254" ht="12.75" customHeight="1">
+    <row r="254" spans="3:4" ht="12.75" customHeight="1">
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
     </row>
-    <row r="255" ht="12.75" customHeight="1">
+    <row r="255" spans="3:4" ht="12.75" customHeight="1">
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
     </row>
-    <row r="256" ht="12.75" customHeight="1">
+    <row r="256" spans="3:4" ht="12.75" customHeight="1">
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
     </row>
-    <row r="257" ht="12.75" customHeight="1">
+    <row r="257" spans="3:4" ht="12.75" customHeight="1">
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
     </row>
-    <row r="258" ht="12.75" customHeight="1">
+    <row r="258" spans="3:4" ht="12.75" customHeight="1">
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
     </row>
-    <row r="259" ht="12.75" customHeight="1">
+    <row r="259" spans="3:4" ht="12.75" customHeight="1">
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
     </row>
-    <row r="260" ht="12.75" customHeight="1">
+    <row r="260" spans="3:4" ht="12.75" customHeight="1">
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
     </row>
-    <row r="261" ht="12.75" customHeight="1">
+    <row r="261" spans="3:4" ht="12.75" customHeight="1">
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
     </row>
-    <row r="262" ht="12.75" customHeight="1">
+    <row r="262" spans="3:4" ht="12.75" customHeight="1">
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
     </row>
-    <row r="263" ht="12.75" customHeight="1">
+    <row r="263" spans="3:4" ht="12.75" customHeight="1">
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
     </row>
-    <row r="264" ht="12.75" customHeight="1">
+    <row r="264" spans="3:4" ht="12.75" customHeight="1">
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
     </row>
-    <row r="265" ht="12.75" customHeight="1">
+    <row r="265" spans="3:4" ht="12.75" customHeight="1">
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
     </row>
-    <row r="266" ht="12.75" customHeight="1">
+    <row r="266" spans="3:4" ht="12.75" customHeight="1">
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
     </row>
-    <row r="267" ht="12.75" customHeight="1">
+    <row r="267" spans="3:4" ht="12.75" customHeight="1">
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
     </row>
-    <row r="268" ht="12.75" customHeight="1">
+    <row r="268" spans="3:4" ht="12.75" customHeight="1">
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
     </row>
-    <row r="269" ht="12.75" customHeight="1">
+    <row r="269" spans="3:4" ht="12.75" customHeight="1">
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
     </row>
-    <row r="270" ht="12.75" customHeight="1">
+    <row r="270" spans="3:4" ht="12.75" customHeight="1">
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
     </row>
-    <row r="271" ht="12.75" customHeight="1">
+    <row r="271" spans="3:4" ht="12.75" customHeight="1">
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
     </row>
-    <row r="272" ht="12.75" customHeight="1">
+    <row r="272" spans="3:4" ht="12.75" customHeight="1">
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
     </row>
-    <row r="273" ht="12.75" customHeight="1">
+    <row r="273" spans="3:4" ht="12.75" customHeight="1">
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
     </row>
-    <row r="274" ht="12.75" customHeight="1">
+    <row r="274" spans="3:4" ht="12.75" customHeight="1">
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
     </row>
-    <row r="275" ht="12.75" customHeight="1">
+    <row r="275" spans="3:4" ht="12.75" customHeight="1">
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
     </row>
-    <row r="276" ht="12.75" customHeight="1">
+    <row r="276" spans="3:4" ht="12.75" customHeight="1">
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
     </row>
-    <row r="277" ht="12.75" customHeight="1">
+    <row r="277" spans="3:4" ht="12.75" customHeight="1">
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
     </row>
-    <row r="278" ht="12.75" customHeight="1">
+    <row r="278" spans="3:4" ht="12.75" customHeight="1">
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
     </row>
-    <row r="279" ht="12.75" customHeight="1">
+    <row r="279" spans="3:4" ht="12.75" customHeight="1">
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
     </row>
-    <row r="280" ht="12.75" customHeight="1">
+    <row r="280" spans="3:4" ht="12.75" customHeight="1">
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
     </row>
-    <row r="281" ht="12.75" customHeight="1">
+    <row r="281" spans="3:4" ht="12.75" customHeight="1">
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
     </row>
-    <row r="282" ht="12.75" customHeight="1">
+    <row r="282" spans="3:4" ht="12.75" customHeight="1">
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
     </row>
-    <row r="283" ht="12.75" customHeight="1">
+    <row r="283" spans="3:4" ht="12.75" customHeight="1">
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
     </row>
-    <row r="284" ht="12.75" customHeight="1">
+    <row r="284" spans="3:4" ht="12.75" customHeight="1">
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
     </row>
-    <row r="285" ht="12.75" customHeight="1">
+    <row r="285" spans="3:4" ht="12.75" customHeight="1">
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
     </row>
-    <row r="286" ht="12.75" customHeight="1">
+    <row r="286" spans="3:4" ht="12.75" customHeight="1">
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
     </row>
-    <row r="287" ht="12.75" customHeight="1">
+    <row r="287" spans="3:4" ht="12.75" customHeight="1">
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
     </row>
-    <row r="288" ht="12.75" customHeight="1">
+    <row r="288" spans="3:4" ht="12.75" customHeight="1">
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
     </row>
-    <row r="289" ht="12.75" customHeight="1">
+    <row r="289" spans="3:4" ht="12.75" customHeight="1">
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
     </row>
-    <row r="290" ht="12.75" customHeight="1">
+    <row r="290" spans="3:4" ht="12.75" customHeight="1">
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
     </row>
-    <row r="291" ht="12.75" customHeight="1">
+    <row r="291" spans="3:4" ht="12.75" customHeight="1">
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
     </row>
-    <row r="292" ht="12.75" customHeight="1">
+    <row r="292" spans="3:4" ht="12.75" customHeight="1">
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
     </row>
-    <row r="293" ht="12.75" customHeight="1">
+    <row r="293" spans="3:4" ht="12.75" customHeight="1">
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
     </row>
-    <row r="294" ht="12.75" customHeight="1">
+    <row r="294" spans="3:4" ht="12.75" customHeight="1">
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
     </row>
-    <row r="295" ht="12.75" customHeight="1">
+    <row r="295" spans="3:4" ht="12.75" customHeight="1">
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
     </row>
-    <row r="296" ht="12.75" customHeight="1">
+    <row r="296" spans="3:4" ht="12.75" customHeight="1">
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1">
+    <row r="297" spans="3:4" ht="12.75" customHeight="1">
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1">
+    <row r="298" spans="3:4" ht="12.75" customHeight="1">
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
     </row>
-    <row r="299" ht="12.75" customHeight="1">
+    <row r="299" spans="3:4" ht="12.75" customHeight="1">
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
     </row>
-    <row r="300" ht="12.75" customHeight="1">
+    <row r="300" spans="3:4" ht="12.75" customHeight="1">
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
     </row>
-    <row r="301" ht="12.75" customHeight="1">
+    <row r="301" spans="3:4" ht="12.75" customHeight="1">
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
     </row>
-    <row r="302" ht="12.75" customHeight="1">
+    <row r="302" spans="3:4" ht="12.75" customHeight="1">
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
     </row>
-    <row r="303" ht="12.75" customHeight="1">
+    <row r="303" spans="3:4" ht="12.75" customHeight="1">
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
     </row>
-    <row r="304" ht="12.75" customHeight="1">
+    <row r="304" spans="3:4" ht="12.75" customHeight="1">
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
     </row>
-    <row r="305" ht="12.75" customHeight="1">
+    <row r="305" spans="3:4" ht="12.75" customHeight="1">
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
     </row>
-    <row r="306" ht="12.75" customHeight="1">
+    <row r="306" spans="3:4" ht="12.75" customHeight="1">
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
     </row>
-    <row r="307" ht="12.75" customHeight="1">
+    <row r="307" spans="3:4" ht="12.75" customHeight="1">
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
     </row>
-    <row r="308" ht="12.75" customHeight="1">
+    <row r="308" spans="3:4" ht="12.75" customHeight="1">
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
     </row>
-    <row r="309" ht="12.75" customHeight="1">
+    <row r="309" spans="3:4" ht="12.75" customHeight="1">
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
     </row>
-    <row r="310" ht="12.75" customHeight="1">
+    <row r="310" spans="3:4" ht="12.75" customHeight="1">
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
     </row>
-    <row r="311" ht="12.75" customHeight="1">
+    <row r="311" spans="3:4" ht="12.75" customHeight="1">
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
     </row>
-    <row r="312" ht="12.75" customHeight="1">
+    <row r="312" spans="3:4" ht="12.75" customHeight="1">
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
     </row>
-    <row r="313" ht="12.75" customHeight="1">
+    <row r="313" spans="3:4" ht="12.75" customHeight="1">
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
     </row>
-    <row r="314" ht="12.75" customHeight="1">
+    <row r="314" spans="3:4" ht="12.75" customHeight="1">
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
     </row>
-    <row r="315" ht="12.75" customHeight="1">
+    <row r="315" spans="3:4" ht="12.75" customHeight="1">
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
     </row>
-    <row r="316" ht="12.75" customHeight="1">
+    <row r="316" spans="3:4" ht="12.75" customHeight="1">
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
     </row>
-    <row r="317" ht="12.75" customHeight="1">
+    <row r="317" spans="3:4" ht="12.75" customHeight="1">
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1">
+    <row r="318" spans="3:4" ht="12.75" customHeight="1">
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
     </row>
-    <row r="319" ht="12.75" customHeight="1">
+    <row r="319" spans="3:4" ht="12.75" customHeight="1">
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
     </row>
-    <row r="320" ht="12.75" customHeight="1">
+    <row r="320" spans="3:4" ht="12.75" customHeight="1">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
     </row>
-    <row r="321" ht="12.75" customHeight="1">
+    <row r="321" spans="3:4" ht="12.75" customHeight="1">
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
     </row>
-    <row r="322" ht="12.75" customHeight="1">
+    <row r="322" spans="3:4" ht="12.75" customHeight="1">
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
     </row>
-    <row r="323" ht="12.75" customHeight="1">
+    <row r="323" spans="3:4" ht="12.75" customHeight="1">
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
     </row>
-    <row r="324" ht="12.75" customHeight="1">
+    <row r="324" spans="3:4" ht="12.75" customHeight="1">
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
     </row>
-    <row r="325" ht="12.75" customHeight="1">
+    <row r="325" spans="3:4" ht="12.75" customHeight="1">
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
     </row>
-    <row r="326" ht="12.75" customHeight="1">
+    <row r="326" spans="3:4" ht="12.75" customHeight="1">
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
     </row>
-    <row r="327" ht="12.75" customHeight="1">
+    <row r="327" spans="3:4" ht="12.75" customHeight="1">
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
     </row>
-    <row r="328" ht="12.75" customHeight="1">
+    <row r="328" spans="3:4" ht="12.75" customHeight="1">
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
     </row>
-    <row r="329" ht="12.75" customHeight="1">
+    <row r="329" spans="3:4" ht="12.75" customHeight="1">
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1">
+    <row r="330" spans="3:4" ht="12.75" customHeight="1">
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
     </row>
-    <row r="331" ht="12.75" customHeight="1">
+    <row r="331" spans="3:4" ht="12.75" customHeight="1">
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
     </row>
-    <row r="332" ht="12.75" customHeight="1">
+    <row r="332" spans="3:4" ht="12.75" customHeight="1">
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
     </row>
-    <row r="333" ht="12.75" customHeight="1">
+    <row r="333" spans="3:4" ht="12.75" customHeight="1">
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
     </row>
-    <row r="334" ht="12.75" customHeight="1">
+    <row r="334" spans="3:4" ht="12.75" customHeight="1">
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
     </row>
-    <row r="335" ht="12.75" customHeight="1">
+    <row r="335" spans="3:4" ht="12.75" customHeight="1">
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
     </row>
-    <row r="336" ht="12.75" customHeight="1">
+    <row r="336" spans="3:4" ht="12.75" customHeight="1">
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
     </row>
-    <row r="337" ht="12.75" customHeight="1">
+    <row r="337" spans="3:4" ht="12.75" customHeight="1">
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
     </row>
-    <row r="338" ht="12.75" customHeight="1">
+    <row r="338" spans="3:4" ht="12.75" customHeight="1">
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
     </row>
-    <row r="339" ht="12.75" customHeight="1">
+    <row r="339" spans="3:4" ht="12.75" customHeight="1">
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
     </row>
-    <row r="340" ht="12.75" customHeight="1">
+    <row r="340" spans="3:4" ht="12.75" customHeight="1">
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
     </row>
-    <row r="341" ht="12.75" customHeight="1">
+    <row r="341" spans="3:4" ht="12.75" customHeight="1">
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
     </row>
-    <row r="342" ht="12.75" customHeight="1">
+    <row r="342" spans="3:4" ht="12.75" customHeight="1">
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1">
+    <row r="343" spans="3:4" ht="12.75" customHeight="1">
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
     </row>
-    <row r="344" ht="12.75" customHeight="1">
+    <row r="344" spans="3:4" ht="12.75" customHeight="1">
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
     </row>
-    <row r="345" ht="12.75" customHeight="1">
+    <row r="345" spans="3:4" ht="12.75" customHeight="1">
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
     </row>
-    <row r="346" ht="12.75" customHeight="1">
+    <row r="346" spans="3:4" ht="12.75" customHeight="1">
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
     </row>
-    <row r="347" ht="12.75" customHeight="1">
+    <row r="347" spans="3:4" ht="12.75" customHeight="1">
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
     </row>
-    <row r="348" ht="12.75" customHeight="1">
+    <row r="348" spans="3:4" ht="12.75" customHeight="1">
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
     </row>
-    <row r="349" ht="12.75" customHeight="1">
+    <row r="349" spans="3:4" ht="12.75" customHeight="1">
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
     </row>
-    <row r="350" ht="12.75" customHeight="1">
+    <row r="350" spans="3:4" ht="12.75" customHeight="1">
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
     </row>
-    <row r="351" ht="12.75" customHeight="1">
+    <row r="351" spans="3:4" ht="12.75" customHeight="1">
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
     </row>
-    <row r="352" ht="12.75" customHeight="1">
+    <row r="352" spans="3:4" ht="12.75" customHeight="1">
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
     </row>
-    <row r="353" ht="12.75" customHeight="1">
+    <row r="353" spans="3:4" ht="12.75" customHeight="1">
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
     </row>
-    <row r="354" ht="12.75" customHeight="1">
+    <row r="354" spans="3:4" ht="12.75" customHeight="1">
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
     </row>
-    <row r="355" ht="12.75" customHeight="1">
+    <row r="355" spans="3:4" ht="12.75" customHeight="1">
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
     </row>
-    <row r="356" ht="12.75" customHeight="1">
+    <row r="356" spans="3:4" ht="12.75" customHeight="1">
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
     </row>
-    <row r="357" ht="12.75" customHeight="1">
+    <row r="357" spans="3:4" ht="12.75" customHeight="1">
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
     </row>
-    <row r="358" ht="12.75" customHeight="1">
+    <row r="358" spans="3:4" ht="12.75" customHeight="1">
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
     </row>
-    <row r="359" ht="12.75" customHeight="1">
+    <row r="359" spans="3:4" ht="12.75" customHeight="1">
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
     </row>
-    <row r="360" ht="12.75" customHeight="1">
+    <row r="360" spans="3:4" ht="12.75" customHeight="1">
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
     </row>
-    <row r="361" ht="12.75" customHeight="1">
+    <row r="361" spans="3:4" ht="12.75" customHeight="1">
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
     </row>
-    <row r="362" ht="12.75" customHeight="1">
+    <row r="362" spans="3:4" ht="12.75" customHeight="1">
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
     </row>
-    <row r="363" ht="12.75" customHeight="1">
+    <row r="363" spans="3:4" ht="12.75" customHeight="1">
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
     </row>
-    <row r="364" ht="12.75" customHeight="1">
+    <row r="364" spans="3:4" ht="12.75" customHeight="1">
       <c r="C364" s="1"/>
       <c r="D364" s="1"/>
     </row>
-    <row r="365" ht="12.75" customHeight="1">
+    <row r="365" spans="3:4" ht="12.75" customHeight="1">
       <c r="C365" s="1"/>
       <c r="D365" s="1"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1">
+    <row r="366" spans="3:4" ht="12.75" customHeight="1">
       <c r="C366" s="1"/>
       <c r="D366" s="1"/>
     </row>
-    <row r="367" ht="12.75" customHeight="1">
+    <row r="367" spans="3:4" ht="12.75" customHeight="1">
       <c r="C367" s="1"/>
       <c r="D367" s="1"/>
     </row>
-    <row r="368" ht="12.75" customHeight="1">
+    <row r="368" spans="3:4" ht="12.75" customHeight="1">
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
     </row>
-    <row r="369" ht="12.75" customHeight="1">
+    <row r="369" spans="3:4" ht="12.75" customHeight="1">
       <c r="C369" s="1"/>
       <c r="D369" s="1"/>
     </row>
-    <row r="370" ht="12.75" customHeight="1">
+    <row r="370" spans="3:4" ht="12.75" customHeight="1">
       <c r="C370" s="1"/>
       <c r="D370" s="1"/>
     </row>
-    <row r="371" ht="12.75" customHeight="1">
+    <row r="371" spans="3:4" ht="12.75" customHeight="1">
       <c r="C371" s="1"/>
       <c r="D371" s="1"/>
     </row>
-    <row r="372" ht="12.75" customHeight="1">
+    <row r="372" spans="3:4" ht="12.75" customHeight="1">
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
     </row>
-    <row r="373" ht="12.75" customHeight="1">
+    <row r="373" spans="3:4" ht="12.75" customHeight="1">
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
     </row>
-    <row r="374" ht="12.75" customHeight="1">
+    <row r="374" spans="3:4" ht="12.75" customHeight="1">
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
     </row>
-    <row r="375" ht="12.75" customHeight="1">
+    <row r="375" spans="3:4" ht="12.75" customHeight="1">
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
     </row>
-    <row r="376" ht="12.75" customHeight="1">
+    <row r="376" spans="3:4" ht="12.75" customHeight="1">
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
     </row>
-    <row r="377" ht="12.75" customHeight="1">
+    <row r="377" spans="3:4" ht="12.75" customHeight="1">
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
     </row>
-    <row r="378" ht="12.75" customHeight="1">
+    <row r="378" spans="3:4" ht="12.75" customHeight="1">
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
     </row>
-    <row r="379" ht="12.75" customHeight="1">
+    <row r="379" spans="3:4" ht="12.75" customHeight="1">
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
     </row>
-    <row r="380" ht="12.75" customHeight="1">
+    <row r="380" spans="3:4" ht="12.75" customHeight="1">
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
     </row>
-    <row r="381" ht="12.75" customHeight="1">
+    <row r="381" spans="3:4" ht="12.75" customHeight="1">
       <c r="C381" s="1"/>
       <c r="D381" s="1"/>
     </row>
-    <row r="382" ht="12.75" customHeight="1">
+    <row r="382" spans="3:4" ht="12.75" customHeight="1">
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
     </row>
-    <row r="383" ht="12.75" customHeight="1">
+    <row r="383" spans="3:4" ht="12.75" customHeight="1">
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
     </row>
-    <row r="384" ht="12.75" customHeight="1">
+    <row r="384" spans="3:4" ht="12.75" customHeight="1">
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
     </row>
-    <row r="385" ht="12.75" customHeight="1">
+    <row r="385" spans="3:4" ht="12.75" customHeight="1">
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
     </row>
-    <row r="386" ht="12.75" customHeight="1">
+    <row r="386" spans="3:4" ht="12.75" customHeight="1">
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
     </row>
-    <row r="387" ht="12.75" customHeight="1">
+    <row r="387" spans="3:4" ht="12.75" customHeight="1">
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
     </row>
-    <row r="388" ht="12.75" customHeight="1">
+    <row r="388" spans="3:4" ht="12.75" customHeight="1">
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
     </row>
-    <row r="389" ht="12.75" customHeight="1">
+    <row r="389" spans="3:4" ht="12.75" customHeight="1">
       <c r="C389" s="1"/>
       <c r="D389" s="1"/>
     </row>
-    <row r="390" ht="12.75" customHeight="1">
+    <row r="390" spans="3:4" ht="12.75" customHeight="1">
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
     </row>
-    <row r="391" ht="12.75" customHeight="1">
+    <row r="391" spans="3:4" ht="12.75" customHeight="1">
       <c r="C391" s="1"/>
       <c r="D391" s="1"/>
     </row>
-    <row r="392" ht="12.75" customHeight="1">
+    <row r="392" spans="3:4" ht="12.75" customHeight="1">
       <c r="C392" s="1"/>
       <c r="D392" s="1"/>
     </row>
-    <row r="393" ht="12.75" customHeight="1">
+    <row r="393" spans="3:4" ht="12.75" customHeight="1">
       <c r="C393" s="1"/>
       <c r="D393" s="1"/>
     </row>
-    <row r="394" ht="12.75" customHeight="1">
+    <row r="394" spans="3:4" ht="12.75" customHeight="1">
       <c r="C394" s="1"/>
       <c r="D394" s="1"/>
     </row>
-    <row r="395" ht="12.75" customHeight="1">
+    <row r="395" spans="3:4" ht="12.75" customHeight="1">
       <c r="C395" s="1"/>
       <c r="D395" s="1"/>
     </row>
-    <row r="396" ht="12.75" customHeight="1">
+    <row r="396" spans="3:4" ht="12.75" customHeight="1">
       <c r="C396" s="1"/>
       <c r="D396" s="1"/>
     </row>
-    <row r="397" ht="12.75" customHeight="1">
+    <row r="397" spans="3:4" ht="12.75" customHeight="1">
       <c r="C397" s="1"/>
       <c r="D397" s="1"/>
     </row>
-    <row r="398" ht="12.75" customHeight="1">
+    <row r="398" spans="3:4" ht="12.75" customHeight="1">
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
     </row>
-    <row r="399" ht="12.75" customHeight="1">
+    <row r="399" spans="3:4" ht="12.75" customHeight="1">
       <c r="C399" s="1"/>
       <c r="D399" s="1"/>
     </row>
-    <row r="400" ht="12.75" customHeight="1">
+    <row r="400" spans="3:4" ht="12.75" customHeight="1">
       <c r="C400" s="1"/>
       <c r="D400" s="1"/>
     </row>
-    <row r="401" ht="12.75" customHeight="1">
+    <row r="401" spans="3:4" ht="12.75" customHeight="1">
       <c r="C401" s="1"/>
       <c r="D401" s="1"/>
     </row>
-    <row r="402" ht="12.75" customHeight="1">
+    <row r="402" spans="3:4" ht="12.75" customHeight="1">
       <c r="C402" s="1"/>
       <c r="D402" s="1"/>
     </row>
-    <row r="403" ht="12.75" customHeight="1">
+    <row r="403" spans="3:4" ht="12.75" customHeight="1">
       <c r="C403" s="1"/>
       <c r="D403" s="1"/>
     </row>
-    <row r="404" ht="12.75" customHeight="1">
+    <row r="404" spans="3:4" ht="12.75" customHeight="1">
       <c r="C404" s="1"/>
       <c r="D404" s="1"/>
     </row>
-    <row r="405" ht="12.75" customHeight="1">
+    <row r="405" spans="3:4" ht="12.75" customHeight="1">
       <c r="C405" s="1"/>
       <c r="D405" s="1"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1">
+    <row r="406" spans="3:4" ht="12.75" customHeight="1">
       <c r="C406" s="1"/>
       <c r="D406" s="1"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1">
+    <row r="407" spans="3:4" ht="12.75" customHeight="1">
       <c r="C407" s="1"/>
       <c r="D407" s="1"/>
     </row>
-    <row r="408" ht="12.75" customHeight="1">
+    <row r="408" spans="3:4" ht="12.75" customHeight="1">
       <c r="C408" s="1"/>
       <c r="D408" s="1"/>
     </row>
-    <row r="409" ht="12.75" customHeight="1">
+    <row r="409" spans="3:4" ht="12.75" customHeight="1">
       <c r="C409" s="1"/>
       <c r="D409" s="1"/>
     </row>
-    <row r="410" ht="12.75" customHeight="1">
+    <row r="410" spans="3:4" ht="12.75" customHeight="1">
       <c r="C410" s="1"/>
       <c r="D410" s="1"/>
     </row>
-    <row r="411" ht="12.75" customHeight="1">
+    <row r="411" spans="3:4" ht="12.75" customHeight="1">
       <c r="C411" s="1"/>
       <c r="D411" s="1"/>
     </row>
-    <row r="412" ht="12.75" customHeight="1">
+    <row r="412" spans="3:4" ht="12.75" customHeight="1">
       <c r="C412" s="1"/>
       <c r="D412" s="1"/>
     </row>
-    <row r="413" ht="12.75" customHeight="1">
+    <row r="413" spans="3:4" ht="12.75" customHeight="1">
       <c r="C413" s="1"/>
       <c r="D413" s="1"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1">
+    <row r="414" spans="3:4" ht="12.75" customHeight="1">
       <c r="C414" s="1"/>
       <c r="D414" s="1"/>
     </row>
-    <row r="415" ht="12.75" customHeight="1">
+    <row r="415" spans="3:4" ht="12.75" customHeight="1">
       <c r="C415" s="1"/>
       <c r="D415" s="1"/>
     </row>
-    <row r="416" ht="12.75" customHeight="1">
+    <row r="416" spans="3:4" ht="12.75" customHeight="1">
       <c r="C416" s="1"/>
       <c r="D416" s="1"/>
     </row>
-    <row r="417" ht="12.75" customHeight="1">
+    <row r="417" spans="3:4" ht="12.75" customHeight="1">
       <c r="C417" s="1"/>
       <c r="D417" s="1"/>
     </row>
-    <row r="418" ht="12.75" customHeight="1">
+    <row r="418" spans="3:4" ht="12.75" customHeight="1">
       <c r="C418" s="1"/>
       <c r="D418" s="1"/>
     </row>
-    <row r="419" ht="12.75" customHeight="1">
+    <row r="419" spans="3:4" ht="12.75" customHeight="1">
       <c r="C419" s="1"/>
       <c r="D419" s="1"/>
     </row>
-    <row r="420" ht="12.75" customHeight="1">
+    <row r="420" spans="3:4" ht="12.75" customHeight="1">
       <c r="C420" s="1"/>
       <c r="D420" s="1"/>
     </row>
-    <row r="421" ht="12.75" customHeight="1">
+    <row r="421" spans="3:4" ht="12.75" customHeight="1">
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
     </row>
-    <row r="422" ht="12.75" customHeight="1">
+    <row r="422" spans="3:4" ht="12.75" customHeight="1">
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
     </row>
-    <row r="423" ht="12.75" customHeight="1">
+    <row r="423" spans="3:4" ht="12.75" customHeight="1">
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
     </row>
-    <row r="424" ht="12.75" customHeight="1">
+    <row r="424" spans="3:4" ht="12.75" customHeight="1">
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
     </row>
-    <row r="425" ht="12.75" customHeight="1">
+    <row r="425" spans="3:4" ht="12.75" customHeight="1">
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
     </row>
-    <row r="426" ht="12.75" customHeight="1">
+    <row r="426" spans="3:4" ht="12.75" customHeight="1">
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
     </row>
-    <row r="427" ht="12.75" customHeight="1">
+    <row r="427" spans="3:4" ht="12.75" customHeight="1">
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
     </row>
-    <row r="428" ht="12.75" customHeight="1">
+    <row r="428" spans="3:4" ht="12.75" customHeight="1">
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
     </row>
-    <row r="429" ht="12.75" customHeight="1">
+    <row r="429" spans="3:4" ht="12.75" customHeight="1">
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
     </row>
-    <row r="430" ht="12.75" customHeight="1">
+    <row r="430" spans="3:4" ht="12.75" customHeight="1">
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
     </row>
-    <row r="431" ht="12.75" customHeight="1">
+    <row r="431" spans="3:4" ht="12.75" customHeight="1">
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1">
+    <row r="432" spans="3:4" ht="12.75" customHeight="1">
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
     </row>
-    <row r="433" ht="12.75" customHeight="1">
+    <row r="433" spans="3:4" ht="12.75" customHeight="1">
       <c r="C433" s="1"/>
       <c r="D433" s="1"/>
     </row>
-    <row r="434" ht="12.75" customHeight="1">
+    <row r="434" spans="3:4" ht="12.75" customHeight="1">
       <c r="C434" s="1"/>
       <c r="D434" s="1"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1">
+    <row r="435" spans="3:4" ht="12.75" customHeight="1">
       <c r="C435" s="1"/>
       <c r="D435" s="1"/>
     </row>
-    <row r="436" ht="12.75" customHeight="1">
+    <row r="436" spans="3:4" ht="12.75" customHeight="1">
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
     </row>
-    <row r="437" ht="12.75" customHeight="1">
+    <row r="437" spans="3:4" ht="12.75" customHeight="1">
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
     </row>
-    <row r="438" ht="12.75" customHeight="1">
+    <row r="438" spans="3:4" ht="12.75" customHeight="1">
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
     </row>
-    <row r="439" ht="12.75" customHeight="1">
+    <row r="439" spans="3:4" ht="12.75" customHeight="1">
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
     </row>
-    <row r="440" ht="12.75" customHeight="1">
+    <row r="440" spans="3:4" ht="12.75" customHeight="1">
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
     </row>
-    <row r="441" ht="12.75" customHeight="1">
+    <row r="441" spans="3:4" ht="12.75" customHeight="1">
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
     </row>
-    <row r="442" ht="12.75" customHeight="1">
+    <row r="442" spans="3:4" ht="12.75" customHeight="1">
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
     </row>
-    <row r="443" ht="12.75" customHeight="1">
+    <row r="443" spans="3:4" ht="12.75" customHeight="1">
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
     </row>
-    <row r="444" ht="12.75" customHeight="1">
+    <row r="444" spans="3:4" ht="12.75" customHeight="1">
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
     </row>
-    <row r="445" ht="12.75" customHeight="1">
+    <row r="445" spans="3:4" ht="12.75" customHeight="1">
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
     </row>
-    <row r="446" ht="12.75" customHeight="1">
+    <row r="446" spans="3:4" ht="12.75" customHeight="1">
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
     </row>
-    <row r="447" ht="12.75" customHeight="1">
+    <row r="447" spans="3:4" ht="12.75" customHeight="1">
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
     </row>
-    <row r="448" ht="12.75" customHeight="1">
+    <row r="448" spans="3:4" ht="12.75" customHeight="1">
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
     </row>
-    <row r="449" ht="12.75" customHeight="1">
+    <row r="449" spans="3:4" ht="12.75" customHeight="1">
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
     </row>
-    <row r="450" ht="12.75" customHeight="1">
+    <row r="450" spans="3:4" ht="12.75" customHeight="1">
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
     </row>
-    <row r="451" ht="12.75" customHeight="1">
+    <row r="451" spans="3:4" ht="12.75" customHeight="1">
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
     </row>
-    <row r="452" ht="12.75" customHeight="1">
+    <row r="452" spans="3:4" ht="12.75" customHeight="1">
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
     </row>
-    <row r="453" ht="12.75" customHeight="1">
+    <row r="453" spans="3:4" ht="12.75" customHeight="1">
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
     </row>
-    <row r="454" ht="12.75" customHeight="1">
+    <row r="454" spans="3:4" ht="12.75" customHeight="1">
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
     </row>
-    <row r="455" ht="12.75" customHeight="1">
+    <row r="455" spans="3:4" ht="12.75" customHeight="1">
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
     </row>
-    <row r="456" ht="12.75" customHeight="1">
+    <row r="456" spans="3:4" ht="12.75" customHeight="1">
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
     </row>
-    <row r="457" ht="12.75" customHeight="1">
+    <row r="457" spans="3:4" ht="12.75" customHeight="1">
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
     </row>
-    <row r="458" ht="12.75" customHeight="1">
+    <row r="458" spans="3:4" ht="12.75" customHeight="1">
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
     </row>
-    <row r="459" ht="12.75" customHeight="1">
+    <row r="459" spans="3:4" ht="12.75" customHeight="1">
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
     </row>
-    <row r="460" ht="12.75" customHeight="1">
+    <row r="460" spans="3:4" ht="12.75" customHeight="1">
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
     </row>
-    <row r="461" ht="12.75" customHeight="1">
+    <row r="461" spans="3:4" ht="12.75" customHeight="1">
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
     </row>
-    <row r="462" ht="12.75" customHeight="1">
+    <row r="462" spans="3:4" ht="12.75" customHeight="1">
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1">
+    <row r="463" spans="3:4" ht="12.75" customHeight="1">
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
     </row>
-    <row r="464" ht="12.75" customHeight="1">
+    <row r="464" spans="3:4" ht="12.75" customHeight="1">
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
     </row>
-    <row r="465" ht="12.75" customHeight="1">
+    <row r="465" spans="3:4" ht="12.75" customHeight="1">
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
     </row>
-    <row r="466" ht="12.75" customHeight="1">
+    <row r="466" spans="3:4" ht="12.75" customHeight="1">
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
     </row>
-    <row r="467" ht="12.75" customHeight="1">
+    <row r="467" spans="3:4" ht="12.75" customHeight="1">
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
     </row>
-    <row r="468" ht="12.75" customHeight="1">
+    <row r="468" spans="3:4" ht="12.75" customHeight="1">
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1">
+    <row r="469" spans="3:4" ht="12.75" customHeight="1">
       <c r="C469" s="1"/>
       <c r="D469" s="1"/>
     </row>
-    <row r="470" ht="12.75" customHeight="1">
+    <row r="470" spans="3:4" ht="12.75" customHeight="1">
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
     </row>
-    <row r="471" ht="12.75" customHeight="1">
+    <row r="471" spans="3:4" ht="12.75" customHeight="1">
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
     </row>
-    <row r="472" ht="12.75" customHeight="1">
+    <row r="472" spans="3:4" ht="12.75" customHeight="1">
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
     </row>
-    <row r="473" ht="12.75" customHeight="1">
+    <row r="473" spans="3:4" ht="12.75" customHeight="1">
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
     </row>
-    <row r="474" ht="12.75" customHeight="1">
+    <row r="474" spans="3:4" ht="12.75" customHeight="1">
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
     </row>
-    <row r="475" ht="12.75" customHeight="1">
+    <row r="475" spans="3:4" ht="12.75" customHeight="1">
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
     </row>
-    <row r="476" ht="12.75" customHeight="1">
+    <row r="476" spans="3:4" ht="12.75" customHeight="1">
       <c r="C476" s="1"/>
       <c r="D476" s="1"/>
     </row>
-    <row r="477" ht="12.75" customHeight="1">
+    <row r="477" spans="3:4" ht="12.75" customHeight="1">
       <c r="C477" s="1"/>
       <c r="D477" s="1"/>
     </row>
-    <row r="478" ht="12.75" customHeight="1">
+    <row r="478" spans="3:4" ht="12.75" customHeight="1">
       <c r="C478" s="1"/>
       <c r="D478" s="1"/>
     </row>
-    <row r="479" ht="12.75" customHeight="1">
+    <row r="479" spans="3:4" ht="12.75" customHeight="1">
       <c r="C479" s="1"/>
       <c r="D479" s="1"/>
     </row>
-    <row r="480" ht="12.75" customHeight="1">
+    <row r="480" spans="3:4" ht="12.75" customHeight="1">
       <c r="C480" s="1"/>
       <c r="D480" s="1"/>
     </row>
-    <row r="481" ht="12.75" customHeight="1">
+    <row r="481" spans="3:4" ht="12.75" customHeight="1">
       <c r="C481" s="1"/>
       <c r="D481" s="1"/>
     </row>
-    <row r="482" ht="12.75" customHeight="1">
+    <row r="482" spans="3:4" ht="12.75" customHeight="1">
       <c r="C482" s="1"/>
       <c r="D482" s="1"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1">
+    <row r="483" spans="3:4" ht="12.75" customHeight="1">
       <c r="C483" s="1"/>
       <c r="D483" s="1"/>
     </row>
-    <row r="484" ht="12.75" customHeight="1">
+    <row r="484" spans="3:4" ht="12.75" customHeight="1">
       <c r="C484" s="1"/>
       <c r="D484" s="1"/>
     </row>
-    <row r="485" ht="12.75" customHeight="1">
+    <row r="485" spans="3:4" ht="12.75" customHeight="1">
       <c r="C485" s="1"/>
       <c r="D485" s="1"/>
     </row>
-    <row r="486" ht="12.75" customHeight="1">
+    <row r="486" spans="3:4" ht="12.75" customHeight="1">
       <c r="C486" s="1"/>
       <c r="D486" s="1"/>
     </row>
-    <row r="487" ht="12.75" customHeight="1">
+    <row r="487" spans="3:4" ht="12.75" customHeight="1">
       <c r="C487" s="1"/>
       <c r="D487" s="1"/>
     </row>
-    <row r="488" ht="12.75" customHeight="1">
+    <row r="488" spans="3:4" ht="12.75" customHeight="1">
       <c r="C488" s="1"/>
       <c r="D488" s="1"/>
     </row>
-    <row r="489" ht="12.75" customHeight="1">
+    <row r="489" spans="3:4" ht="12.75" customHeight="1">
       <c r="C489" s="1"/>
       <c r="D489" s="1"/>
     </row>
-    <row r="490" ht="12.75" customHeight="1">
+    <row r="490" spans="3:4" ht="12.75" customHeight="1">
       <c r="C490" s="1"/>
       <c r="D490" s="1"/>
     </row>
-    <row r="491" ht="12.75" customHeight="1">
+    <row r="491" spans="3:4" ht="12.75" customHeight="1">
       <c r="C491" s="1"/>
       <c r="D491" s="1"/>
     </row>
-    <row r="492" ht="12.75" customHeight="1">
+    <row r="492" spans="3:4" ht="12.75" customHeight="1">
       <c r="C492" s="1"/>
       <c r="D492" s="1"/>
     </row>
-    <row r="493" ht="12.75" customHeight="1">
+    <row r="493" spans="3:4" ht="12.75" customHeight="1">
       <c r="C493" s="1"/>
       <c r="D493" s="1"/>
     </row>
-    <row r="494" ht="12.75" customHeight="1">
+    <row r="494" spans="3:4" ht="12.75" customHeight="1">
       <c r="C494" s="1"/>
       <c r="D494" s="1"/>
     </row>
-    <row r="495" ht="12.75" customHeight="1">
+    <row r="495" spans="3:4" ht="12.75" customHeight="1">
       <c r="C495" s="1"/>
       <c r="D495" s="1"/>
     </row>
-    <row r="496" ht="12.75" customHeight="1">
+    <row r="496" spans="3:4" ht="12.75" customHeight="1">
       <c r="C496" s="1"/>
       <c r="D496" s="1"/>
     </row>
-    <row r="497" ht="12.75" customHeight="1">
+    <row r="497" spans="3:4" ht="12.75" customHeight="1">
       <c r="C497" s="1"/>
       <c r="D497" s="1"/>
     </row>
-    <row r="498" ht="12.75" customHeight="1">
+    <row r="498" spans="3:4" ht="12.75" customHeight="1">
       <c r="C498" s="1"/>
       <c r="D498" s="1"/>
     </row>
-    <row r="499" ht="12.75" customHeight="1">
+    <row r="499" spans="3:4" ht="12.75" customHeight="1">
       <c r="C499" s="1"/>
       <c r="D499" s="1"/>
     </row>
-    <row r="500" ht="12.75" customHeight="1">
+    <row r="500" spans="3:4" ht="12.75" customHeight="1">
       <c r="C500" s="1"/>
       <c r="D500" s="1"/>
     </row>
-    <row r="501" ht="12.75" customHeight="1">
+    <row r="501" spans="3:4" ht="12.75" customHeight="1">
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
     </row>
-    <row r="502" ht="12.75" customHeight="1">
+    <row r="502" spans="3:4" ht="12.75" customHeight="1">
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
     </row>
-    <row r="503" ht="12.75" customHeight="1">
+    <row r="503" spans="3:4" ht="12.75" customHeight="1">
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
     </row>
-    <row r="504" ht="12.75" customHeight="1">
+    <row r="504" spans="3:4" ht="12.75" customHeight="1">
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
     </row>
-    <row r="505" ht="12.75" customHeight="1">
+    <row r="505" spans="3:4" ht="12.75" customHeight="1">
       <c r="C505" s="1"/>
       <c r="D505" s="1"/>
     </row>
-    <row r="506" ht="12.75" customHeight="1">
+    <row r="506" spans="3:4" ht="12.75" customHeight="1">
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
     </row>
-    <row r="507" ht="12.75" customHeight="1">
+    <row r="507" spans="3:4" ht="12.75" customHeight="1">
       <c r="C507" s="1"/>
       <c r="D507" s="1"/>
     </row>
-    <row r="508" ht="12.75" customHeight="1">
+    <row r="508" spans="3:4" ht="12.75" customHeight="1">
       <c r="C508" s="1"/>
       <c r="D508" s="1"/>
     </row>
-    <row r="509" ht="12.75" customHeight="1">
+    <row r="509" spans="3:4" ht="12.75" customHeight="1">
       <c r="C509" s="1"/>
       <c r="D509" s="1"/>
     </row>
-    <row r="510" ht="12.75" customHeight="1">
+    <row r="510" spans="3:4" ht="12.75" customHeight="1">
       <c r="C510" s="1"/>
       <c r="D510" s="1"/>
     </row>
-    <row r="511" ht="12.75" customHeight="1">
+    <row r="511" spans="3:4" ht="12.75" customHeight="1">
       <c r="C511" s="1"/>
       <c r="D511" s="1"/>
     </row>
-    <row r="512" ht="12.75" customHeight="1">
+    <row r="512" spans="3:4" ht="12.75" customHeight="1">
       <c r="C512" s="1"/>
       <c r="D512" s="1"/>
     </row>
-    <row r="513" ht="12.75" customHeight="1">
+    <row r="513" spans="3:4" ht="12.75" customHeight="1">
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
     </row>
-    <row r="514" ht="12.75" customHeight="1">
+    <row r="514" spans="3:4" ht="12.75" customHeight="1">
       <c r="C514" s="1"/>
       <c r="D514" s="1"/>
     </row>
-    <row r="515" ht="12.75" customHeight="1">
+    <row r="515" spans="3:4" ht="12.75" customHeight="1">
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
     </row>
-    <row r="516" ht="12.75" customHeight="1">
+    <row r="516" spans="3:4" ht="12.75" customHeight="1">
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
     </row>
-    <row r="517" ht="12.75" customHeight="1">
+    <row r="517" spans="3:4" ht="12.75" customHeight="1">
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
     </row>
-    <row r="518" ht="12.75" customHeight="1">
+    <row r="518" spans="3:4" ht="12.75" customHeight="1">
       <c r="C518" s="1"/>
       <c r="D518" s="1"/>
     </row>
-    <row r="519" ht="12.75" customHeight="1">
+    <row r="519" spans="3:4" ht="12.75" customHeight="1">
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
     </row>
-    <row r="520" ht="12.75" customHeight="1">
+    <row r="520" spans="3:4" ht="12.75" customHeight="1">
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
     </row>
-    <row r="521" ht="12.75" customHeight="1">
+    <row r="521" spans="3:4" ht="12.75" customHeight="1">
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
     </row>
-    <row r="522" ht="12.75" customHeight="1">
+    <row r="522" spans="3:4" ht="12.75" customHeight="1">
       <c r="C522" s="1"/>
       <c r="D522" s="1"/>
     </row>
-    <row r="523" ht="12.75" customHeight="1">
+    <row r="523" spans="3:4" ht="12.75" customHeight="1">
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
     </row>
-    <row r="524" ht="12.75" customHeight="1">
+    <row r="524" spans="3:4" ht="12.75" customHeight="1">
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
     </row>
-    <row r="525" ht="12.75" customHeight="1">
+    <row r="525" spans="3:4" ht="12.75" customHeight="1">
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
     </row>
-    <row r="526" ht="12.75" customHeight="1">
+    <row r="526" spans="3:4" ht="12.75" customHeight="1">
       <c r="C526" s="1"/>
       <c r="D526" s="1"/>
     </row>
-    <row r="527" ht="12.75" customHeight="1">
+    <row r="527" spans="3:4" ht="12.75" customHeight="1">
       <c r="C527" s="1"/>
       <c r="D527" s="1"/>
     </row>
-    <row r="528" ht="12.75" customHeight="1">
+    <row r="528" spans="3:4" ht="12.75" customHeight="1">
       <c r="C528" s="1"/>
       <c r="D528" s="1"/>
     </row>
-    <row r="529" ht="12.75" customHeight="1">
+    <row r="529" spans="3:4" ht="12.75" customHeight="1">
       <c r="C529" s="1"/>
       <c r="D529" s="1"/>
     </row>
-    <row r="530" ht="12.75" customHeight="1">
+    <row r="530" spans="3:4" ht="12.75" customHeight="1">
       <c r="C530" s="1"/>
       <c r="D530" s="1"/>
     </row>
-    <row r="531" ht="12.75" customHeight="1">
+    <row r="531" spans="3:4" ht="12.75" customHeight="1">
       <c r="C531" s="1"/>
       <c r="D531" s="1"/>
     </row>
-    <row r="532" ht="12.75" customHeight="1">
+    <row r="532" spans="3:4" ht="12.75" customHeight="1">
       <c r="C532" s="1"/>
       <c r="D532" s="1"/>
     </row>
-    <row r="533" ht="12.75" customHeight="1">
+    <row r="533" spans="3:4" ht="12.75" customHeight="1">
       <c r="C533" s="1"/>
       <c r="D533" s="1"/>
     </row>
-    <row r="534" ht="12.75" customHeight="1">
+    <row r="534" spans="3:4" ht="12.75" customHeight="1">
       <c r="C534" s="1"/>
       <c r="D534" s="1"/>
     </row>
-    <row r="535" ht="12.75" customHeight="1">
+    <row r="535" spans="3:4" ht="12.75" customHeight="1">
       <c r="C535" s="1"/>
       <c r="D535" s="1"/>
     </row>
-    <row r="536" ht="12.75" customHeight="1">
+    <row r="536" spans="3:4" ht="12.75" customHeight="1">
       <c r="C536" s="1"/>
       <c r="D536" s="1"/>
     </row>
-    <row r="537" ht="12.75" customHeight="1">
+    <row r="537" spans="3:4" ht="12.75" customHeight="1">
       <c r="C537" s="1"/>
       <c r="D537" s="1"/>
     </row>
-    <row r="538" ht="12.75" customHeight="1">
+    <row r="538" spans="3:4" ht="12.75" customHeight="1">
       <c r="C538" s="1"/>
       <c r="D538" s="1"/>
     </row>
-    <row r="539" ht="12.75" customHeight="1">
+    <row r="539" spans="3:4" ht="12.75" customHeight="1">
       <c r="C539" s="1"/>
       <c r="D539" s="1"/>
     </row>
-    <row r="540" ht="12.75" customHeight="1">
+    <row r="540" spans="3:4" ht="12.75" customHeight="1">
       <c r="C540" s="1"/>
       <c r="D540" s="1"/>
     </row>
-    <row r="541" ht="12.75" customHeight="1">
+    <row r="541" spans="3:4" ht="12.75" customHeight="1">
       <c r="C541" s="1"/>
       <c r="D541" s="1"/>
     </row>
-    <row r="542" ht="12.75" customHeight="1">
+    <row r="542" spans="3:4" ht="12.75" customHeight="1">
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
     </row>
-    <row r="543" ht="12.75" customHeight="1">
+    <row r="543" spans="3:4" ht="12.75" customHeight="1">
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
     </row>
-    <row r="544" ht="12.75" customHeight="1">
+    <row r="544" spans="3:4" ht="12.75" customHeight="1">
       <c r="C544" s="1"/>
       <c r="D544" s="1"/>
     </row>
-    <row r="545" ht="12.75" customHeight="1">
+    <row r="545" spans="3:4" ht="12.75" customHeight="1">
       <c r="C545" s="1"/>
       <c r="D545" s="1"/>
     </row>
-    <row r="546" ht="12.75" customHeight="1">
+    <row r="546" spans="3:4" ht="12.75" customHeight="1">
       <c r="C546" s="1"/>
       <c r="D546" s="1"/>
     </row>
-    <row r="547" ht="12.75" customHeight="1">
+    <row r="547" spans="3:4" ht="12.75" customHeight="1">
       <c r="C547" s="1"/>
       <c r="D547" s="1"/>
     </row>
-    <row r="548" ht="12.75" customHeight="1">
+    <row r="548" spans="3:4" ht="12.75" customHeight="1">
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
     </row>
-    <row r="549" ht="12.75" customHeight="1">
+    <row r="549" spans="3:4" ht="12.75" customHeight="1">
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
     </row>
-    <row r="550" ht="12.75" customHeight="1">
+    <row r="550" spans="3:4" ht="12.75" customHeight="1">
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
     </row>
-    <row r="551" ht="12.75" customHeight="1">
+    <row r="551" spans="3:4" ht="12.75" customHeight="1">
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
     </row>
-    <row r="552" ht="12.75" customHeight="1">
+    <row r="552" spans="3:4" ht="12.75" customHeight="1">
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
     </row>
-    <row r="553" ht="12.75" customHeight="1">
+    <row r="553" spans="3:4" ht="12.75" customHeight="1">
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
     </row>
-    <row r="554" ht="12.75" customHeight="1">
+    <row r="554" spans="3:4" ht="12.75" customHeight="1">
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
     </row>
-    <row r="555" ht="12.75" customHeight="1">
+    <row r="555" spans="3:4" ht="12.75" customHeight="1">
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
     </row>
-    <row r="556" ht="12.75" customHeight="1">
+    <row r="556" spans="3:4" ht="12.75" customHeight="1">
       <c r="C556" s="1"/>
       <c r="D556" s="1"/>
     </row>
-    <row r="557" ht="12.75" customHeight="1">
+    <row r="557" spans="3:4" ht="12.75" customHeight="1">
       <c r="C557" s="1"/>
       <c r="D557" s="1"/>
     </row>
-    <row r="558" ht="12.75" customHeight="1">
+    <row r="558" spans="3:4" ht="12.75" customHeight="1">
       <c r="C558" s="1"/>
       <c r="D558" s="1"/>
     </row>
-    <row r="559" ht="12.75" customHeight="1">
+    <row r="559" spans="3:4" ht="12.75" customHeight="1">
       <c r="C559" s="1"/>
       <c r="D559" s="1"/>
     </row>
-    <row r="560" ht="12.75" customHeight="1">
+    <row r="560" spans="3:4" ht="12.75" customHeight="1">
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
     </row>
-    <row r="561" ht="12.75" customHeight="1">
+    <row r="561" spans="3:4" ht="12.75" customHeight="1">
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
     </row>
-    <row r="562" ht="12.75" customHeight="1">
+    <row r="562" spans="3:4" ht="12.75" customHeight="1">
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
     </row>
-    <row r="563" ht="12.75" customHeight="1">
+    <row r="563" spans="3:4" ht="12.75" customHeight="1">
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
     </row>
-    <row r="564" ht="12.75" customHeight="1">
+    <row r="564" spans="3:4" ht="12.75" customHeight="1">
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
     </row>
-    <row r="565" ht="12.75" customHeight="1">
+    <row r="565" spans="3:4" ht="12.75" customHeight="1">
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
     </row>
-    <row r="566" ht="12.75" customHeight="1">
+    <row r="566" spans="3:4" ht="12.75" customHeight="1">
       <c r="C566" s="1"/>
       <c r="D566" s="1"/>
     </row>
-    <row r="567" ht="12.75" customHeight="1">
+    <row r="567" spans="3:4" ht="12.75" customHeight="1">
       <c r="C567" s="1"/>
       <c r="D567" s="1"/>
     </row>
-    <row r="568" ht="12.75" customHeight="1">
+    <row r="568" spans="3:4" ht="12.75" customHeight="1">
       <c r="C568" s="1"/>
       <c r="D568" s="1"/>
     </row>
-    <row r="569" ht="12.75" customHeight="1">
+    <row r="569" spans="3:4" ht="12.75" customHeight="1">
       <c r="C569" s="1"/>
       <c r="D569" s="1"/>
     </row>
-    <row r="570" ht="12.75" customHeight="1">
+    <row r="570" spans="3:4" ht="12.75" customHeight="1">
       <c r="C570" s="1"/>
       <c r="D570" s="1"/>
     </row>
-    <row r="571" ht="12.75" customHeight="1">
+    <row r="571" spans="3:4" ht="12.75" customHeight="1">
       <c r="C571" s="1"/>
       <c r="D571" s="1"/>
     </row>
-    <row r="572" ht="12.75" customHeight="1">
+    <row r="572" spans="3:4" ht="12.75" customHeight="1">
       <c r="C572" s="1"/>
       <c r="D572" s="1"/>
     </row>
-    <row r="573" ht="12.75" customHeight="1">
+    <row r="573" spans="3:4" ht="12.75" customHeight="1">
       <c r="C573" s="1"/>
       <c r="D573" s="1"/>
     </row>
-    <row r="574" ht="12.75" customHeight="1">
+    <row r="574" spans="3:4" ht="12.75" customHeight="1">
       <c r="C574" s="1"/>
       <c r="D574" s="1"/>
     </row>
-    <row r="575" ht="12.75" customHeight="1">
+    <row r="575" spans="3:4" ht="12.75" customHeight="1">
       <c r="C575" s="1"/>
       <c r="D575" s="1"/>
     </row>
-    <row r="576" ht="12.75" customHeight="1">
+    <row r="576" spans="3:4" ht="12.75" customHeight="1">
       <c r="C576" s="1"/>
       <c r="D576" s="1"/>
     </row>
-    <row r="577" ht="12.75" customHeight="1">
+    <row r="577" spans="3:4" ht="12.75" customHeight="1">
       <c r="C577" s="1"/>
       <c r="D577" s="1"/>
     </row>
-    <row r="578" ht="12.75" customHeight="1">
+    <row r="578" spans="3:4" ht="12.75" customHeight="1">
       <c r="C578" s="1"/>
       <c r="D578" s="1"/>
     </row>
-    <row r="579" ht="12.75" customHeight="1">
+    <row r="579" spans="3:4" ht="12.75" customHeight="1">
       <c r="C579" s="1"/>
       <c r="D579" s="1"/>
     </row>
-    <row r="580" ht="12.75" customHeight="1">
+    <row r="580" spans="3:4" ht="12.75" customHeight="1">
       <c r="C580" s="1"/>
       <c r="D580" s="1"/>
     </row>
-    <row r="581" ht="12.75" customHeight="1">
+    <row r="581" spans="3:4" ht="12.75" customHeight="1">
       <c r="C581" s="1"/>
       <c r="D581" s="1"/>
     </row>
-    <row r="582" ht="12.75" customHeight="1">
+    <row r="582" spans="3:4" ht="12.75" customHeight="1">
       <c r="C582" s="1"/>
       <c r="D582" s="1"/>
     </row>
-    <row r="583" ht="12.75" customHeight="1">
+    <row r="583" spans="3:4" ht="12.75" customHeight="1">
       <c r="C583" s="1"/>
       <c r="D583" s="1"/>
     </row>
-    <row r="584" ht="12.75" customHeight="1">
+    <row r="584" spans="3:4" ht="12.75" customHeight="1">
       <c r="C584" s="1"/>
       <c r="D584" s="1"/>
     </row>
-    <row r="585" ht="12.75" customHeight="1">
+    <row r="585" spans="3:4" ht="12.75" customHeight="1">
       <c r="C585" s="1"/>
       <c r="D585" s="1"/>
     </row>
-    <row r="586" ht="12.75" customHeight="1">
+    <row r="586" spans="3:4" ht="12.75" customHeight="1">
       <c r="C586" s="1"/>
       <c r="D586" s="1"/>
     </row>
-    <row r="587" ht="12.75" customHeight="1">
+    <row r="587" spans="3:4" ht="12.75" customHeight="1">
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
     </row>
-    <row r="588" ht="12.75" customHeight="1">
+    <row r="588" spans="3:4" ht="12.75" customHeight="1">
       <c r="C588" s="1"/>
       <c r="D588" s="1"/>
     </row>
-    <row r="589" ht="12.75" customHeight="1">
+    <row r="589" spans="3:4" ht="12.75" customHeight="1">
       <c r="C589" s="1"/>
       <c r="D589" s="1"/>
     </row>
-    <row r="590" ht="12.75" customHeight="1">
+    <row r="590" spans="3:4" ht="12.75" customHeight="1">
       <c r="C590" s="1"/>
       <c r="D590" s="1"/>
     </row>
-    <row r="591" ht="12.75" customHeight="1">
+    <row r="591" spans="3:4" ht="12.75" customHeight="1">
       <c r="C591" s="1"/>
       <c r="D591" s="1"/>
     </row>
-    <row r="592" ht="12.75" customHeight="1">
+    <row r="592" spans="3:4" ht="12.75" customHeight="1">
       <c r="C592" s="1"/>
       <c r="D592" s="1"/>
     </row>
-    <row r="593" ht="12.75" customHeight="1">
+    <row r="593" spans="3:4" ht="12.75" customHeight="1">
       <c r="C593" s="1"/>
       <c r="D593" s="1"/>
     </row>
-    <row r="594" ht="12.75" customHeight="1">
+    <row r="594" spans="3:4" ht="12.75" customHeight="1">
       <c r="C594" s="1"/>
       <c r="D594" s="1"/>
     </row>
-    <row r="595" ht="12.75" customHeight="1">
+    <row r="595" spans="3:4" ht="12.75" customHeight="1">
       <c r="C595" s="1"/>
       <c r="D595" s="1"/>
     </row>
-    <row r="596" ht="12.75" customHeight="1">
+    <row r="596" spans="3:4" ht="12.75" customHeight="1">
       <c r="C596" s="1"/>
       <c r="D596" s="1"/>
     </row>
-    <row r="597" ht="12.75" customHeight="1">
+    <row r="597" spans="3:4" ht="12.75" customHeight="1">
       <c r="C597" s="1"/>
       <c r="D597" s="1"/>
     </row>
-    <row r="598" ht="12.75" customHeight="1">
+    <row r="598" spans="3:4" ht="12.75" customHeight="1">
       <c r="C598" s="1"/>
       <c r="D598" s="1"/>
     </row>
-    <row r="599" ht="12.75" customHeight="1">
+    <row r="599" spans="3:4" ht="12.75" customHeight="1">
       <c r="C599" s="1"/>
       <c r="D599" s="1"/>
     </row>
-    <row r="600" ht="12.75" customHeight="1">
+    <row r="600" spans="3:4" ht="12.75" customHeight="1">
       <c r="C600" s="1"/>
       <c r="D600" s="1"/>
     </row>
-    <row r="601" ht="12.75" customHeight="1">
+    <row r="601" spans="3:4" ht="12.75" customHeight="1">
       <c r="C601" s="1"/>
       <c r="D601" s="1"/>
     </row>
-    <row r="602" ht="12.75" customHeight="1">
+    <row r="602" spans="3:4" ht="12.75" customHeight="1">
       <c r="C602" s="1"/>
       <c r="D602" s="1"/>
     </row>
-    <row r="603" ht="12.75" customHeight="1">
+    <row r="603" spans="3:4" ht="12.75" customHeight="1">
       <c r="C603" s="1"/>
       <c r="D603" s="1"/>
     </row>
-    <row r="604" ht="12.75" customHeight="1">
+    <row r="604" spans="3:4" ht="12.75" customHeight="1">
       <c r="C604" s="1"/>
       <c r="D604" s="1"/>
     </row>
-    <row r="605" ht="12.75" customHeight="1">
+    <row r="605" spans="3:4" ht="12.75" customHeight="1">
       <c r="C605" s="1"/>
       <c r="D605" s="1"/>
     </row>
-    <row r="606" ht="12.75" customHeight="1">
+    <row r="606" spans="3:4" ht="12.75" customHeight="1">
       <c r="C606" s="1"/>
       <c r="D606" s="1"/>
     </row>
-    <row r="607" ht="12.75" customHeight="1">
+    <row r="607" spans="3:4" ht="12.75" customHeight="1">
       <c r="C607" s="1"/>
       <c r="D607" s="1"/>
     </row>
-    <row r="608" ht="12.75" customHeight="1">
+    <row r="608" spans="3:4" ht="12.75" customHeight="1">
       <c r="C608" s="1"/>
       <c r="D608" s="1"/>
     </row>
-    <row r="609" ht="12.75" customHeight="1">
+    <row r="609" spans="3:4" ht="12.75" customHeight="1">
       <c r="C609" s="1"/>
       <c r="D609" s="1"/>
     </row>
-    <row r="610" ht="12.75" customHeight="1">
+    <row r="610" spans="3:4" ht="12.75" customHeight="1">
       <c r="C610" s="1"/>
       <c r="D610" s="1"/>
     </row>
-    <row r="611" ht="12.75" customHeight="1">
+    <row r="611" spans="3:4" ht="12.75" customHeight="1">
       <c r="C611" s="1"/>
       <c r="D611" s="1"/>
     </row>
-    <row r="612" ht="12.75" customHeight="1">
+    <row r="612" spans="3:4" ht="12.75" customHeight="1">
       <c r="C612" s="1"/>
       <c r="D612" s="1"/>
     </row>
-    <row r="613" ht="12.75" customHeight="1">
+    <row r="613" spans="3:4" ht="12.75" customHeight="1">
       <c r="C613" s="1"/>
       <c r="D613" s="1"/>
     </row>
-    <row r="614" ht="12.75" customHeight="1">
+    <row r="614" spans="3:4" ht="12.75" customHeight="1">
       <c r="C614" s="1"/>
       <c r="D614" s="1"/>
     </row>
-    <row r="615" ht="12.75" customHeight="1">
+    <row r="615" spans="3:4" ht="12.75" customHeight="1">
       <c r="C615" s="1"/>
       <c r="D615" s="1"/>
     </row>
-    <row r="616" ht="12.75" customHeight="1">
+    <row r="616" spans="3:4" ht="12.75" customHeight="1">
       <c r="C616" s="1"/>
       <c r="D616" s="1"/>
     </row>
-    <row r="617" ht="12.75" customHeight="1">
+    <row r="617" spans="3:4" ht="12.75" customHeight="1">
       <c r="C617" s="1"/>
       <c r="D617" s="1"/>
     </row>
-    <row r="618" ht="12.75" customHeight="1">
+    <row r="618" spans="3:4" ht="12.75" customHeight="1">
       <c r="C618" s="1"/>
       <c r="D618" s="1"/>
     </row>
-    <row r="619" ht="12.75" customHeight="1">
+    <row r="619" spans="3:4" ht="12.75" customHeight="1">
       <c r="C619" s="1"/>
       <c r="D619" s="1"/>
     </row>
-    <row r="620" ht="12.75" customHeight="1">
+    <row r="620" spans="3:4" ht="12.75" customHeight="1">
       <c r="C620" s="1"/>
       <c r="D620" s="1"/>
     </row>
-    <row r="621" ht="12.75" customHeight="1">
+    <row r="621" spans="3:4" ht="12.75" customHeight="1">
       <c r="C621" s="1"/>
       <c r="D621" s="1"/>
     </row>
-    <row r="622" ht="12.75" customHeight="1">
+    <row r="622" spans="3:4" ht="12.75" customHeight="1">
       <c r="C622" s="1"/>
       <c r="D622" s="1"/>
     </row>
-    <row r="623" ht="12.75" customHeight="1">
+    <row r="623" spans="3:4" ht="12.75" customHeight="1">
       <c r="C623" s="1"/>
       <c r="D623" s="1"/>
     </row>
-    <row r="624" ht="12.75" customHeight="1">
+    <row r="624" spans="3:4" ht="12.75" customHeight="1">
       <c r="C624" s="1"/>
       <c r="D624" s="1"/>
     </row>
-    <row r="625" ht="12.75" customHeight="1">
+    <row r="625" spans="3:4" ht="12.75" customHeight="1">
       <c r="C625" s="1"/>
       <c r="D625" s="1"/>
     </row>
-    <row r="626" ht="12.75" customHeight="1">
+    <row r="626" spans="3:4" ht="12.75" customHeight="1">
       <c r="C626" s="1"/>
       <c r="D626" s="1"/>
     </row>
-    <row r="627" ht="12.75" customHeight="1">
+    <row r="627" spans="3:4" ht="12.75" customHeight="1">
       <c r="C627" s="1"/>
       <c r="D627" s="1"/>
     </row>
-    <row r="628" ht="12.75" customHeight="1">
+    <row r="628" spans="3:4" ht="12.75" customHeight="1">
       <c r="C628" s="1"/>
       <c r="D628" s="1"/>
     </row>
-    <row r="629" ht="12.75" customHeight="1">
+    <row r="629" spans="3:4" ht="12.75" customHeight="1">
       <c r="C629" s="1"/>
       <c r="D629" s="1"/>
     </row>
-    <row r="630" ht="12.75" customHeight="1">
+    <row r="630" spans="3:4" ht="12.75" customHeight="1">
       <c r="C630" s="1"/>
       <c r="D630" s="1"/>
     </row>
-    <row r="631" ht="12.75" customHeight="1">
+    <row r="631" spans="3:4" ht="12.75" customHeight="1">
       <c r="C631" s="1"/>
       <c r="D631" s="1"/>
     </row>
-    <row r="632" ht="12.75" customHeight="1">
+    <row r="632" spans="3:4" ht="12.75" customHeight="1">
       <c r="C632" s="1"/>
       <c r="D632" s="1"/>
     </row>
-    <row r="633" ht="12.75" customHeight="1">
+    <row r="633" spans="3:4" ht="12.75" customHeight="1">
       <c r="C633" s="1"/>
       <c r="D633" s="1"/>
     </row>
-    <row r="634" ht="12.75" customHeight="1">
+    <row r="634" spans="3:4" ht="12.75" customHeight="1">
       <c r="C634" s="1"/>
       <c r="D634" s="1"/>
     </row>
-    <row r="635" ht="12.75" customHeight="1">
+    <row r="635" spans="3:4" ht="12.75" customHeight="1">
       <c r="C635" s="1"/>
       <c r="D635" s="1"/>
     </row>
-    <row r="636" ht="12.75" customHeight="1">
+    <row r="636" spans="3:4" ht="12.75" customHeight="1">
       <c r="C636" s="1"/>
       <c r="D636" s="1"/>
     </row>
-    <row r="637" ht="12.75" customHeight="1">
+    <row r="637" spans="3:4" ht="12.75" customHeight="1">
       <c r="C637" s="1"/>
       <c r="D637" s="1"/>
     </row>
-    <row r="638" ht="12.75" customHeight="1">
+    <row r="638" spans="3:4" ht="12.75" customHeight="1">
       <c r="C638" s="1"/>
       <c r="D638" s="1"/>
     </row>
-    <row r="639" ht="12.75" customHeight="1">
+    <row r="639" spans="3:4" ht="12.75" customHeight="1">
       <c r="C639" s="1"/>
       <c r="D639" s="1"/>
     </row>
-    <row r="640" ht="12.75" customHeight="1">
+    <row r="640" spans="3:4" ht="12.75" customHeight="1">
       <c r="C640" s="1"/>
       <c r="D640" s="1"/>
     </row>
-    <row r="641" ht="12.75" customHeight="1">
+    <row r="641" spans="3:4" ht="12.75" customHeight="1">
       <c r="C641" s="1"/>
       <c r="D641" s="1"/>
     </row>
-    <row r="642" ht="12.75" customHeight="1">
+    <row r="642" spans="3:4" ht="12.75" customHeight="1">
       <c r="C642" s="1"/>
       <c r="D642" s="1"/>
     </row>
-    <row r="643" ht="12.75" customHeight="1">
+    <row r="643" spans="3:4" ht="12.75" customHeight="1">
       <c r="C643" s="1"/>
       <c r="D643" s="1"/>
     </row>
-    <row r="644" ht="12.75" customHeight="1">
+    <row r="644" spans="3:4" ht="12.75" customHeight="1">
       <c r="C644" s="1"/>
       <c r="D644" s="1"/>
     </row>
-    <row r="645" ht="12.75" customHeight="1">
+    <row r="645" spans="3:4" ht="12.75" customHeight="1">
       <c r="C645" s="1"/>
       <c r="D645" s="1"/>
     </row>
-    <row r="646" ht="12.75" customHeight="1">
+    <row r="646" spans="3:4" ht="12.75" customHeight="1">
       <c r="C646" s="1"/>
       <c r="D646" s="1"/>
     </row>
-    <row r="647" ht="12.75" customHeight="1">
+    <row r="647" spans="3:4" ht="12.75" customHeight="1">
       <c r="C647" s="1"/>
       <c r="D647" s="1"/>
     </row>
-    <row r="648" ht="12.75" customHeight="1">
+    <row r="648" spans="3:4" ht="12.75" customHeight="1">
       <c r="C648" s="1"/>
       <c r="D648" s="1"/>
     </row>
-    <row r="649" ht="12.75" customHeight="1">
+    <row r="649" spans="3:4" ht="12.75" customHeight="1">
       <c r="C649" s="1"/>
       <c r="D649" s="1"/>
     </row>
-    <row r="650" ht="12.75" customHeight="1">
+    <row r="650" spans="3:4" ht="12.75" customHeight="1">
       <c r="C650" s="1"/>
       <c r="D650" s="1"/>
     </row>
-    <row r="651" ht="12.75" customHeight="1">
+    <row r="651" spans="3:4" ht="12.75" customHeight="1">
       <c r="C651" s="1"/>
       <c r="D651" s="1"/>
     </row>
-    <row r="652" ht="12.75" customHeight="1">
+    <row r="652" spans="3:4" ht="12.75" customHeight="1">
       <c r="C652" s="1"/>
       <c r="D652" s="1"/>
     </row>
-    <row r="653" ht="12.75" customHeight="1">
+    <row r="653" spans="3:4" ht="12.75" customHeight="1">
       <c r="C653" s="1"/>
       <c r="D653" s="1"/>
     </row>
-    <row r="654" ht="12.75" customHeight="1">
+    <row r="654" spans="3:4" ht="12.75" customHeight="1">
       <c r="C654" s="1"/>
       <c r="D654" s="1"/>
     </row>
-    <row r="655" ht="12.75" customHeight="1">
+    <row r="655" spans="3:4" ht="12.75" customHeight="1">
       <c r="C655" s="1"/>
       <c r="D655" s="1"/>
     </row>
-    <row r="656" ht="12.75" customHeight="1">
+    <row r="656" spans="3:4" ht="12.75" customHeight="1">
       <c r="C656" s="1"/>
       <c r="D656" s="1"/>
     </row>
-    <row r="657" ht="12.75" customHeight="1">
+    <row r="657" spans="3:4" ht="12.75" customHeight="1">
       <c r="C657" s="1"/>
       <c r="D657" s="1"/>
     </row>
-    <row r="658" ht="12.75" customHeight="1">
+    <row r="658" spans="3:4" ht="12.75" customHeight="1">
       <c r="C658" s="1"/>
       <c r="D658" s="1"/>
     </row>
-    <row r="659" ht="12.75" customHeight="1">
+    <row r="659" spans="3:4" ht="12.75" customHeight="1">
       <c r="C659" s="1"/>
       <c r="D659" s="1"/>
     </row>
-    <row r="660" ht="12.75" customHeight="1">
+    <row r="660" spans="3:4" ht="12.75" customHeight="1">
       <c r="C660" s="1"/>
       <c r="D660" s="1"/>
     </row>
-    <row r="661" ht="12.75" customHeight="1">
+    <row r="661" spans="3:4" ht="12.75" customHeight="1">
       <c r="C661" s="1"/>
       <c r="D661" s="1"/>
     </row>
-    <row r="662" ht="12.75" customHeight="1">
+    <row r="662" spans="3:4" ht="12.75" customHeight="1">
       <c r="C662" s="1"/>
       <c r="D662" s="1"/>
     </row>
-    <row r="663" ht="12.75" customHeight="1">
+    <row r="663" spans="3:4" ht="12.75" customHeight="1">
       <c r="C663" s="1"/>
       <c r="D663" s="1"/>
     </row>
-    <row r="664" ht="12.75" customHeight="1">
+    <row r="664" spans="3:4" ht="12.75" customHeight="1">
       <c r="C664" s="1"/>
       <c r="D664" s="1"/>
     </row>
-    <row r="665" ht="12.75" customHeight="1">
+    <row r="665" spans="3:4" ht="12.75" customHeight="1">
       <c r="C665" s="1"/>
       <c r="D665" s="1"/>
     </row>
-    <row r="666" ht="12.75" customHeight="1">
+    <row r="666" spans="3:4" ht="12.75" customHeight="1">
       <c r="C666" s="1"/>
       <c r="D666" s="1"/>
     </row>
-    <row r="667" ht="12.75" customHeight="1">
+    <row r="667" spans="3:4" ht="12.75" customHeight="1">
       <c r="C667" s="1"/>
       <c r="D667" s="1"/>
     </row>
-    <row r="668" ht="12.75" customHeight="1">
+    <row r="668" spans="3:4" ht="12.75" customHeight="1">
       <c r="C668" s="1"/>
       <c r="D668" s="1"/>
     </row>
-    <row r="669" ht="12.75" customHeight="1">
+    <row r="669" spans="3:4" ht="12.75" customHeight="1">
       <c r="C669" s="1"/>
       <c r="D669" s="1"/>
     </row>
-    <row r="670" ht="12.75" customHeight="1">
+    <row r="670" spans="3:4" ht="12.75" customHeight="1">
       <c r="C670" s="1"/>
       <c r="D670" s="1"/>
     </row>
-    <row r="671" ht="12.75" customHeight="1">
+    <row r="671" spans="3:4" ht="12.75" customHeight="1">
       <c r="C671" s="1"/>
       <c r="D671" s="1"/>
     </row>
-    <row r="672" ht="12.75" customHeight="1">
+    <row r="672" spans="3:4" ht="12.75" customHeight="1">
       <c r="C672" s="1"/>
       <c r="D672" s="1"/>
     </row>
-    <row r="673" ht="12.75" customHeight="1">
+    <row r="673" spans="3:4" ht="12.75" customHeight="1">
       <c r="C673" s="1"/>
       <c r="D673" s="1"/>
     </row>
-    <row r="674" ht="12.75" customHeight="1">
+    <row r="674" spans="3:4" ht="12.75" customHeight="1">
       <c r="C674" s="1"/>
       <c r="D674" s="1"/>
     </row>
-    <row r="675" ht="12.75" customHeight="1">
+    <row r="675" spans="3:4" ht="12.75" customHeight="1">
       <c r="C675" s="1"/>
       <c r="D675" s="1"/>
     </row>
-    <row r="676" ht="12.75" customHeight="1">
+    <row r="676" spans="3:4" ht="12.75" customHeight="1">
       <c r="C676" s="1"/>
       <c r="D676" s="1"/>
     </row>
-    <row r="677" ht="12.75" customHeight="1">
+    <row r="677" spans="3:4" ht="12.75" customHeight="1">
       <c r="C677" s="1"/>
       <c r="D677" s="1"/>
     </row>
-    <row r="678" ht="12.75" customHeight="1">
+    <row r="678" spans="3:4" ht="12.75" customHeight="1">
       <c r="C678" s="1"/>
       <c r="D678" s="1"/>
     </row>
-    <row r="679" ht="12.75" customHeight="1">
+    <row r="679" spans="3:4" ht="12.75" customHeight="1">
       <c r="C679" s="1"/>
       <c r="D679" s="1"/>
     </row>
-    <row r="680" ht="12.75" customHeight="1">
+    <row r="680" spans="3:4" ht="12.75" customHeight="1">
       <c r="C680" s="1"/>
       <c r="D680" s="1"/>
     </row>
-    <row r="681" ht="12.75" customHeight="1">
+    <row r="681" spans="3:4" ht="12.75" customHeight="1">
       <c r="C681" s="1"/>
       <c r="D681" s="1"/>
     </row>
-    <row r="682" ht="12.75" customHeight="1">
+    <row r="682" spans="3:4" ht="12.75" customHeight="1">
       <c r="C682" s="1"/>
       <c r="D682" s="1"/>
     </row>
-    <row r="683" ht="12.75" customHeight="1">
+    <row r="683" spans="3:4" ht="12.75" customHeight="1">
       <c r="C683" s="1"/>
       <c r="D683" s="1"/>
     </row>
-    <row r="684" ht="12.75" customHeight="1">
+    <row r="684" spans="3:4" ht="12.75" customHeight="1">
       <c r="C684" s="1"/>
       <c r="D684" s="1"/>
     </row>
-    <row r="685" ht="12.75" customHeight="1">
+    <row r="685" spans="3:4" ht="12.75" customHeight="1">
       <c r="C685" s="1"/>
       <c r="D685" s="1"/>
     </row>
-    <row r="686" ht="12.75" customHeight="1">
+    <row r="686" spans="3:4" ht="12.75" customHeight="1">
       <c r="C686" s="1"/>
       <c r="D686" s="1"/>
     </row>
-    <row r="687" ht="12.75" customHeight="1">
+    <row r="687" spans="3:4" ht="12.75" customHeight="1">
       <c r="C687" s="1"/>
       <c r="D687" s="1"/>
     </row>
-    <row r="688" ht="12.75" customHeight="1">
+    <row r="688" spans="3:4" ht="12.75" customHeight="1">
       <c r="C688" s="1"/>
       <c r="D688" s="1"/>
     </row>
-    <row r="689" ht="12.75" customHeight="1">
+    <row r="689" spans="3:4" ht="12.75" customHeight="1">
       <c r="C689" s="1"/>
       <c r="D689" s="1"/>
     </row>
-    <row r="690" ht="12.75" customHeight="1">
+    <row r="690" spans="3:4" ht="12.75" customHeight="1">
       <c r="C690" s="1"/>
       <c r="D690" s="1"/>
     </row>
-    <row r="691" ht="12.75" customHeight="1">
+    <row r="691" spans="3:4" ht="12.75" customHeight="1">
       <c r="C691" s="1"/>
       <c r="D691" s="1"/>
     </row>
-    <row r="692" ht="12.75" customHeight="1">
+    <row r="692" spans="3:4" ht="12.75" customHeight="1">
       <c r="C692" s="1"/>
       <c r="D692" s="1"/>
     </row>
-    <row r="693" ht="12.75" customHeight="1">
+    <row r="693" spans="3:4" ht="12.75" customHeight="1">
       <c r="C693" s="1"/>
       <c r="D693" s="1"/>
     </row>
-    <row r="694" ht="12.75" customHeight="1">
+    <row r="694" spans="3:4" ht="12.75" customHeight="1">
       <c r="C694" s="1"/>
       <c r="D694" s="1"/>
     </row>
-    <row r="695" ht="12.75" customHeight="1">
+    <row r="695" spans="3:4" ht="12.75" customHeight="1">
       <c r="C695" s="1"/>
       <c r="D695" s="1"/>
     </row>
-    <row r="696" ht="12.75" customHeight="1">
+    <row r="696" spans="3:4" ht="12.75" customHeight="1">
       <c r="C696" s="1"/>
       <c r="D696" s="1"/>
     </row>
-    <row r="697" ht="12.75" customHeight="1">
+    <row r="697" spans="3:4" ht="12.75" customHeight="1">
       <c r="C697" s="1"/>
       <c r="D697" s="1"/>
     </row>
-    <row r="698" ht="12.75" customHeight="1">
+    <row r="698" spans="3:4" ht="12.75" customHeight="1">
       <c r="C698" s="1"/>
       <c r="D698" s="1"/>
     </row>
-    <row r="699" ht="12.75" customHeight="1">
+    <row r="699" spans="3:4" ht="12.75" customHeight="1">
       <c r="C699" s="1"/>
       <c r="D699" s="1"/>
     </row>
-    <row r="700" ht="12.75" customHeight="1">
+    <row r="700" spans="3:4" ht="12.75" customHeight="1">
       <c r="C700" s="1"/>
       <c r="D700" s="1"/>
     </row>
-    <row r="701" ht="12.75" customHeight="1">
+    <row r="701" spans="3:4" ht="12.75" customHeight="1">
       <c r="C701" s="1"/>
       <c r="D701" s="1"/>
     </row>
-    <row r="702" ht="12.75" customHeight="1">
+    <row r="702" spans="3:4" ht="12.75" customHeight="1">
       <c r="C702" s="1"/>
       <c r="D702" s="1"/>
     </row>
-    <row r="703" ht="12.75" customHeight="1">
+    <row r="703" spans="3:4" ht="12.75" customHeight="1">
       <c r="C703" s="1"/>
       <c r="D703" s="1"/>
     </row>
-    <row r="704" ht="12.75" customHeight="1">
+    <row r="704" spans="3:4" ht="12.75" customHeight="1">
       <c r="C704" s="1"/>
       <c r="D704" s="1"/>
     </row>
-    <row r="705" ht="12.75" customHeight="1">
+    <row r="705" spans="3:4" ht="12.75" customHeight="1">
       <c r="C705" s="1"/>
       <c r="D705" s="1"/>
     </row>
-    <row r="706" ht="12.75" customHeight="1">
+    <row r="706" spans="3:4" ht="12.75" customHeight="1">
       <c r="C706" s="1"/>
       <c r="D706" s="1"/>
     </row>
-    <row r="707" ht="12.75" customHeight="1">
+    <row r="707" spans="3:4" ht="12.75" customHeight="1">
       <c r="C707" s="1"/>
       <c r="D707" s="1"/>
     </row>
-    <row r="708" ht="12.75" customHeight="1">
+    <row r="708" spans="3:4" ht="12.75" customHeight="1">
       <c r="C708" s="1"/>
       <c r="D708" s="1"/>
     </row>
-    <row r="709" ht="12.75" customHeight="1">
+    <row r="709" spans="3:4" ht="12.75" customHeight="1">
       <c r="C709" s="1"/>
       <c r="D709" s="1"/>
     </row>
-    <row r="710" ht="12.75" customHeight="1">
+    <row r="710" spans="3:4" ht="12.75" customHeight="1">
       <c r="C710" s="1"/>
       <c r="D710" s="1"/>
     </row>
-    <row r="711" ht="12.75" customHeight="1">
+    <row r="711" spans="3:4" ht="12.75" customHeight="1">
       <c r="C711" s="1"/>
       <c r="D711" s="1"/>
     </row>
-    <row r="712" ht="12.75" customHeight="1">
+    <row r="712" spans="3:4" ht="12.75" customHeight="1">
       <c r="C712" s="1"/>
       <c r="D712" s="1"/>
     </row>
-    <row r="713" ht="12.75" customHeight="1">
+    <row r="713" spans="3:4" ht="12.75" customHeight="1">
       <c r="C713" s="1"/>
       <c r="D713" s="1"/>
     </row>
-    <row r="714" ht="12.75" customHeight="1">
+    <row r="714" spans="3:4" ht="12.75" customHeight="1">
       <c r="C714" s="1"/>
       <c r="D714" s="1"/>
     </row>
-    <row r="715" ht="12.75" customHeight="1">
+    <row r="715" spans="3:4" ht="12.75" customHeight="1">
       <c r="C715" s="1"/>
       <c r="D715" s="1"/>
     </row>
-    <row r="716" ht="12.75" customHeight="1">
+    <row r="716" spans="3:4" ht="12.75" customHeight="1">
       <c r="C716" s="1"/>
       <c r="D716" s="1"/>
     </row>
-    <row r="717" ht="12.75" customHeight="1">
+    <row r="717" spans="3:4" ht="12.75" customHeight="1">
       <c r="C717" s="1"/>
       <c r="D717" s="1"/>
     </row>
-    <row r="718" ht="12.75" customHeight="1">
+    <row r="718" spans="3:4" ht="12.75" customHeight="1">
       <c r="C718" s="1"/>
       <c r="D718" s="1"/>
     </row>
-    <row r="719" ht="12.75" customHeight="1">
+    <row r="719" spans="3:4" ht="12.75" customHeight="1">
       <c r="C719" s="1"/>
       <c r="D719" s="1"/>
     </row>
-    <row r="720" ht="12.75" customHeight="1">
+    <row r="720" spans="3:4" ht="12.75" customHeight="1">
       <c r="C720" s="1"/>
       <c r="D720" s="1"/>
     </row>
-    <row r="721" ht="12.75" customHeight="1">
+    <row r="721" spans="3:4" ht="12.75" customHeight="1">
       <c r="C721" s="1"/>
       <c r="D721" s="1"/>
     </row>
-    <row r="722" ht="12.75" customHeight="1">
+    <row r="722" spans="3:4" ht="12.75" customHeight="1">
       <c r="C722" s="1"/>
       <c r="D722" s="1"/>
     </row>
-    <row r="723" ht="12.75" customHeight="1">
+    <row r="723" spans="3:4" ht="12.75" customHeight="1">
       <c r="C723" s="1"/>
       <c r="D723" s="1"/>
     </row>
-    <row r="724" ht="12.75" customHeight="1">
+    <row r="724" spans="3:4" ht="12.75" customHeight="1">
       <c r="C724" s="1"/>
       <c r="D724" s="1"/>
     </row>
-    <row r="725" ht="12.75" customHeight="1">
+    <row r="725" spans="3:4" ht="12.75" customHeight="1">
       <c r="C725" s="1"/>
       <c r="D725" s="1"/>
     </row>
-    <row r="726" ht="12.75" customHeight="1">
+    <row r="726" spans="3:4" ht="12.75" customHeight="1">
       <c r="C726" s="1"/>
       <c r="D726" s="1"/>
     </row>
-    <row r="727" ht="12.75" customHeight="1">
+    <row r="727" spans="3:4" ht="12.75" customHeight="1">
       <c r="C727" s="1"/>
       <c r="D727" s="1"/>
     </row>
-    <row r="728" ht="12.75" customHeight="1">
+    <row r="728" spans="3:4" ht="12.75" customHeight="1">
       <c r="C728" s="1"/>
       <c r="D728" s="1"/>
     </row>
-    <row r="729" ht="12.75" customHeight="1">
+    <row r="729" spans="3:4" ht="12.75" customHeight="1">
       <c r="C729" s="1"/>
       <c r="D729" s="1"/>
     </row>
-    <row r="730" ht="12.75" customHeight="1">
+    <row r="730" spans="3:4" ht="12.75" customHeight="1">
       <c r="C730" s="1"/>
       <c r="D730" s="1"/>
     </row>
-    <row r="731" ht="12.75" customHeight="1">
+    <row r="731" spans="3:4" ht="12.75" customHeight="1">
       <c r="C731" s="1"/>
       <c r="D731" s="1"/>
     </row>
-    <row r="732" ht="12.75" customHeight="1">
+    <row r="732" spans="3:4" ht="12.75" customHeight="1">
       <c r="C732" s="1"/>
       <c r="D732" s="1"/>
     </row>
-    <row r="733" ht="12.75" customHeight="1">
+    <row r="733" spans="3:4" ht="12.75" customHeight="1">
       <c r="C733" s="1"/>
       <c r="D733" s="1"/>
     </row>
-    <row r="734" ht="12.75" customHeight="1">
+    <row r="734" spans="3:4" ht="12.75" customHeight="1">
       <c r="C734" s="1"/>
       <c r="D734" s="1"/>
     </row>
-    <row r="735" ht="12.75" customHeight="1">
+    <row r="735" spans="3:4" ht="12.75" customHeight="1">
       <c r="C735" s="1"/>
       <c r="D735" s="1"/>
     </row>
-    <row r="736" ht="12.75" customHeight="1">
+    <row r="736" spans="3:4" ht="12.75" customHeight="1">
       <c r="C736" s="1"/>
       <c r="D736" s="1"/>
     </row>
-    <row r="737" ht="12.75" customHeight="1">
+    <row r="737" spans="3:4" ht="12.75" customHeight="1">
       <c r="C737" s="1"/>
       <c r="D737" s="1"/>
     </row>
-    <row r="738" ht="12.75" customHeight="1">
+    <row r="738" spans="3:4" ht="12.75" customHeight="1">
       <c r="C738" s="1"/>
       <c r="D738" s="1"/>
     </row>
-    <row r="739" ht="12.75" customHeight="1">
+    <row r="739" spans="3:4" ht="12.75" customHeight="1">
       <c r="C739" s="1"/>
       <c r="D739" s="1"/>
     </row>
-    <row r="740" ht="12.75" customHeight="1">
+    <row r="740" spans="3:4" ht="12.75" customHeight="1">
       <c r="C740" s="1"/>
       <c r="D740" s="1"/>
     </row>
-    <row r="741" ht="12.75" customHeight="1">
+    <row r="741" spans="3:4" ht="12.75" customHeight="1">
       <c r="C741" s="1"/>
       <c r="D741" s="1"/>
     </row>
-    <row r="742" ht="12.75" customHeight="1">
+    <row r="742" spans="3:4" ht="12.75" customHeight="1">
       <c r="C742" s="1"/>
       <c r="D742" s="1"/>
     </row>
-    <row r="743" ht="12.75" customHeight="1">
+    <row r="743" spans="3:4" ht="12.75" customHeight="1">
       <c r="C743" s="1"/>
       <c r="D743" s="1"/>
     </row>
-    <row r="744" ht="12.75" customHeight="1">
+    <row r="744" spans="3:4" ht="12.75" customHeight="1">
       <c r="C744" s="1"/>
       <c r="D744" s="1"/>
     </row>
-    <row r="745" ht="12.75" customHeight="1">
+    <row r="745" spans="3:4" ht="12.75" customHeight="1">
       <c r="C745" s="1"/>
       <c r="D745" s="1"/>
     </row>
-    <row r="746" ht="12.75" customHeight="1">
+    <row r="746" spans="3:4" ht="12.75" customHeight="1">
       <c r="C746" s="1"/>
       <c r="D746" s="1"/>
     </row>
-    <row r="747" ht="12.75" customHeight="1">
+    <row r="747" spans="3:4" ht="12.75" customHeight="1">
       <c r="C747" s="1"/>
       <c r="D747" s="1"/>
     </row>
-    <row r="748" ht="12.75" customHeight="1">
+    <row r="748" spans="3:4" ht="12.75" customHeight="1">
       <c r="C748" s="1"/>
       <c r="D748" s="1"/>
     </row>
-    <row r="749" ht="12.75" customHeight="1">
+    <row r="749" spans="3:4" ht="12.75" customHeight="1">
       <c r="C749" s="1"/>
       <c r="D749" s="1"/>
     </row>
-    <row r="750" ht="12.75" customHeight="1">
+    <row r="750" spans="3:4" ht="12.75" customHeight="1">
       <c r="C750" s="1"/>
       <c r="D750" s="1"/>
     </row>
-    <row r="751" ht="12.75" customHeight="1">
+    <row r="751" spans="3:4" ht="12.75" customHeight="1">
       <c r="C751" s="1"/>
       <c r="D751" s="1"/>
     </row>
-    <row r="752" ht="12.75" customHeight="1">
+    <row r="752" spans="3:4" ht="12.75" customHeight="1">
       <c r="C752" s="1"/>
       <c r="D752" s="1"/>
     </row>
-    <row r="753" ht="12.75" customHeight="1">
+    <row r="753" spans="3:4" ht="12.75" customHeight="1">
       <c r="C753" s="1"/>
       <c r="D753" s="1"/>
     </row>
-    <row r="754" ht="12.75" customHeight="1">
+    <row r="754" spans="3:4" ht="12.75" customHeight="1">
       <c r="C754" s="1"/>
       <c r="D754" s="1"/>
     </row>
-    <row r="755" ht="12.75" customHeight="1">
+    <row r="755" spans="3:4" ht="12.75" customHeight="1">
       <c r="C755" s="1"/>
       <c r="D755" s="1"/>
     </row>
-    <row r="756" ht="12.75" customHeight="1">
+    <row r="756" spans="3:4" ht="12.75" customHeight="1">
       <c r="C756" s="1"/>
       <c r="D756" s="1"/>
     </row>
-    <row r="757" ht="12.75" customHeight="1">
+    <row r="757" spans="3:4" ht="12.75" customHeight="1">
       <c r="C757" s="1"/>
       <c r="D757" s="1"/>
     </row>
-    <row r="758" ht="12.75" customHeight="1">
+    <row r="758" spans="3:4" ht="12.75" customHeight="1">
       <c r="C758" s="1"/>
       <c r="D758" s="1"/>
     </row>
-    <row r="759" ht="12.75" customHeight="1">
+    <row r="759" spans="3:4" ht="12.75" customHeight="1">
       <c r="C759" s="1"/>
       <c r="D759" s="1"/>
     </row>
-    <row r="760" ht="12.75" customHeight="1">
+    <row r="760" spans="3:4" ht="12.75" customHeight="1">
       <c r="C760" s="1"/>
       <c r="D760" s="1"/>
     </row>
-    <row r="761" ht="12.75" customHeight="1">
+    <row r="761" spans="3:4" ht="12.75" customHeight="1">
       <c r="C761" s="1"/>
       <c r="D761" s="1"/>
     </row>
-    <row r="762" ht="12.75" customHeight="1">
+    <row r="762" spans="3:4" ht="12.75" customHeight="1">
       <c r="C762" s="1"/>
       <c r="D762" s="1"/>
     </row>
-    <row r="763" ht="12.75" customHeight="1">
+    <row r="763" spans="3:4" ht="12.75" customHeight="1">
       <c r="C763" s="1"/>
       <c r="D763" s="1"/>
     </row>
-    <row r="764" ht="12.75" customHeight="1">
+    <row r="764" spans="3:4" ht="12.75" customHeight="1">
       <c r="C764" s="1"/>
       <c r="D764" s="1"/>
     </row>
-    <row r="765" ht="12.75" customHeight="1">
+    <row r="765" spans="3:4" ht="12.75" customHeight="1">
       <c r="C765" s="1"/>
       <c r="D765" s="1"/>
     </row>
-    <row r="766" ht="12.75" customHeight="1">
+    <row r="766" spans="3:4" ht="12.75" customHeight="1">
       <c r="C766" s="1"/>
       <c r="D766" s="1"/>
     </row>
-    <row r="767" ht="12.75" customHeight="1">
+    <row r="767" spans="3:4" ht="12.75" customHeight="1">
       <c r="C767" s="1"/>
       <c r="D767" s="1"/>
     </row>
-    <row r="768" ht="12.75" customHeight="1">
+    <row r="768" spans="3:4" ht="12.75" customHeight="1">
       <c r="C768" s="1"/>
       <c r="D768" s="1"/>
     </row>
-    <row r="769" ht="12.75" customHeight="1">
+    <row r="769" spans="3:4" ht="12.75" customHeight="1">
       <c r="C769" s="1"/>
       <c r="D769" s="1"/>
     </row>
-    <row r="770" ht="12.75" customHeight="1">
+    <row r="770" spans="3:4" ht="12.75" customHeight="1">
       <c r="C770" s="1"/>
       <c r="D770" s="1"/>
     </row>
-    <row r="771" ht="12.75" customHeight="1">
+    <row r="771" spans="3:4" ht="12.75" customHeight="1">
       <c r="C771" s="1"/>
       <c r="D771" s="1"/>
     </row>
-    <row r="772" ht="12.75" customHeight="1">
+    <row r="772" spans="3:4" ht="12.75" customHeight="1">
       <c r="C772" s="1"/>
       <c r="D772" s="1"/>
     </row>
-    <row r="773" ht="12.75" customHeight="1">
+    <row r="773" spans="3:4" ht="12.75" customHeight="1">
       <c r="C773" s="1"/>
       <c r="D773" s="1"/>
     </row>
-    <row r="774" ht="12.75" customHeight="1">
+    <row r="774" spans="3:4" ht="12.75" customHeight="1">
       <c r="C774" s="1"/>
       <c r="D774" s="1"/>
     </row>
-    <row r="775" ht="12.75" customHeight="1">
+    <row r="775" spans="3:4" ht="12.75" customHeight="1">
       <c r="C775" s="1"/>
       <c r="D775" s="1"/>
     </row>
-    <row r="776" ht="12.75" customHeight="1">
+    <row r="776" spans="3:4" ht="12.75" customHeight="1">
       <c r="C776" s="1"/>
       <c r="D776" s="1"/>
     </row>
-    <row r="777" ht="12.75" customHeight="1">
+    <row r="777" spans="3:4" ht="12.75" customHeight="1">
       <c r="C777" s="1"/>
       <c r="D777" s="1"/>
     </row>
-    <row r="778" ht="12.75" customHeight="1">
+    <row r="778" spans="3:4" ht="12.75" customHeight="1">
       <c r="C778" s="1"/>
       <c r="D778" s="1"/>
     </row>
-    <row r="779" ht="12.75" customHeight="1">
+    <row r="779" spans="3:4" ht="12.75" customHeight="1">
       <c r="C779" s="1"/>
       <c r="D779" s="1"/>
     </row>
-    <row r="780" ht="12.75" customHeight="1">
+    <row r="780" spans="3:4" ht="12.75" customHeight="1">
       <c r="C780" s="1"/>
       <c r="D780" s="1"/>
     </row>
-    <row r="781" ht="12.75" customHeight="1">
+    <row r="781" spans="3:4" ht="12.75" customHeight="1">
       <c r="C781" s="1"/>
       <c r="D781" s="1"/>
     </row>
-    <row r="782" ht="12.75" customHeight="1">
+    <row r="782" spans="3:4" ht="12.75" customHeight="1">
       <c r="C782" s="1"/>
       <c r="D782" s="1"/>
     </row>
-    <row r="783" ht="12.75" customHeight="1">
+    <row r="783" spans="3:4" ht="12.75" customHeight="1">
       <c r="C783" s="1"/>
       <c r="D783" s="1"/>
     </row>
-    <row r="784" ht="12.75" customHeight="1">
+    <row r="784" spans="3:4" ht="12.75" customHeight="1">
       <c r="C784" s="1"/>
       <c r="D784" s="1"/>
     </row>
-    <row r="785" ht="12.75" customHeight="1">
+    <row r="785" spans="3:4" ht="12.75" customHeight="1">
       <c r="C785" s="1"/>
       <c r="D785" s="1"/>
     </row>
-    <row r="786" ht="12.75" customHeight="1">
+    <row r="786" spans="3:4" ht="12.75" customHeight="1">
       <c r="C786" s="1"/>
       <c r="D786" s="1"/>
     </row>
-    <row r="787" ht="12.75" customHeight="1">
+    <row r="787" spans="3:4" ht="12.75" customHeight="1">
       <c r="C787" s="1"/>
       <c r="D787" s="1"/>
     </row>
-    <row r="788" ht="12.75" customHeight="1">
+    <row r="788" spans="3:4" ht="12.75" customHeight="1">
       <c r="C788" s="1"/>
       <c r="D788" s="1"/>
     </row>
-    <row r="789" ht="12.75" customHeight="1">
+    <row r="789" spans="3:4" ht="12.75" customHeight="1">
       <c r="C789" s="1"/>
       <c r="D789" s="1"/>
     </row>
-    <row r="790" ht="12.75" customHeight="1">
+    <row r="790" spans="3:4" ht="12.75" customHeight="1">
       <c r="C790" s="1"/>
       <c r="D790" s="1"/>
     </row>
-    <row r="791" ht="12.75" customHeight="1">
+    <row r="791" spans="3:4" ht="12.75" customHeight="1">
       <c r="C791" s="1"/>
       <c r="D791" s="1"/>
     </row>
-    <row r="792" ht="12.75" customHeight="1">
+    <row r="792" spans="3:4" ht="12.75" customHeight="1">
       <c r="C792" s="1"/>
       <c r="D792" s="1"/>
     </row>
-    <row r="793" ht="12.75" customHeight="1">
+    <row r="793" spans="3:4" ht="12.75" customHeight="1">
       <c r="C793" s="1"/>
       <c r="D793" s="1"/>
     </row>
-    <row r="794" ht="12.75" customHeight="1">
+    <row r="794" spans="3:4" ht="12.75" customHeight="1">
       <c r="C794" s="1"/>
       <c r="D794" s="1"/>
     </row>
-    <row r="795" ht="12.75" customHeight="1">
+    <row r="795" spans="3:4" ht="12.75" customHeight="1">
       <c r="C795" s="1"/>
       <c r="D795" s="1"/>
     </row>
-    <row r="796" ht="12.75" customHeight="1">
+    <row r="796" spans="3:4" ht="12.75" customHeight="1">
       <c r="C796" s="1"/>
       <c r="D796" s="1"/>
     </row>
-    <row r="797" ht="12.75" customHeight="1">
+    <row r="797" spans="3:4" ht="12.75" customHeight="1">
       <c r="C797" s="1"/>
       <c r="D797" s="1"/>
     </row>
-    <row r="798" ht="12.75" customHeight="1">
+    <row r="798" spans="3:4" ht="12.75" customHeight="1">
       <c r="C798" s="1"/>
       <c r="D798" s="1"/>
     </row>
-    <row r="799" ht="12.75" customHeight="1">
+    <row r="799" spans="3:4" ht="12.75" customHeight="1">
       <c r="C799" s="1"/>
       <c r="D799" s="1"/>
     </row>
-    <row r="800" ht="12.75" customHeight="1">
+    <row r="800" spans="3:4" ht="12.75" customHeight="1">
       <c r="C800" s="1"/>
       <c r="D800" s="1"/>
     </row>
-    <row r="801" ht="12.75" customHeight="1">
+    <row r="801" spans="3:4" ht="12.75" customHeight="1">
       <c r="C801" s="1"/>
       <c r="D801" s="1"/>
     </row>
-    <row r="802" ht="12.75" customHeight="1">
+    <row r="802" spans="3:4" ht="12.75" customHeight="1">
       <c r="C802" s="1"/>
       <c r="D802" s="1"/>
     </row>
-    <row r="803" ht="12.75" customHeight="1">
+    <row r="803" spans="3:4" ht="12.75" customHeight="1">
       <c r="C803" s="1"/>
       <c r="D803" s="1"/>
     </row>
-    <row r="804" ht="12.75" customHeight="1">
+    <row r="804" spans="3:4" ht="12.75" customHeight="1">
       <c r="C804" s="1"/>
       <c r="D804" s="1"/>
     </row>
-    <row r="805" ht="12.75" customHeight="1">
+    <row r="805" spans="3:4" ht="12.75" customHeight="1">
       <c r="C805" s="1"/>
       <c r="D805" s="1"/>
     </row>
-    <row r="806" ht="12.75" customHeight="1">
+    <row r="806" spans="3:4" ht="12.75" customHeight="1">
       <c r="C806" s="1"/>
       <c r="D806" s="1"/>
     </row>
-    <row r="807" ht="12.75" customHeight="1">
+    <row r="807" spans="3:4" ht="12.75" customHeight="1">
       <c r="C807" s="1"/>
       <c r="D807" s="1"/>
     </row>
-    <row r="808" ht="12.75" customHeight="1">
+    <row r="808" spans="3:4" ht="12.75" customHeight="1">
       <c r="C808" s="1"/>
       <c r="D808" s="1"/>
     </row>
-    <row r="809" ht="12.75" customHeight="1">
+    <row r="809" spans="3:4" ht="12.75" customHeight="1">
       <c r="C809" s="1"/>
       <c r="D809" s="1"/>
     </row>
-    <row r="810" ht="12.75" customHeight="1">
+    <row r="810" spans="3:4" ht="12.75" customHeight="1">
       <c r="C810" s="1"/>
       <c r="D810" s="1"/>
     </row>
-    <row r="811" ht="12.75" customHeight="1">
+    <row r="811" spans="3:4" ht="12.75" customHeight="1">
       <c r="C811" s="1"/>
       <c r="D811" s="1"/>
     </row>
-    <row r="812" ht="12.75" customHeight="1">
+    <row r="812" spans="3:4" ht="12.75" customHeight="1">
       <c r="C812" s="1"/>
       <c r="D812" s="1"/>
     </row>
-    <row r="813" ht="12.75" customHeight="1">
+    <row r="813" spans="3:4" ht="12.75" customHeight="1">
       <c r="C813" s="1"/>
       <c r="D813" s="1"/>
     </row>
-    <row r="814" ht="12.75" customHeight="1">
+    <row r="814" spans="3:4" ht="12.75" customHeight="1">
       <c r="C814" s="1"/>
       <c r="D814" s="1"/>
     </row>
-    <row r="815" ht="12.75" customHeight="1">
+    <row r="815" spans="3:4" ht="12.75" customHeight="1">
       <c r="C815" s="1"/>
       <c r="D815" s="1"/>
     </row>
-    <row r="816" ht="12.75" customHeight="1">
+    <row r="816" spans="3:4" ht="12.75" customHeight="1">
       <c r="C816" s="1"/>
       <c r="D816" s="1"/>
     </row>
-    <row r="817" ht="12.75" customHeight="1">
+    <row r="817" spans="3:4" ht="12.75" customHeight="1">
       <c r="C817" s="1"/>
       <c r="D817" s="1"/>
     </row>
-    <row r="818" ht="12.75" customHeight="1">
+    <row r="818" spans="3:4" ht="12.75" customHeight="1">
       <c r="C818" s="1"/>
       <c r="D818" s="1"/>
     </row>
-    <row r="819" ht="12.75" customHeight="1">
+    <row r="819" spans="3:4" ht="12.75" customHeight="1">
       <c r="C819" s="1"/>
       <c r="D819" s="1"/>
     </row>
-    <row r="820" ht="12.75" customHeight="1">
+    <row r="820" spans="3:4" ht="12.75" customHeight="1">
       <c r="C820" s="1"/>
       <c r="D820" s="1"/>
     </row>
-    <row r="821" ht="12.75" customHeight="1">
+    <row r="821" spans="3:4" ht="12.75" customHeight="1">
       <c r="C821" s="1"/>
       <c r="D821" s="1"/>
     </row>
-    <row r="822" ht="12.75" customHeight="1">
+    <row r="822" spans="3:4" ht="12.75" customHeight="1">
       <c r="C822" s="1"/>
       <c r="D822" s="1"/>
     </row>
-    <row r="823" ht="12.75" customHeight="1">
+    <row r="823" spans="3:4" ht="12.75" customHeight="1">
       <c r="C823" s="1"/>
       <c r="D823" s="1"/>
     </row>
-    <row r="824" ht="12.75" customHeight="1">
+    <row r="824" spans="3:4" ht="12.75" customHeight="1">
       <c r="C824" s="1"/>
       <c r="D824" s="1"/>
     </row>
-    <row r="825" ht="12.75" customHeight="1">
+    <row r="825" spans="3:4" ht="12.75" customHeight="1">
       <c r="C825" s="1"/>
       <c r="D825" s="1"/>
     </row>
-    <row r="826" ht="12.75" customHeight="1">
+    <row r="826" spans="3:4" ht="12.75" customHeight="1">
       <c r="C826" s="1"/>
       <c r="D826" s="1"/>
     </row>
-    <row r="827" ht="12.75" customHeight="1">
+    <row r="827" spans="3:4" ht="12.75" customHeight="1">
       <c r="C827" s="1"/>
       <c r="D827" s="1"/>
     </row>
-    <row r="828" ht="12.75" customHeight="1">
+    <row r="828" spans="3:4" ht="12.75" customHeight="1">
       <c r="C828" s="1"/>
       <c r="D828" s="1"/>
     </row>
-    <row r="829" ht="12.75" customHeight="1">
+    <row r="829" spans="3:4" ht="12.75" customHeight="1">
       <c r="C829" s="1"/>
       <c r="D829" s="1"/>
     </row>
-    <row r="830" ht="12.75" customHeight="1">
+    <row r="830" spans="3:4" ht="12.75" customHeight="1">
       <c r="C830" s="1"/>
       <c r="D830" s="1"/>
     </row>
-    <row r="831" ht="12.75" customHeight="1">
+    <row r="831" spans="3:4" ht="12.75" customHeight="1">
       <c r="C831" s="1"/>
       <c r="D831" s="1"/>
     </row>
-    <row r="832" ht="12.75" customHeight="1">
+    <row r="832" spans="3:4" ht="12.75" customHeight="1">
       <c r="C832" s="1"/>
       <c r="D832" s="1"/>
     </row>
-    <row r="833" ht="12.75" customHeight="1">
+    <row r="833" spans="3:4" ht="12.75" customHeight="1">
       <c r="C833" s="1"/>
       <c r="D833" s="1"/>
     </row>
-    <row r="834" ht="12.75" customHeight="1">
+    <row r="834" spans="3:4" ht="12.75" customHeight="1">
       <c r="C834" s="1"/>
       <c r="D834" s="1"/>
     </row>
-    <row r="835" ht="12.75" customHeight="1">
+    <row r="835" spans="3:4" ht="12.75" customHeight="1">
       <c r="C835" s="1"/>
       <c r="D835" s="1"/>
     </row>
-    <row r="836" ht="12.75" customHeight="1">
+    <row r="836" spans="3:4" ht="12.75" customHeight="1">
       <c r="C836" s="1"/>
       <c r="D836" s="1"/>
     </row>
-    <row r="837" ht="12.75" customHeight="1">
+    <row r="837" spans="3:4" ht="12.75" customHeight="1">
       <c r="C837" s="1"/>
       <c r="D837" s="1"/>
     </row>
-    <row r="838" ht="12.75" customHeight="1">
+    <row r="838" spans="3:4" ht="12.75" customHeight="1">
       <c r="C838" s="1"/>
       <c r="D838" s="1"/>
     </row>
-    <row r="839" ht="12.75" customHeight="1">
+    <row r="839" spans="3:4" ht="12.75" customHeight="1">
       <c r="C839" s="1"/>
       <c r="D839" s="1"/>
     </row>
-    <row r="840" ht="12.75" customHeight="1">
+    <row r="840" spans="3:4" ht="12.75" customHeight="1">
       <c r="C840" s="1"/>
       <c r="D840" s="1"/>
     </row>
-    <row r="841" ht="12.75" customHeight="1">
+    <row r="841" spans="3:4" ht="12.75" customHeight="1">
       <c r="C841" s="1"/>
       <c r="D841" s="1"/>
     </row>
-    <row r="842" ht="12.75" customHeight="1">
+    <row r="842" spans="3:4" ht="12.75" customHeight="1">
       <c r="C842" s="1"/>
       <c r="D842" s="1"/>
     </row>
-    <row r="843" ht="12.75" customHeight="1">
+    <row r="843" spans="3:4" ht="12.75" customHeight="1">
       <c r="C843" s="1"/>
       <c r="D843" s="1"/>
     </row>
-    <row r="844" ht="12.75" customHeight="1">
+    <row r="844" spans="3:4" ht="12.75" customHeight="1">
       <c r="C844" s="1"/>
       <c r="D844" s="1"/>
     </row>
-    <row r="845" ht="12.75" customHeight="1">
+    <row r="845" spans="3:4" ht="12.75" customHeight="1">
       <c r="C845" s="1"/>
       <c r="D845" s="1"/>
     </row>
-    <row r="846" ht="12.75" customHeight="1">
+    <row r="846" spans="3:4" ht="12.75" customHeight="1">
       <c r="C846" s="1"/>
       <c r="D846" s="1"/>
     </row>
-    <row r="847" ht="12.75" customHeight="1">
+    <row r="847" spans="3:4" ht="12.75" customHeight="1">
       <c r="C847" s="1"/>
       <c r="D847" s="1"/>
     </row>
-    <row r="848" ht="12.75" customHeight="1">
+    <row r="848" spans="3:4" ht="12.75" customHeight="1">
       <c r="C848" s="1"/>
       <c r="D848" s="1"/>
     </row>
-    <row r="849" ht="12.75" customHeight="1">
+    <row r="849" spans="3:4" ht="12.75" customHeight="1">
       <c r="C849" s="1"/>
       <c r="D849" s="1"/>
     </row>
-    <row r="850" ht="12.75" customHeight="1">
+    <row r="850" spans="3:4" ht="12.75" customHeight="1">
       <c r="C850" s="1"/>
       <c r="D850" s="1"/>
     </row>
-    <row r="851" ht="12.75" customHeight="1">
+    <row r="851" spans="3:4" ht="12.75" customHeight="1">
       <c r="C851" s="1"/>
       <c r="D851" s="1"/>
     </row>
-    <row r="852" ht="12.75" customHeight="1">
+    <row r="852" spans="3:4" ht="12.75" customHeight="1">
       <c r="C852" s="1"/>
       <c r="D852" s="1"/>
     </row>
-    <row r="853" ht="12.75" customHeight="1">
+    <row r="853" spans="3:4" ht="12.75" customHeight="1">
       <c r="C853" s="1"/>
       <c r="D853" s="1"/>
     </row>
-    <row r="854" ht="12.75" customHeight="1">
+    <row r="854" spans="3:4" ht="12.75" customHeight="1">
       <c r="C854" s="1"/>
       <c r="D854" s="1"/>
     </row>
-    <row r="855" ht="12.75" customHeight="1">
+    <row r="855" spans="3:4" ht="12.75" customHeight="1">
       <c r="C855" s="1"/>
       <c r="D855" s="1"/>
     </row>
-    <row r="856" ht="12.75" customHeight="1">
+    <row r="856" spans="3:4" ht="12.75" customHeight="1">
       <c r="C856" s="1"/>
       <c r="D856" s="1"/>
     </row>
-    <row r="857" ht="12.75" customHeight="1">
+    <row r="857" spans="3:4" ht="12.75" customHeight="1">
       <c r="C857" s="1"/>
       <c r="D857" s="1"/>
     </row>
-    <row r="858" ht="12.75" customHeight="1">
+    <row r="858" spans="3:4" ht="12.75" customHeight="1">
       <c r="C858" s="1"/>
       <c r="D858" s="1"/>
     </row>
-    <row r="859" ht="12.75" customHeight="1">
+    <row r="859" spans="3:4" ht="12.75" customHeight="1">
       <c r="C859" s="1"/>
       <c r="D859" s="1"/>
     </row>
-    <row r="860" ht="12.75" customHeight="1">
+    <row r="860" spans="3:4" ht="12.75" customHeight="1">
       <c r="C860" s="1"/>
       <c r="D860" s="1"/>
     </row>
-    <row r="861" ht="12.75" customHeight="1">
+    <row r="861" spans="3:4" ht="12.75" customHeight="1">
       <c r="C861" s="1"/>
       <c r="D861" s="1"/>
     </row>
-    <row r="862" ht="12.75" customHeight="1">
+    <row r="862" spans="3:4" ht="12.75" customHeight="1">
       <c r="C862" s="1"/>
       <c r="D862" s="1"/>
     </row>
-    <row r="863" ht="12.75" customHeight="1">
+    <row r="863" spans="3:4" ht="12.75" customHeight="1">
       <c r="C863" s="1"/>
       <c r="D863" s="1"/>
     </row>
-    <row r="864" ht="12.75" customHeight="1">
+    <row r="864" spans="3:4" ht="12.75" customHeight="1">
       <c r="C864" s="1"/>
       <c r="D864" s="1"/>
     </row>
-    <row r="865" ht="12.75" customHeight="1">
+    <row r="865" spans="3:4" ht="12.75" customHeight="1">
       <c r="C865" s="1"/>
       <c r="D865" s="1"/>
     </row>
-    <row r="866" ht="12.75" customHeight="1">
+    <row r="866" spans="3:4" ht="12.75" customHeight="1">
       <c r="C866" s="1"/>
       <c r="D866" s="1"/>
     </row>
-    <row r="867" ht="12.75" customHeight="1">
+    <row r="867" spans="3:4" ht="12.75" customHeight="1">
       <c r="C867" s="1"/>
       <c r="D867" s="1"/>
     </row>
-    <row r="868" ht="12.75" customHeight="1">
+    <row r="868" spans="3:4" ht="12.75" customHeight="1">
       <c r="C868" s="1"/>
       <c r="D868" s="1"/>
     </row>
-    <row r="869" ht="12.75" customHeight="1">
+    <row r="869" spans="3:4" ht="12.75" customHeight="1">
       <c r="C869" s="1"/>
       <c r="D869" s="1"/>
     </row>
-    <row r="870" ht="12.75" customHeight="1">
+    <row r="870" spans="3:4" ht="12.75" customHeight="1">
       <c r="C870" s="1"/>
       <c r="D870" s="1"/>
     </row>
-    <row r="871" ht="12.75" customHeight="1">
+    <row r="871" spans="3:4" ht="12.75" customHeight="1">
       <c r="C871" s="1"/>
       <c r="D871" s="1"/>
     </row>
-    <row r="872" ht="12.75" customHeight="1">
+    <row r="872" spans="3:4" ht="12.75" customHeight="1">
       <c r="C872" s="1"/>
       <c r="D872" s="1"/>
     </row>
-    <row r="873" ht="12.75" customHeight="1">
+    <row r="873" spans="3:4" ht="12.75" customHeight="1">
       <c r="C873" s="1"/>
       <c r="D873" s="1"/>
     </row>
-    <row r="874" ht="12.75" customHeight="1">
+    <row r="874" spans="3:4" ht="12.75" customHeight="1">
       <c r="C874" s="1"/>
       <c r="D874" s="1"/>
     </row>
-    <row r="875" ht="12.75" customHeight="1">
+    <row r="875" spans="3:4" ht="12.75" customHeight="1">
       <c r="C875" s="1"/>
       <c r="D875" s="1"/>
     </row>
-    <row r="876" ht="12.75" customHeight="1">
+    <row r="876" spans="3:4" ht="12.75" customHeight="1">
       <c r="C876" s="1"/>
       <c r="D876" s="1"/>
     </row>
-    <row r="877" ht="12.75" customHeight="1">
+    <row r="877" spans="3:4" ht="12.75" customHeight="1">
       <c r="C877" s="1"/>
       <c r="D877" s="1"/>
     </row>
-    <row r="878" ht="12.75" customHeight="1">
+    <row r="878" spans="3:4" ht="12.75" customHeight="1">
       <c r="C878" s="1"/>
       <c r="D878" s="1"/>
     </row>
-    <row r="879" ht="12.75" customHeight="1">
+    <row r="879" spans="3:4" ht="12.75" customHeight="1">
       <c r="C879" s="1"/>
       <c r="D879" s="1"/>
     </row>
-    <row r="880" ht="12.75" customHeight="1">
+    <row r="880" spans="3:4" ht="12.75" customHeight="1">
       <c r="C880" s="1"/>
       <c r="D880" s="1"/>
     </row>
-    <row r="881" ht="12.75" customHeight="1">
+    <row r="881" spans="3:4" ht="12.75" customHeight="1">
       <c r="C881" s="1"/>
       <c r="D881" s="1"/>
     </row>
-    <row r="882" ht="12.75" customHeight="1">
+    <row r="882" spans="3:4" ht="12.75" customHeight="1">
       <c r="C882" s="1"/>
       <c r="D882" s="1"/>
     </row>
-    <row r="883" ht="12.75" customHeight="1">
+    <row r="883" spans="3:4" ht="12.75" customHeight="1">
       <c r="C883" s="1"/>
       <c r="D883" s="1"/>
     </row>
-    <row r="884" ht="12.75" customHeight="1">
+    <row r="884" spans="3:4" ht="12.75" customHeight="1">
       <c r="C884" s="1"/>
       <c r="D884" s="1"/>
     </row>
-    <row r="885" ht="12.75" customHeight="1">
+    <row r="885" spans="3:4" ht="12.75" customHeight="1">
       <c r="C885" s="1"/>
       <c r="D885" s="1"/>
     </row>
-    <row r="886" ht="12.75" customHeight="1">
+    <row r="886" spans="3:4" ht="12.75" customHeight="1">
       <c r="C886" s="1"/>
       <c r="D886" s="1"/>
     </row>
-    <row r="887" ht="12.75" customHeight="1">
+    <row r="887" spans="3:4" ht="12.75" customHeight="1">
       <c r="C887" s="1"/>
       <c r="D887" s="1"/>
     </row>
-    <row r="888" ht="12.75" customHeight="1">
+    <row r="888" spans="3:4" ht="12.75" customHeight="1">
       <c r="C888" s="1"/>
       <c r="D888" s="1"/>
     </row>
-    <row r="889" ht="12.75" customHeight="1">
+    <row r="889" spans="3:4" ht="12.75" customHeight="1">
       <c r="C889" s="1"/>
       <c r="D889" s="1"/>
     </row>
-    <row r="890" ht="12.75" customHeight="1">
+    <row r="890" spans="3:4" ht="12.75" customHeight="1">
       <c r="C890" s="1"/>
       <c r="D890" s="1"/>
     </row>
-    <row r="891" ht="12.75" customHeight="1">
+    <row r="891" spans="3:4" ht="12.75" customHeight="1">
       <c r="C891" s="1"/>
       <c r="D891" s="1"/>
     </row>
-    <row r="892" ht="12.75" customHeight="1">
+    <row r="892" spans="3:4" ht="12.75" customHeight="1">
       <c r="C892" s="1"/>
       <c r="D892" s="1"/>
     </row>
-    <row r="893" ht="12.75" customHeight="1">
+    <row r="893" spans="3:4" ht="12.75" customHeight="1">
       <c r="C893" s="1"/>
       <c r="D893" s="1"/>
     </row>
-    <row r="894" ht="12.75" customHeight="1">
+    <row r="894" spans="3:4" ht="12.75" customHeight="1">
       <c r="C894" s="1"/>
       <c r="D894" s="1"/>
     </row>
-    <row r="895" ht="12.75" customHeight="1">
+    <row r="895" spans="3:4" ht="12.75" customHeight="1">
       <c r="C895" s="1"/>
       <c r="D895" s="1"/>
     </row>
-    <row r="896" ht="12.75" customHeight="1">
+    <row r="896" spans="3:4" ht="12.75" customHeight="1">
       <c r="C896" s="1"/>
       <c r="D896" s="1"/>
     </row>
-    <row r="897" ht="12.75" customHeight="1">
+    <row r="897" spans="3:4" ht="12.75" customHeight="1">
       <c r="C897" s="1"/>
       <c r="D897" s="1"/>
     </row>
-    <row r="898" ht="12.75" customHeight="1">
+    <row r="898" spans="3:4" ht="12.75" customHeight="1">
       <c r="C898" s="1"/>
       <c r="D898" s="1"/>
     </row>
-    <row r="899" ht="12.75" customHeight="1">
+    <row r="899" spans="3:4" ht="12.75" customHeight="1">
       <c r="C899" s="1"/>
       <c r="D899" s="1"/>
     </row>
-    <row r="900" ht="12.75" customHeight="1">
+    <row r="900" spans="3:4" ht="12.75" customHeight="1">
       <c r="C900" s="1"/>
       <c r="D900" s="1"/>
     </row>
-    <row r="901" ht="12.75" customHeight="1">
+    <row r="901" spans="3:4" ht="12.75" customHeight="1">
       <c r="C901" s="1"/>
       <c r="D901" s="1"/>
     </row>
-    <row r="902" ht="12.75" customHeight="1">
+    <row r="902" spans="3:4" ht="12.75" customHeight="1">
       <c r="C902" s="1"/>
       <c r="D902" s="1"/>
     </row>
-    <row r="903" ht="12.75" customHeight="1">
+    <row r="903" spans="3:4" ht="12.75" customHeight="1">
       <c r="C903" s="1"/>
       <c r="D903" s="1"/>
     </row>
-    <row r="904" ht="12.75" customHeight="1">
+    <row r="904" spans="3:4" ht="12.75" customHeight="1">
       <c r="C904" s="1"/>
       <c r="D904" s="1"/>
     </row>
-    <row r="905" ht="12.75" customHeight="1">
+    <row r="905" spans="3:4" ht="12.75" customHeight="1">
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
     </row>
-    <row r="906" ht="12.75" customHeight="1">
+    <row r="906" spans="3:4" ht="12.75" customHeight="1">
       <c r="C906" s="1"/>
       <c r="D906" s="1"/>
     </row>
-    <row r="907" ht="12.75" customHeight="1">
+    <row r="907" spans="3:4" ht="12.75" customHeight="1">
       <c r="C907" s="1"/>
       <c r="D907" s="1"/>
     </row>
-    <row r="908" ht="12.75" customHeight="1">
+    <row r="908" spans="3:4" ht="12.75" customHeight="1">
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
     </row>
-    <row r="909" ht="12.75" customHeight="1">
+    <row r="909" spans="3:4" ht="12.75" customHeight="1">
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
     </row>
-    <row r="910" ht="12.75" customHeight="1">
+    <row r="910" spans="3:4" ht="12.75" customHeight="1">
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
     </row>
-    <row r="911" ht="12.75" customHeight="1">
+    <row r="911" spans="3:4" ht="12.75" customHeight="1">
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
     </row>
-    <row r="912" ht="12.75" customHeight="1">
+    <row r="912" spans="3:4" ht="12.75" customHeight="1">
       <c r="C912" s="1"/>
       <c r="D912" s="1"/>
     </row>
-    <row r="913" ht="12.75" customHeight="1">
+    <row r="913" spans="3:4" ht="12.75" customHeight="1">
       <c r="C913" s="1"/>
       <c r="D913" s="1"/>
     </row>
-    <row r="914" ht="12.75" customHeight="1">
+    <row r="914" spans="3:4" ht="12.75" customHeight="1">
       <c r="C914" s="1"/>
       <c r="D914" s="1"/>
     </row>
-    <row r="915" ht="12.75" customHeight="1">
+    <row r="915" spans="3:4" ht="12.75" customHeight="1">
       <c r="C915" s="1"/>
       <c r="D915" s="1"/>
     </row>
-    <row r="916" ht="12.75" customHeight="1">
+    <row r="916" spans="3:4" ht="12.75" customHeight="1">
       <c r="C916" s="1"/>
       <c r="D916" s="1"/>
     </row>
-    <row r="917" ht="12.75" customHeight="1">
+    <row r="917" spans="3:4" ht="12.75" customHeight="1">
       <c r="C917" s="1"/>
       <c r="D917" s="1"/>
     </row>
-    <row r="918" ht="12.75" customHeight="1">
+    <row r="918" spans="3:4" ht="12.75" customHeight="1">
       <c r="C918" s="1"/>
       <c r="D918" s="1"/>
     </row>
-    <row r="919" ht="12.75" customHeight="1">
+    <row r="919" spans="3:4" ht="12.75" customHeight="1">
       <c r="C919" s="1"/>
       <c r="D919" s="1"/>
     </row>
-    <row r="920" ht="12.75" customHeight="1">
+    <row r="920" spans="3:4" ht="12.75" customHeight="1">
       <c r="C920" s="1"/>
       <c r="D920" s="1"/>
     </row>
-    <row r="921" ht="12.75" customHeight="1">
+    <row r="921" spans="3:4" ht="12.75" customHeight="1">
       <c r="C921" s="1"/>
       <c r="D921" s="1"/>
     </row>
-    <row r="922" ht="12.75" customHeight="1">
+    <row r="922" spans="3:4" ht="12.75" customHeight="1">
       <c r="C922" s="1"/>
       <c r="D922" s="1"/>
     </row>
-    <row r="923" ht="12.75" customHeight="1">
+    <row r="923" spans="3:4" ht="12.75" customHeight="1">
       <c r="C923" s="1"/>
       <c r="D923" s="1"/>
     </row>
-    <row r="924" ht="12.75" customHeight="1">
+    <row r="924" spans="3:4" ht="12.75" customHeight="1">
       <c r="C924" s="1"/>
       <c r="D924" s="1"/>
     </row>
-    <row r="925" ht="12.75" customHeight="1">
+    <row r="925" spans="3:4" ht="12.75" customHeight="1">
       <c r="C925" s="1"/>
       <c r="D925" s="1"/>
     </row>
-    <row r="926" ht="12.75" customHeight="1">
+    <row r="926" spans="3:4" ht="12.75" customHeight="1">
       <c r="C926" s="1"/>
       <c r="D926" s="1"/>
     </row>
-    <row r="927" ht="12.75" customHeight="1">
+    <row r="927" spans="3:4" ht="12.75" customHeight="1">
       <c r="C927" s="1"/>
       <c r="D927" s="1"/>
     </row>
-    <row r="928" ht="12.75" customHeight="1">
+    <row r="928" spans="3:4" ht="12.75" customHeight="1">
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
     </row>
-    <row r="929" ht="12.75" customHeight="1">
+    <row r="929" spans="3:4" ht="12.75" customHeight="1">
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
     </row>
-    <row r="930" ht="12.75" customHeight="1">
+    <row r="930" spans="3:4" ht="12.75" customHeight="1">
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
     </row>
-    <row r="931" ht="12.75" customHeight="1">
+    <row r="931" spans="3:4" ht="12.75" customHeight="1">
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
     </row>
-    <row r="932" ht="12.75" customHeight="1">
+    <row r="932" spans="3:4" ht="12.75" customHeight="1">
       <c r="C932" s="1"/>
       <c r="D932" s="1"/>
     </row>
-    <row r="933" ht="12.75" customHeight="1">
+    <row r="933" spans="3:4" ht="12.75" customHeight="1">
       <c r="C933" s="1"/>
       <c r="D933" s="1"/>
     </row>
-    <row r="934" ht="12.75" customHeight="1">
+    <row r="934" spans="3:4" ht="12.75" customHeight="1">
       <c r="C934" s="1"/>
       <c r="D934" s="1"/>
     </row>
-    <row r="935" ht="12.75" customHeight="1">
+    <row r="935" spans="3:4" ht="12.75" customHeight="1">
       <c r="C935" s="1"/>
       <c r="D935" s="1"/>
     </row>
-    <row r="936" ht="12.75" customHeight="1">
+    <row r="936" spans="3:4" ht="12.75" customHeight="1">
       <c r="C936" s="1"/>
       <c r="D936" s="1"/>
     </row>
-    <row r="937" ht="12.75" customHeight="1">
+    <row r="937" spans="3:4" ht="12.75" customHeight="1">
       <c r="C937" s="1"/>
       <c r="D937" s="1"/>
     </row>
-    <row r="938" ht="12.75" customHeight="1">
+    <row r="938" spans="3:4" ht="12.75" customHeight="1">
       <c r="C938" s="1"/>
       <c r="D938" s="1"/>
     </row>
-    <row r="939" ht="12.75" customHeight="1">
+    <row r="939" spans="3:4" ht="12.75" customHeight="1">
       <c r="C939" s="1"/>
       <c r="D939" s="1"/>
     </row>
-    <row r="940" ht="12.75" customHeight="1">
+    <row r="940" spans="3:4" ht="12.75" customHeight="1">
       <c r="C940" s="1"/>
       <c r="D940" s="1"/>
     </row>
-    <row r="941" ht="12.75" customHeight="1">
+    <row r="941" spans="3:4" ht="12.75" customHeight="1">
       <c r="C941" s="1"/>
       <c r="D941" s="1"/>
     </row>
-    <row r="942" ht="12.75" customHeight="1">
+    <row r="942" spans="3:4" ht="12.75" customHeight="1">
       <c r="C942" s="1"/>
       <c r="D942" s="1"/>
     </row>
-    <row r="943" ht="12.75" customHeight="1">
+    <row r="943" spans="3:4" ht="12.75" customHeight="1">
       <c r="C943" s="1"/>
       <c r="D943" s="1"/>
     </row>
-    <row r="944" ht="12.75" customHeight="1">
+    <row r="944" spans="3:4" ht="12.75" customHeight="1">
       <c r="C944" s="1"/>
       <c r="D944" s="1"/>
     </row>
-    <row r="945" ht="12.75" customHeight="1">
+    <row r="945" spans="3:4" ht="12.75" customHeight="1">
       <c r="C945" s="1"/>
       <c r="D945" s="1"/>
     </row>
-    <row r="946" ht="12.75" customHeight="1">
+    <row r="946" spans="3:4" ht="12.75" customHeight="1">
       <c r="C946" s="1"/>
       <c r="D946" s="1"/>
     </row>
-    <row r="947" ht="12.75" customHeight="1">
+    <row r="947" spans="3:4" ht="12.75" customHeight="1">
       <c r="C947" s="1"/>
       <c r="D947" s="1"/>
     </row>
-    <row r="948" ht="12.75" customHeight="1">
+    <row r="948" spans="3:4" ht="12.75" customHeight="1">
       <c r="C948" s="1"/>
       <c r="D948" s="1"/>
     </row>
-    <row r="949" ht="12.75" customHeight="1">
+    <row r="949" spans="3:4" ht="12.75" customHeight="1">
       <c r="C949" s="1"/>
       <c r="D949" s="1"/>
     </row>
-    <row r="950" ht="12.75" customHeight="1">
+    <row r="950" spans="3:4" ht="12.75" customHeight="1">
       <c r="C950" s="1"/>
       <c r="D950" s="1"/>
     </row>
-    <row r="951" ht="12.75" customHeight="1">
+    <row r="951" spans="3:4" ht="12.75" customHeight="1">
       <c r="C951" s="1"/>
       <c r="D951" s="1"/>
     </row>
-    <row r="952" ht="12.75" customHeight="1">
+    <row r="952" spans="3:4" ht="12.75" customHeight="1">
       <c r="C952" s="1"/>
       <c r="D952" s="1"/>
     </row>
-    <row r="953" ht="12.75" customHeight="1">
+    <row r="953" spans="3:4" ht="12.75" customHeight="1">
       <c r="C953" s="1"/>
       <c r="D953" s="1"/>
     </row>
-    <row r="954" ht="12.75" customHeight="1">
+    <row r="954" spans="3:4" ht="12.75" customHeight="1">
       <c r="C954" s="1"/>
       <c r="D954" s="1"/>
     </row>
-    <row r="955" ht="12.75" customHeight="1">
+    <row r="955" spans="3:4" ht="12.75" customHeight="1">
       <c r="C955" s="1"/>
       <c r="D955" s="1"/>
     </row>
-    <row r="956" ht="12.75" customHeight="1">
+    <row r="956" spans="3:4" ht="12.75" customHeight="1">
       <c r="C956" s="1"/>
       <c r="D956" s="1"/>
     </row>
-    <row r="957" ht="12.75" customHeight="1">
+    <row r="957" spans="3:4" ht="12.75" customHeight="1">
       <c r="C957" s="1"/>
       <c r="D957" s="1"/>
     </row>
-    <row r="958" ht="12.75" customHeight="1">
+    <row r="958" spans="3:4" ht="12.75" customHeight="1">
       <c r="C958" s="1"/>
       <c r="D958" s="1"/>
     </row>
-    <row r="959" ht="12.75" customHeight="1">
+    <row r="959" spans="3:4" ht="12.75" customHeight="1">
       <c r="C959" s="1"/>
       <c r="D959" s="1"/>
     </row>
-    <row r="960" ht="12.75" customHeight="1">
+    <row r="960" spans="3:4" ht="12.75" customHeight="1">
       <c r="C960" s="1"/>
       <c r="D960" s="1"/>
     </row>
-    <row r="961" ht="12.75" customHeight="1">
+    <row r="961" spans="3:4" ht="12.75" customHeight="1">
       <c r="C961" s="1"/>
       <c r="D961" s="1"/>
     </row>
-    <row r="962" ht="12.75" customHeight="1">
+    <row r="962" spans="3:4" ht="12.75" customHeight="1">
       <c r="C962" s="1"/>
       <c r="D962" s="1"/>
     </row>
-    <row r="963" ht="12.75" customHeight="1">
+    <row r="963" spans="3:4" ht="12.75" customHeight="1">
       <c r="C963" s="1"/>
       <c r="D963" s="1"/>
     </row>
-    <row r="964" ht="12.75" customHeight="1">
+    <row r="964" spans="3:4" ht="12.75" customHeight="1">
       <c r="C964" s="1"/>
       <c r="D964" s="1"/>
     </row>
-    <row r="965" ht="12.75" customHeight="1">
+    <row r="965" spans="3:4" ht="12.75" customHeight="1">
       <c r="C965" s="1"/>
       <c r="D965" s="1"/>
     </row>
-    <row r="966" ht="12.75" customHeight="1">
+    <row r="966" spans="3:4" ht="12.75" customHeight="1">
       <c r="C966" s="1"/>
       <c r="D966" s="1"/>
     </row>
-    <row r="967" ht="12.75" customHeight="1">
+    <row r="967" spans="3:4" ht="12.75" customHeight="1">
       <c r="C967" s="1"/>
       <c r="D967" s="1"/>
     </row>
-    <row r="968" ht="12.75" customHeight="1">
+    <row r="968" spans="3:4" ht="12.75" customHeight="1">
       <c r="C968" s="1"/>
       <c r="D968" s="1"/>
     </row>
-    <row r="969" ht="12.75" customHeight="1">
+    <row r="969" spans="3:4" ht="12.75" customHeight="1">
       <c r="C969" s="1"/>
       <c r="D969" s="1"/>
     </row>
-    <row r="970" ht="12.75" customHeight="1">
+    <row r="970" spans="3:4" ht="12.75" customHeight="1">
       <c r="C970" s="1"/>
       <c r="D970" s="1"/>
     </row>
-    <row r="971" ht="12.75" customHeight="1">
+    <row r="971" spans="3:4" ht="12.75" customHeight="1">
       <c r="C971" s="1"/>
       <c r="D971" s="1"/>
     </row>
-    <row r="972" ht="12.75" customHeight="1">
+    <row r="972" spans="3:4" ht="12.75" customHeight="1">
       <c r="C972" s="1"/>
       <c r="D972" s="1"/>
     </row>
-    <row r="973" ht="12.75" customHeight="1">
+    <row r="973" spans="3:4" ht="12.75" customHeight="1">
       <c r="C973" s="1"/>
       <c r="D973" s="1"/>
     </row>
-    <row r="974" ht="12.75" customHeight="1">
+    <row r="974" spans="3:4" ht="12.75" customHeight="1">
       <c r="C974" s="1"/>
       <c r="D974" s="1"/>
     </row>
-    <row r="975" ht="12.75" customHeight="1">
+    <row r="975" spans="3:4" ht="12.75" customHeight="1">
       <c r="C975" s="1"/>
       <c r="D975" s="1"/>
     </row>
-    <row r="976" ht="12.75" customHeight="1">
+    <row r="976" spans="3:4" ht="12.75" customHeight="1">
       <c r="C976" s="1"/>
       <c r="D976" s="1"/>
     </row>
-    <row r="977" ht="12.75" customHeight="1">
+    <row r="977" spans="3:4" ht="12.75" customHeight="1">
       <c r="C977" s="1"/>
       <c r="D977" s="1"/>
     </row>
-    <row r="978" ht="12.75" customHeight="1">
+    <row r="978" spans="3:4" ht="12.75" customHeight="1">
       <c r="C978" s="1"/>
       <c r="D978" s="1"/>
     </row>
-    <row r="979" ht="12.75" customHeight="1">
+    <row r="979" spans="3:4" ht="12.75" customHeight="1">
       <c r="C979" s="1"/>
       <c r="D979" s="1"/>
     </row>
-    <row r="980" ht="12.75" customHeight="1">
+    <row r="980" spans="3:4" ht="12.75" customHeight="1">
       <c r="C980" s="1"/>
       <c r="D980" s="1"/>
     </row>
-    <row r="981" ht="12.75" customHeight="1">
+    <row r="981" spans="3:4" ht="12.75" customHeight="1">
       <c r="C981" s="1"/>
       <c r="D981" s="1"/>
     </row>
-    <row r="982" ht="12.75" customHeight="1">
+    <row r="982" spans="3:4" ht="12.75" customHeight="1">
       <c r="C982" s="1"/>
       <c r="D982" s="1"/>
     </row>
-    <row r="983" ht="12.75" customHeight="1">
+    <row r="983" spans="3:4" ht="12.75" customHeight="1">
       <c r="C983" s="1"/>
       <c r="D983" s="1"/>
     </row>
-    <row r="984" ht="12.75" customHeight="1">
+    <row r="984" spans="3:4" ht="12.75" customHeight="1">
       <c r="C984" s="1"/>
       <c r="D984" s="1"/>
     </row>
-    <row r="985" ht="12.75" customHeight="1">
+    <row r="985" spans="3:4" ht="12.75" customHeight="1">
       <c r="C985" s="1"/>
       <c r="D985" s="1"/>
     </row>
-    <row r="986" ht="12.75" customHeight="1">
+    <row r="986" spans="3:4" ht="12.75" customHeight="1">
       <c r="C986" s="1"/>
       <c r="D986" s="1"/>
     </row>
-    <row r="987" ht="12.75" customHeight="1">
+    <row r="987" spans="3:4" ht="12.75" customHeight="1">
       <c r="C987" s="1"/>
       <c r="D987" s="1"/>
     </row>
-    <row r="988" ht="12.75" customHeight="1">
+    <row r="988" spans="3:4" ht="12.75" customHeight="1">
       <c r="C988" s="1"/>
       <c r="D988" s="1"/>
     </row>
-    <row r="989" ht="12.75" customHeight="1">
+    <row r="989" spans="3:4" ht="12.75" customHeight="1">
       <c r="C989" s="1"/>
       <c r="D989" s="1"/>
     </row>
-    <row r="990" ht="12.75" customHeight="1">
+    <row r="990" spans="3:4" ht="12.75" customHeight="1">
       <c r="C990" s="1"/>
       <c r="D990" s="1"/>
     </row>
-    <row r="991" ht="12.75" customHeight="1">
+    <row r="991" spans="3:4" ht="12.75" customHeight="1">
       <c r="C991" s="1"/>
       <c r="D991" s="1"/>
     </row>
-    <row r="992" ht="12.75" customHeight="1">
+    <row r="992" spans="3:4" ht="12.75" customHeight="1">
       <c r="C992" s="1"/>
       <c r="D992" s="1"/>
     </row>
-    <row r="993" ht="12.75" customHeight="1">
+    <row r="993" spans="3:4" ht="12.75" customHeight="1">
       <c r="C993" s="1"/>
       <c r="D993" s="1"/>
     </row>
-    <row r="994" ht="12.75" customHeight="1">
+    <row r="994" spans="3:4" ht="12.75" customHeight="1">
       <c r="C994" s="1"/>
       <c r="D994" s="1"/>
     </row>
-    <row r="995" ht="12.75" customHeight="1">
+    <row r="995" spans="3:4" ht="12.75" customHeight="1">
       <c r="C995" s="1"/>
       <c r="D995" s="1"/>
     </row>
-    <row r="996" ht="12.75" customHeight="1">
+    <row r="996" spans="3:4" ht="12.75" customHeight="1">
       <c r="C996" s="1"/>
       <c r="D996" s="1"/>
     </row>
-    <row r="997" ht="12.75" customHeight="1">
+    <row r="997" spans="3:4" ht="12.75" customHeight="1">
       <c r="C997" s="1"/>
       <c r="D997" s="1"/>
     </row>
-    <row r="998" ht="12.75" customHeight="1">
+    <row r="998" spans="3:4" ht="12.75" customHeight="1">
       <c r="C998" s="1"/>
       <c r="D998" s="1"/>
     </row>
-    <row r="999" ht="12.75" customHeight="1">
+    <row r="999" spans="3:4" ht="12.75" customHeight="1">
       <c r="C999" s="1"/>
       <c r="D999" s="1"/>
     </row>
-    <row r="1000" ht="12.75" customHeight="1">
+    <row r="1000" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1000" s="1"/>
       <c r="D1000" s="1"/>
     </row>
-    <row r="1001" ht="12.75" customHeight="1">
+    <row r="1001" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1001" s="1"/>
       <c r="D1001" s="1"/>
     </row>
-    <row r="1002" ht="12.75" customHeight="1">
+    <row r="1002" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1002" s="1"/>
       <c r="D1002" s="1"/>
     </row>
-    <row r="1003" ht="12.75" customHeight="1">
+    <row r="1003" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1003" s="1"/>
       <c r="D1003" s="1"/>
     </row>
-    <row r="1004" ht="12.75" customHeight="1">
+    <row r="1004" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1004" s="1"/>
       <c r="D1004" s="1"/>
     </row>
-    <row r="1005" ht="12.75" customHeight="1">
+    <row r="1005" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1005" s="1"/>
       <c r="D1005" s="1"/>
     </row>
-    <row r="1006" ht="12.75" customHeight="1">
+    <row r="1006" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1006" s="1"/>
       <c r="D1006" s="1"/>
     </row>
-    <row r="1007" ht="12.75" customHeight="1">
+    <row r="1007" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1007" s="1"/>
       <c r="D1007" s="1"/>
     </row>
-    <row r="1008" ht="12.75" customHeight="1">
+    <row r="1008" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1008" s="1"/>
       <c r="D1008" s="1"/>
     </row>
-    <row r="1009" ht="12.75" customHeight="1">
+    <row r="1009" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1009" s="1"/>
       <c r="D1009" s="1"/>
     </row>
-    <row r="1010" ht="12.75" customHeight="1">
+    <row r="1010" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1010" s="1"/>
       <c r="D1010" s="1"/>
     </row>
-    <row r="1011" ht="12.75" customHeight="1">
+    <row r="1011" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1011" s="1"/>
       <c r="D1011" s="1"/>
     </row>
-    <row r="1012" ht="12.75" customHeight="1">
+    <row r="1012" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1012" s="1"/>
       <c r="D1012" s="1"/>
     </row>
-    <row r="1013" ht="12.75" customHeight="1">
+    <row r="1013" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1013" s="1"/>
       <c r="D1013" s="1"/>
     </row>
-    <row r="1014" ht="12.75" customHeight="1">
+    <row r="1014" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1014" s="1"/>
       <c r="D1014" s="1"/>
     </row>
-    <row r="1015" ht="12.75" customHeight="1">
+    <row r="1015" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1015" s="1"/>
       <c r="D1015" s="1"/>
     </row>
-    <row r="1016" ht="12.75" customHeight="1">
+    <row r="1016" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1016" s="1"/>
       <c r="D1016" s="1"/>
     </row>
-    <row r="1017" ht="12.75" customHeight="1">
+    <row r="1017" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1017" s="1"/>
       <c r="D1017" s="1"/>
     </row>
-    <row r="1018" ht="12.75" customHeight="1">
+    <row r="1018" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1018" s="1"/>
       <c r="D1018" s="1"/>
     </row>
-    <row r="1019" ht="12.75" customHeight="1">
+    <row r="1019" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1019" s="1"/>
       <c r="D1019" s="1"/>
     </row>
-    <row r="1020" ht="12.75" customHeight="1">
+    <row r="1020" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1020" s="1"/>
       <c r="D1020" s="1"/>
     </row>
-    <row r="1021" ht="12.75" customHeight="1">
+    <row r="1021" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1021" s="1"/>
       <c r="D1021" s="1"/>
     </row>
-    <row r="1022" ht="12.75" customHeight="1">
+    <row r="1022" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1022" s="1"/>
       <c r="D1022" s="1"/>
     </row>
-    <row r="1023" ht="12.75" customHeight="1">
+    <row r="1023" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1023" s="1"/>
       <c r="D1023" s="1"/>
     </row>
-    <row r="1024" ht="12.75" customHeight="1">
+    <row r="1024" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1024" s="1"/>
       <c r="D1024" s="1"/>
     </row>
-    <row r="1025" ht="12.75" customHeight="1">
+    <row r="1025" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1025" s="1"/>
       <c r="D1025" s="1"/>
     </row>
-    <row r="1026" ht="12.75" customHeight="1">
+    <row r="1026" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1026" s="1"/>
       <c r="D1026" s="1"/>
     </row>
-    <row r="1027" ht="12.75" customHeight="1">
+    <row r="1027" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1027" s="1"/>
       <c r="D1027" s="1"/>
     </row>
-    <row r="1028" ht="12.75" customHeight="1">
+    <row r="1028" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1028" s="1"/>
       <c r="D1028" s="1"/>
     </row>
-    <row r="1029" ht="12.75" customHeight="1">
+    <row r="1029" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1029" s="1"/>
       <c r="D1029" s="1"/>
     </row>
-    <row r="1030" ht="12.75" customHeight="1">
+    <row r="1030" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1030" s="1"/>
       <c r="D1030" s="1"/>
     </row>
-    <row r="1031" ht="12.75" customHeight="1">
+    <row r="1031" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1031" s="1"/>
       <c r="D1031" s="1"/>
     </row>
-    <row r="1032" ht="12.75" customHeight="1">
+    <row r="1032" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1032" s="1"/>
       <c r="D1032" s="1"/>
     </row>
-    <row r="1033" ht="12.75" customHeight="1">
+    <row r="1033" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1033" s="1"/>
       <c r="D1033" s="1"/>
     </row>
-    <row r="1034" ht="12.75" customHeight="1">
+    <row r="1034" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1034" s="1"/>
       <c r="D1034" s="1"/>
     </row>
-    <row r="1035" ht="12.75" customHeight="1">
+    <row r="1035" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1035" s="1"/>
       <c r="D1035" s="1"/>
     </row>
-    <row r="1036" ht="12.75" customHeight="1">
+    <row r="1036" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1036" s="1"/>
       <c r="D1036" s="1"/>
     </row>
-    <row r="1037" ht="12.75" customHeight="1">
+    <row r="1037" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1037" s="1"/>
       <c r="D1037" s="1"/>
     </row>
-    <row r="1038" ht="12.75" customHeight="1">
+    <row r="1038" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1038" s="1"/>
       <c r="D1038" s="1"/>
     </row>
-    <row r="1039" ht="12.75" customHeight="1">
+    <row r="1039" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1039" s="1"/>
       <c r="D1039" s="1"/>
     </row>
-    <row r="1040" ht="12.75" customHeight="1">
+    <row r="1040" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1040" s="1"/>
       <c r="D1040" s="1"/>
     </row>
-    <row r="1041" ht="12.75" customHeight="1">
+    <row r="1041" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1041" s="1"/>
       <c r="D1041" s="1"/>
     </row>
-    <row r="1042" ht="12.75" customHeight="1">
+    <row r="1042" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1042" s="1"/>
       <c r="D1042" s="1"/>
     </row>
-    <row r="1043" ht="12.75" customHeight="1">
+    <row r="1043" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1043" s="1"/>
       <c r="D1043" s="1"/>
     </row>
-    <row r="1044" ht="12.75" customHeight="1">
+    <row r="1044" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1044" s="1"/>
       <c r="D1044" s="1"/>
     </row>
-    <row r="1045" ht="12.75" customHeight="1">
+    <row r="1045" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1045" s="1"/>
       <c r="D1045" s="1"/>
     </row>
-    <row r="1046" ht="12.75" customHeight="1">
+    <row r="1046" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1046" s="1"/>
       <c r="D1046" s="1"/>
     </row>
-    <row r="1047" ht="12.75" customHeight="1">
+    <row r="1047" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1047" s="1"/>
       <c r="D1047" s="1"/>
     </row>
-    <row r="1048" ht="12.75" customHeight="1">
+    <row r="1048" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1048" s="1"/>
       <c r="D1048" s="1"/>
     </row>
-    <row r="1049" ht="12.75" customHeight="1">
+    <row r="1049" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1049" s="1"/>
       <c r="D1049" s="1"/>
     </row>
-    <row r="1050" ht="12.75" customHeight="1">
+    <row r="1050" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1050" s="1"/>
       <c r="D1050" s="1"/>
     </row>
-    <row r="1051" ht="12.75" customHeight="1">
+    <row r="1051" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1051" s="1"/>
       <c r="D1051" s="1"/>
     </row>
-    <row r="1052" ht="12.75" customHeight="1">
+    <row r="1052" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1052" s="1"/>
       <c r="D1052" s="1"/>
     </row>
-    <row r="1053" ht="12.75" customHeight="1">
+    <row r="1053" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1053" s="1"/>
       <c r="D1053" s="1"/>
     </row>
-    <row r="1054" ht="12.75" customHeight="1">
+    <row r="1054" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1054" s="1"/>
       <c r="D1054" s="1"/>
     </row>
-    <row r="1055" ht="12.75" customHeight="1">
+    <row r="1055" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1055" s="1"/>
       <c r="D1055" s="1"/>
     </row>
-    <row r="1056" ht="12.75" customHeight="1">
+    <row r="1056" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1056" s="1"/>
       <c r="D1056" s="1"/>
     </row>
-    <row r="1057" ht="12.75" customHeight="1">
+    <row r="1057" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1057" s="1"/>
       <c r="D1057" s="1"/>
     </row>
-    <row r="1058" ht="12.75" customHeight="1">
+    <row r="1058" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1058" s="1"/>
       <c r="D1058" s="1"/>
     </row>
-    <row r="1059" ht="12.75" customHeight="1">
+    <row r="1059" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1059" s="1"/>
       <c r="D1059" s="1"/>
     </row>
-    <row r="1060" ht="12.75" customHeight="1">
+    <row r="1060" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1060" s="1"/>
       <c r="D1060" s="1"/>
     </row>
-    <row r="1061" ht="12.75" customHeight="1">
+    <row r="1061" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1061" s="1"/>
       <c r="D1061" s="1"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="34.0"/>
-    <col customWidth="1" min="2" max="2" width="26.86"/>
-    <col customWidth="1" min="3" max="3" width="53.57"/>
-    <col customWidth="1" min="4" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="26.86328125" customWidth="1"/>
+    <col min="3" max="3" width="53.54296875" customWidth="1"/>
+    <col min="4" max="6" width="14.40625" customWidth="1"/>
+    <col min="7" max="26" width="8.6796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>1</v>
@@ -6660,177 +6940,177 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C2" s="19" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="C3" s="19" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="19" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="19" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" s="19" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="D5" t="s">
         <v>265</v>
       </c>
-      <c r="C5" s="19" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C6" s="19" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="D6" t="s">
         <v>268</v>
       </c>
-      <c r="C6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A7" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C7" s="19" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="B7" s="19" t="s">
+      <c r="D7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="19" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B8" s="3" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
+    </row>
+    <row r="13" spans="1:4" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D13" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="12.75" customHeight="1"/>
+    <row r="15" spans="1:4" ht="12.75" customHeight="1"/>
+    <row r="16" spans="1:4" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -7816,77 +8096,73 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.29"/>
-    <col customWidth="1" min="2" max="2" width="22.71"/>
-    <col customWidth="1" min="3" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="22.6796875" customWidth="1"/>
+    <col min="3" max="6" width="14.40625" customWidth="1"/>
+    <col min="7" max="26" width="8.6796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="19" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="20">
+        <v>43584</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
+      <c r="E2" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="B2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="20">
-        <v>43584.0</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
-    <row r="8" ht="12.75" customHeight="1"/>
-    <row r="9" ht="12.75" customHeight="1"/>
-    <row r="10" ht="12.75" customHeight="1"/>
-    <row r="11" ht="12.75" customHeight="1"/>
-    <row r="12" ht="12.75" customHeight="1"/>
-    <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="5" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="6" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="7" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="13" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="14" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="15" spans="1:6" ht="12.75" customHeight="1"/>
+    <row r="16" spans="1:6" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -8872,9 +9148,7 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20376"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20382"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314ACE0B-493E-49E8-8E84-6B4C3FE9A041}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6790B5-A57F-4EB5-AD9E-4B124BBC4090}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="302">
   <si>
     <t>type</t>
   </si>
@@ -633,9 +633,6 @@
     <t>reason_refer_flag_anc_visit_6m_or_more</t>
   </si>
   <si>
-    <t>&lt;span style="display:block;padding-left:1em"&gt;To get ANC services since your pregnancy is 6 months or more.&lt;/span&gt;</t>
-  </si>
-  <si>
     <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kupatiwa huduma za mama mjamzito kwa vile mimba yako ni miezi sita au zaidi.&lt;/span&gt;</t>
   </si>
   <si>
@@ -798,15 +795,9 @@
     <t>has_postpartum_referral</t>
   </si>
   <si>
-    <t xml:space="preserve">../inputs/refer_flag_postpartum_danger_signs = 1 or ../inputs/refer_flag_postpartum_other_signs = 1 </t>
-  </si>
-  <si>
     <t xml:space="preserve">has_pregnancy_counselling_referral </t>
   </si>
   <si>
-    <t>../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1</t>
-  </si>
-  <si>
     <t>referral_days</t>
   </si>
   <si>
@@ -946,6 +937,24 @@
   </si>
   <si>
     <t>../inputs/contact/dob</t>
+  </si>
+  <si>
+    <t>refer_flag_postpartum_pnc_visit</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_postpartum_pnc_visit</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To attend healthcare facility for PNC visit.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kuhudhuria kituo cha afya kwajili ya uchunguzi baada ya kujifungua&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_postpartum_danger_signs = 1 or ../inputs/refer_flag_postpartum_other_signs = 1 or ../inputs/refer_flag_postpartum_pnc_visit = 1</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To get ANC services since your pregnancy is 6 months or more&lt;/span&gt;</t>
   </si>
 </sst>
 </file>
@@ -961,7 +970,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -971,13 +979,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -987,7 +993,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1366,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1061"/>
+  <dimension ref="A1:Z1064"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1694,37 +1699,37 @@
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1"/>
     </row>
@@ -1733,10 +1738,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26" s="1"/>
     </row>
@@ -1745,68 +1750,68 @@
         <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>19</v>
@@ -1818,7 +1823,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>297</v>
+        <v>56</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>19</v>
@@ -1827,12 +1832,14 @@
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="1"/>
+        <v>294</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D34" s="1"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
@@ -1840,61 +1847,58 @@
         <v>51</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="L36" s="1" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>62</v>
+      <c r="B38" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="L38" s="3" t="s">
-        <v>63</v>
+      <c r="L38" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>64</v>
+      <c r="B39" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="L39" s="1" t="s">
-        <v>65</v>
+      <c r="L39" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1">
@@ -1902,51 +1906,51 @@
         <v>57</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>68</v>
+      <c r="B41" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="L41" s="4" t="s">
-        <v>69</v>
+      <c r="L41" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>28</v>
+      <c r="B42" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="L42" t="s">
-        <v>70</v>
+      <c r="L42" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>29</v>
+      <c r="B43" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="L43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
@@ -1954,12 +1958,12 @@
         <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="L44" s="3" t="s">
-        <v>72</v>
+      <c r="L44" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
@@ -1967,38 +1971,38 @@
         <v>57</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="L45" t="s">
-        <v>73</v>
+      <c r="L45" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>32</v>
+      <c r="B46" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="L46" s="3" t="s">
-        <v>74</v>
+      <c r="L46" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>33</v>
+      <c r="B47" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="L47" t="s">
-        <v>75</v>
+      <c r="L47" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
@@ -2006,12 +2010,12 @@
         <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="L48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
@@ -2019,12 +2023,12 @@
         <v>57</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="L49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
@@ -2032,12 +2036,12 @@
         <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="L50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1">
@@ -2045,12 +2049,12 @@
         <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="L51" s="1" t="s">
-        <v>59</v>
+      <c r="L51" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1">
@@ -2058,25 +2062,25 @@
         <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="L52" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="L53" s="1" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="6"/>
-      <c r="L53" s="3" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1">
@@ -2084,12 +2088,12 @@
         <v>57</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="L54" s="3" t="s">
-        <v>83</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1">
@@ -2097,12 +2101,12 @@
         <v>57</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
       <c r="L55" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1">
@@ -2110,12 +2114,12 @@
         <v>57</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
-      <c r="L56" s="7" t="s">
-        <v>86</v>
+      <c r="L56" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
@@ -2123,12 +2127,12 @@
         <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
       <c r="L57" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
@@ -2136,12 +2140,12 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="6"/>
       <c r="L58" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
@@ -2149,12 +2153,12 @@
         <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="6"/>
       <c r="L59" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
@@ -2162,12 +2166,12 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="6"/>
       <c r="L60" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
@@ -2175,12 +2179,12 @@
         <v>57</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="6"/>
       <c r="L61" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
@@ -2188,12 +2192,12 @@
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C62" s="5"/>
-      <c r="D62" s="6"/>
-      <c r="L62" s="8" t="s">
-        <v>93</v>
+        <v>296</v>
+      </c>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="L62" s="7" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
@@ -2201,12 +2205,12 @@
         <v>57</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="6"/>
-      <c r="L63" s="9" t="s">
-        <v>95</v>
+      <c r="L63" s="7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
@@ -2214,51 +2218,51 @@
         <v>57</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="6"/>
-      <c r="L64" s="9" t="s">
-        <v>97</v>
+      <c r="L64" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>98</v>
+      <c r="B65" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="6"/>
       <c r="L65" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>100</v>
+      <c r="B66" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="6"/>
-      <c r="L66" s="12" t="s">
-        <v>101</v>
+      <c r="L66" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B67" s="11" t="s">
-        <v>102</v>
+      <c r="B67" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="6"/>
-      <c r="L67" s="12" t="s">
-        <v>103</v>
+      <c r="L67" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="15.75" customHeight="1">
@@ -2266,12 +2270,12 @@
         <v>57</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="6"/>
       <c r="L68" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:26" ht="15.75" customHeight="1">
@@ -2279,91 +2283,49 @@
         <v>57</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="6"/>
       <c r="L69" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="6"/>
+      <c r="L70" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A71" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="6"/>
+      <c r="L71" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A70" s="11" t="s">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A72" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B72" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C70" s="13"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="15"/>
-      <c r="R70" s="15"/>
-      <c r="S70" s="15"/>
-      <c r="T70" s="15"/>
-      <c r="U70" s="15"/>
-      <c r="V70" s="15"/>
-      <c r="W70" s="15"/>
-      <c r="X70" s="15"/>
-      <c r="Y70" s="15"/>
-      <c r="Z70" s="15"/>
-    </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A71" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
-      <c r="P71" s="15"/>
-      <c r="Q71" s="15"/>
-      <c r="R71" s="15"/>
-      <c r="S71" s="15"/>
-      <c r="T71" s="15"/>
-      <c r="U71" s="15"/>
-      <c r="V71" s="15"/>
-      <c r="W71" s="15"/>
-      <c r="X71" s="15"/>
-      <c r="Y71" s="15"/>
-      <c r="Z71" s="15"/>
-    </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A72" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" s="17" t="s">
-        <v>113</v>
-      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="14"/>
       <c r="E72" s="15"/>
       <c r="F72" s="15"/>
       <c r="G72" s="14"/>
@@ -2371,7 +2333,7 @@
       <c r="I72" s="15"/>
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
+      <c r="L72" s="16"/>
       <c r="M72" s="15"/>
       <c r="N72" s="15"/>
       <c r="O72" s="15"/>
@@ -2379,20 +2341,23 @@
       <c r="Q72" s="15"/>
       <c r="R72" s="15"/>
       <c r="S72" s="15"/>
+      <c r="T72" s="15"/>
+      <c r="U72" s="15"/>
+      <c r="V72" s="15"/>
+      <c r="W72" s="15"/>
+      <c r="X72" s="15"/>
+      <c r="Y72" s="15"/>
+      <c r="Z72" s="15"/>
     </row>
     <row r="73" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A73" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>117</v>
-      </c>
+      <c r="A73" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
       <c r="E73" s="15"/>
       <c r="F73" s="15"/>
       <c r="G73" s="14"/>
@@ -2400,7 +2365,7 @@
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
+      <c r="L73" s="16"/>
       <c r="M73" s="15"/>
       <c r="N73" s="15"/>
       <c r="O73" s="15"/>
@@ -2408,16 +2373,27 @@
       <c r="Q73" s="15"/>
       <c r="R73" s="15"/>
       <c r="S73" s="15"/>
+      <c r="T73" s="15"/>
+      <c r="U73" s="15"/>
+      <c r="V73" s="15"/>
+      <c r="W73" s="15"/>
+      <c r="X73" s="15"/>
+      <c r="Y73" s="15"/>
+      <c r="Z73" s="15"/>
     </row>
     <row r="74" spans="1:26" ht="15.75" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
+      <c r="C74" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="E74" s="15"/>
       <c r="F74" s="15"/>
       <c r="G74" s="14"/>
@@ -2435,48 +2411,74 @@
       <c r="S74" s="15"/>
     </row>
     <row r="75" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A75" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="A75" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="15"/>
+      <c r="S75" s="15"/>
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="A76" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="13"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="15"/>
+      <c r="P76" s="15"/>
+      <c r="Q76" s="15"/>
+      <c r="R76" s="15"/>
+      <c r="S76" s="15"/>
     </row>
     <row r="77" spans="1:26" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="15.75" customHeight="1">
@@ -2484,13 +2486,13 @@
         <v>114</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="15.75" customHeight="1">
@@ -2498,71 +2500,68 @@
         <v>114</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A81" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A82" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A81" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="4"/>
     </row>
     <row r="83" spans="1:7" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1">
@@ -2570,33 +2569,30 @@
         <v>114</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F84" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>151</v>
+      <c r="B85" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1">
@@ -2604,16 +2600,16 @@
         <v>114</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F86" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1">
@@ -2621,16 +2617,16 @@
         <v>114</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1">
@@ -2638,33 +2634,33 @@
         <v>114</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F88" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F89" t="s">
-        <v>168</v>
+      <c r="B89" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1">
@@ -2672,16 +2668,16 @@
         <v>114</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F90" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1">
@@ -2689,52 +2685,50 @@
         <v>114</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F92" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C93" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D93" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F93" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A92" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E92" s="1"/>
-      <c r="F92" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A93" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1">
@@ -2742,17 +2736,17 @@
         <v>114</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E94" s="1"/>
-      <c r="F94" s="3" t="s">
-        <v>188</v>
+      <c r="F94" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1">
@@ -2760,17 +2754,17 @@
         <v>114</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1">
@@ -2778,344 +2772,357 @@
         <v>114</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E96" s="1"/>
+      <c r="F96" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A97" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A98" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="3"/>
+    </row>
+    <row r="99" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A99" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C99" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E99" s="1"/>
+      <c r="F99" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E96" s="1"/>
-      <c r="F96" s="2" t="s">
+    </row>
+    <row r="100" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A97" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="D100" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="E100" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E97" s="1" t="s">
+    </row>
+    <row r="101" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A98" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="4" t="s">
+      <c r="C101" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A99" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="F99" s="1"/>
-    </row>
-    <row r="100" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A100" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F100" s="1"/>
-    </row>
-    <row r="101" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A101" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15.75" customHeight="1">
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A104" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="D105" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="F105" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A106" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A103" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-    </row>
-    <row r="104" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A104" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C104" s="1" t="s">
+      <c r="C107" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A106" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A107" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
-    </row>
-    <row r="108" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A108" s="4" t="s">
+      <c r="F107" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A111" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B111" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="4" t="s">
+    </row>
+    <row r="112" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A112" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A109" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B109" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="D112" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A110" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A111" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="L111" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A112" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="E112" s="4"/>
-      <c r="F112" t="s">
-        <v>241</v>
+      <c r="E112" s="1" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A114" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="L114" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A115" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A116" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-    </row>
-    <row r="114" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A114" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-    </row>
-    <row r="115" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A115" t="s">
-        <v>57</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="L115" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A116" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>244</v>
+      <c r="B116" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="L116" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A117" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>246</v>
+    </row>
+    <row r="117" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="L117" s="2" t="s">
-        <v>247</v>
-      </c>
     </row>
     <row r="118" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A118" s="3" t="s">
+      <c r="A118" t="s">
         <v>57</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="L118" s="3" t="s">
-        <v>249</v>
+      <c r="L118" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="12.75" customHeight="1">
@@ -3123,38 +3130,65 @@
         <v>57</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="L119" s="3" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>252</v>
+      <c r="B120" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
-      <c r="L120">
-        <v>3</v>
+      <c r="L120" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A121" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
+      <c r="L121" s="3" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="122" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A122" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
+      <c r="L122" s="3" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="123" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A123" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>249</v>
+      </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
+      <c r="L123">
+        <v>3</v>
+      </c>
     </row>
     <row r="124" spans="1:12" ht="12.75" customHeight="1">
       <c r="C124" s="1"/>
@@ -6907,6 +6941,18 @@
     <row r="1061" spans="3:4" ht="12.75" customHeight="1">
       <c r="C1061" s="1"/>
       <c r="D1061" s="1"/>
+    </row>
+    <row r="1062" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1062" s="1"/>
+      <c r="D1062" s="1"/>
+    </row>
+    <row r="1063" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1063" s="1"/>
+      <c r="D1063" s="1"/>
+    </row>
+    <row r="1064" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1064" s="1"/>
+      <c r="D1064" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -6928,7 +6974,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>1</v>
@@ -6942,170 +6988,170 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>257</v>
-      </c>
       <c r="C3" s="19" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" customHeight="1"/>
@@ -8114,27 +8160,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>290</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
         <v>135</v>
@@ -8143,10 +8189,10 @@
         <v>43584</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1"/>

--- a/forms/app/referral_follow_up.xlsx
+++ b/forms/app/referral_follow_up.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20382"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20386"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6790B5-A57F-4EB5-AD9E-4B124BBC4090}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7922A6AD-C78F-44C8-93EC-7B19DE4B3A40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,12 @@
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="315">
   <si>
     <t>type</t>
   </si>
@@ -156,9 +156,6 @@
     <t>refer_flag_postpartum_other_signs</t>
   </si>
   <si>
-    <t>refer_flag_anc_visit_6m_or_more</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
@@ -295,9 +292,6 @@
   </si>
   <si>
     <t>../inputs/refer_flag_postpartum_other_signs</t>
-  </si>
-  <si>
-    <t>../inputs/refer_flag_anc_visit_6m_or_more</t>
   </si>
   <si>
     <t>age_days</t>
@@ -630,15 +624,6 @@
     <t>../../inputs/refer_flag_postpartum_other_signs= 1</t>
   </si>
   <si>
-    <t>reason_refer_flag_anc_visit_6m_or_more</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kupatiwa huduma za mama mjamzito kwa vile mimba yako ni miezi sita au zaidi.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>../../inputs/refer_flag_anc_visit_6m_or_more= 1</t>
-  </si>
-  <si>
     <t>select_one yes_no</t>
   </si>
   <si>
@@ -663,9 +648,6 @@
     <t>congratulate</t>
   </si>
   <si>
-    <t>_Congratulate the client on making the visit to the health facility._</t>
-  </si>
-  <si>
     <t>_Mpongeze mteja kwa kuenda kituo cha afya._</t>
   </si>
   <si>
@@ -783,9 +765,6 @@
     <t>has_pregnancy_referral</t>
   </si>
   <si>
-    <t>../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1 or ../inputs/refer_flag_anc_visit_6m_or_more = 1</t>
-  </si>
-  <si>
     <t>has_infant_child_referral</t>
   </si>
   <si>
@@ -933,12 +912,6 @@
     <t>data</t>
   </si>
   <si>
-    <t>dob</t>
-  </si>
-  <si>
-    <t>../inputs/contact/dob</t>
-  </si>
-  <si>
     <t>refer_flag_postpartum_pnc_visit</t>
   </si>
   <si>
@@ -954,14 +927,80 @@
     <t>../inputs/refer_flag_postpartum_danger_signs = 1 or ../inputs/refer_flag_postpartum_other_signs = 1 or ../inputs/refer_flag_postpartum_pnc_visit = 1</t>
   </si>
   <si>
-    <t>&lt;span style="display:block;padding-left:1em"&gt;To get ANC services since your pregnancy is 6 months or more&lt;/span&gt;</t>
+    <t>reason_refer_flag_anc_visit</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;To attend healthcare facility for ANC services&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span style="display:block;padding-left:1em"&gt;Ili kupatiwa huduma za mama mjamzito.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_anc_visit= 1</t>
+  </si>
+  <si>
+    <t>refer_flag_anc_visit</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_anc_visit</t>
+  </si>
+  <si>
+    <t>went_to_facility_with_partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Did you attend the ANC with your partner? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je ulienda kliniki ya wajawazito na mwenza wako? </t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility},"yes") and ../../inputs/refer_flag_anc_visit= 1</t>
+  </si>
+  <si>
+    <t>congratulate_for_anc_with_partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congratulate the mother and her partner for attending the ANC and emphasize on the importance of doing that throughout their pregnancy. </t>
+  </si>
+  <si>
+    <t>Congratulate the client on making the visit to the health facility._</t>
+  </si>
+  <si>
+    <t>Kama ndio, mpongeze mama na mwenza wake kwa kuhudhuria kliniki ya wajawazito na wasisitize umuhimu wa kufanya hivyo mara zote kwenye ujauzito wao.</t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility_with_partner},"yes")</t>
+  </si>
+  <si>
+    <t>emphasize_to_go_with_partner</t>
+  </si>
+  <si>
+    <t>Please emphasize on talking with her partner and encourage them both on the importance of attending ANC together.</t>
+  </si>
+  <si>
+    <t>Msisitize juu ya kuongea na mwenza wake  na wahimize juu ya umuhimu wa kuambatana na mwenza kwenye kliniki ya waja wazito.</t>
+  </si>
+  <si>
+    <t>selected(${went_to_facility_with_partner},"no")</t>
+  </si>
+  <si>
+    <t>../inputs/refer_flag_emergency_danger_sign  = 1 or ../inputs/refer_flag_pregnancy_issues  = 1 or  ../inputs/refer_flag_pregnancy_complications = 1 or ../inputs/refer_flag_anc_visit = 1</t>
+  </si>
+  <si>
+    <t>../../inputs/refer_flag_postpartum_pnc_visit=1</t>
+  </si>
+  <si>
+    <t>../inputs/contact/date_of_birth</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -993,6 +1032,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1034,7 +1078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1057,6 +1101,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,12 +1419,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1064"/>
+  <dimension ref="A1:Z1067"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="43.54296875" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" customWidth="1"/>
+    <col min="3" max="3" width="255.58984375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.40625" customWidth="1"/>
     <col min="6" max="6" width="91" customWidth="1"/>
     <col min="7" max="17" width="14.40625" customWidth="1"/>
@@ -1702,7 +1750,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -1714,7 +1762,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -1726,7 +1774,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>19</v>
@@ -1738,10 +1786,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D26" s="1"/>
     </row>
@@ -1750,10 +1798,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D27" s="1"/>
     </row>
@@ -1765,16 +1813,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -1784,7 +1832,7 @@
         <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
@@ -1793,17 +1841,17 @@
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="1"/>
       <c r="G31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -1823,7 +1871,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>19</v>
@@ -1835,7 +1883,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>19</v>
@@ -1844,17 +1892,17 @@
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>18</v>
@@ -1864,85 +1912,85 @@
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="L37" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="L38" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="L39" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="L40" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="L41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="L42" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>28</v>
@@ -1950,12 +1998,12 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="L43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>29</v>
@@ -1963,12 +2011,12 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="L44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>30</v>
@@ -1976,12 +2024,12 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="L45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>31</v>
@@ -1989,12 +2037,12 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="L46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>32</v>
@@ -2002,12 +2050,12 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="L47" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>33</v>
@@ -2015,12 +2063,12 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="L48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>34</v>
@@ -2028,12 +2076,12 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="L49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
@@ -2041,12 +2089,12 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="L50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>36</v>
@@ -2054,51 +2102,51 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="L51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="L52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="L53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="L54" s="3" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>37</v>
@@ -2106,25 +2154,25 @@
       <c r="C55" s="5"/>
       <c r="D55" s="6"/>
       <c r="L55" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="6"/>
       <c r="L56" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -2132,12 +2180,12 @@
       <c r="C57" s="5"/>
       <c r="D57" s="6"/>
       <c r="L57" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>40</v>
@@ -2145,12 +2193,12 @@
       <c r="C58" s="5"/>
       <c r="D58" s="6"/>
       <c r="L58" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>41</v>
@@ -2158,12 +2206,12 @@
       <c r="C59" s="5"/>
       <c r="D59" s="6"/>
       <c r="L59" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>42</v>
@@ -2171,12 +2219,12 @@
       <c r="C60" s="5"/>
       <c r="D60" s="6"/>
       <c r="L60" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>43</v>
@@ -2184,145 +2232,145 @@
       <c r="C61" s="5"/>
       <c r="D61" s="6"/>
       <c r="L61" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
       <c r="L62" s="7" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>44</v>
+        <v>296</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="6"/>
       <c r="L63" s="7" t="s">
-        <v>91</v>
+        <v>297</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="6"/>
       <c r="L64" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:26" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="6"/>
       <c r="L65" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:26" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="6"/>
       <c r="L66" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:26" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="6"/>
       <c r="L67" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:26" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="6"/>
       <c r="L68" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:26" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C69" s="5"/>
       <c r="D69" s="6"/>
       <c r="L69" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:26" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="6"/>
       <c r="L70" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:26" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C71" s="5"/>
       <c r="D71" s="6"/>
       <c r="L71" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:26" ht="15.75" customHeight="1">
       <c r="A72" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C72" s="13"/>
       <c r="D72" s="14"/>
@@ -2351,10 +2399,10 @@
     </row>
     <row r="73" spans="1:26" ht="15.75" customHeight="1">
       <c r="A73" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C73" s="13"/>
       <c r="D73" s="14"/>
@@ -2383,16 +2431,16 @@
     </row>
     <row r="74" spans="1:26" ht="15.75" customHeight="1">
       <c r="A74" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="D74" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" s="17" t="s">
-        <v>113</v>
       </c>
       <c r="E74" s="15"/>
       <c r="F74" s="15"/>
@@ -2412,16 +2460,16 @@
     </row>
     <row r="75" spans="1:26" ht="15.75" customHeight="1">
       <c r="A75" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="D75" s="18" t="s">
         <v>115</v>
-      </c>
-      <c r="C75" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>117</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="15"/>
@@ -2441,10 +2489,10 @@
     </row>
     <row r="76" spans="1:26" ht="15.75" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B76" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C76" s="13"/>
       <c r="D76" s="14"/>
@@ -2469,80 +2517,80 @@
         <v>17</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="G77" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="78" spans="1:26" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:26" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="4"/>
@@ -2552,655 +2600,700 @@
         <v>17</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="F85" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="F86" t="s">
         <v>146</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F86" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="F87" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="F88" t="s">
         <v>154</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F88" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="F90" t="s">
         <v>162</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F90" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="F91" t="s">
         <v>166</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F91" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="F92" t="s">
         <v>170</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F92" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="F93" t="s">
         <v>174</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F93" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="E98" s="4"/>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>193</v>
+        <v>292</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="2" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1">
       <c r="A101" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A102" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B101" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C101" s="4" t="s">
+      <c r="B102" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A102" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>196</v>
+        <v>112</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F103" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1">
       <c r="A104" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>210</v>
+        <v>112</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="E104" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F104" s="22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A105" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="F105" s="22" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A106" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B106" s="4" t="s">
+      <c r="C106" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
+      <c r="D106" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A107" s="1" t="s">
-        <v>17</v>
+      <c r="A107" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1" t="s">
-        <v>218</v>
+        <v>204</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>220</v>
+        <v>112</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A109" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>225</v>
-      </c>
+      <c r="A109" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
     </row>
     <row r="110" spans="1:6" ht="15.75" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C110" s="1"/>
+        <v>211</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A111" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>226</v>
+      <c r="A111" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="4" t="s">
-        <v>227</v>
+        <v>215</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>196</v>
+        <v>112</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>234</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
     </row>
     <row r="114" spans="1:12" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="L114" s="4" t="s">
-        <v>236</v>
+        <v>220</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="4" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A115" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>237</v>
+      <c r="A115" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E115" s="4"/>
-      <c r="F115" t="s">
-        <v>240</v>
+        <v>224</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15.75" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="D116" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="117" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A117" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-    </row>
-    <row r="118" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A118" t="s">
-        <v>57</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="L118" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A119" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>243</v>
+      <c r="A117" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="L117" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A118" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A119" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>220</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
-      <c r="L119" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A120" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>245</v>
+    </row>
+    <row r="120" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
-      <c r="L120" s="2" t="s">
-        <v>246</v>
-      </c>
     </row>
     <row r="121" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A121" s="3" t="s">
-        <v>57</v>
+      <c r="A121" t="s">
+        <v>56</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
-      <c r="L121" s="3" t="s">
-        <v>300</v>
+      <c r="L121" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="12.75" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="L122" s="3" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A123" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>249</v>
+      <c r="A123" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
-      <c r="L123">
-        <v>3</v>
+      <c r="L123" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A124" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
+      <c r="L124" s="3" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="125" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A125" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
+      <c r="L125" s="3" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="126" spans="1:12" ht="12.75" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
+      <c r="L126">
+        <v>3</v>
+      </c>
     </row>
     <row r="127" spans="1:12" ht="12.75" customHeight="1">
       <c r="C127" s="1"/>
@@ -6954,9 +7047,21 @@
       <c r="C1064" s="1"/>
       <c r="D1064" s="1"/>
     </row>
+    <row r="1065" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1065" s="1"/>
+      <c r="D1065" s="1"/>
+    </row>
+    <row r="1066" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1066" s="1"/>
+      <c r="D1066" s="1"/>
+    </row>
+    <row r="1067" spans="3:4" ht="12.75" customHeight="1">
+      <c r="C1067" s="1"/>
+      <c r="D1067" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6974,7 +7079,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>1</v>
@@ -6988,170 +7093,170 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="19" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D6" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75" customHeight="1"/>
@@ -8160,39 +8265,39 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C2" s="20">
         <v>43584</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1"/>
